--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="291">
   <si>
     <t>filename</t>
   </si>
@@ -133,10 +133,10 @@
     <t>micro_0109_SL40III.jpg</t>
   </si>
   <si>
-    <t>micro_0296_SL4082600.jpg</t>
-  </si>
-  <si>
-    <t>micro_0291_SL407.jpg</t>
+    <t>micro_0291_SL4082600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0296_SL407.jpg</t>
   </si>
   <si>
     <t>micro_0112_SL406.jpg</t>
@@ -313,7 +313,7 @@
     <t>micro_0263_D406.jpg</t>
   </si>
   <si>
-    <t>micro_0134_D405.jpg</t>
+    <t>micro_0296_D405.jpg</t>
   </si>
   <si>
     <t>micro_0261_D404.jpg</t>
@@ -322,7 +322,10 @@
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
-    <t>micro_0131_D401.jpg</t>
+    <t>micro_0292_D401.jpg</t>
+  </si>
+  <si>
+    <t>micro_0290_D401.jpg</t>
   </si>
   <si>
     <t>micro_0133_YD409_D403.jpg</t>
@@ -1215,7 +1218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N138"/>
+  <dimension ref="A1:N139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1267,13 +1270,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C2">
         <v>0.9341862201690674</v>
       </c>
       <c r="D2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1288,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1311,13 +1314,13 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3">
         <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1332,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1355,13 +1358,13 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4">
         <v>0.9089775085449219</v>
       </c>
       <c r="D4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1376,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1399,13 +1402,13 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5">
         <v>0.7567664980888367</v>
       </c>
       <c r="D5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1420,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1443,13 +1446,13 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>0.9360489845275879</v>
       </c>
       <c r="D6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1464,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1487,13 +1490,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>0.9875660538673401</v>
       </c>
       <c r="D7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1508,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1531,13 +1534,13 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C8">
         <v>0.9800205826759338</v>
       </c>
       <c r="D8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1552,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1575,13 +1578,13 @@
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C9">
         <v>0.9866096377372742</v>
       </c>
       <c r="D9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1596,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1619,13 +1622,13 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C10">
         <v>0.9825887680053711</v>
       </c>
       <c r="D10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1640,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1663,13 +1666,13 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C11">
         <v>0.9854358434677124</v>
       </c>
       <c r="D11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1684,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1707,13 +1710,13 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C12">
         <v>0.9869511127471924</v>
       </c>
       <c r="D12" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1728,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1751,13 +1754,13 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13">
         <v>0.9883586168289185</v>
       </c>
       <c r="D13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1772,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1795,13 +1798,13 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14">
         <v>0.9827210903167725</v>
       </c>
       <c r="D14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1816,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1839,13 +1842,13 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15">
         <v>0.9891344904899597</v>
       </c>
       <c r="D15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1860,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1883,13 +1886,13 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C16">
         <v>0.9849019646644592</v>
       </c>
       <c r="D16" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1904,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1927,13 +1930,13 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C17">
         <v>0.9831116795539856</v>
       </c>
       <c r="D17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1948,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1971,13 +1974,13 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C18">
         <v>0.979184627532959</v>
       </c>
       <c r="D18" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1992,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2015,13 +2018,13 @@
         <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C19">
         <v>0.9820773601531982</v>
       </c>
       <c r="D19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2036,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2059,13 +2062,13 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20">
         <v>0.9926210641860962</v>
       </c>
       <c r="D20" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2080,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2103,13 +2106,13 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C21">
         <v>0.991193413734436</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2124,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2147,13 +2150,13 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22">
         <v>0.9759405851364136</v>
       </c>
       <c r="D22" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2168,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2191,13 +2194,13 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C23">
         <v>0.9936316609382629</v>
       </c>
       <c r="D23" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2212,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2235,13 +2238,13 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C24">
         <v>0.768846869468689</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2256,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2279,13 +2282,13 @@
         <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25">
         <v>0.7151024341583252</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2300,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2323,13 +2326,13 @@
         <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C26">
         <v>0.9909618496894836</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2344,13 +2347,13 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -2367,13 +2370,13 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C27">
         <v>0.9938899278640747</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2388,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2411,13 +2414,13 @@
         <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C28">
-        <v>0.9961646199226379</v>
+        <v>0.9962404370307922</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2432,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2455,13 +2458,13 @@
         <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C29">
         <v>0.9971726536750793</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2476,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2499,13 +2502,13 @@
         <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C30">
         <v>0.9959992170333862</v>
       </c>
       <c r="D30" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2520,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2543,13 +2546,13 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C31">
         <v>0.9987277984619141</v>
       </c>
       <c r="D31" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2564,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2587,13 +2590,13 @@
         <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C32">
         <v>0.990104079246521</v>
       </c>
       <c r="D32" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2608,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2631,13 +2634,13 @@
         <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C33">
         <v>0.9917885661125183</v>
       </c>
       <c r="D33" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2652,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2675,13 +2678,13 @@
         <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C34">
         <v>0.9959156513214111</v>
       </c>
       <c r="D34" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2696,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2719,13 +2722,13 @@
         <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C35">
         <v>0.9986041784286499</v>
       </c>
       <c r="D35" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2740,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2763,13 +2766,13 @@
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C36">
         <v>0.9965012669563293</v>
       </c>
       <c r="D36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2784,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2807,13 +2810,13 @@
         <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C37">
         <v>0.9989038705825806</v>
       </c>
       <c r="D37" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2828,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2851,13 +2854,13 @@
         <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C38">
         <v>0.9787384867668152</v>
       </c>
       <c r="D38" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2872,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2895,13 +2898,13 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C39">
         <v>0.9673787951469421</v>
       </c>
       <c r="D39" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2916,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2939,13 +2942,13 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C40">
         <v>0.9990044236183167</v>
       </c>
       <c r="D40" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2960,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2983,13 +2986,13 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C41">
         <v>0.7677456140518188</v>
       </c>
       <c r="D41" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3004,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -3027,13 +3030,13 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C42">
         <v>0.8940553665161133</v>
       </c>
       <c r="D42" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3048,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -3071,13 +3074,13 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C43">
         <v>0.9920957684516907</v>
       </c>
       <c r="D43" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3092,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -3115,13 +3118,13 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C44">
         <v>0.9965819120407104</v>
       </c>
       <c r="D44" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3136,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3159,13 +3162,13 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C45">
         <v>0.9981755018234253</v>
       </c>
       <c r="D45" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3180,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3203,13 +3206,13 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C46">
         <v>0.9990609288215637</v>
       </c>
       <c r="D46" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3224,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3247,13 +3250,13 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C47">
         <v>0.9990001320838928</v>
       </c>
       <c r="D47" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3268,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3291,13 +3294,13 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C48">
         <v>0.9990422129631042</v>
       </c>
       <c r="D48" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3312,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3335,13 +3338,13 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C49">
         <v>0.9962484240531921</v>
       </c>
       <c r="D49" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3356,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3379,13 +3382,13 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C50">
         <v>0.9956099390983582</v>
       </c>
       <c r="D50" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3400,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3423,13 +3426,13 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C51">
         <v>0.9993695020675659</v>
       </c>
       <c r="D51" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3444,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3467,13 +3470,13 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C52">
         <v>0.9990277886390686</v>
       </c>
       <c r="D52" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3488,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3511,13 +3514,13 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C53">
         <v>0.9995902180671692</v>
       </c>
       <c r="D53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3532,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3555,13 +3558,13 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C54">
         <v>0.9994117021560669</v>
       </c>
       <c r="D54" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3576,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3599,13 +3602,13 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C55">
         <v>0.9994282722473145</v>
       </c>
       <c r="D55" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3620,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3643,13 +3646,13 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C56">
         <v>0.999479353427887</v>
       </c>
       <c r="D56" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3664,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3687,13 +3690,13 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C57">
         <v>0.9984571933746338</v>
       </c>
       <c r="D57" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3708,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -3731,13 +3734,13 @@
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C58">
         <v>0.9981318712234497</v>
       </c>
       <c r="D58" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3752,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -3775,13 +3778,13 @@
         <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C59">
         <v>0.999025285243988</v>
       </c>
       <c r="D59" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3796,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3819,13 +3822,13 @@
         <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C60">
         <v>0.933538019657135</v>
       </c>
       <c r="D60" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3840,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3863,13 +3866,13 @@
         <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C61">
         <v>0.9989953637123108</v>
       </c>
       <c r="D61" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3884,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -3907,13 +3910,13 @@
         <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C62">
         <v>0.9986401796340942</v>
       </c>
       <c r="D62" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3928,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -3951,13 +3954,13 @@
         <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C63">
         <v>0.9990375638008118</v>
       </c>
       <c r="D63" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3972,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -3995,13 +3998,13 @@
         <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C64">
         <v>0.8789094686508179</v>
       </c>
       <c r="D64" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4016,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4039,13 +4042,13 @@
         <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C65">
         <v>0.9988136887550354</v>
       </c>
       <c r="D65" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4060,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4083,13 +4086,13 @@
         <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C66">
         <v>0.9909911155700684</v>
       </c>
       <c r="D66" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4104,7 +4107,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4127,13 +4130,13 @@
         <v>79</v>
       </c>
       <c r="B67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C67">
         <v>0.9983184337615967</v>
       </c>
       <c r="D67" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4148,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4171,13 +4174,13 @@
         <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C68">
         <v>0.9994446039199829</v>
       </c>
       <c r="D68" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4192,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4215,13 +4218,13 @@
         <v>81</v>
       </c>
       <c r="B69" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C69">
         <v>0.9993821382522583</v>
       </c>
       <c r="D69" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4236,7 +4239,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4259,13 +4262,13 @@
         <v>82</v>
       </c>
       <c r="B70" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C70">
         <v>0.9976016283035278</v>
       </c>
       <c r="D70" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4280,7 +4283,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4303,13 +4306,13 @@
         <v>83</v>
       </c>
       <c r="B71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C71">
         <v>0.9990072250366211</v>
       </c>
       <c r="D71" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4324,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4347,13 +4350,13 @@
         <v>84</v>
       </c>
       <c r="B72" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C72">
         <v>0.9991657733917236</v>
       </c>
       <c r="D72" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4368,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4391,13 +4394,13 @@
         <v>85</v>
       </c>
       <c r="B73" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C73">
         <v>0.997841477394104</v>
       </c>
       <c r="D73" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4412,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4435,13 +4438,13 @@
         <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C74">
         <v>0.9976445436477661</v>
       </c>
       <c r="D74" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4456,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4479,13 +4482,13 @@
         <v>87</v>
       </c>
       <c r="B75" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C75">
         <v>0.9980232715606689</v>
       </c>
       <c r="D75" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4500,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4523,13 +4526,13 @@
         <v>88</v>
       </c>
       <c r="B76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C76">
         <v>0.9990618228912354</v>
       </c>
       <c r="D76" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4544,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4567,13 +4570,13 @@
         <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C77">
         <v>0.9994759559631348</v>
       </c>
       <c r="D77" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4588,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4611,13 +4614,13 @@
         <v>90</v>
       </c>
       <c r="B78" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C78">
         <v>0.9992071986198425</v>
       </c>
       <c r="D78" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4632,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4655,13 +4658,13 @@
         <v>91</v>
       </c>
       <c r="B79" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C79">
         <v>0.9985552430152893</v>
       </c>
       <c r="D79" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -4676,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4699,13 +4702,13 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C80">
         <v>0.9976009726524353</v>
       </c>
       <c r="D80" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -4720,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4743,13 +4746,13 @@
         <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C81">
         <v>0.9884098172187805</v>
       </c>
       <c r="D81" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -4764,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4787,13 +4790,13 @@
         <v>94</v>
       </c>
       <c r="B82" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C82">
         <v>0.7832491993904114</v>
       </c>
       <c r="D82" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -4808,7 +4811,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -4831,13 +4834,13 @@
         <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C83">
         <v>0.9955025911331177</v>
       </c>
       <c r="D83" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4852,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -4875,13 +4878,13 @@
         <v>96</v>
       </c>
       <c r="B84" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C84">
         <v>0.9995555877685547</v>
       </c>
       <c r="D84" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -4896,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -4919,13 +4922,13 @@
         <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C85">
         <v>0.9975136518478394</v>
       </c>
       <c r="D85" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4940,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -4963,13 +4966,13 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C86">
         <v>0.9972119331359863</v>
       </c>
       <c r="D86" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4984,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -5007,13 +5010,13 @@
         <v>99</v>
       </c>
       <c r="B87" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C87">
-        <v>0.9970172047615051</v>
+        <v>0.9980412721633911</v>
       </c>
       <c r="D87" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5028,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5040,10 +5043,10 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N87">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -5051,13 +5054,13 @@
         <v>100</v>
       </c>
       <c r="B88" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C88">
         <v>0.997714638710022</v>
       </c>
       <c r="D88" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5072,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5095,13 +5098,13 @@
         <v>101</v>
       </c>
       <c r="B89" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C89">
         <v>0.9981099367141724</v>
       </c>
       <c r="D89" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5116,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5139,13 +5142,13 @@
         <v>102</v>
       </c>
       <c r="B90" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C90">
-        <v>0.9986376166343689</v>
+        <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5160,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5186,10 +5189,10 @@
         <v>240</v>
       </c>
       <c r="C91">
-        <v>0.9316359758377075</v>
+        <v>0.996095597743988</v>
       </c>
       <c r="D91" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5204,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5219,7 +5222,7 @@
         <v>1</v>
       </c>
       <c r="N91">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -5230,10 +5233,10 @@
         <v>241</v>
       </c>
       <c r="C92">
-        <v>0.9997719526290894</v>
+        <v>0.9316359758377075</v>
       </c>
       <c r="D92" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5248,7 +5251,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5260,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N92">
         <v>1</v>
@@ -5274,10 +5277,10 @@
         <v>242</v>
       </c>
       <c r="C93">
-        <v>0.9881560802459717</v>
+        <v>0.9997719526290894</v>
       </c>
       <c r="D93" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5292,7 +5295,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5304,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="M93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -5318,10 +5321,10 @@
         <v>243</v>
       </c>
       <c r="C94">
-        <v>0.9993869662284851</v>
+        <v>0.9881560802459717</v>
       </c>
       <c r="D94" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5336,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5351,7 +5354,7 @@
         <v>1</v>
       </c>
       <c r="N94">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -5362,10 +5365,10 @@
         <v>244</v>
       </c>
       <c r="C95">
-        <v>0.9876304268836975</v>
+        <v>0.9993869662284851</v>
       </c>
       <c r="D95" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5380,7 +5383,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5395,7 +5398,7 @@
         <v>1</v>
       </c>
       <c r="N95">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -5406,10 +5409,10 @@
         <v>245</v>
       </c>
       <c r="C96">
-        <v>0.9915251135826111</v>
+        <v>0.9876304268836975</v>
       </c>
       <c r="D96" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5424,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5450,10 +5453,10 @@
         <v>246</v>
       </c>
       <c r="C97">
-        <v>0.9993435144424438</v>
+        <v>0.9915251135826111</v>
       </c>
       <c r="D97" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -5468,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -5494,10 +5497,10 @@
         <v>247</v>
       </c>
       <c r="C98">
-        <v>0.9956748485565186</v>
+        <v>0.9993435144424438</v>
       </c>
       <c r="D98" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -5512,22 +5515,22 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98">
         <v>0</v>
       </c>
       <c r="L98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M98">
         <v>1</v>
       </c>
       <c r="N98">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -5538,10 +5541,10 @@
         <v>248</v>
       </c>
       <c r="C99">
-        <v>0.9915837645530701</v>
+        <v>0.9956748485565186</v>
       </c>
       <c r="D99" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -5556,22 +5559,22 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99">
         <v>0</v>
       </c>
       <c r="L99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M99">
         <v>1</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -5582,10 +5585,10 @@
         <v>249</v>
       </c>
       <c r="C100">
-        <v>0.9992069602012634</v>
+        <v>0.9915837645530701</v>
       </c>
       <c r="D100" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -5600,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -5626,10 +5629,10 @@
         <v>250</v>
       </c>
       <c r="C101">
-        <v>0.9964823126792908</v>
+        <v>0.9992069602012634</v>
       </c>
       <c r="D101" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -5644,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -5670,10 +5673,10 @@
         <v>251</v>
       </c>
       <c r="C102">
-        <v>0.9991474747657776</v>
+        <v>0.9964823126792908</v>
       </c>
       <c r="D102" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -5688,7 +5691,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -5714,10 +5717,10 @@
         <v>252</v>
       </c>
       <c r="C103">
-        <v>0.9979246258735657</v>
+        <v>0.9991474747657776</v>
       </c>
       <c r="D103" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -5732,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -5758,10 +5761,10 @@
         <v>253</v>
       </c>
       <c r="C104">
-        <v>0.9995026588439941</v>
+        <v>0.9979246258735657</v>
       </c>
       <c r="D104" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -5776,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -5791,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="N104">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -5802,10 +5805,10 @@
         <v>254</v>
       </c>
       <c r="C105">
-        <v>0.9919981956481934</v>
+        <v>0.9995026588439941</v>
       </c>
       <c r="D105" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -5820,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -5835,7 +5838,7 @@
         <v>1</v>
       </c>
       <c r="N105">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -5846,10 +5849,10 @@
         <v>255</v>
       </c>
       <c r="C106">
-        <v>0.8529298901557922</v>
+        <v>0.9919981956481934</v>
       </c>
       <c r="D106" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -5864,10 +5867,10 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106">
         <v>0</v>
@@ -5890,10 +5893,10 @@
         <v>256</v>
       </c>
       <c r="C107">
-        <v>0.9926774501800537</v>
+        <v>0.8529298901557922</v>
       </c>
       <c r="D107" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -5908,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -5934,10 +5937,10 @@
         <v>257</v>
       </c>
       <c r="C108">
-        <v>0.9982547760009766</v>
+        <v>0.9926774501800537</v>
       </c>
       <c r="D108" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -5952,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -5978,10 +5981,10 @@
         <v>258</v>
       </c>
       <c r="C109">
-        <v>0.9919293522834778</v>
+        <v>0.9982547760009766</v>
       </c>
       <c r="D109" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -5996,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -6022,10 +6025,10 @@
         <v>259</v>
       </c>
       <c r="C110">
-        <v>0.9978511333465576</v>
+        <v>0.9919293522834778</v>
       </c>
       <c r="D110" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6040,22 +6043,22 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N110">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -6066,10 +6069,10 @@
         <v>260</v>
       </c>
       <c r="C111">
-        <v>0.999393105506897</v>
+        <v>0.9978511333465576</v>
       </c>
       <c r="D111" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6084,22 +6087,22 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N111">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -6110,10 +6113,10 @@
         <v>261</v>
       </c>
       <c r="C112">
-        <v>0.9981414675712585</v>
+        <v>0.999393105506897</v>
       </c>
       <c r="D112" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6128,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -6154,10 +6157,10 @@
         <v>262</v>
       </c>
       <c r="C113">
-        <v>0.995561420917511</v>
+        <v>0.9981414675712585</v>
       </c>
       <c r="D113" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6172,7 +6175,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6198,10 +6201,10 @@
         <v>263</v>
       </c>
       <c r="C114">
-        <v>0.99856036901474</v>
+        <v>0.995561420917511</v>
       </c>
       <c r="D114" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6216,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -6228,10 +6231,10 @@
         <v>0</v>
       </c>
       <c r="M114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N114">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -6242,10 +6245,10 @@
         <v>264</v>
       </c>
       <c r="C115">
-        <v>0.9979491829872131</v>
+        <v>0.99856036901474</v>
       </c>
       <c r="D115" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6260,7 +6263,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6275,7 +6278,7 @@
         <v>2</v>
       </c>
       <c r="N115">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -6286,10 +6289,10 @@
         <v>265</v>
       </c>
       <c r="C116">
-        <v>0.9989242553710938</v>
+        <v>0.9979491829872131</v>
       </c>
       <c r="D116" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6304,22 +6307,22 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116">
         <v>2</v>
       </c>
       <c r="N116">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -6330,10 +6333,10 @@
         <v>266</v>
       </c>
       <c r="C117">
-        <v>0.9987018704414368</v>
+        <v>0.9989242553710938</v>
       </c>
       <c r="D117" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6348,22 +6351,22 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N117">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -6374,10 +6377,10 @@
         <v>267</v>
       </c>
       <c r="C118">
-        <v>0.9980301260948181</v>
+        <v>0.9987018704414368</v>
       </c>
       <c r="D118" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -6392,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -6404,10 +6407,10 @@
         <v>0</v>
       </c>
       <c r="M118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -6418,10 +6421,10 @@
         <v>268</v>
       </c>
       <c r="C119">
-        <v>0.9988909959793091</v>
+        <v>0.9980301260948181</v>
       </c>
       <c r="D119" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -6436,7 +6439,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6451,7 +6454,7 @@
         <v>2</v>
       </c>
       <c r="N119">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -6462,10 +6465,10 @@
         <v>269</v>
       </c>
       <c r="C120">
-        <v>0.9961404204368591</v>
+        <v>0.9988909959793091</v>
       </c>
       <c r="D120" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6480,7 +6483,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6492,7 +6495,7 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N120">
         <v>3</v>
@@ -6506,10 +6509,10 @@
         <v>270</v>
       </c>
       <c r="C121">
-        <v>0.9958701133728027</v>
+        <v>0.9961404204368591</v>
       </c>
       <c r="D121" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -6524,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6536,7 +6539,7 @@
         <v>0</v>
       </c>
       <c r="M121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N121">
         <v>3</v>
@@ -6550,10 +6553,10 @@
         <v>271</v>
       </c>
       <c r="C122">
-        <v>0.998413622379303</v>
+        <v>0.9958701133728027</v>
       </c>
       <c r="D122" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -6568,7 +6571,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -6580,10 +6583,10 @@
         <v>0</v>
       </c>
       <c r="M122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N122">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -6594,10 +6597,10 @@
         <v>272</v>
       </c>
       <c r="C123">
-        <v>0.9992607235908508</v>
+        <v>0.998413622379303</v>
       </c>
       <c r="D123" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -6612,7 +6615,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -6624,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="M123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -6638,10 +6641,10 @@
         <v>273</v>
       </c>
       <c r="C124">
-        <v>0.9961749315261841</v>
+        <v>0.9992607235908508</v>
       </c>
       <c r="D124" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -6656,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -6671,7 +6674,7 @@
         <v>2</v>
       </c>
       <c r="N124">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -6682,10 +6685,10 @@
         <v>274</v>
       </c>
       <c r="C125">
-        <v>0.9993590712547302</v>
+        <v>0.9961749315261841</v>
       </c>
       <c r="D125" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -6700,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -6715,7 +6718,7 @@
         <v>2</v>
       </c>
       <c r="N125">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6726,10 +6729,10 @@
         <v>275</v>
       </c>
       <c r="C126">
-        <v>0.9987558722496033</v>
+        <v>0.9993590712547302</v>
       </c>
       <c r="D126" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -6744,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -6759,7 +6762,7 @@
         <v>2</v>
       </c>
       <c r="N126">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6770,10 +6773,10 @@
         <v>276</v>
       </c>
       <c r="C127">
-        <v>0.9992091655731201</v>
+        <v>0.9987558722496033</v>
       </c>
       <c r="D127" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -6788,7 +6791,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -6814,10 +6817,10 @@
         <v>277</v>
       </c>
       <c r="C128">
-        <v>0.9622448682785034</v>
+        <v>0.9992091655731201</v>
       </c>
       <c r="D128" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -6832,7 +6835,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -6847,7 +6850,7 @@
         <v>2</v>
       </c>
       <c r="N128">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6858,10 +6861,10 @@
         <v>278</v>
       </c>
       <c r="C129">
-        <v>0.9945164322853088</v>
+        <v>0.9622448682785034</v>
       </c>
       <c r="D129" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -6876,7 +6879,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -6888,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N129">
         <v>3</v>
@@ -6902,10 +6905,10 @@
         <v>279</v>
       </c>
       <c r="C130">
-        <v>0.995938241481781</v>
+        <v>0.9945164322853088</v>
       </c>
       <c r="D130" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -6920,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -6932,7 +6935,7 @@
         <v>0</v>
       </c>
       <c r="M130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N130">
         <v>3</v>
@@ -6946,10 +6949,10 @@
         <v>280</v>
       </c>
       <c r="C131">
-        <v>0.998788058757782</v>
+        <v>0.995938241481781</v>
       </c>
       <c r="D131" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -6964,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -6976,10 +6979,10 @@
         <v>0</v>
       </c>
       <c r="M131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N131">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6990,10 +6993,10 @@
         <v>281</v>
       </c>
       <c r="C132">
-        <v>0.9871893525123596</v>
+        <v>0.998788058757782</v>
       </c>
       <c r="D132" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7008,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -7020,10 +7023,10 @@
         <v>0</v>
       </c>
       <c r="M132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N132">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -7034,10 +7037,10 @@
         <v>282</v>
       </c>
       <c r="C133">
-        <v>0.9990460872650146</v>
+        <v>0.9871893525123596</v>
       </c>
       <c r="D133" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7052,7 +7055,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -7064,10 +7067,10 @@
         <v>0</v>
       </c>
       <c r="M133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N133">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -7078,10 +7081,10 @@
         <v>283</v>
       </c>
       <c r="C134">
-        <v>0.978120744228363</v>
+        <v>0.9990460872650146</v>
       </c>
       <c r="D134" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -7096,7 +7099,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -7122,10 +7125,10 @@
         <v>284</v>
       </c>
       <c r="C135">
-        <v>0.9937021136283875</v>
+        <v>0.978120744228363</v>
       </c>
       <c r="D135" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -7140,10 +7143,10 @@
         <v>0</v>
       </c>
       <c r="I135" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K135">
         <v>0</v>
@@ -7152,10 +7155,10 @@
         <v>0</v>
       </c>
       <c r="M135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N135">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:14">
@@ -7166,10 +7169,10 @@
         <v>285</v>
       </c>
       <c r="C136">
-        <v>0.9984340667724609</v>
+        <v>0.9937021136283875</v>
       </c>
       <c r="D136" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -7184,10 +7187,10 @@
         <v>0</v>
       </c>
       <c r="I136" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136">
         <v>0</v>
@@ -7196,10 +7199,10 @@
         <v>0</v>
       </c>
       <c r="M136">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N136">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -7210,10 +7213,10 @@
         <v>286</v>
       </c>
       <c r="C137">
-        <v>0.9967972040176392</v>
+        <v>0.9984340667724609</v>
       </c>
       <c r="D137" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -7228,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="I137" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137">
         <v>0</v>
@@ -7240,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="M137">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N137">
         <v>2</v>
@@ -7254,39 +7257,83 @@
         <v>287</v>
       </c>
       <c r="C138">
+        <v>0.9967972040176392</v>
+      </c>
+      <c r="D138" t="s">
+        <v>289</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138" t="b">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138" t="s">
+        <v>290</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14">
+      <c r="A139" t="s">
+        <v>151</v>
+      </c>
+      <c r="B139" t="s">
+        <v>288</v>
+      </c>
+      <c r="C139">
         <v>0.9973806738853455</v>
       </c>
-      <c r="D138" t="s">
-        <v>288</v>
-      </c>
-      <c r="E138">
-        <v>0</v>
-      </c>
-      <c r="F138" t="b">
-        <v>0</v>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138" t="s">
-        <v>289</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>2</v>
-      </c>
-      <c r="N138">
+      <c r="D139" t="s">
+        <v>289</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139" t="b">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139" t="s">
+        <v>290</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>2</v>
+      </c>
+      <c r="N139">
         <v>5</v>
       </c>
     </row>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="287">
   <si>
     <t>filename</t>
   </si>
@@ -73,7 +73,7 @@
     <t>micro_0031_1700X400.jpg</t>
   </si>
   <si>
-    <t>micro_0223_2300X408.jpg</t>
+    <t>micro_0160_2300X408.jpg</t>
   </si>
   <si>
     <t>micro_0159_1700X407.jpg</t>
@@ -124,16 +124,13 @@
     <t>micro_0167_2300X201.jpg</t>
   </si>
   <si>
-    <t>micro_0160_2300X408.jpg</t>
-  </si>
-  <si>
     <t>micro_0123_XJ.jpg</t>
   </si>
   <si>
     <t>micro_0109_SL40III.jpg</t>
   </si>
   <si>
-    <t>micro_0291_SL4082600.jpg</t>
+    <t>micro_0293_SL4082600.jpg</t>
   </si>
   <si>
     <t>micro_0296_SL407.jpg</t>
@@ -160,7 +157,7 @@
     <t>micro_0152_SL301.jpg</t>
   </si>
   <si>
-    <t>micro_0173_O_O_SL20VI.jpg</t>
+    <t>micro_0185_OO_0_SL20VI.jpg</t>
   </si>
   <si>
     <t>micro_0273_SL203.jpg</t>
@@ -172,9 +169,6 @@
     <t>micro_0211_SL201.jpg</t>
   </si>
   <si>
-    <t>micro_0185_OO_0_SL20VI.jpg</t>
-  </si>
-  <si>
     <t>micro_0190_O_SBII.jpg</t>
   </si>
   <si>
@@ -319,18 +313,18 @@
     <t>micro_0261_D404.jpg</t>
   </si>
   <si>
+    <t>micro_0133_YD409_D403.jpg</t>
+  </si>
+  <si>
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
+    <t>micro_0290_D401.jpg</t>
+  </si>
+  <si>
     <t>micro_0292_D401.jpg</t>
   </si>
   <si>
-    <t>micro_0290_D401.jpg</t>
-  </si>
-  <si>
-    <t>micro_0133_YD409_D403.jpg</t>
-  </si>
-  <si>
     <t>micro_0089_D3116.jpg</t>
   </si>
   <si>
@@ -538,9 +532,6 @@
     <t>X201</t>
   </si>
   <si>
-    <t>X0028</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
@@ -586,9 +577,6 @@
     <t>SL201</t>
   </si>
   <si>
-    <t>SL2008Ⅴ</t>
-  </si>
-  <si>
     <t>SBⅡ</t>
   </si>
   <si>
@@ -733,13 +721,13 @@
     <t>D404</t>
   </si>
   <si>
+    <t>D403</t>
+  </si>
+  <si>
     <t>D402</t>
   </si>
   <si>
     <t>D401</t>
-  </si>
-  <si>
-    <t>D400349</t>
   </si>
   <si>
     <t>D3116</t>
@@ -1218,7 +1206,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N139"/>
+  <dimension ref="A1:N137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1270,13 +1258,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C2">
-        <v>0.9341862201690674</v>
+        <v>0.922767162322998</v>
       </c>
       <c r="D2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1291,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1314,13 +1302,13 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C3">
         <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1335,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1358,13 +1346,13 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C4">
         <v>0.9089775085449219</v>
       </c>
       <c r="D4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1379,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1402,13 +1390,13 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C5">
         <v>0.7567664980888367</v>
       </c>
       <c r="D5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1423,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1446,13 +1434,13 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C6">
         <v>0.9360489845275879</v>
       </c>
       <c r="D6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1467,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1490,13 +1478,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C7">
-        <v>0.9875660538673401</v>
+        <v>0.9898043870925903</v>
       </c>
       <c r="D7" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1511,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1534,13 +1522,13 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C8">
         <v>0.9800205826759338</v>
       </c>
       <c r="D8" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1555,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1578,13 +1566,13 @@
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C9">
         <v>0.9866096377372742</v>
       </c>
       <c r="D9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1599,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1622,13 +1610,13 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C10">
         <v>0.9825887680053711</v>
       </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1643,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1666,13 +1654,13 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C11">
         <v>0.9854358434677124</v>
       </c>
       <c r="D11" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1687,7 +1675,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1710,13 +1698,13 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C12">
         <v>0.9869511127471924</v>
       </c>
       <c r="D12" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1731,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1754,13 +1742,13 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C13">
         <v>0.9883586168289185</v>
       </c>
       <c r="D13" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1775,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1798,13 +1786,13 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C14">
         <v>0.9827210903167725</v>
       </c>
       <c r="D14" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1819,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1842,13 +1830,13 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C15">
         <v>0.9891344904899597</v>
       </c>
       <c r="D15" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1863,7 +1851,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1886,13 +1874,13 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C16">
         <v>0.9849019646644592</v>
       </c>
       <c r="D16" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1907,7 +1895,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1930,13 +1918,13 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C17">
         <v>0.9831116795539856</v>
       </c>
       <c r="D17" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1951,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1974,13 +1962,13 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C18">
         <v>0.979184627532959</v>
       </c>
       <c r="D18" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1995,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2018,13 +2006,13 @@
         <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C19">
         <v>0.9820773601531982</v>
       </c>
       <c r="D19" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2039,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2062,13 +2050,13 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C20">
         <v>0.9926210641860962</v>
       </c>
       <c r="D20" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2083,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2106,13 +2094,13 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C21">
         <v>0.991193413734436</v>
       </c>
       <c r="D21" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2127,7 +2115,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2150,13 +2138,13 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C22">
         <v>0.9759405851364136</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2171,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2194,13 +2182,13 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C23">
         <v>0.9936316609382629</v>
       </c>
       <c r="D23" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2215,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2238,16 +2226,16 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C24">
-        <v>0.768846869468689</v>
+        <v>0.7151024341583252</v>
       </c>
       <c r="D24" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -2259,13 +2247,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>1</v>
@@ -2282,13 +2270,13 @@
         <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C25">
-        <v>0.7151024341583252</v>
+        <v>0.9834394454956055</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2303,22 +2291,22 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -2326,13 +2314,13 @@
         <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C26">
-        <v>0.9909618496894836</v>
+        <v>0.9938239455223083</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2347,22 +2335,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2370,13 +2358,13 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C27">
-        <v>0.9938899278640747</v>
+        <v>0.9959491491317749</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2391,22 +2379,22 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J27">
         <v>1</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27">
         <v>0</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -2414,13 +2402,13 @@
         <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C28">
-        <v>0.9962404370307922</v>
+        <v>0.9976895451545715</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2435,22 +2423,22 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J28">
         <v>1</v>
       </c>
       <c r="K28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28">
         <v>0</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -2458,13 +2446,13 @@
         <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C29">
-        <v>0.9971726536750793</v>
+        <v>0.9959992170333862</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2479,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2494,7 +2482,7 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2502,13 +2490,13 @@
         <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C30">
-        <v>0.9959992170333862</v>
+        <v>0.9971073865890503</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2523,7 +2511,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2538,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2546,13 +2534,13 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C31">
-        <v>0.9987277984619141</v>
+        <v>0.9968833923339844</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2567,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2582,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2590,13 +2578,13 @@
         <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C32">
-        <v>0.990104079246521</v>
+        <v>0.9585862159729004</v>
       </c>
       <c r="D32" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2611,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2634,13 +2622,13 @@
         <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C33">
-        <v>0.9917885661125183</v>
+        <v>0.9959156513214111</v>
       </c>
       <c r="D33" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2655,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2678,13 +2666,13 @@
         <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C34">
-        <v>0.9959156513214111</v>
+        <v>0.9984833598136902</v>
       </c>
       <c r="D34" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2699,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2722,13 +2710,13 @@
         <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C35">
-        <v>0.9986041784286499</v>
+        <v>0.9960424304008484</v>
       </c>
       <c r="D35" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2743,22 +2731,22 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35">
         <v>1</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2766,13 +2754,13 @@
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C36">
-        <v>0.9965012669563293</v>
+        <v>0.9988101124763489</v>
       </c>
       <c r="D36" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2787,22 +2775,22 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36">
         <v>1</v>
       </c>
       <c r="M36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N36">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2810,13 +2798,13 @@
         <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C37">
-        <v>0.9989038705825806</v>
+        <v>0.9754772186279297</v>
       </c>
       <c r="D37" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2831,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2854,13 +2842,13 @@
         <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C38">
-        <v>0.9787384867668152</v>
+        <v>0.9673787951469421</v>
       </c>
       <c r="D38" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2875,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2898,13 +2886,13 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C39">
-        <v>0.9673787951469421</v>
+        <v>0.7677456140518188</v>
       </c>
       <c r="D39" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2919,13 +2907,13 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J39">
         <v>1</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39">
         <v>1</v>
@@ -2934,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2942,13 +2930,13 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C40">
-        <v>0.9990044236183167</v>
+        <v>0.8940553665161133</v>
       </c>
       <c r="D40" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2963,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2975,10 +2963,10 @@
         <v>1</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N40">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2986,13 +2974,13 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C41">
-        <v>0.7677456140518188</v>
+        <v>0.9920957684516907</v>
       </c>
       <c r="D41" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3007,13 +2995,13 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J41">
         <v>1</v>
       </c>
       <c r="K41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L41">
         <v>1</v>
@@ -3022,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -3030,13 +3018,13 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C42">
-        <v>0.8940553665161133</v>
+        <v>0.9965819120407104</v>
       </c>
       <c r="D42" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3051,13 +3039,13 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42">
         <v>1</v>
@@ -3066,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="N42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -3074,13 +3062,13 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C43">
-        <v>0.9920957684516907</v>
+        <v>0.9989708662033081</v>
       </c>
       <c r="D43" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3095,13 +3083,13 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43">
         <v>1</v>
@@ -3110,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="N43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -3118,13 +3106,13 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C44">
-        <v>0.9965819120407104</v>
+        <v>0.9991652369499207</v>
       </c>
       <c r="D44" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3139,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3154,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -3162,13 +3150,13 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C45">
-        <v>0.9981755018234253</v>
+        <v>0.9990001320838928</v>
       </c>
       <c r="D45" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3183,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3192,13 +3180,13 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -3206,13 +3194,13 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C46">
-        <v>0.9990609288215637</v>
+        <v>0.9990422129631042</v>
       </c>
       <c r="D46" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3227,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3236,13 +3224,13 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N46">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -3250,13 +3238,13 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C47">
-        <v>0.9990001320838928</v>
+        <v>0.9962484240531921</v>
       </c>
       <c r="D47" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3271,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3286,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -3294,13 +3282,13 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C48">
-        <v>0.9990422129631042</v>
+        <v>0.9956099390983582</v>
       </c>
       <c r="D48" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3315,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3327,10 +3315,10 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -3338,13 +3326,13 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C49">
-        <v>0.9962484240531921</v>
+        <v>0.9993695020675659</v>
       </c>
       <c r="D49" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3359,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3374,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -3382,13 +3370,13 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C50">
-        <v>0.9956099390983582</v>
+        <v>0.9990277886390686</v>
       </c>
       <c r="D50" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3403,7 +3391,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3418,7 +3406,7 @@
         <v>2</v>
       </c>
       <c r="N50">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -3426,13 +3414,13 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C51">
-        <v>0.9993695020675659</v>
+        <v>0.9995902180671692</v>
       </c>
       <c r="D51" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3447,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3462,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="N51">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -3470,13 +3458,13 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C52">
-        <v>0.9990277886390686</v>
+        <v>0.9994117021560669</v>
       </c>
       <c r="D52" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3491,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3503,10 +3491,10 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N52">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -3514,13 +3502,13 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C53">
-        <v>0.9995902180671692</v>
+        <v>0.9994282722473145</v>
       </c>
       <c r="D53" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3535,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3558,13 +3546,13 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C54">
-        <v>0.9994117021560669</v>
+        <v>0.999479353427887</v>
       </c>
       <c r="D54" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3579,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3594,7 +3582,7 @@
         <v>1</v>
       </c>
       <c r="N54">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -3602,13 +3590,13 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C55">
-        <v>0.9994282722473145</v>
+        <v>0.9984571933746338</v>
       </c>
       <c r="D55" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3623,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3638,7 +3626,7 @@
         <v>1</v>
       </c>
       <c r="N55">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -3646,13 +3634,13 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C56">
-        <v>0.999479353427887</v>
+        <v>0.9981318712234497</v>
       </c>
       <c r="D56" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3667,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3682,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -3690,13 +3678,13 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C57">
-        <v>0.9984571933746338</v>
+        <v>0.999025285243988</v>
       </c>
       <c r="D57" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3711,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -3723,10 +3711,10 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N57">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3734,13 +3722,13 @@
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C58">
-        <v>0.9981318712234497</v>
+        <v>0.933538019657135</v>
       </c>
       <c r="D58" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3755,7 +3743,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -3767,10 +3755,10 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N58">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3778,13 +3766,13 @@
         <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C59">
-        <v>0.999025285243988</v>
+        <v>0.9989953637123108</v>
       </c>
       <c r="D59" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3799,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3811,10 +3799,10 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3822,13 +3810,13 @@
         <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C60">
-        <v>0.933538019657135</v>
+        <v>0.9986401796340942</v>
       </c>
       <c r="D60" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3843,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3858,7 +3846,7 @@
         <v>3</v>
       </c>
       <c r="N60">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3866,13 +3854,13 @@
         <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C61">
-        <v>0.9989953637123108</v>
+        <v>0.9990375638008118</v>
       </c>
       <c r="D61" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3887,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -3899,10 +3887,10 @@
         <v>0</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N61">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3910,13 +3898,13 @@
         <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C62">
-        <v>0.9986401796340942</v>
+        <v>0.8789094686508179</v>
       </c>
       <c r="D62" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3931,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -3946,7 +3934,7 @@
         <v>3</v>
       </c>
       <c r="N62">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3954,13 +3942,13 @@
         <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C63">
-        <v>0.9990375638008118</v>
+        <v>0.9988136887550354</v>
       </c>
       <c r="D63" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3975,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -3990,7 +3978,7 @@
         <v>1</v>
       </c>
       <c r="N63">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3998,13 +3986,13 @@
         <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C64">
-        <v>0.8789094686508179</v>
+        <v>0.9909911155700684</v>
       </c>
       <c r="D64" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4019,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4031,10 +4019,10 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N64">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -4042,13 +4030,13 @@
         <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C65">
-        <v>0.9988136887550354</v>
+        <v>0.9983184337615967</v>
       </c>
       <c r="D65" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4063,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4075,10 +4063,10 @@
         <v>0</v>
       </c>
       <c r="M65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N65">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -4086,13 +4074,13 @@
         <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C66">
-        <v>0.9909911155700684</v>
+        <v>0.9994446039199829</v>
       </c>
       <c r="D66" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4107,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4119,10 +4107,10 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -4130,13 +4118,13 @@
         <v>79</v>
       </c>
       <c r="B67" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C67">
-        <v>0.9983184337615967</v>
+        <v>0.9993821382522583</v>
       </c>
       <c r="D67" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4151,7 +4139,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4163,10 +4151,10 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -4174,13 +4162,13 @@
         <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C68">
-        <v>0.9994446039199829</v>
+        <v>0.9976016283035278</v>
       </c>
       <c r="D68" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4195,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4207,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -4218,13 +4206,13 @@
         <v>81</v>
       </c>
       <c r="B69" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C69">
-        <v>0.9993821382522583</v>
+        <v>0.9990072250366211</v>
       </c>
       <c r="D69" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4239,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4251,10 +4239,10 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -4262,13 +4250,13 @@
         <v>82</v>
       </c>
       <c r="B70" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C70">
-        <v>0.9976016283035278</v>
+        <v>0.9991657733917236</v>
       </c>
       <c r="D70" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4283,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4295,10 +4283,10 @@
         <v>0</v>
       </c>
       <c r="M70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N70">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -4306,13 +4294,13 @@
         <v>83</v>
       </c>
       <c r="B71" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C71">
-        <v>0.9990072250366211</v>
+        <v>0.997841477394104</v>
       </c>
       <c r="D71" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4327,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4339,10 +4327,10 @@
         <v>0</v>
       </c>
       <c r="M71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N71">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -4350,13 +4338,13 @@
         <v>84</v>
       </c>
       <c r="B72" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C72">
-        <v>0.9991657733917236</v>
+        <v>0.9976445436477661</v>
       </c>
       <c r="D72" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4371,7 +4359,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4383,10 +4371,10 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -4394,13 +4382,13 @@
         <v>85</v>
       </c>
       <c r="B73" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C73">
-        <v>0.997841477394104</v>
+        <v>0.9980232715606689</v>
       </c>
       <c r="D73" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4415,7 +4403,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4438,13 +4426,13 @@
         <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C74">
-        <v>0.9976445436477661</v>
+        <v>0.9990618228912354</v>
       </c>
       <c r="D74" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4459,7 +4447,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4471,10 +4459,10 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N74">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -4482,13 +4470,13 @@
         <v>87</v>
       </c>
       <c r="B75" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C75">
-        <v>0.9980232715606689</v>
+        <v>0.9994759559631348</v>
       </c>
       <c r="D75" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4503,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4515,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N75">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -4526,13 +4514,13 @@
         <v>88</v>
       </c>
       <c r="B76" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C76">
-        <v>0.9990618228912354</v>
+        <v>0.9992071986198425</v>
       </c>
       <c r="D76" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4547,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4559,10 +4547,10 @@
         <v>0</v>
       </c>
       <c r="M76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N76">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -4570,13 +4558,13 @@
         <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C77">
-        <v>0.9994759559631348</v>
+        <v>0.9985552430152893</v>
       </c>
       <c r="D77" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4591,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4603,10 +4591,10 @@
         <v>0</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N77">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -4614,13 +4602,13 @@
         <v>90</v>
       </c>
       <c r="B78" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C78">
-        <v>0.9992071986198425</v>
+        <v>0.9976009726524353</v>
       </c>
       <c r="D78" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4635,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4647,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N78">
         <v>3</v>
@@ -4658,13 +4646,13 @@
         <v>91</v>
       </c>
       <c r="B79" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C79">
-        <v>0.9985552430152893</v>
+        <v>0.9884098172187805</v>
       </c>
       <c r="D79" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -4679,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4691,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="M79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -4702,13 +4690,13 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C80">
-        <v>0.9976009726524353</v>
+        <v>0.7832491993904114</v>
       </c>
       <c r="D80" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -4723,7 +4711,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4735,10 +4723,10 @@
         <v>0</v>
       </c>
       <c r="M80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N80">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4746,13 +4734,13 @@
         <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C81">
-        <v>0.9884098172187805</v>
+        <v>0.9955025911331177</v>
       </c>
       <c r="D81" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -4767,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4790,13 +4778,13 @@
         <v>94</v>
       </c>
       <c r="B82" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C82">
-        <v>0.7832491993904114</v>
+        <v>0.9995555877685547</v>
       </c>
       <c r="D82" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -4811,7 +4799,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -4826,7 +4814,7 @@
         <v>2</v>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4834,13 +4822,13 @@
         <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C83">
-        <v>0.9955025911331177</v>
+        <v>0.9975136518478394</v>
       </c>
       <c r="D83" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4855,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -4867,10 +4855,10 @@
         <v>0</v>
       </c>
       <c r="M83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N83">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4878,13 +4866,13 @@
         <v>96</v>
       </c>
       <c r="B84" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C84">
-        <v>0.9995555877685547</v>
+        <v>0.9972119331359863</v>
       </c>
       <c r="D84" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -4899,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -4911,10 +4899,10 @@
         <v>0</v>
       </c>
       <c r="M84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N84">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4922,13 +4910,13 @@
         <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C85">
-        <v>0.9975136518478394</v>
+        <v>0.9980412721633911</v>
       </c>
       <c r="D85" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4943,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -4955,10 +4943,10 @@
         <v>0</v>
       </c>
       <c r="M85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N85">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4966,13 +4954,13 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C86">
-        <v>0.9972119331359863</v>
+        <v>0.997714638710022</v>
       </c>
       <c r="D86" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4987,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -4999,10 +4987,10 @@
         <v>0</v>
       </c>
       <c r="M86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N86">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -5010,13 +4998,13 @@
         <v>99</v>
       </c>
       <c r="B87" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C87">
-        <v>0.9980412721633911</v>
+        <v>0.9316359758377075</v>
       </c>
       <c r="D87" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5031,7 +5019,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5043,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N87">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -5054,13 +5042,13 @@
         <v>100</v>
       </c>
       <c r="B88" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C88">
-        <v>0.997714638710022</v>
+        <v>0.9981099367141724</v>
       </c>
       <c r="D88" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5075,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5087,7 +5075,7 @@
         <v>0</v>
       </c>
       <c r="M88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -5098,13 +5086,13 @@
         <v>101</v>
       </c>
       <c r="B89" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C89">
-        <v>0.9981099367141724</v>
+        <v>0.996095597743988</v>
       </c>
       <c r="D89" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5119,7 +5107,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5134,7 +5122,7 @@
         <v>1</v>
       </c>
       <c r="N89">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -5142,13 +5130,13 @@
         <v>102</v>
       </c>
       <c r="B90" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C90">
         <v>1</v>
       </c>
       <c r="D90" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5163,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5186,13 +5174,13 @@
         <v>103</v>
       </c>
       <c r="B91" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C91">
-        <v>0.996095597743988</v>
+        <v>0.9997719526290894</v>
       </c>
       <c r="D91" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5207,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5219,10 +5207,10 @@
         <v>0</v>
       </c>
       <c r="M91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N91">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -5230,13 +5218,13 @@
         <v>104</v>
       </c>
       <c r="B92" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C92">
-        <v>0.9316359758377075</v>
+        <v>0.9881560802459717</v>
       </c>
       <c r="D92" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5251,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5274,13 +5262,13 @@
         <v>105</v>
       </c>
       <c r="B93" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C93">
-        <v>0.9997719526290894</v>
+        <v>0.9993869662284851</v>
       </c>
       <c r="D93" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5295,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5307,10 +5295,10 @@
         <v>0</v>
       </c>
       <c r="M93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N93">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -5318,13 +5306,13 @@
         <v>106</v>
       </c>
       <c r="B94" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C94">
-        <v>0.9881560802459717</v>
+        <v>0.9876304268836975</v>
       </c>
       <c r="D94" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5339,7 +5327,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5362,13 +5350,13 @@
         <v>107</v>
       </c>
       <c r="B95" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C95">
-        <v>0.9993869662284851</v>
+        <v>0.9915251135826111</v>
       </c>
       <c r="D95" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5383,7 +5371,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5398,7 +5386,7 @@
         <v>1</v>
       </c>
       <c r="N95">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -5406,13 +5394,13 @@
         <v>108</v>
       </c>
       <c r="B96" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C96">
-        <v>0.9876304268836975</v>
+        <v>0.9993435144424438</v>
       </c>
       <c r="D96" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5427,7 +5415,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5450,13 +5438,13 @@
         <v>109</v>
       </c>
       <c r="B97" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C97">
-        <v>0.9915251135826111</v>
+        <v>0.9956748485565186</v>
       </c>
       <c r="D97" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -5471,22 +5459,22 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97">
         <v>0</v>
       </c>
       <c r="L97">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M97">
         <v>1</v>
       </c>
       <c r="N97">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -5494,13 +5482,13 @@
         <v>110</v>
       </c>
       <c r="B98" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C98">
-        <v>0.9993435144424438</v>
+        <v>0.9915837645530701</v>
       </c>
       <c r="D98" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -5515,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -5538,13 +5526,13 @@
         <v>111</v>
       </c>
       <c r="B99" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C99">
-        <v>0.9956748485565186</v>
+        <v>0.9992069602012634</v>
       </c>
       <c r="D99" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -5559,22 +5547,22 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99">
         <v>0</v>
       </c>
       <c r="L99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M99">
         <v>1</v>
       </c>
       <c r="N99">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -5582,13 +5570,13 @@
         <v>112</v>
       </c>
       <c r="B100" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C100">
-        <v>0.9915837645530701</v>
+        <v>0.9964823126792908</v>
       </c>
       <c r="D100" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -5603,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -5626,13 +5614,13 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C101">
-        <v>0.9992069602012634</v>
+        <v>0.9991474747657776</v>
       </c>
       <c r="D101" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -5647,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -5670,13 +5658,13 @@
         <v>114</v>
       </c>
       <c r="B102" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C102">
-        <v>0.9964823126792908</v>
+        <v>0.9979246258735657</v>
       </c>
       <c r="D102" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -5691,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -5714,13 +5702,13 @@
         <v>115</v>
       </c>
       <c r="B103" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C103">
-        <v>0.9991474747657776</v>
+        <v>0.9995026588439941</v>
       </c>
       <c r="D103" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -5735,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -5750,7 +5738,7 @@
         <v>1</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5758,13 +5746,13 @@
         <v>116</v>
       </c>
       <c r="B104" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C104">
-        <v>0.9979246258735657</v>
+        <v>0.9919981956481934</v>
       </c>
       <c r="D104" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -5779,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -5802,13 +5790,13 @@
         <v>117</v>
       </c>
       <c r="B105" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C105">
-        <v>0.9995026588439941</v>
+        <v>0.8529298901557922</v>
       </c>
       <c r="D105" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -5823,10 +5811,10 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105">
         <v>0</v>
@@ -5838,7 +5826,7 @@
         <v>1</v>
       </c>
       <c r="N105">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -5846,13 +5834,13 @@
         <v>118</v>
       </c>
       <c r="B106" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C106">
-        <v>0.9919981956481934</v>
+        <v>0.9926774501800537</v>
       </c>
       <c r="D106" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -5867,7 +5855,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -5890,13 +5878,13 @@
         <v>119</v>
       </c>
       <c r="B107" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C107">
-        <v>0.8529298901557922</v>
+        <v>0.9982547760009766</v>
       </c>
       <c r="D107" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -5911,10 +5899,10 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K107">
         <v>0</v>
@@ -5934,13 +5922,13 @@
         <v>120</v>
       </c>
       <c r="B108" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C108">
-        <v>0.9926774501800537</v>
+        <v>0.9919293522834778</v>
       </c>
       <c r="D108" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -5955,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -5978,13 +5966,13 @@
         <v>121</v>
       </c>
       <c r="B109" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C109">
-        <v>0.9982547760009766</v>
+        <v>0.9978511333465576</v>
       </c>
       <c r="D109" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -5999,22 +5987,22 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N109">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -6022,13 +6010,13 @@
         <v>122</v>
       </c>
       <c r="B110" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C110">
-        <v>0.9919293522834778</v>
+        <v>0.999393105506897</v>
       </c>
       <c r="D110" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6043,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6066,13 +6054,13 @@
         <v>123</v>
       </c>
       <c r="B111" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C111">
-        <v>0.9978511333465576</v>
+        <v>0.9981414675712585</v>
       </c>
       <c r="D111" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6087,22 +6075,22 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N111">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -6110,13 +6098,13 @@
         <v>124</v>
       </c>
       <c r="B112" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C112">
-        <v>0.999393105506897</v>
+        <v>0.995561420917511</v>
       </c>
       <c r="D112" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6131,7 +6119,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -6154,13 +6142,13 @@
         <v>125</v>
       </c>
       <c r="B113" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C113">
-        <v>0.9981414675712585</v>
+        <v>0.99856036901474</v>
       </c>
       <c r="D113" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6175,7 +6163,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6187,10 +6175,10 @@
         <v>0</v>
       </c>
       <c r="M113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N113">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -6198,13 +6186,13 @@
         <v>126</v>
       </c>
       <c r="B114" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C114">
-        <v>0.995561420917511</v>
+        <v>0.9979491829872131</v>
       </c>
       <c r="D114" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6219,7 +6207,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -6231,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="M114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -6242,13 +6230,13 @@
         <v>127</v>
       </c>
       <c r="B115" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C115">
-        <v>0.99856036901474</v>
+        <v>0.9989242553710938</v>
       </c>
       <c r="D115" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6263,22 +6251,22 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115">
         <v>2</v>
       </c>
       <c r="N115">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -6286,13 +6274,13 @@
         <v>128</v>
       </c>
       <c r="B116" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C116">
-        <v>0.9979491829872131</v>
+        <v>0.9987018704414368</v>
       </c>
       <c r="D116" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6307,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6319,10 +6307,10 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N116">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -6330,13 +6318,13 @@
         <v>129</v>
       </c>
       <c r="B117" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C117">
-        <v>0.9989242553710938</v>
+        <v>0.9980301260948181</v>
       </c>
       <c r="D117" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6351,22 +6339,22 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M117">
         <v>2</v>
       </c>
       <c r="N117">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -6374,13 +6362,13 @@
         <v>130</v>
       </c>
       <c r="B118" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C118">
-        <v>0.9987018704414368</v>
+        <v>0.9988909959793091</v>
       </c>
       <c r="D118" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -6395,7 +6383,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -6407,10 +6395,10 @@
         <v>0</v>
       </c>
       <c r="M118">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N118">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -6418,13 +6406,13 @@
         <v>131</v>
       </c>
       <c r="B119" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C119">
-        <v>0.9980301260948181</v>
+        <v>0.9961404204368591</v>
       </c>
       <c r="D119" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -6439,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6451,10 +6439,10 @@
         <v>0</v>
       </c>
       <c r="M119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N119">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -6462,13 +6450,13 @@
         <v>132</v>
       </c>
       <c r="B120" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C120">
-        <v>0.9988909959793091</v>
+        <v>0.9958701133728027</v>
       </c>
       <c r="D120" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6483,7 +6471,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6506,13 +6494,13 @@
         <v>133</v>
       </c>
       <c r="B121" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C121">
-        <v>0.9961404204368591</v>
+        <v>0.998413622379303</v>
       </c>
       <c r="D121" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -6527,7 +6515,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6539,10 +6527,10 @@
         <v>0</v>
       </c>
       <c r="M121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N121">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -6550,13 +6538,13 @@
         <v>134</v>
       </c>
       <c r="B122" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C122">
-        <v>0.9958701133728027</v>
+        <v>0.9992607235908508</v>
       </c>
       <c r="D122" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -6571,7 +6559,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -6594,13 +6582,13 @@
         <v>135</v>
       </c>
       <c r="B123" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C123">
-        <v>0.998413622379303</v>
+        <v>0.9961749315261841</v>
       </c>
       <c r="D123" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -6615,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -6627,7 +6615,7 @@
         <v>0</v>
       </c>
       <c r="M123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N123">
         <v>1</v>
@@ -6638,13 +6626,13 @@
         <v>136</v>
       </c>
       <c r="B124" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C124">
-        <v>0.9992607235908508</v>
+        <v>0.9993590712547302</v>
       </c>
       <c r="D124" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -6659,7 +6647,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -6674,7 +6662,7 @@
         <v>2</v>
       </c>
       <c r="N124">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -6682,13 +6670,13 @@
         <v>137</v>
       </c>
       <c r="B125" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C125">
-        <v>0.9961749315261841</v>
+        <v>0.9987558722496033</v>
       </c>
       <c r="D125" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -6703,7 +6691,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -6726,13 +6714,13 @@
         <v>138</v>
       </c>
       <c r="B126" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C126">
-        <v>0.9993590712547302</v>
+        <v>0.9992091655731201</v>
       </c>
       <c r="D126" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -6747,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -6762,7 +6750,7 @@
         <v>2</v>
       </c>
       <c r="N126">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6770,13 +6758,13 @@
         <v>139</v>
       </c>
       <c r="B127" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C127">
-        <v>0.9987558722496033</v>
+        <v>0.9622448682785034</v>
       </c>
       <c r="D127" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -6791,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -6806,7 +6794,7 @@
         <v>2</v>
       </c>
       <c r="N127">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -6814,13 +6802,13 @@
         <v>140</v>
       </c>
       <c r="B128" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C128">
-        <v>0.9992091655731201</v>
+        <v>0.9945164322853088</v>
       </c>
       <c r="D128" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -6835,7 +6823,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -6847,10 +6835,10 @@
         <v>0</v>
       </c>
       <c r="M128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N128">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6858,13 +6846,13 @@
         <v>141</v>
       </c>
       <c r="B129" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C129">
-        <v>0.9622448682785034</v>
+        <v>0.995938241481781</v>
       </c>
       <c r="D129" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -6879,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -6902,13 +6890,13 @@
         <v>142</v>
       </c>
       <c r="B130" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C130">
-        <v>0.9945164322853088</v>
+        <v>0.998788058757782</v>
       </c>
       <c r="D130" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -6923,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -6938,7 +6926,7 @@
         <v>1</v>
       </c>
       <c r="N130">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6946,13 +6934,13 @@
         <v>143</v>
       </c>
       <c r="B131" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C131">
-        <v>0.995938241481781</v>
+        <v>0.9871893525123596</v>
       </c>
       <c r="D131" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -6967,7 +6955,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -6990,13 +6978,13 @@
         <v>144</v>
       </c>
       <c r="B132" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C132">
-        <v>0.998788058757782</v>
+        <v>0.9990460872650146</v>
       </c>
       <c r="D132" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7011,7 +6999,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -7034,13 +7022,13 @@
         <v>145</v>
       </c>
       <c r="B133" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C133">
-        <v>0.9871893525123596</v>
+        <v>0.978120744228363</v>
       </c>
       <c r="D133" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7055,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -7067,10 +7055,10 @@
         <v>0</v>
       </c>
       <c r="M133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N133">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -7078,13 +7066,13 @@
         <v>146</v>
       </c>
       <c r="B134" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C134">
-        <v>0.9990460872650146</v>
+        <v>0.9937021136283875</v>
       </c>
       <c r="D134" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -7099,10 +7087,10 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134">
         <v>0</v>
@@ -7111,10 +7099,10 @@
         <v>0</v>
       </c>
       <c r="M134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N134">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -7122,13 +7110,13 @@
         <v>147</v>
       </c>
       <c r="B135" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C135">
-        <v>0.978120744228363</v>
+        <v>0.9984340667724609</v>
       </c>
       <c r="D135" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -7143,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="I135" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -7155,7 +7143,7 @@
         <v>0</v>
       </c>
       <c r="M135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N135">
         <v>2</v>
@@ -7166,13 +7154,13 @@
         <v>148</v>
       </c>
       <c r="B136" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C136">
-        <v>0.9937021136283875</v>
+        <v>0.9967972040176392</v>
       </c>
       <c r="D136" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -7187,7 +7175,7 @@
         <v>0</v>
       </c>
       <c r="I136" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J136">
         <v>1</v>
@@ -7202,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="N136">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -7210,13 +7198,13 @@
         <v>149</v>
       </c>
       <c r="B137" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C137">
-        <v>0.9984340667724609</v>
+        <v>0.9973806738853455</v>
       </c>
       <c r="D137" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -7231,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="I137" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -7246,94 +7234,6 @@
         <v>2</v>
       </c>
       <c r="N137">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:14">
-      <c r="A138" t="s">
-        <v>150</v>
-      </c>
-      <c r="B138" t="s">
-        <v>287</v>
-      </c>
-      <c r="C138">
-        <v>0.9967972040176392</v>
-      </c>
-      <c r="D138" t="s">
-        <v>289</v>
-      </c>
-      <c r="E138">
-        <v>0</v>
-      </c>
-      <c r="F138" t="b">
-        <v>0</v>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138" t="s">
-        <v>290</v>
-      </c>
-      <c r="J138">
-        <v>1</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138">
-        <v>0</v>
-      </c>
-      <c r="N138">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:14">
-      <c r="A139" t="s">
-        <v>151</v>
-      </c>
-      <c r="B139" t="s">
-        <v>288</v>
-      </c>
-      <c r="C139">
-        <v>0.9973806738853455</v>
-      </c>
-      <c r="D139" t="s">
-        <v>289</v>
-      </c>
-      <c r="E139">
-        <v>0</v>
-      </c>
-      <c r="F139" t="b">
-        <v>0</v>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139" t="s">
-        <v>290</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139">
-        <v>2</v>
-      </c>
-      <c r="N139">
         <v>5</v>
       </c>
     </row>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="282">
   <si>
     <t>filename</t>
   </si>
@@ -130,10 +130,10 @@
     <t>micro_0109_SL40III.jpg</t>
   </si>
   <si>
-    <t>micro_0293_SL4082600.jpg</t>
-  </si>
-  <si>
-    <t>micro_0296_SL407.jpg</t>
+    <t>micro_0291_SL4082600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0113_SL407.jpg</t>
   </si>
   <si>
     <t>micro_0112_SL406.jpg</t>
@@ -151,9 +151,6 @@
     <t>micro_0105_SL401.jpg</t>
   </si>
   <si>
-    <t>micro_0107_X.jpg</t>
-  </si>
-  <si>
     <t>micro_0152_SL301.jpg</t>
   </si>
   <si>
@@ -175,9 +172,6 @@
     <t>micro_0289_SBI.jpg</t>
   </si>
   <si>
-    <t>micro_0154_X.jpg</t>
-  </si>
-  <si>
     <t>micro_0231_FX201.jpg</t>
   </si>
   <si>
@@ -319,10 +313,7 @@
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
-    <t>micro_0290_D401.jpg</t>
-  </si>
-  <si>
-    <t>micro_0292_D401.jpg</t>
+    <t>micro_0131_D401.jpg</t>
   </si>
   <si>
     <t>micro_0089_D3116.jpg</t>
@@ -559,9 +550,6 @@
     <t>SL401</t>
   </si>
   <si>
-    <t>SL4</t>
-  </si>
-  <si>
     <t>SL301</t>
   </si>
   <si>
@@ -581,9 +569,6 @@
   </si>
   <si>
     <t>SBⅠ</t>
-  </si>
-  <si>
-    <t>S</t>
   </si>
   <si>
     <t>FX201</t>
@@ -1206,7 +1191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N137"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1258,13 +1243,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C2">
         <v>0.922767162322998</v>
       </c>
       <c r="D2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1279,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1302,13 +1287,13 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C3">
         <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1323,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1346,13 +1331,13 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C4">
         <v>0.9089775085449219</v>
       </c>
       <c r="D4" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1367,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1390,13 +1375,13 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C5">
         <v>0.7567664980888367</v>
       </c>
       <c r="D5" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1411,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1434,13 +1419,13 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C6">
         <v>0.9360489845275879</v>
       </c>
       <c r="D6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1455,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1478,13 +1463,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C7">
         <v>0.9898043870925903</v>
       </c>
       <c r="D7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1499,7 +1484,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1522,13 +1507,13 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C8">
         <v>0.9800205826759338</v>
       </c>
       <c r="D8" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1543,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1566,13 +1551,13 @@
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C9">
         <v>0.9866096377372742</v>
       </c>
       <c r="D9" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1587,7 +1572,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1610,13 +1595,13 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C10">
         <v>0.9825887680053711</v>
       </c>
       <c r="D10" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1631,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1654,13 +1639,13 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C11">
         <v>0.9854358434677124</v>
       </c>
       <c r="D11" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1675,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1698,13 +1683,13 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C12">
         <v>0.9869511127471924</v>
       </c>
       <c r="D12" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1719,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1742,13 +1727,13 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C13">
         <v>0.9883586168289185</v>
       </c>
       <c r="D13" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1763,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1786,13 +1771,13 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C14">
         <v>0.9827210903167725</v>
       </c>
       <c r="D14" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1807,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1830,13 +1815,13 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C15">
         <v>0.9891344904899597</v>
       </c>
       <c r="D15" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1851,7 +1836,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1874,13 +1859,13 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C16">
         <v>0.9849019646644592</v>
       </c>
       <c r="D16" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1895,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1918,13 +1903,13 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C17">
         <v>0.9831116795539856</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1939,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1962,13 +1947,13 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C18">
         <v>0.979184627532959</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1983,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2006,13 +1991,13 @@
         <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C19">
         <v>0.9820773601531982</v>
       </c>
       <c r="D19" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2027,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2050,13 +2035,13 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C20">
         <v>0.9926210641860962</v>
       </c>
       <c r="D20" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2071,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2094,13 +2079,13 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C21">
         <v>0.991193413734436</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2115,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2138,13 +2123,13 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C22">
         <v>0.9759405851364136</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2159,7 +2144,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2182,13 +2167,13 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C23">
         <v>0.9936316609382629</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2203,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2226,13 +2211,13 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C24">
         <v>0.7151024341583252</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2247,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2270,13 +2255,13 @@
         <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C25">
         <v>0.9834394454956055</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2291,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2314,13 +2299,13 @@
         <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C26">
         <v>0.9938239455223083</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2335,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2358,13 +2343,13 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C27">
-        <v>0.9959491491317749</v>
+        <v>0.9970995783805847</v>
       </c>
       <c r="D27" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2379,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J27">
         <v>1</v>
       </c>
       <c r="K27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -2402,13 +2387,13 @@
         <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C28">
         <v>0.9976895451545715</v>
       </c>
       <c r="D28" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2423,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2446,13 +2431,13 @@
         <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C29">
         <v>0.9959992170333862</v>
       </c>
       <c r="D29" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2467,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2490,13 +2475,13 @@
         <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C30">
         <v>0.9971073865890503</v>
       </c>
       <c r="D30" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2511,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2534,13 +2519,13 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C31">
         <v>0.9968833923339844</v>
       </c>
       <c r="D31" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2555,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2578,13 +2563,13 @@
         <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C32">
         <v>0.9585862159729004</v>
       </c>
       <c r="D32" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2599,7 +2584,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2622,13 +2607,13 @@
         <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C33">
-        <v>0.9959156513214111</v>
+        <v>0.9984833598136902</v>
       </c>
       <c r="D33" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2643,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2666,13 +2651,13 @@
         <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C34">
-        <v>0.9984833598136902</v>
+        <v>0.9960424304008484</v>
       </c>
       <c r="D34" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2687,22 +2672,22 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L34">
         <v>1</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -2710,13 +2695,13 @@
         <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C35">
-        <v>0.9960424304008484</v>
+        <v>0.9988101124763489</v>
       </c>
       <c r="D35" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2731,22 +2716,22 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J35">
         <v>1</v>
       </c>
       <c r="K35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35">
         <v>1</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2754,13 +2739,13 @@
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C36">
-        <v>0.9988101124763489</v>
+        <v>0.9754772186279297</v>
       </c>
       <c r="D36" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2775,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2798,13 +2783,13 @@
         <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C37">
-        <v>0.9754772186279297</v>
+        <v>0.9673787951469421</v>
       </c>
       <c r="D37" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2819,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2842,13 +2827,13 @@
         <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C38">
-        <v>0.9673787951469421</v>
+        <v>0.7677456140518188</v>
       </c>
       <c r="D38" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2863,13 +2848,13 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J38">
         <v>1</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L38">
         <v>1</v>
@@ -2878,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2886,13 +2871,13 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C39">
-        <v>0.7677456140518188</v>
+        <v>0.8940553665161133</v>
       </c>
       <c r="D39" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2907,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2922,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2930,13 +2915,13 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C40">
-        <v>0.8940553665161133</v>
+        <v>0.9965819120407104</v>
       </c>
       <c r="D40" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2951,13 +2936,13 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L40">
         <v>1</v>
@@ -2966,7 +2951,7 @@
         <v>0</v>
       </c>
       <c r="N40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2974,13 +2959,13 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C41">
-        <v>0.9920957684516907</v>
+        <v>0.9989708662033081</v>
       </c>
       <c r="D41" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2995,13 +2980,13 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41">
         <v>1</v>
@@ -3010,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -3018,13 +3003,13 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C42">
-        <v>0.9965819120407104</v>
+        <v>0.9991652369499207</v>
       </c>
       <c r="D42" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3039,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3054,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -3062,13 +3047,13 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C43">
-        <v>0.9989708662033081</v>
+        <v>0.9990001320838928</v>
       </c>
       <c r="D43" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3083,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3092,13 +3077,13 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -3106,13 +3091,13 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C44">
-        <v>0.9991652369499207</v>
+        <v>0.9990422129631042</v>
       </c>
       <c r="D44" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3127,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3136,13 +3121,13 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -3150,13 +3135,13 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C45">
-        <v>0.9990001320838928</v>
+        <v>0.9962484240531921</v>
       </c>
       <c r="D45" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3171,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3186,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="N45">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -3194,13 +3179,13 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C46">
-        <v>0.9990422129631042</v>
+        <v>0.9956099390983582</v>
       </c>
       <c r="D46" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3215,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3227,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="M46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N46">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -3238,13 +3223,13 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C47">
-        <v>0.9962484240531921</v>
+        <v>0.9993695020675659</v>
       </c>
       <c r="D47" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3259,7 +3244,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3274,7 +3259,7 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -3282,13 +3267,13 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C48">
-        <v>0.9956099390983582</v>
+        <v>0.9990277886390686</v>
       </c>
       <c r="D48" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3303,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3318,7 +3303,7 @@
         <v>2</v>
       </c>
       <c r="N48">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -3326,13 +3311,13 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C49">
-        <v>0.9993695020675659</v>
+        <v>0.9995902180671692</v>
       </c>
       <c r="D49" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3347,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3362,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="N49">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -3370,13 +3355,13 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C50">
-        <v>0.9990277886390686</v>
+        <v>0.9994117021560669</v>
       </c>
       <c r="D50" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3391,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3403,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N50">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -3414,13 +3399,13 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C51">
-        <v>0.9995902180671692</v>
+        <v>0.9994282722473145</v>
       </c>
       <c r="D51" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3435,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3458,13 +3443,13 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C52">
-        <v>0.9994117021560669</v>
+        <v>0.999479353427887</v>
       </c>
       <c r="D52" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3479,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3494,7 +3479,7 @@
         <v>1</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -3502,13 +3487,13 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C53">
-        <v>0.9994282722473145</v>
+        <v>0.9984571933746338</v>
       </c>
       <c r="D53" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3523,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3538,7 +3523,7 @@
         <v>1</v>
       </c>
       <c r="N53">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -3546,13 +3531,13 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C54">
-        <v>0.999479353427887</v>
+        <v>0.9981318712234497</v>
       </c>
       <c r="D54" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3567,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3582,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="N54">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -3590,13 +3575,13 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C55">
-        <v>0.9984571933746338</v>
+        <v>0.999025285243988</v>
       </c>
       <c r="D55" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3611,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3623,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -3634,13 +3619,13 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C56">
-        <v>0.9981318712234497</v>
+        <v>0.933538019657135</v>
       </c>
       <c r="D56" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3655,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3667,10 +3652,10 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N56">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -3678,13 +3663,13 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C57">
-        <v>0.999025285243988</v>
+        <v>0.9989953637123108</v>
       </c>
       <c r="D57" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3699,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -3711,10 +3696,10 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N57">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -3722,13 +3707,13 @@
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C58">
-        <v>0.933538019657135</v>
+        <v>0.9986401796340942</v>
       </c>
       <c r="D58" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3743,7 +3728,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -3758,7 +3743,7 @@
         <v>3</v>
       </c>
       <c r="N58">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3766,13 +3751,13 @@
         <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C59">
-        <v>0.9989953637123108</v>
+        <v>0.9990375638008118</v>
       </c>
       <c r="D59" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3787,7 +3772,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3799,10 +3784,10 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N59">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3810,13 +3795,13 @@
         <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C60">
-        <v>0.9986401796340942</v>
+        <v>0.8789094686508179</v>
       </c>
       <c r="D60" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3831,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3846,7 +3831,7 @@
         <v>3</v>
       </c>
       <c r="N60">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3854,13 +3839,13 @@
         <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C61">
-        <v>0.9990375638008118</v>
+        <v>0.9988136887550354</v>
       </c>
       <c r="D61" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3875,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -3890,7 +3875,7 @@
         <v>1</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -3898,13 +3883,13 @@
         <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C62">
-        <v>0.8789094686508179</v>
+        <v>0.9909911155700684</v>
       </c>
       <c r="D62" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3919,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -3931,10 +3916,10 @@
         <v>0</v>
       </c>
       <c r="M62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N62">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -3942,13 +3927,13 @@
         <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C63">
-        <v>0.9988136887550354</v>
+        <v>0.9983184337615967</v>
       </c>
       <c r="D63" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3963,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -3975,10 +3960,10 @@
         <v>0</v>
       </c>
       <c r="M63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N63">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3986,13 +3971,13 @@
         <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C64">
-        <v>0.9909911155700684</v>
+        <v>0.9994446039199829</v>
       </c>
       <c r="D64" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4007,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4019,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N64">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -4030,13 +4015,13 @@
         <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C65">
-        <v>0.9983184337615967</v>
+        <v>0.9993821382522583</v>
       </c>
       <c r="D65" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4051,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4063,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="M65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -4074,13 +4059,13 @@
         <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C66">
-        <v>0.9994446039199829</v>
+        <v>0.9976016283035278</v>
       </c>
       <c r="D66" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4095,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4107,10 +4092,10 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -4118,13 +4103,13 @@
         <v>79</v>
       </c>
       <c r="B67" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C67">
-        <v>0.9993821382522583</v>
+        <v>0.9990072250366211</v>
       </c>
       <c r="D67" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4139,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4151,10 +4136,10 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -4162,13 +4147,13 @@
         <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C68">
-        <v>0.9976016283035278</v>
+        <v>0.9991657733917236</v>
       </c>
       <c r="D68" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4183,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4195,10 +4180,10 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -4206,13 +4191,13 @@
         <v>81</v>
       </c>
       <c r="B69" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C69">
-        <v>0.9990072250366211</v>
+        <v>0.997841477394104</v>
       </c>
       <c r="D69" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4227,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4239,10 +4224,10 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -4250,13 +4235,13 @@
         <v>82</v>
       </c>
       <c r="B70" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C70">
-        <v>0.9991657733917236</v>
+        <v>0.9976445436477661</v>
       </c>
       <c r="D70" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4271,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4283,10 +4268,10 @@
         <v>0</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -4294,13 +4279,13 @@
         <v>83</v>
       </c>
       <c r="B71" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C71">
-        <v>0.997841477394104</v>
+        <v>0.9980232715606689</v>
       </c>
       <c r="D71" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4315,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4338,13 +4323,13 @@
         <v>84</v>
       </c>
       <c r="B72" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C72">
-        <v>0.9976445436477661</v>
+        <v>0.9990618228912354</v>
       </c>
       <c r="D72" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4359,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4371,10 +4356,10 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N72">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -4382,13 +4367,13 @@
         <v>85</v>
       </c>
       <c r="B73" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C73">
-        <v>0.9980232715606689</v>
+        <v>0.9994759559631348</v>
       </c>
       <c r="D73" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4403,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4415,10 +4400,10 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N73">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -4426,13 +4411,13 @@
         <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C74">
-        <v>0.9990618228912354</v>
+        <v>0.9992071986198425</v>
       </c>
       <c r="D74" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4447,7 +4432,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4459,10 +4444,10 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N74">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -4470,13 +4455,13 @@
         <v>87</v>
       </c>
       <c r="B75" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C75">
-        <v>0.9994759559631348</v>
+        <v>0.9985552430152893</v>
       </c>
       <c r="D75" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4491,7 +4476,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4503,10 +4488,10 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N75">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -4514,13 +4499,13 @@
         <v>88</v>
       </c>
       <c r="B76" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C76">
-        <v>0.9992071986198425</v>
+        <v>0.9976009726524353</v>
       </c>
       <c r="D76" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4535,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4547,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="M76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N76">
         <v>3</v>
@@ -4558,13 +4543,13 @@
         <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C77">
-        <v>0.9985552430152893</v>
+        <v>0.9884098172187805</v>
       </c>
       <c r="D77" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4579,7 +4564,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4591,10 +4576,10 @@
         <v>0</v>
       </c>
       <c r="M77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -4602,13 +4587,13 @@
         <v>90</v>
       </c>
       <c r="B78" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C78">
-        <v>0.9976009726524353</v>
+        <v>0.7832491993904114</v>
       </c>
       <c r="D78" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4623,7 +4608,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4635,10 +4620,10 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N78">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -4646,13 +4631,13 @@
         <v>91</v>
       </c>
       <c r="B79" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C79">
-        <v>0.9884098172187805</v>
+        <v>0.9955025911331177</v>
       </c>
       <c r="D79" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -4667,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4690,13 +4675,13 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C80">
-        <v>0.7832491993904114</v>
+        <v>0.9995555877685547</v>
       </c>
       <c r="D80" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -4711,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4726,7 +4711,7 @@
         <v>2</v>
       </c>
       <c r="N80">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -4734,13 +4719,13 @@
         <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C81">
-        <v>0.9955025911331177</v>
+        <v>0.9975136518478394</v>
       </c>
       <c r="D81" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -4755,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4767,10 +4752,10 @@
         <v>0</v>
       </c>
       <c r="M81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N81">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -4778,13 +4763,13 @@
         <v>94</v>
       </c>
       <c r="B82" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C82">
-        <v>0.9995555877685547</v>
+        <v>0.9972119331359863</v>
       </c>
       <c r="D82" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -4799,7 +4784,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -4811,10 +4796,10 @@
         <v>0</v>
       </c>
       <c r="M82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N82">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -4822,13 +4807,13 @@
         <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C83">
-        <v>0.9975136518478394</v>
+        <v>0.9980412721633911</v>
       </c>
       <c r="D83" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4843,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -4855,10 +4840,10 @@
         <v>0</v>
       </c>
       <c r="M83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4866,13 +4851,13 @@
         <v>96</v>
       </c>
       <c r="B84" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C84">
-        <v>0.9972119331359863</v>
+        <v>0.997714638710022</v>
       </c>
       <c r="D84" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -4887,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -4899,10 +4884,10 @@
         <v>0</v>
       </c>
       <c r="M84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N84">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -4910,13 +4895,13 @@
         <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C85">
-        <v>0.9980412721633911</v>
+        <v>0.9316359758377075</v>
       </c>
       <c r="D85" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4931,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -4943,10 +4928,10 @@
         <v>0</v>
       </c>
       <c r="M85">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N85">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -4954,13 +4939,13 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C86">
-        <v>0.997714638710022</v>
+        <v>0.9981099367141724</v>
       </c>
       <c r="D86" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4975,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -4987,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="M86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -4998,13 +4983,13 @@
         <v>99</v>
       </c>
       <c r="B87" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C87">
-        <v>0.9316359758377075</v>
+        <v>0.9986376166343689</v>
       </c>
       <c r="D87" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5019,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5034,7 +5019,7 @@
         <v>1</v>
       </c>
       <c r="N87">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -5042,13 +5027,13 @@
         <v>100</v>
       </c>
       <c r="B88" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C88">
-        <v>0.9981099367141724</v>
+        <v>0.9997719526290894</v>
       </c>
       <c r="D88" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5063,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5075,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="M88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -5086,13 +5071,13 @@
         <v>101</v>
       </c>
       <c r="B89" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C89">
-        <v>0.996095597743988</v>
+        <v>0.9881560802459717</v>
       </c>
       <c r="D89" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5107,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5122,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="N89">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -5130,13 +5115,13 @@
         <v>102</v>
       </c>
       <c r="B90" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>0.9993869662284851</v>
       </c>
       <c r="D90" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5151,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5174,13 +5159,13 @@
         <v>103</v>
       </c>
       <c r="B91" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C91">
-        <v>0.9997719526290894</v>
+        <v>0.9876304268836975</v>
       </c>
       <c r="D91" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5195,7 +5180,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5207,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="M91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N91">
         <v>1</v>
@@ -5218,13 +5203,13 @@
         <v>104</v>
       </c>
       <c r="B92" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C92">
-        <v>0.9881560802459717</v>
+        <v>0.9915251135826111</v>
       </c>
       <c r="D92" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5239,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5262,13 +5247,13 @@
         <v>105</v>
       </c>
       <c r="B93" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C93">
-        <v>0.9993869662284851</v>
+        <v>0.9993435144424438</v>
       </c>
       <c r="D93" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5283,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5298,7 +5283,7 @@
         <v>1</v>
       </c>
       <c r="N93">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -5306,13 +5291,13 @@
         <v>106</v>
       </c>
       <c r="B94" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C94">
-        <v>0.9876304268836975</v>
+        <v>0.9956748485565186</v>
       </c>
       <c r="D94" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5327,22 +5312,22 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94">
         <v>0</v>
       </c>
       <c r="L94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94">
         <v>1</v>
       </c>
       <c r="N94">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -5350,13 +5335,13 @@
         <v>107</v>
       </c>
       <c r="B95" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C95">
-        <v>0.9915251135826111</v>
+        <v>0.9915837645530701</v>
       </c>
       <c r="D95" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5371,7 +5356,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5394,13 +5379,13 @@
         <v>108</v>
       </c>
       <c r="B96" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C96">
-        <v>0.9993435144424438</v>
+        <v>0.9992069602012634</v>
       </c>
       <c r="D96" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5415,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5438,13 +5423,13 @@
         <v>109</v>
       </c>
       <c r="B97" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C97">
-        <v>0.9956748485565186</v>
+        <v>0.9964823126792908</v>
       </c>
       <c r="D97" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -5459,22 +5444,22 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97">
         <v>0</v>
       </c>
       <c r="L97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M97">
         <v>1</v>
       </c>
       <c r="N97">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -5482,13 +5467,13 @@
         <v>110</v>
       </c>
       <c r="B98" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C98">
-        <v>0.9915837645530701</v>
+        <v>0.9991474747657776</v>
       </c>
       <c r="D98" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -5503,7 +5488,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -5526,13 +5511,13 @@
         <v>111</v>
       </c>
       <c r="B99" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C99">
-        <v>0.9992069602012634</v>
+        <v>0.9979246258735657</v>
       </c>
       <c r="D99" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -5547,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -5570,13 +5555,13 @@
         <v>112</v>
       </c>
       <c r="B100" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C100">
-        <v>0.9964823126792908</v>
+        <v>0.9995026588439941</v>
       </c>
       <c r="D100" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -5591,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -5606,7 +5591,7 @@
         <v>1</v>
       </c>
       <c r="N100">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -5614,13 +5599,13 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C101">
-        <v>0.9991474747657776</v>
+        <v>0.9919981956481934</v>
       </c>
       <c r="D101" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -5635,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -5658,13 +5643,13 @@
         <v>114</v>
       </c>
       <c r="B102" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C102">
-        <v>0.9979246258735657</v>
+        <v>0.8529298901557922</v>
       </c>
       <c r="D102" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -5679,10 +5664,10 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K102">
         <v>0</v>
@@ -5702,13 +5687,13 @@
         <v>115</v>
       </c>
       <c r="B103" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C103">
-        <v>0.9995026588439941</v>
+        <v>0.9926774501800537</v>
       </c>
       <c r="D103" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -5723,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -5738,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="N103">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5746,13 +5731,13 @@
         <v>116</v>
       </c>
       <c r="B104" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C104">
-        <v>0.9919981956481934</v>
+        <v>0.9982547760009766</v>
       </c>
       <c r="D104" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -5767,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -5790,13 +5775,13 @@
         <v>117</v>
       </c>
       <c r="B105" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C105">
-        <v>0.8529298901557922</v>
+        <v>0.9919293522834778</v>
       </c>
       <c r="D105" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -5811,10 +5796,10 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105">
         <v>0</v>
@@ -5834,13 +5819,13 @@
         <v>118</v>
       </c>
       <c r="B106" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C106">
-        <v>0.9926774501800537</v>
+        <v>0.9978511333465576</v>
       </c>
       <c r="D106" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -5855,22 +5840,22 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N106">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -5878,13 +5863,13 @@
         <v>119</v>
       </c>
       <c r="B107" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C107">
-        <v>0.9982547760009766</v>
+        <v>0.999393105506897</v>
       </c>
       <c r="D107" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -5899,7 +5884,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -5922,13 +5907,13 @@
         <v>120</v>
       </c>
       <c r="B108" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C108">
-        <v>0.9919293522834778</v>
+        <v>0.9981414675712585</v>
       </c>
       <c r="D108" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -5943,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -5966,13 +5951,13 @@
         <v>121</v>
       </c>
       <c r="B109" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C109">
-        <v>0.9978511333465576</v>
+        <v>0.995561420917511</v>
       </c>
       <c r="D109" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -5987,22 +5972,22 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N109">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -6010,13 +5995,13 @@
         <v>122</v>
       </c>
       <c r="B110" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C110">
-        <v>0.999393105506897</v>
+        <v>0.99856036901474</v>
       </c>
       <c r="D110" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6031,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6043,10 +6028,10 @@
         <v>0</v>
       </c>
       <c r="M110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N110">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -6054,13 +6039,13 @@
         <v>123</v>
       </c>
       <c r="B111" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C111">
-        <v>0.9981414675712585</v>
+        <v>0.9979491829872131</v>
       </c>
       <c r="D111" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6075,7 +6060,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6087,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="M111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N111">
         <v>1</v>
@@ -6098,13 +6083,13 @@
         <v>124</v>
       </c>
       <c r="B112" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C112">
-        <v>0.995561420917511</v>
+        <v>0.9989242553710938</v>
       </c>
       <c r="D112" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6119,22 +6104,22 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N112">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -6142,13 +6127,13 @@
         <v>125</v>
       </c>
       <c r="B113" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C113">
-        <v>0.99856036901474</v>
+        <v>0.9987018704414368</v>
       </c>
       <c r="D113" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6163,7 +6148,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6175,10 +6160,10 @@
         <v>0</v>
       </c>
       <c r="M113">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N113">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -6186,13 +6171,13 @@
         <v>126</v>
       </c>
       <c r="B114" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C114">
-        <v>0.9979491829872131</v>
+        <v>0.9980301260948181</v>
       </c>
       <c r="D114" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6207,7 +6192,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -6222,7 +6207,7 @@
         <v>2</v>
       </c>
       <c r="N114">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -6230,13 +6215,13 @@
         <v>127</v>
       </c>
       <c r="B115" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C115">
-        <v>0.9989242553710938</v>
+        <v>0.9988909959793091</v>
       </c>
       <c r="D115" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6251,16 +6236,16 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115">
         <v>2</v>
@@ -6274,13 +6259,13 @@
         <v>128</v>
       </c>
       <c r="B116" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C116">
-        <v>0.9987018704414368</v>
+        <v>0.9961404204368591</v>
       </c>
       <c r="D116" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6295,7 +6280,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6307,10 +6292,10 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N116">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -6318,13 +6303,13 @@
         <v>129</v>
       </c>
       <c r="B117" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C117">
-        <v>0.9980301260948181</v>
+        <v>0.9958701133728027</v>
       </c>
       <c r="D117" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6339,7 +6324,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -6354,7 +6339,7 @@
         <v>2</v>
       </c>
       <c r="N117">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -6362,13 +6347,13 @@
         <v>130</v>
       </c>
       <c r="B118" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C118">
-        <v>0.9988909959793091</v>
+        <v>0.998413622379303</v>
       </c>
       <c r="D118" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -6383,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -6395,10 +6380,10 @@
         <v>0</v>
       </c>
       <c r="M118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N118">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -6406,13 +6391,13 @@
         <v>131</v>
       </c>
       <c r="B119" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C119">
-        <v>0.9961404204368591</v>
+        <v>0.9992607235908508</v>
       </c>
       <c r="D119" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -6427,7 +6412,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6439,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="M119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N119">
         <v>3</v>
@@ -6450,13 +6435,13 @@
         <v>132</v>
       </c>
       <c r="B120" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C120">
-        <v>0.9958701133728027</v>
+        <v>0.9961749315261841</v>
       </c>
       <c r="D120" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6471,7 +6456,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6486,7 +6471,7 @@
         <v>2</v>
       </c>
       <c r="N120">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -6494,13 +6479,13 @@
         <v>133</v>
       </c>
       <c r="B121" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C121">
-        <v>0.998413622379303</v>
+        <v>0.9993590712547302</v>
       </c>
       <c r="D121" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -6515,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6527,10 +6512,10 @@
         <v>0</v>
       </c>
       <c r="M121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N121">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -6538,13 +6523,13 @@
         <v>134</v>
       </c>
       <c r="B122" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C122">
-        <v>0.9992607235908508</v>
+        <v>0.9987558722496033</v>
       </c>
       <c r="D122" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -6559,7 +6544,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -6574,7 +6559,7 @@
         <v>2</v>
       </c>
       <c r="N122">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -6582,13 +6567,13 @@
         <v>135</v>
       </c>
       <c r="B123" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C123">
-        <v>0.9961749315261841</v>
+        <v>0.9992091655731201</v>
       </c>
       <c r="D123" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -6603,7 +6588,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -6626,13 +6611,13 @@
         <v>136</v>
       </c>
       <c r="B124" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C124">
-        <v>0.9993590712547302</v>
+        <v>0.9622448682785034</v>
       </c>
       <c r="D124" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -6647,7 +6632,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -6662,7 +6647,7 @@
         <v>2</v>
       </c>
       <c r="N124">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -6670,13 +6655,13 @@
         <v>137</v>
       </c>
       <c r="B125" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C125">
-        <v>0.9987558722496033</v>
+        <v>0.9945164322853088</v>
       </c>
       <c r="D125" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -6691,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -6703,10 +6688,10 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N125">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6714,13 +6699,13 @@
         <v>138</v>
       </c>
       <c r="B126" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C126">
-        <v>0.9992091655731201</v>
+        <v>0.995938241481781</v>
       </c>
       <c r="D126" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -6735,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -6750,7 +6735,7 @@
         <v>2</v>
       </c>
       <c r="N126">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6758,13 +6743,13 @@
         <v>139</v>
       </c>
       <c r="B127" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C127">
-        <v>0.9622448682785034</v>
+        <v>0.998788058757782</v>
       </c>
       <c r="D127" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -6779,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -6791,10 +6776,10 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N127">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -6802,13 +6787,13 @@
         <v>140</v>
       </c>
       <c r="B128" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C128">
-        <v>0.9945164322853088</v>
+        <v>0.9871893525123596</v>
       </c>
       <c r="D128" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -6823,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -6835,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="M128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N128">
         <v>3</v>
@@ -6846,13 +6831,13 @@
         <v>141</v>
       </c>
       <c r="B129" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C129">
-        <v>0.995938241481781</v>
+        <v>0.9990460872650146</v>
       </c>
       <c r="D129" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -6867,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -6879,10 +6864,10 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N129">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6890,13 +6875,13 @@
         <v>142</v>
       </c>
       <c r="B130" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C130">
-        <v>0.998788058757782</v>
+        <v>0.978120744228363</v>
       </c>
       <c r="D130" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -6911,7 +6896,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -6934,13 +6919,13 @@
         <v>143</v>
       </c>
       <c r="B131" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C131">
-        <v>0.9871893525123596</v>
+        <v>0.9937021136283875</v>
       </c>
       <c r="D131" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -6955,10 +6940,10 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -6967,10 +6952,10 @@
         <v>0</v>
       </c>
       <c r="M131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N131">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6978,13 +6963,13 @@
         <v>144</v>
       </c>
       <c r="B132" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C132">
-        <v>0.9990460872650146</v>
+        <v>0.9984340667724609</v>
       </c>
       <c r="D132" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -6999,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -7011,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="M132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N132">
         <v>2</v>
@@ -7022,13 +7007,13 @@
         <v>145</v>
       </c>
       <c r="B133" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C133">
-        <v>0.978120744228363</v>
+        <v>0.9967972040176392</v>
       </c>
       <c r="D133" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7043,10 +7028,10 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -7055,7 +7040,7 @@
         <v>0</v>
       </c>
       <c r="M133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N133">
         <v>2</v>
@@ -7066,13 +7051,13 @@
         <v>146</v>
       </c>
       <c r="B134" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C134">
-        <v>0.9937021136283875</v>
+        <v>0.9973806738853455</v>
       </c>
       <c r="D134" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -7087,10 +7072,10 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134">
         <v>0</v>
@@ -7099,141 +7084,9 @@
         <v>0</v>
       </c>
       <c r="M134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N134">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="135" spans="1:14">
-      <c r="A135" t="s">
-        <v>147</v>
-      </c>
-      <c r="B135" t="s">
-        <v>282</v>
-      </c>
-      <c r="C135">
-        <v>0.9984340667724609</v>
-      </c>
-      <c r="D135" t="s">
-        <v>285</v>
-      </c>
-      <c r="E135">
-        <v>0</v>
-      </c>
-      <c r="F135" t="b">
-        <v>0</v>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135" t="s">
-        <v>286</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>2</v>
-      </c>
-      <c r="N135">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:14">
-      <c r="A136" t="s">
-        <v>148</v>
-      </c>
-      <c r="B136" t="s">
-        <v>283</v>
-      </c>
-      <c r="C136">
-        <v>0.9967972040176392</v>
-      </c>
-      <c r="D136" t="s">
-        <v>285</v>
-      </c>
-      <c r="E136">
-        <v>0</v>
-      </c>
-      <c r="F136" t="b">
-        <v>0</v>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136" t="s">
-        <v>286</v>
-      </c>
-      <c r="J136">
-        <v>1</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136">
-        <v>0</v>
-      </c>
-      <c r="N136">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:14">
-      <c r="A137" t="s">
-        <v>149</v>
-      </c>
-      <c r="B137" t="s">
-        <v>284</v>
-      </c>
-      <c r="C137">
-        <v>0.9973806738853455</v>
-      </c>
-      <c r="D137" t="s">
-        <v>285</v>
-      </c>
-      <c r="E137">
-        <v>0</v>
-      </c>
-      <c r="F137" t="b">
-        <v>0</v>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137" t="s">
-        <v>286</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137">
-        <v>2</v>
-      </c>
-      <c r="N137">
         <v>5</v>
       </c>
     </row>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="29400" windowHeight="10700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="280">
   <si>
     <t>filename</t>
   </si>
@@ -61,829 +74,1166 @@
     <t>micro_0192_YSB_II.jpg</t>
   </si>
   <si>
+    <t>YSBⅡ</t>
+  </si>
+  <si>
+    <t>color_detection</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>micro_0103_1700XL1_80_00.jpg</t>
   </si>
   <si>
+    <t>XLⅠ</t>
+  </si>
+  <si>
     <t>micro_0234_XJOO.jpg</t>
   </si>
   <si>
+    <t>XJ</t>
+  </si>
+  <si>
     <t>micro_0004_XDII.jpg</t>
   </si>
   <si>
+    <t>XDⅡ2</t>
+  </si>
+  <si>
     <t>micro_0031_1700X400.jpg</t>
   </si>
   <si>
+    <t>X40Ⅲ</t>
+  </si>
+  <si>
     <t>micro_0160_2300X408.jpg</t>
   </si>
   <si>
+    <t>X408</t>
+  </si>
+  <si>
     <t>micro_0159_1700X407.jpg</t>
   </si>
   <si>
+    <t>X407</t>
+  </si>
+  <si>
     <t>micro_0157_2300X406.jpg</t>
   </si>
   <si>
+    <t>X406</t>
+  </si>
+  <si>
     <t>micro_0156_1700X405.jpg</t>
   </si>
   <si>
+    <t>X405</t>
+  </si>
+  <si>
     <t>micro_0155_2300X404.jpg</t>
   </si>
   <si>
+    <t>X404</t>
+  </si>
+  <si>
     <t>micro_0029_2300X402.jpg</t>
   </si>
   <si>
+    <t>X402</t>
+  </si>
+  <si>
     <t>micro_0142_X401.jpg</t>
   </si>
   <si>
+    <t>X401</t>
+  </si>
+  <si>
     <t>micro_0141_X325.jpg</t>
   </si>
   <si>
+    <t>X325</t>
+  </si>
+  <si>
     <t>micro_0075_X20VI.jpg</t>
   </si>
   <si>
+    <t>X20Ⅵ</t>
+  </si>
+  <si>
     <t>micro_0140_X209.jpg</t>
   </si>
   <si>
+    <t>X209</t>
+  </si>
+  <si>
     <t>micro_0139_X208.jpg</t>
   </si>
   <si>
+    <t>X208</t>
+  </si>
+  <si>
     <t>micro_0138_X207.jpg</t>
   </si>
   <si>
+    <t>X207</t>
+  </si>
+  <si>
     <t>micro_0079_X206.jpg</t>
   </si>
   <si>
+    <t>X206</t>
+  </si>
+  <si>
     <t>micro_0135_X205.jpg</t>
   </si>
   <si>
+    <t>X205</t>
+  </si>
+  <si>
     <t>micro_0074_X203.jpg</t>
   </si>
   <si>
+    <t>X203</t>
+  </si>
+  <si>
     <t>micro_0168_1700X202.jpg</t>
   </si>
   <si>
+    <t>X202</t>
+  </si>
+  <si>
     <t>micro_0167_2300X201.jpg</t>
   </si>
   <si>
-    <t>micro_0123_XJ.jpg</t>
+    <t>X201</t>
   </si>
   <si>
     <t>micro_0109_SL40III.jpg</t>
   </si>
   <si>
+    <t>SL40Ⅲ</t>
+  </si>
+  <si>
     <t>micro_0291_SL4082600.jpg</t>
   </si>
   <si>
+    <t>SL408</t>
+  </si>
+  <si>
     <t>micro_0113_SL407.jpg</t>
   </si>
   <si>
+    <t>SL407</t>
+  </si>
+  <si>
     <t>micro_0112_SL406.jpg</t>
   </si>
   <si>
+    <t>SL406</t>
+  </si>
+  <si>
     <t>micro_0111_SL405.jpg</t>
   </si>
   <si>
+    <t>SL405</t>
+  </si>
+  <si>
     <t>micro_0110_SL404.jpg</t>
   </si>
   <si>
+    <t>SL404</t>
+  </si>
+  <si>
     <t>micro_0108_SL402.jpg</t>
   </si>
   <si>
+    <t>SL402</t>
+  </si>
+  <si>
     <t>micro_0105_SL401.jpg</t>
   </si>
   <si>
+    <t>SL401</t>
+  </si>
+  <si>
     <t>micro_0152_SL301.jpg</t>
   </si>
   <si>
+    <t>SL301</t>
+  </si>
+  <si>
     <t>micro_0185_OO_0_SL20VI.jpg</t>
   </si>
   <si>
+    <t>SL20Ⅵ</t>
+  </si>
+  <si>
     <t>micro_0273_SL203.jpg</t>
   </si>
   <si>
+    <t>SL203</t>
+  </si>
+  <si>
     <t>micro_0212_SL202.jpg</t>
   </si>
   <si>
+    <t>SL202</t>
+  </si>
+  <si>
     <t>micro_0211_SL201.jpg</t>
   </si>
   <si>
+    <t>SL201</t>
+  </si>
+  <si>
     <t>micro_0190_O_SBII.jpg</t>
   </si>
   <si>
+    <t>SBⅡ</t>
+  </si>
+  <si>
     <t>micro_0289_SBI.jpg</t>
   </si>
   <si>
+    <t>SBⅠ</t>
+  </si>
+  <si>
     <t>micro_0231_FX201.jpg</t>
   </si>
   <si>
+    <t>FX201</t>
+  </si>
+  <si>
     <t>micro_0287_FSL20VI.jpg</t>
   </si>
   <si>
+    <t>FSL20Ⅵ</t>
+  </si>
+  <si>
     <t>micro_0272_AFSL201.jpg</t>
   </si>
   <si>
+    <t>FSL201</t>
+  </si>
+  <si>
     <t>micro_0007_0D527.jpg</t>
   </si>
   <si>
+    <t>D527</t>
+  </si>
+  <si>
     <t>micro_0096_D523.jpg</t>
   </si>
   <si>
+    <t>D523</t>
+  </si>
+  <si>
     <t>micro_0095_D521.jpg</t>
   </si>
   <si>
+    <t>D521</t>
+  </si>
+  <si>
     <t>micro_0098_D519.jpg</t>
   </si>
   <si>
+    <t>D519</t>
+  </si>
+  <si>
     <t>micro_0100_D517.jpg</t>
   </si>
   <si>
+    <t>D517</t>
+  </si>
+  <si>
     <t>micro_0226_D515.jpg</t>
   </si>
   <si>
+    <t>D515</t>
+  </si>
+  <si>
     <t>micro_0218_D514.jpg</t>
   </si>
   <si>
+    <t>D514</t>
+  </si>
+  <si>
     <t>micro_0270_D513.jpg</t>
   </si>
   <si>
+    <t>D513</t>
+  </si>
+  <si>
     <t>micro_0230_D512.jpg</t>
   </si>
   <si>
+    <t>D512</t>
+  </si>
+  <si>
     <t>micro_0271_D511.jpg</t>
   </si>
   <si>
+    <t>D511</t>
+  </si>
+  <si>
     <t>micro_0010_D510.jpg</t>
   </si>
   <si>
+    <t>D510</t>
+  </si>
+  <si>
     <t>micro_0201_D509.jpg</t>
   </si>
   <si>
+    <t>D509</t>
+  </si>
+  <si>
     <t>micro_0164_D508.jpg</t>
   </si>
   <si>
+    <t>D508</t>
+  </si>
+  <si>
     <t>micro_0199_D507.jpg</t>
   </si>
   <si>
+    <t>D507</t>
+  </si>
+  <si>
     <t>micro_0220_D506.jpg</t>
   </si>
   <si>
+    <t>D506</t>
+  </si>
+  <si>
     <t>micro_0264_D505.jpg</t>
   </si>
   <si>
+    <t>D505</t>
+  </si>
+  <si>
     <t>micro_0163_D504.jpg</t>
   </si>
   <si>
+    <t>D504</t>
+  </si>
+  <si>
     <t>micro_0114_O_D503.jpg</t>
   </si>
   <si>
+    <t>D503</t>
+  </si>
+  <si>
     <t>micro_0166_D502.jpg</t>
   </si>
   <si>
+    <t>D502</t>
+  </si>
+  <si>
     <t>micro_0117_D501.jpg</t>
   </si>
   <si>
+    <t>D501</t>
+  </si>
+  <si>
     <t>micro_0034_D432.jpg</t>
   </si>
   <si>
+    <t>D432</t>
+  </si>
+  <si>
     <t>micro_0032_D430.jpg</t>
   </si>
   <si>
+    <t>D430</t>
+  </si>
+  <si>
     <t>micro_0035_D426.jpg</t>
   </si>
   <si>
+    <t>D426</t>
+  </si>
+  <si>
     <t>micro_0056_D424.jpg</t>
   </si>
   <si>
+    <t>D424</t>
+  </si>
+  <si>
     <t>micro_0049_D422.jpg</t>
   </si>
   <si>
+    <t>D422</t>
+  </si>
+  <si>
     <t>micro_0051_D420.jpg</t>
   </si>
   <si>
+    <t>D420</t>
+  </si>
+  <si>
     <t>micro_0104_D419.jpg</t>
   </si>
   <si>
+    <t>D419</t>
+  </si>
+  <si>
     <t>micro_0025_D418.jpg</t>
   </si>
   <si>
+    <t>D418</t>
+  </si>
+  <si>
     <t>micro_0275_0D417.jpg</t>
   </si>
   <si>
+    <t>D417</t>
+  </si>
+  <si>
     <t>micro_0066_D416.jpg</t>
   </si>
   <si>
+    <t>D416</t>
+  </si>
+  <si>
     <t>micro_0281_D415.jpg</t>
   </si>
   <si>
+    <t>D415</t>
+  </si>
+  <si>
     <t>micro_0064_D414.jpg</t>
   </si>
   <si>
+    <t>D414</t>
+  </si>
+  <si>
     <t>micro_0283_D413.jpg</t>
   </si>
   <si>
+    <t>D413</t>
+  </si>
+  <si>
     <t>micro_0047_D412.jpg</t>
   </si>
   <si>
+    <t>D412</t>
+  </si>
+  <si>
     <t>micro_0277_D411.jpg</t>
   </si>
   <si>
+    <t>D411</t>
+  </si>
+  <si>
     <t>micro_0057_D410.jpg</t>
   </si>
   <si>
+    <t>D410</t>
+  </si>
+  <si>
     <t>micro_0279_D409.jpg</t>
   </si>
   <si>
+    <t>D409</t>
+  </si>
+  <si>
     <t>micro_0063_D408.jpg</t>
   </si>
   <si>
+    <t>D408</t>
+  </si>
+  <si>
     <t>micro_0132_D407.jpg</t>
   </si>
   <si>
+    <t>D407</t>
+  </si>
+  <si>
     <t>micro_0263_D406.jpg</t>
   </si>
   <si>
+    <t>D406</t>
+  </si>
+  <si>
     <t>micro_0296_D405.jpg</t>
   </si>
   <si>
+    <t>D405</t>
+  </si>
+  <si>
     <t>micro_0261_D404.jpg</t>
   </si>
   <si>
+    <t>D404</t>
+  </si>
+  <si>
     <t>micro_0133_YD409_D403.jpg</t>
   </si>
   <si>
+    <t>D403</t>
+  </si>
+  <si>
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
+    <t>D402</t>
+  </si>
+  <si>
     <t>micro_0131_D401.jpg</t>
   </si>
   <si>
+    <t>D401</t>
+  </si>
+  <si>
     <t>micro_0089_D3116.jpg</t>
   </si>
   <si>
+    <t>D3116</t>
+  </si>
+  <si>
     <t>micro_0255_D250.jpg</t>
   </si>
   <si>
+    <t>D250</t>
+  </si>
+  <si>
     <t>micro_0071_D248.jpg</t>
   </si>
   <si>
+    <t>D248</t>
+  </si>
+  <si>
     <t>micro_0151_D2472600.jpg</t>
   </si>
   <si>
+    <t>D247</t>
+  </si>
+  <si>
     <t>micro_0016_D246.jpg</t>
   </si>
   <si>
+    <t>D246</t>
+  </si>
+  <si>
     <t>micro_0150_D245.jpg</t>
   </si>
   <si>
+    <t>D245</t>
+  </si>
+  <si>
     <t>micro_0073_D242.jpg</t>
   </si>
   <si>
+    <t>D242</t>
+  </si>
+  <si>
     <t>micro_0090_OD240.jpg</t>
   </si>
   <si>
+    <t>D240</t>
+  </si>
+  <si>
     <t>micro_0148_D2392000.jpg</t>
   </si>
   <si>
+    <t>D239</t>
+  </si>
+  <si>
     <t>micro_0018_D238.jpg</t>
   </si>
   <si>
+    <t>D238</t>
+  </si>
+  <si>
     <t>micro_0147_D2372600.jpg</t>
   </si>
   <si>
+    <t>D237</t>
+  </si>
+  <si>
     <t>micro_0021_2D236.jpg</t>
   </si>
   <si>
+    <t>D236</t>
+  </si>
+  <si>
     <t>micro_0043_D235.jpg</t>
   </si>
   <si>
+    <t>D235</t>
+  </si>
+  <si>
     <t>micro_0203_0D234.jpg</t>
   </si>
   <si>
+    <t>D234</t>
+  </si>
+  <si>
     <t>micro_0210_D233.jpg</t>
   </si>
   <si>
+    <t>D233</t>
+  </si>
+  <si>
     <t>micro_0249_OD232.jpg</t>
   </si>
   <si>
+    <t>D232</t>
+  </si>
+  <si>
     <t>micro_0182_D231.jpg</t>
   </si>
   <si>
+    <t>D231</t>
+  </si>
+  <si>
     <t>micro_0252_OOD230.jpg</t>
   </si>
   <si>
+    <t>D230</t>
+  </si>
+  <si>
     <t>micro_0237_D229.jpg</t>
   </si>
   <si>
+    <t>D229</t>
+  </si>
+  <si>
     <t>micro_0256_D228.jpg</t>
   </si>
   <si>
+    <t>D228</t>
+  </si>
+  <si>
     <t>micro_0042_D227.jpg</t>
   </si>
   <si>
+    <t>D227</t>
+  </si>
+  <si>
     <t>micro_0254_D226.jpg</t>
   </si>
   <si>
+    <t>D226</t>
+  </si>
+  <si>
     <t>micro_0183_D225.jpg</t>
   </si>
   <si>
+    <t>D225</t>
+  </si>
+  <si>
     <t>micro_0125_D224.jpg</t>
   </si>
   <si>
+    <t>D224</t>
+  </si>
+  <si>
     <t>micro_0235_D223.jpg</t>
   </si>
   <si>
+    <t>D223</t>
+  </si>
+  <si>
     <t>micro_0129_D222.jpg</t>
   </si>
   <si>
+    <t>D222</t>
+  </si>
+  <si>
     <t>micro_0239_D221.jpg</t>
   </si>
   <si>
+    <t>D221</t>
+  </si>
+  <si>
     <t>micro_0127_D220.jpg</t>
   </si>
   <si>
+    <t>D220</t>
+  </si>
+  <si>
     <t>micro_0170_D219.jpg</t>
   </si>
   <si>
+    <t>D219</t>
+  </si>
+  <si>
     <t>micro_0126_D218.jpg</t>
   </si>
   <si>
+    <t>D218</t>
+  </si>
+  <si>
     <t>micro_0244_D217.jpg</t>
   </si>
   <si>
+    <t>D217</t>
+  </si>
+  <si>
     <t>micro_0087_D216.jpg</t>
   </si>
   <si>
+    <t>D216</t>
+  </si>
+  <si>
     <t>micro_0175_D215.jpg</t>
   </si>
   <si>
+    <t>D215</t>
+  </si>
+  <si>
     <t>micro_0086_D214.jpg</t>
   </si>
   <si>
+    <t>D214</t>
+  </si>
+  <si>
     <t>micro_0179_D213.jpg</t>
   </si>
   <si>
+    <t>D213</t>
+  </si>
+  <si>
     <t>micro_0083_D212.jpg</t>
   </si>
   <si>
+    <t>D212</t>
+  </si>
+  <si>
     <t>micro_0246_D211.jpg</t>
   </si>
   <si>
+    <t>D211</t>
+  </si>
+  <si>
     <t>micro_0084_D210.jpg</t>
   </si>
   <si>
+    <t>D210</t>
+  </si>
+  <si>
     <t>micro_0245_D209.jpg</t>
   </si>
   <si>
+    <t>D209</t>
+  </si>
+  <si>
     <t>micro_0088_D208.jpg</t>
   </si>
   <si>
+    <t>D208</t>
+  </si>
+  <si>
     <t>micro_0241_D207.jpg</t>
   </si>
   <si>
+    <t>D207</t>
+  </si>
+  <si>
     <t>micro_0081_D206.jpg</t>
   </si>
   <si>
+    <t>D206</t>
+  </si>
+  <si>
     <t>micro_0000_DD205.jpg</t>
   </si>
   <si>
+    <t>D205</t>
+  </si>
+  <si>
     <t>micro_0193_D204.jpg</t>
   </si>
   <si>
+    <t>D204</t>
+  </si>
+  <si>
     <t>micro_0169_D203.jpg</t>
   </si>
   <si>
+    <t>D203</t>
+  </si>
+  <si>
     <t>micro_0189_D202.jpg</t>
   </si>
   <si>
+    <t>D202</t>
+  </si>
+  <si>
     <t>micro_0068_D201_QO.jpg</t>
   </si>
   <si>
-    <t>YSBⅡ</t>
-  </si>
-  <si>
-    <t>XLⅠ</t>
-  </si>
-  <si>
-    <t>XJ</t>
-  </si>
-  <si>
-    <t>XDⅡ2</t>
-  </si>
-  <si>
-    <t>X40Ⅲ</t>
-  </si>
-  <si>
-    <t>X408</t>
-  </si>
-  <si>
-    <t>X407</t>
-  </si>
-  <si>
-    <t>X406</t>
-  </si>
-  <si>
-    <t>X405</t>
-  </si>
-  <si>
-    <t>X404</t>
-  </si>
-  <si>
-    <t>X402</t>
-  </si>
-  <si>
-    <t>X401</t>
-  </si>
-  <si>
-    <t>X325</t>
-  </si>
-  <si>
-    <t>X20Ⅵ</t>
-  </si>
-  <si>
-    <t>X209</t>
-  </si>
-  <si>
-    <t>X208</t>
-  </si>
-  <si>
-    <t>X207</t>
-  </si>
-  <si>
-    <t>X206</t>
-  </si>
-  <si>
-    <t>X205</t>
-  </si>
-  <si>
-    <t>X203</t>
-  </si>
-  <si>
-    <t>X202</t>
-  </si>
-  <si>
-    <t>X201</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>SL40Ⅲ</t>
-  </si>
-  <si>
-    <t>SL408</t>
-  </si>
-  <si>
-    <t>SL407</t>
-  </si>
-  <si>
-    <t>SL406</t>
-  </si>
-  <si>
-    <t>SL405</t>
-  </si>
-  <si>
-    <t>SL404</t>
-  </si>
-  <si>
-    <t>SL402</t>
-  </si>
-  <si>
-    <t>SL401</t>
-  </si>
-  <si>
-    <t>SL301</t>
-  </si>
-  <si>
-    <t>SL20Ⅵ</t>
-  </si>
-  <si>
-    <t>SL203</t>
-  </si>
-  <si>
-    <t>SL202</t>
-  </si>
-  <si>
-    <t>SL201</t>
-  </si>
-  <si>
-    <t>SBⅡ</t>
-  </si>
-  <si>
-    <t>SBⅠ</t>
-  </si>
-  <si>
-    <t>FX201</t>
-  </si>
-  <si>
-    <t>FSL20Ⅵ</t>
-  </si>
-  <si>
-    <t>FSL201</t>
-  </si>
-  <si>
-    <t>D527</t>
-  </si>
-  <si>
-    <t>D523</t>
-  </si>
-  <si>
-    <t>D521</t>
-  </si>
-  <si>
-    <t>D519</t>
-  </si>
-  <si>
-    <t>D517</t>
-  </si>
-  <si>
-    <t>D515</t>
-  </si>
-  <si>
-    <t>D514</t>
-  </si>
-  <si>
-    <t>D513</t>
-  </si>
-  <si>
-    <t>D512</t>
-  </si>
-  <si>
-    <t>D511</t>
-  </si>
-  <si>
-    <t>D510</t>
-  </si>
-  <si>
-    <t>D509</t>
-  </si>
-  <si>
-    <t>D508</t>
-  </si>
-  <si>
-    <t>D507</t>
-  </si>
-  <si>
-    <t>D506</t>
-  </si>
-  <si>
-    <t>D505</t>
-  </si>
-  <si>
-    <t>D504</t>
-  </si>
-  <si>
-    <t>D503</t>
-  </si>
-  <si>
-    <t>D502</t>
-  </si>
-  <si>
-    <t>D501</t>
-  </si>
-  <si>
-    <t>D432</t>
-  </si>
-  <si>
-    <t>D430</t>
-  </si>
-  <si>
-    <t>D426</t>
-  </si>
-  <si>
-    <t>D424</t>
-  </si>
-  <si>
-    <t>D422</t>
-  </si>
-  <si>
-    <t>D420</t>
-  </si>
-  <si>
-    <t>D419</t>
-  </si>
-  <si>
-    <t>D418</t>
-  </si>
-  <si>
-    <t>D417</t>
-  </si>
-  <si>
-    <t>D416</t>
-  </si>
-  <si>
-    <t>D415</t>
-  </si>
-  <si>
-    <t>D414</t>
-  </si>
-  <si>
-    <t>D413</t>
-  </si>
-  <si>
-    <t>D412</t>
-  </si>
-  <si>
-    <t>D411</t>
-  </si>
-  <si>
-    <t>D410</t>
-  </si>
-  <si>
-    <t>D409</t>
-  </si>
-  <si>
-    <t>D408</t>
-  </si>
-  <si>
-    <t>D407</t>
-  </si>
-  <si>
-    <t>D406</t>
-  </si>
-  <si>
-    <t>D405</t>
-  </si>
-  <si>
-    <t>D404</t>
-  </si>
-  <si>
-    <t>D403</t>
-  </si>
-  <si>
-    <t>D402</t>
-  </si>
-  <si>
-    <t>D401</t>
-  </si>
-  <si>
-    <t>D3116</t>
-  </si>
-  <si>
-    <t>D250</t>
-  </si>
-  <si>
-    <t>D248</t>
-  </si>
-  <si>
-    <t>D247</t>
-  </si>
-  <si>
-    <t>D246</t>
-  </si>
-  <si>
-    <t>D245</t>
-  </si>
-  <si>
-    <t>D242</t>
-  </si>
-  <si>
-    <t>D240</t>
-  </si>
-  <si>
-    <t>D239</t>
-  </si>
-  <si>
-    <t>D238</t>
-  </si>
-  <si>
-    <t>D237</t>
-  </si>
-  <si>
-    <t>D236</t>
-  </si>
-  <si>
-    <t>D235</t>
-  </si>
-  <si>
-    <t>D234</t>
-  </si>
-  <si>
-    <t>D233</t>
-  </si>
-  <si>
-    <t>D232</t>
-  </si>
-  <si>
-    <t>D231</t>
-  </si>
-  <si>
-    <t>D230</t>
-  </si>
-  <si>
-    <t>D229</t>
-  </si>
-  <si>
-    <t>D228</t>
-  </si>
-  <si>
-    <t>D227</t>
-  </si>
-  <si>
-    <t>D226</t>
-  </si>
-  <si>
-    <t>D225</t>
-  </si>
-  <si>
-    <t>D224</t>
-  </si>
-  <si>
-    <t>D223</t>
-  </si>
-  <si>
-    <t>D222</t>
-  </si>
-  <si>
-    <t>D221</t>
-  </si>
-  <si>
-    <t>D220</t>
-  </si>
-  <si>
-    <t>D219</t>
-  </si>
-  <si>
-    <t>D218</t>
-  </si>
-  <si>
-    <t>D217</t>
-  </si>
-  <si>
-    <t>D216</t>
-  </si>
-  <si>
-    <t>D215</t>
-  </si>
-  <si>
-    <t>D214</t>
-  </si>
-  <si>
-    <t>D213</t>
-  </si>
-  <si>
-    <t>D212</t>
-  </si>
-  <si>
-    <t>D211</t>
-  </si>
-  <si>
-    <t>D210</t>
-  </si>
-  <si>
-    <t>D209</t>
-  </si>
-  <si>
-    <t>D208</t>
-  </si>
-  <si>
-    <t>D207</t>
-  </si>
-  <si>
-    <t>D206</t>
-  </si>
-  <si>
-    <t>D205</t>
-  </si>
-  <si>
-    <t>D204</t>
-  </si>
-  <si>
-    <t>D203</t>
-  </si>
-  <si>
-    <t>D202</t>
-  </si>
-  <si>
     <t>D201</t>
-  </si>
-  <si>
-    <t>color_detection</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -891,18 +1241,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1185,14 +1829,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N134"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N133"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="3" max="3" width="12.9230769230769"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
@@ -1243,13 +1890,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>0.922767162322998</v>
       </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1264,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1284,16 +1931,16 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>0.9794343709945679</v>
+        <v>0.979434370994568</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1308,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1328,16 +1975,16 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>0.9089775085449219</v>
+        <v>0.908977508544922</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1352,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1372,16 +2019,16 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>0.7567664980888367</v>
+        <v>0.756766498088837</v>
       </c>
       <c r="D5" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1396,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1416,16 +2063,16 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>0.9360489845275879</v>
+        <v>0.936048984527588</v>
       </c>
       <c r="D6" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1440,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1460,16 +2107,16 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>27</v>
       </c>
       <c r="C7">
-        <v>0.9898043870925903</v>
+        <v>0.98980438709259</v>
       </c>
       <c r="D7" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1484,7 +2131,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1504,16 +2151,16 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="C8">
-        <v>0.9800205826759338</v>
+        <v>0.980020582675934</v>
       </c>
       <c r="D8" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1528,7 +2175,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1548,16 +2195,16 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>0.9866096377372742</v>
+        <v>0.986609637737274</v>
       </c>
       <c r="D9" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1572,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1592,16 +2239,16 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="C10">
-        <v>0.9825887680053711</v>
+        <v>0.982588768005371</v>
       </c>
       <c r="D10" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1616,7 +2263,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1636,16 +2283,16 @@
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="C11">
-        <v>0.9854358434677124</v>
+        <v>0.985435843467712</v>
       </c>
       <c r="D11" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1660,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1680,16 +2327,16 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>157</v>
+        <v>37</v>
       </c>
       <c r="C12">
-        <v>0.9869511127471924</v>
+        <v>0.986951112747192</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1704,7 +2351,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1724,16 +2371,16 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>39</v>
       </c>
       <c r="C13">
-        <v>0.9883586168289185</v>
+        <v>0.988358616828918</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1748,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1768,16 +2415,16 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>41</v>
       </c>
       <c r="C14">
-        <v>0.9827210903167725</v>
+        <v>0.982721090316772</v>
       </c>
       <c r="D14" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1792,7 +2439,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1812,16 +2459,16 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>43</v>
       </c>
       <c r="C15">
-        <v>0.9891344904899597</v>
+        <v>0.98913449048996</v>
       </c>
       <c r="D15" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1836,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1856,16 +2503,16 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="C16">
-        <v>0.9849019646644592</v>
+        <v>0.984901964664459</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1880,7 +2527,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1900,16 +2547,16 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>47</v>
       </c>
       <c r="C17">
-        <v>0.9831116795539856</v>
+        <v>0.983111679553986</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1924,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1944,16 +2591,16 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="C18">
         <v>0.979184627532959</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1968,7 +2615,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1988,16 +2635,16 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="C19">
-        <v>0.9820773601531982</v>
+        <v>0.982077360153198</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2012,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2032,16 +2679,16 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>53</v>
       </c>
       <c r="C20">
-        <v>0.9926210641860962</v>
+        <v>0.992621064186096</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2056,7 +2703,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2076,16 +2723,16 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>55</v>
       </c>
       <c r="C21">
         <v>0.991193413734436</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2100,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2120,16 +2767,16 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="C22">
-        <v>0.9759405851364136</v>
+        <v>0.975940585136414</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2144,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2164,16 +2811,16 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>168</v>
+        <v>59</v>
       </c>
       <c r="C23">
-        <v>0.9936316609382629</v>
+        <v>0.993631660938263</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2188,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2208,16 +2855,16 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C24">
-        <v>0.7151024341583252</v>
+        <v>0.983439445495605</v>
       </c>
       <c r="D24" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2232,36 +2879,36 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="C25">
-        <v>0.9834394454956055</v>
+        <v>0.993823945522308</v>
       </c>
       <c r="D25" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2276,36 +2923,36 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>171</v>
+        <v>65</v>
       </c>
       <c r="C26">
-        <v>0.9938239455223083</v>
+        <v>0.997099578380585</v>
       </c>
       <c r="D26" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2320,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2335,21 +2982,21 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>67</v>
       </c>
       <c r="C27">
-        <v>0.9970995783805847</v>
+        <v>0.997689545154572</v>
       </c>
       <c r="D27" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2364,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2379,21 +3026,21 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>69</v>
       </c>
       <c r="C28">
-        <v>0.9976895451545715</v>
+        <v>0.995999217033386</v>
       </c>
       <c r="D28" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2408,7 +3055,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2423,21 +3070,21 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>71</v>
       </c>
       <c r="C29">
-        <v>0.9959992170333862</v>
+        <v>0.99710738658905</v>
       </c>
       <c r="D29" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2452,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2467,21 +3114,21 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="C30">
-        <v>0.9971073865890503</v>
+        <v>0.996883392333984</v>
       </c>
       <c r="D30" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2496,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2511,21 +3158,21 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="C31">
-        <v>0.9968833923339844</v>
+        <v>0.9585862159729</v>
       </c>
       <c r="D31" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2540,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2560,16 +3207,16 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="C32">
-        <v>0.9585862159729004</v>
+        <v>0.99848335981369</v>
       </c>
       <c r="D32" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2584,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2604,16 +3251,16 @@
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>79</v>
       </c>
       <c r="C33">
-        <v>0.9984833598136902</v>
+        <v>0.996042430400848</v>
       </c>
       <c r="D33" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2628,36 +3275,36 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33">
         <v>1</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N33">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>81</v>
       </c>
       <c r="C34">
-        <v>0.9960424304008484</v>
+        <v>0.998810112476349</v>
       </c>
       <c r="D34" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2672,36 +3319,36 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J34">
         <v>1</v>
       </c>
       <c r="K34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34">
         <v>1</v>
       </c>
       <c r="M34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N34">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="C35">
-        <v>0.9988101124763489</v>
+        <v>0.97547721862793</v>
       </c>
       <c r="D35" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2716,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2736,16 +3383,16 @@
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="C36">
-        <v>0.9754772186279297</v>
+        <v>0.967378795146942</v>
       </c>
       <c r="D36" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2760,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2780,16 +3427,16 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>87</v>
       </c>
       <c r="C37">
-        <v>0.9673787951469421</v>
+        <v>0.767745614051819</v>
       </c>
       <c r="D37" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2804,13 +3451,13 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J37">
         <v>1</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37">
         <v>1</v>
@@ -2819,21 +3466,21 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>183</v>
+        <v>89</v>
       </c>
       <c r="C38">
-        <v>0.7677456140518188</v>
+        <v>0.894055366516113</v>
       </c>
       <c r="D38" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2848,7 +3495,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2863,21 +3510,21 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s">
-        <v>184</v>
+        <v>91</v>
       </c>
       <c r="C39">
-        <v>0.8940553665161133</v>
+        <v>0.99658191204071</v>
       </c>
       <c r="D39" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2892,13 +3539,13 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39">
         <v>1</v>
@@ -2907,21 +3554,21 @@
         <v>0</v>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>93</v>
       </c>
       <c r="C40">
-        <v>0.9965819120407104</v>
+        <v>0.998970866203308</v>
       </c>
       <c r="D40" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2936,7 +3583,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2951,21 +3598,21 @@
         <v>0</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="B41" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="C41">
-        <v>0.9989708662033081</v>
+        <v>0.999165236949921</v>
       </c>
       <c r="D41" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2980,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -3000,16 +3647,16 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>187</v>
+        <v>97</v>
       </c>
       <c r="C42">
-        <v>0.9991652369499207</v>
+        <v>0.999000132083893</v>
       </c>
       <c r="D42" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3024,7 +3671,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3033,27 +3680,27 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="C43">
-        <v>0.9990001320838928</v>
+        <v>0.999042212963104</v>
       </c>
       <c r="D43" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3068,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3080,24 +3727,24 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N43">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>101</v>
       </c>
       <c r="C44">
-        <v>0.9990422129631042</v>
+        <v>0.996248424053192</v>
       </c>
       <c r="D44" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3112,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3124,24 +3771,24 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N44">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="B45" t="s">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="C45">
-        <v>0.9962484240531921</v>
+        <v>0.995609939098358</v>
       </c>
       <c r="D45" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3156,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3168,24 +3815,24 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N45">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>191</v>
+        <v>105</v>
       </c>
       <c r="C46">
-        <v>0.9956099390983582</v>
+        <v>0.999369502067566</v>
       </c>
       <c r="D46" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3200,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3212,24 +3859,24 @@
         <v>0</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N46">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="C47">
-        <v>0.9993695020675659</v>
+        <v>0.999027788639069</v>
       </c>
       <c r="D47" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3244,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3256,24 +3903,24 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N47">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="B48" t="s">
-        <v>193</v>
+        <v>109</v>
       </c>
       <c r="C48">
-        <v>0.9990277886390686</v>
+        <v>0.999590218067169</v>
       </c>
       <c r="D48" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3288,7 +3935,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3300,24 +3947,24 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N48">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="C49">
-        <v>0.9995902180671692</v>
+        <v>0.999411702156067</v>
       </c>
       <c r="D49" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3332,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3347,21 +3994,21 @@
         <v>1</v>
       </c>
       <c r="N49">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>113</v>
       </c>
       <c r="C50">
-        <v>0.9994117021560669</v>
+        <v>0.999428272247314</v>
       </c>
       <c r="D50" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3376,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3391,21 +4038,21 @@
         <v>1</v>
       </c>
       <c r="N50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>196</v>
+        <v>115</v>
       </c>
       <c r="C51">
-        <v>0.9994282722473145</v>
+        <v>0.999479353427887</v>
       </c>
       <c r="D51" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3420,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3440,16 +4087,16 @@
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>197</v>
+        <v>117</v>
       </c>
       <c r="C52">
-        <v>0.999479353427887</v>
+        <v>0.998457193374634</v>
       </c>
       <c r="D52" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3464,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3479,21 +4126,21 @@
         <v>1</v>
       </c>
       <c r="N52">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>198</v>
+        <v>119</v>
       </c>
       <c r="C53">
-        <v>0.9984571933746338</v>
+        <v>0.99813187122345</v>
       </c>
       <c r="D53" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3508,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3523,21 +4170,21 @@
         <v>1</v>
       </c>
       <c r="N53">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>199</v>
+        <v>121</v>
       </c>
       <c r="C54">
-        <v>0.9981318712234497</v>
+        <v>0.999025285243988</v>
       </c>
       <c r="D54" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3552,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3564,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="M54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N54">
         <v>6</v>
@@ -3572,16 +4219,16 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>200</v>
+        <v>123</v>
       </c>
       <c r="C55">
-        <v>0.999025285243988</v>
+        <v>0.933538019657135</v>
       </c>
       <c r="D55" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3596,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3608,24 +4255,24 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N55">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="B56" t="s">
-        <v>201</v>
+        <v>125</v>
       </c>
       <c r="C56">
-        <v>0.933538019657135</v>
+        <v>0.998995363712311</v>
       </c>
       <c r="D56" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3640,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3655,21 +4302,21 @@
         <v>3</v>
       </c>
       <c r="N56">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="B57" t="s">
-        <v>202</v>
+        <v>127</v>
       </c>
       <c r="C57">
-        <v>0.9989953637123108</v>
+        <v>0.998640179634094</v>
       </c>
       <c r="D57" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3684,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -3704,16 +4351,16 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="C58">
-        <v>0.9986401796340942</v>
+        <v>0.999037563800812</v>
       </c>
       <c r="D58" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3728,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -3740,24 +4387,24 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N58">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s">
-        <v>204</v>
+        <v>131</v>
       </c>
       <c r="C59">
-        <v>0.9990375638008118</v>
+        <v>0.878909468650818</v>
       </c>
       <c r="D59" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3772,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3784,24 +4431,24 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>205</v>
+        <v>133</v>
       </c>
       <c r="C60">
-        <v>0.8789094686508179</v>
+        <v>0.998813688755035</v>
       </c>
       <c r="D60" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3816,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3828,24 +4475,24 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N60">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>206</v>
+        <v>135</v>
       </c>
       <c r="C61">
-        <v>0.9988136887550354</v>
+        <v>0.990991115570068</v>
       </c>
       <c r="D61" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3860,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -3875,21 +4522,21 @@
         <v>1</v>
       </c>
       <c r="N61">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="B62" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
       <c r="C62">
-        <v>0.9909911155700684</v>
+        <v>0.998318433761597</v>
       </c>
       <c r="D62" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3904,7 +4551,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -3916,24 +4563,24 @@
         <v>0</v>
       </c>
       <c r="M62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N62">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>208</v>
+        <v>139</v>
       </c>
       <c r="C63">
-        <v>0.9983184337615967</v>
+        <v>0.999444603919983</v>
       </c>
       <c r="D63" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3948,7 +4595,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -3968,16 +4615,16 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
-        <v>209</v>
+        <v>141</v>
       </c>
       <c r="C64">
-        <v>0.9994446039199829</v>
+        <v>0.999382138252258</v>
       </c>
       <c r="D64" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3992,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4004,24 +4651,24 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="C65">
-        <v>0.9993821382522583</v>
+        <v>0.997601628303528</v>
       </c>
       <c r="D65" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4036,7 +4683,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4056,16 +4703,16 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>211</v>
+        <v>145</v>
       </c>
       <c r="C66">
-        <v>0.9976016283035278</v>
+        <v>0.999007225036621</v>
       </c>
       <c r="D66" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4080,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4092,24 +4739,24 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="B67" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
       <c r="C67">
-        <v>0.9990072250366211</v>
+        <v>0.999165773391724</v>
       </c>
       <c r="D67" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4124,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4136,24 +4783,24 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N67">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="B68" t="s">
-        <v>213</v>
+        <v>149</v>
       </c>
       <c r="C68">
-        <v>0.9991657733917236</v>
+        <v>0.997841477394104</v>
       </c>
       <c r="D68" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4168,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4180,24 +4827,24 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N68">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="B69" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="C69">
-        <v>0.997841477394104</v>
+        <v>0.997644543647766</v>
       </c>
       <c r="D69" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4212,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4224,24 +4871,24 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="B70" t="s">
-        <v>215</v>
+        <v>153</v>
       </c>
       <c r="C70">
-        <v>0.9976445436477661</v>
+        <v>0.998023271560669</v>
       </c>
       <c r="D70" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4256,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4268,24 +4915,24 @@
         <v>0</v>
       </c>
       <c r="M70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="B71" t="s">
-        <v>216</v>
+        <v>155</v>
       </c>
       <c r="C71">
-        <v>0.9980232715606689</v>
+        <v>0.999061822891235</v>
       </c>
       <c r="D71" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4300,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4320,16 +4967,16 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="B72" t="s">
-        <v>217</v>
+        <v>157</v>
       </c>
       <c r="C72">
-        <v>0.9990618228912354</v>
+        <v>0.999475955963135</v>
       </c>
       <c r="D72" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4344,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4356,24 +5003,24 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N72">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="B73" t="s">
-        <v>218</v>
+        <v>159</v>
       </c>
       <c r="C73">
-        <v>0.9994759559631348</v>
+        <v>0.999207198619843</v>
       </c>
       <c r="D73" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4388,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4400,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N73">
         <v>3</v>
@@ -4408,16 +5055,16 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="B74" t="s">
-        <v>219</v>
+        <v>161</v>
       </c>
       <c r="C74">
-        <v>0.9992071986198425</v>
+        <v>0.998555243015289</v>
       </c>
       <c r="D74" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4432,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4447,21 +5094,21 @@
         <v>2</v>
       </c>
       <c r="N74">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="B75" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="C75">
-        <v>0.9985552430152893</v>
+        <v>0.997600972652435</v>
       </c>
       <c r="D75" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4476,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4488,24 +5135,24 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="B76" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C76">
-        <v>0.9976009726524353</v>
+        <v>0.988409817218781</v>
       </c>
       <c r="D76" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4520,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4535,21 +5182,21 @@
         <v>3</v>
       </c>
       <c r="N76">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="B77" t="s">
-        <v>222</v>
+        <v>167</v>
       </c>
       <c r="C77">
-        <v>0.9884098172187805</v>
+        <v>0.783249199390411</v>
       </c>
       <c r="D77" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4564,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4576,24 +5223,24 @@
         <v>0</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N77">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" t="s">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="C78">
-        <v>0.7832491993904114</v>
+        <v>0.995502591133118</v>
       </c>
       <c r="D78" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4608,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4620,24 +5267,24 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N78">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" t="s">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="B79" t="s">
-        <v>224</v>
+        <v>171</v>
       </c>
       <c r="C79">
-        <v>0.9955025911331177</v>
+        <v>0.999555587768555</v>
       </c>
       <c r="D79" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -4652,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4664,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="M79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N79">
         <v>4</v>
@@ -4672,16 +5319,16 @@
     </row>
     <row r="80" spans="1:14">
       <c r="A80" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="B80" t="s">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="C80">
-        <v>0.9995555877685547</v>
+        <v>0.997513651847839</v>
       </c>
       <c r="D80" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -4696,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4708,24 +5355,24 @@
         <v>0</v>
       </c>
       <c r="M80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N80">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" t="s">
-        <v>93</v>
+        <v>174</v>
       </c>
       <c r="B81" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="C81">
-        <v>0.9975136518478394</v>
+        <v>0.997211933135986</v>
       </c>
       <c r="D81" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -4740,7 +5387,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4755,21 +5402,21 @@
         <v>1</v>
       </c>
       <c r="N81">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="B82" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="C82">
-        <v>0.9972119331359863</v>
+        <v>0.998041272163391</v>
       </c>
       <c r="D82" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -4784,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -4796,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="M82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N82">
         <v>3</v>
@@ -4804,16 +5451,16 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="B83" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="C83">
-        <v>0.9980412721633911</v>
+        <v>0.997714638710022</v>
       </c>
       <c r="D83" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4828,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -4840,24 +5487,24 @@
         <v>0</v>
       </c>
       <c r="M83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N83">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="B84" t="s">
-        <v>229</v>
+        <v>181</v>
       </c>
       <c r="C84">
-        <v>0.997714638710022</v>
+        <v>0.931635975837708</v>
       </c>
       <c r="D84" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -4872,7 +5519,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -4884,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="M84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N84">
         <v>1</v>
@@ -4892,16 +5539,16 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" t="s">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="C85">
-        <v>0.9316359758377075</v>
+        <v>0.998109936714172</v>
       </c>
       <c r="D85" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4916,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -4936,16 +5583,16 @@
     </row>
     <row r="86" spans="1:14">
       <c r="A86" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
-        <v>231</v>
+        <v>185</v>
       </c>
       <c r="C86">
-        <v>0.9981099367141724</v>
+        <v>0.998637616634369</v>
       </c>
       <c r="D86" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4960,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -4975,21 +5622,21 @@
         <v>1</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="C87">
-        <v>0.9986376166343689</v>
+        <v>0.999771952629089</v>
       </c>
       <c r="D87" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5004,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5016,24 +5663,24 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" t="s">
-        <v>100</v>
+        <v>188</v>
       </c>
       <c r="B88" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
       <c r="C88">
-        <v>0.9997719526290894</v>
+        <v>0.988156080245972</v>
       </c>
       <c r="D88" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5048,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5060,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="M88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -5068,16 +5715,16 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>234</v>
+        <v>191</v>
       </c>
       <c r="C89">
-        <v>0.9881560802459717</v>
+        <v>0.999386966228485</v>
       </c>
       <c r="D89" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5092,7 +5739,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5107,21 +5754,21 @@
         <v>1</v>
       </c>
       <c r="N89">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" t="s">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="B90" t="s">
-        <v>235</v>
+        <v>193</v>
       </c>
       <c r="C90">
-        <v>0.9993869662284851</v>
+        <v>0.987630426883698</v>
       </c>
       <c r="D90" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5136,7 +5783,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5151,21 +5798,21 @@
         <v>1</v>
       </c>
       <c r="N90">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" t="s">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="B91" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="C91">
-        <v>0.9876304268836975</v>
+        <v>0.991525113582611</v>
       </c>
       <c r="D91" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5180,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5200,16 +5847,16 @@
     </row>
     <row r="92" spans="1:14">
       <c r="A92" t="s">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="B92" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C92">
-        <v>0.9915251135826111</v>
+        <v>0.999343514442444</v>
       </c>
       <c r="D92" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5224,7 +5871,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5244,16 +5891,16 @@
     </row>
     <row r="93" spans="1:14">
       <c r="A93" t="s">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="B93" t="s">
-        <v>238</v>
+        <v>199</v>
       </c>
       <c r="C93">
-        <v>0.9993435144424438</v>
+        <v>0.995674848556519</v>
       </c>
       <c r="D93" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5268,36 +5915,36 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K93">
         <v>0</v>
       </c>
       <c r="L93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M93">
         <v>1</v>
       </c>
       <c r="N93">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" t="s">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="B94" t="s">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="C94">
-        <v>0.9956748485565186</v>
+        <v>0.99158376455307</v>
       </c>
       <c r="D94" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5312,36 +5959,36 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94">
         <v>0</v>
       </c>
       <c r="L94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94">
         <v>1</v>
       </c>
       <c r="N94">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" t="s">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="B95" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="C95">
-        <v>0.9915837645530701</v>
+        <v>0.999206960201263</v>
       </c>
       <c r="D95" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5356,7 +6003,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5376,16 +6023,16 @@
     </row>
     <row r="96" spans="1:14">
       <c r="A96" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="B96" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="C96">
-        <v>0.9992069602012634</v>
+        <v>0.996482312679291</v>
       </c>
       <c r="D96" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5400,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5420,16 +6067,16 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" t="s">
-        <v>109</v>
+        <v>206</v>
       </c>
       <c r="B97" t="s">
-        <v>242</v>
+        <v>207</v>
       </c>
       <c r="C97">
-        <v>0.9964823126792908</v>
+        <v>0.999147474765778</v>
       </c>
       <c r="D97" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -5444,7 +6091,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -5464,16 +6111,16 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="B98" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="C98">
-        <v>0.9991474747657776</v>
+        <v>0.997924625873566</v>
       </c>
       <c r="D98" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -5488,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -5508,16 +6155,16 @@
     </row>
     <row r="99" spans="1:14">
       <c r="A99" t="s">
-        <v>111</v>
+        <v>210</v>
       </c>
       <c r="B99" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="C99">
-        <v>0.9979246258735657</v>
+        <v>0.999502658843994</v>
       </c>
       <c r="D99" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -5532,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -5547,21 +6194,21 @@
         <v>1</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" t="s">
-        <v>112</v>
+        <v>212</v>
       </c>
       <c r="B100" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="C100">
-        <v>0.9995026588439941</v>
+        <v>0.991998195648193</v>
       </c>
       <c r="D100" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -5576,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -5591,21 +6238,21 @@
         <v>1</v>
       </c>
       <c r="N100">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="C101">
-        <v>0.9919981956481934</v>
+        <v>0.852929890155792</v>
       </c>
       <c r="D101" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -5620,10 +6267,10 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101">
         <v>0</v>
@@ -5640,16 +6287,16 @@
     </row>
     <row r="102" spans="1:14">
       <c r="A102" t="s">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="B102" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="C102">
-        <v>0.8529298901557922</v>
+        <v>0.992677450180054</v>
       </c>
       <c r="D102" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -5664,10 +6311,10 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K102">
         <v>0</v>
@@ -5684,16 +6331,16 @@
     </row>
     <row r="103" spans="1:14">
       <c r="A103" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="C103">
-        <v>0.9926774501800537</v>
+        <v>0.998254776000977</v>
       </c>
       <c r="D103" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -5708,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -5728,16 +6375,16 @@
     </row>
     <row r="104" spans="1:14">
       <c r="A104" t="s">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="B104" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="C104">
-        <v>0.9982547760009766</v>
+        <v>0.991929352283478</v>
       </c>
       <c r="D104" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -5752,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -5772,16 +6419,16 @@
     </row>
     <row r="105" spans="1:14">
       <c r="A105" t="s">
-        <v>117</v>
+        <v>222</v>
       </c>
       <c r="B105" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="C105">
-        <v>0.9919293522834778</v>
+        <v>0.997851133346558</v>
       </c>
       <c r="D105" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -5796,36 +6443,36 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N105">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="B106" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="C106">
-        <v>0.9978511333465576</v>
+        <v>0.999393105506897</v>
       </c>
       <c r="D106" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -5840,36 +6487,36 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N106">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:14">
       <c r="A107" t="s">
-        <v>119</v>
+        <v>226</v>
       </c>
       <c r="B107" t="s">
-        <v>252</v>
+        <v>227</v>
       </c>
       <c r="C107">
-        <v>0.999393105506897</v>
+        <v>0.998141467571259</v>
       </c>
       <c r="D107" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -5884,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -5904,16 +6551,16 @@
     </row>
     <row r="108" spans="1:14">
       <c r="A108" t="s">
-        <v>120</v>
+        <v>228</v>
       </c>
       <c r="B108" t="s">
-        <v>253</v>
+        <v>229</v>
       </c>
       <c r="C108">
-        <v>0.9981414675712585</v>
+        <v>0.995561420917511</v>
       </c>
       <c r="D108" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -5928,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -5948,16 +6595,16 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" t="s">
-        <v>121</v>
+        <v>230</v>
       </c>
       <c r="B109" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="C109">
-        <v>0.995561420917511</v>
+        <v>0.99856036901474</v>
       </c>
       <c r="D109" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -5972,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -5984,24 +6631,24 @@
         <v>0</v>
       </c>
       <c r="M109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N109">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" t="s">
-        <v>122</v>
+        <v>232</v>
       </c>
       <c r="B110" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="C110">
-        <v>0.99856036901474</v>
+        <v>0.997949182987213</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6016,7 +6663,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6031,21 +6678,21 @@
         <v>2</v>
       </c>
       <c r="N110">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" t="s">
-        <v>123</v>
+        <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="C111">
-        <v>0.9979491829872131</v>
+        <v>0.998924255371094</v>
       </c>
       <c r="D111" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6060,36 +6707,36 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111">
         <v>2</v>
       </c>
       <c r="N111">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" t="s">
-        <v>124</v>
+        <v>236</v>
       </c>
       <c r="B112" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="C112">
-        <v>0.9989242553710938</v>
+        <v>0.998701870441437</v>
       </c>
       <c r="D112" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6104,36 +6751,36 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N112">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" t="s">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="B113" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="C113">
-        <v>0.9987018704414368</v>
+        <v>0.998030126094818</v>
       </c>
       <c r="D113" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6148,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6160,24 +6807,24 @@
         <v>0</v>
       </c>
       <c r="M113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N113">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" t="s">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="B114" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C114">
-        <v>0.9980301260948181</v>
+        <v>0.998890995979309</v>
       </c>
       <c r="D114" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6192,7 +6839,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -6207,21 +6854,21 @@
         <v>2</v>
       </c>
       <c r="N114">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" t="s">
-        <v>127</v>
+        <v>242</v>
       </c>
       <c r="B115" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C115">
-        <v>0.9988909959793091</v>
+        <v>0.996140420436859</v>
       </c>
       <c r="D115" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6236,7 +6883,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6248,7 +6895,7 @@
         <v>0</v>
       </c>
       <c r="M115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N115">
         <v>3</v>
@@ -6256,16 +6903,16 @@
     </row>
     <row r="116" spans="1:14">
       <c r="A116" t="s">
-        <v>128</v>
+        <v>244</v>
       </c>
       <c r="B116" t="s">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="C116">
-        <v>0.9961404204368591</v>
+        <v>0.995870113372803</v>
       </c>
       <c r="D116" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6280,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6292,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N116">
         <v>3</v>
@@ -6300,16 +6947,16 @@
     </row>
     <row r="117" spans="1:14">
       <c r="A117" t="s">
-        <v>129</v>
+        <v>246</v>
       </c>
       <c r="B117" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="C117">
-        <v>0.9958701133728027</v>
+        <v>0.998413622379303</v>
       </c>
       <c r="D117" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6324,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -6336,24 +6983,24 @@
         <v>0</v>
       </c>
       <c r="M117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N117">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" t="s">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="B118" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="C118">
-        <v>0.998413622379303</v>
+        <v>0.999260723590851</v>
       </c>
       <c r="D118" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -6368,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -6380,24 +7027,24 @@
         <v>0</v>
       </c>
       <c r="M118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N118">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" t="s">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="B119" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="C119">
-        <v>0.9992607235908508</v>
+        <v>0.996174931526184</v>
       </c>
       <c r="D119" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -6412,7 +7059,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6427,21 +7074,21 @@
         <v>2</v>
       </c>
       <c r="N119">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="B120" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="C120">
-        <v>0.9961749315261841</v>
+        <v>0.99935907125473</v>
       </c>
       <c r="D120" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6456,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6471,21 +7118,21 @@
         <v>2</v>
       </c>
       <c r="N120">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" t="s">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="B121" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="C121">
-        <v>0.9993590712547302</v>
+        <v>0.998755872249603</v>
       </c>
       <c r="D121" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -6500,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6515,21 +7162,21 @@
         <v>2</v>
       </c>
       <c r="N121">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="B122" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C122">
-        <v>0.9987558722496033</v>
+        <v>0.99920916557312</v>
       </c>
       <c r="D122" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -6544,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -6564,16 +7211,16 @@
     </row>
     <row r="123" spans="1:14">
       <c r="A123" t="s">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="B123" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C123">
-        <v>0.9992091655731201</v>
+        <v>0.962244868278503</v>
       </c>
       <c r="D123" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -6588,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -6603,21 +7250,21 @@
         <v>2</v>
       </c>
       <c r="N123">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" t="s">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="B124" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C124">
-        <v>0.9622448682785034</v>
+        <v>0.994516432285309</v>
       </c>
       <c r="D124" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -6632,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -6644,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="M124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N124">
         <v>3</v>
@@ -6652,16 +7299,16 @@
     </row>
     <row r="125" spans="1:14">
       <c r="A125" t="s">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="B125" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C125">
-        <v>0.9945164322853088</v>
+        <v>0.995938241481781</v>
       </c>
       <c r="D125" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -6676,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -6688,7 +7335,7 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N125">
         <v>3</v>
@@ -6696,16 +7343,16 @@
     </row>
     <row r="126" spans="1:14">
       <c r="A126" t="s">
-        <v>138</v>
+        <v>264</v>
       </c>
       <c r="B126" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C126">
-        <v>0.995938241481781</v>
+        <v>0.998788058757782</v>
       </c>
       <c r="D126" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -6720,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -6732,24 +7379,24 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N126">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" t="s">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="B127" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C127">
-        <v>0.998788058757782</v>
+        <v>0.98718935251236</v>
       </c>
       <c r="D127" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -6764,7 +7411,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -6776,24 +7423,24 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" t="s">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="B128" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C128">
-        <v>0.9871893525123596</v>
+        <v>0.999046087265015</v>
       </c>
       <c r="D128" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -6808,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -6820,24 +7467,24 @@
         <v>0</v>
       </c>
       <c r="M128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N128">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" t="s">
-        <v>141</v>
+        <v>270</v>
       </c>
       <c r="B129" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C129">
-        <v>0.9990460872650146</v>
+        <v>0.978120744228363</v>
       </c>
       <c r="D129" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -6852,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -6872,16 +7519,16 @@
     </row>
     <row r="130" spans="1:14">
       <c r="A130" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="B130" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C130">
-        <v>0.978120744228363</v>
+        <v>0.993702113628387</v>
       </c>
       <c r="D130" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -6896,10 +7543,10 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130">
         <v>0</v>
@@ -6908,24 +7555,24 @@
         <v>0</v>
       </c>
       <c r="M130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N130">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" t="s">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="B131" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C131">
-        <v>0.9937021136283875</v>
+        <v>0.998434066772461</v>
       </c>
       <c r="D131" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -6940,10 +7587,10 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -6952,24 +7599,24 @@
         <v>0</v>
       </c>
       <c r="M131">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N131">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" t="s">
-        <v>144</v>
+        <v>276</v>
       </c>
       <c r="B132" t="s">
         <v>277</v>
       </c>
       <c r="C132">
-        <v>0.9984340667724609</v>
+        <v>0.996797204017639</v>
       </c>
       <c r="D132" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -6984,10 +7631,10 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -6996,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="M132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N132">
         <v>2</v>
@@ -7004,16 +7651,16 @@
     </row>
     <row r="133" spans="1:14">
       <c r="A133" t="s">
-        <v>145</v>
+        <v>278</v>
       </c>
       <c r="B133" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C133">
-        <v>0.9967972040176392</v>
+        <v>0.997380673885345</v>
       </c>
       <c r="D133" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7028,10 +7675,10 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>281</v>
+        <v>17</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -7040,57 +7687,14 @@
         <v>0</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N133">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14">
-      <c r="A134" t="s">
-        <v>146</v>
-      </c>
-      <c r="B134" t="s">
-        <v>279</v>
-      </c>
-      <c r="C134">
-        <v>0.9973806738853455</v>
-      </c>
-      <c r="D134" t="s">
-        <v>280</v>
-      </c>
-      <c r="E134">
-        <v>0</v>
-      </c>
-      <c r="F134" t="b">
-        <v>0</v>
-      </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134" t="s">
-        <v>281</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134">
-        <v>2</v>
-      </c>
-      <c r="N134">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -1,33 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="10700"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="278">
   <si>
     <t>filename</t>
   </si>
@@ -74,1166 +61,817 @@
     <t>micro_0192_YSB_II.jpg</t>
   </si>
   <si>
+    <t>micro_0103_1700XL1_80_00.jpg</t>
+  </si>
+  <si>
+    <t>micro_0234_XJOO.jpg</t>
+  </si>
+  <si>
+    <t>micro_0004_XDII.jpg</t>
+  </si>
+  <si>
+    <t>micro_0031_1700X400.jpg</t>
+  </si>
+  <si>
+    <t>micro_0160_2300X408.jpg</t>
+  </si>
+  <si>
+    <t>micro_0159_1700X407.jpg</t>
+  </si>
+  <si>
+    <t>micro_0157_2300X406.jpg</t>
+  </si>
+  <si>
+    <t>micro_0156_1700X405.jpg</t>
+  </si>
+  <si>
+    <t>micro_0155_2300X404.jpg</t>
+  </si>
+  <si>
+    <t>micro_0029_2300X402.jpg</t>
+  </si>
+  <si>
+    <t>micro_0142_X401.jpg</t>
+  </si>
+  <si>
+    <t>micro_0141_X325.jpg</t>
+  </si>
+  <si>
+    <t>micro_0075_X20VI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0140_X209.jpg</t>
+  </si>
+  <si>
+    <t>micro_0139_X208.jpg</t>
+  </si>
+  <si>
+    <t>micro_0138_X207.jpg</t>
+  </si>
+  <si>
+    <t>micro_0079_X206.jpg</t>
+  </si>
+  <si>
+    <t>micro_0135_X205.jpg</t>
+  </si>
+  <si>
+    <t>micro_0074_X203.jpg</t>
+  </si>
+  <si>
+    <t>micro_0168_1700X202.jpg</t>
+  </si>
+  <si>
+    <t>micro_0167_2300X201.jpg</t>
+  </si>
+  <si>
+    <t>micro_0109_SL40III.jpg</t>
+  </si>
+  <si>
+    <t>micro_0296_SL4082600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0291_SL407.jpg</t>
+  </si>
+  <si>
+    <t>micro_0112_SL406.jpg</t>
+  </si>
+  <si>
+    <t>micro_0111_SL405.jpg</t>
+  </si>
+  <si>
+    <t>micro_0110_SL404.jpg</t>
+  </si>
+  <si>
+    <t>micro_0108_SL402.jpg</t>
+  </si>
+  <si>
+    <t>micro_0105_SL401.jpg</t>
+  </si>
+  <si>
+    <t>micro_0152_SL301.jpg</t>
+  </si>
+  <si>
+    <t>micro_0185_OO_0_SL20VI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0273_SL203.jpg</t>
+  </si>
+  <si>
+    <t>micro_0212_SL202.jpg</t>
+  </si>
+  <si>
+    <t>micro_0211_SL201.jpg</t>
+  </si>
+  <si>
+    <t>micro_0190_O_SBII.jpg</t>
+  </si>
+  <si>
+    <t>micro_0289_SBI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0231_FX201.jpg</t>
+  </si>
+  <si>
+    <t>micro_0287_FSL20VI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0272_AFSL201.jpg</t>
+  </si>
+  <si>
+    <t>micro_0007_0D527.jpg</t>
+  </si>
+  <si>
+    <t>micro_0096_D523.jpg</t>
+  </si>
+  <si>
+    <t>micro_0095_D521.jpg</t>
+  </si>
+  <si>
+    <t>micro_0098_D519.jpg</t>
+  </si>
+  <si>
+    <t>micro_0100_D517.jpg</t>
+  </si>
+  <si>
+    <t>micro_0226_D515.jpg</t>
+  </si>
+  <si>
+    <t>micro_0218_D514.jpg</t>
+  </si>
+  <si>
+    <t>micro_0270_D513.jpg</t>
+  </si>
+  <si>
+    <t>micro_0230_D512.jpg</t>
+  </si>
+  <si>
+    <t>micro_0271_D511.jpg</t>
+  </si>
+  <si>
+    <t>micro_0010_D510.jpg</t>
+  </si>
+  <si>
+    <t>micro_0201_D509.jpg</t>
+  </si>
+  <si>
+    <t>micro_0164_D508.jpg</t>
+  </si>
+  <si>
+    <t>micro_0199_D507.jpg</t>
+  </si>
+  <si>
+    <t>micro_0220_D506.jpg</t>
+  </si>
+  <si>
+    <t>micro_0264_D505.jpg</t>
+  </si>
+  <si>
+    <t>micro_0163_D504.jpg</t>
+  </si>
+  <si>
+    <t>micro_0114_O_D503.jpg</t>
+  </si>
+  <si>
+    <t>micro_0166_D502.jpg</t>
+  </si>
+  <si>
+    <t>micro_0117_D501.jpg</t>
+  </si>
+  <si>
+    <t>micro_0034_D432.jpg</t>
+  </si>
+  <si>
+    <t>micro_0032_D430.jpg</t>
+  </si>
+  <si>
+    <t>micro_0035_D426.jpg</t>
+  </si>
+  <si>
+    <t>micro_0056_D424.jpg</t>
+  </si>
+  <si>
+    <t>micro_0049_D422.jpg</t>
+  </si>
+  <si>
+    <t>micro_0051_D420.jpg</t>
+  </si>
+  <si>
+    <t>micro_0104_D419.jpg</t>
+  </si>
+  <si>
+    <t>micro_0025_D418.jpg</t>
+  </si>
+  <si>
+    <t>micro_0275_0D417.jpg</t>
+  </si>
+  <si>
+    <t>micro_0066_D416.jpg</t>
+  </si>
+  <si>
+    <t>micro_0281_D415.jpg</t>
+  </si>
+  <si>
+    <t>micro_0064_D414.jpg</t>
+  </si>
+  <si>
+    <t>micro_0283_D413.jpg</t>
+  </si>
+  <si>
+    <t>micro_0047_D412.jpg</t>
+  </si>
+  <si>
+    <t>micro_0277_D411.jpg</t>
+  </si>
+  <si>
+    <t>micro_0057_D410.jpg</t>
+  </si>
+  <si>
+    <t>micro_0279_D409.jpg</t>
+  </si>
+  <si>
+    <t>micro_0063_D408.jpg</t>
+  </si>
+  <si>
+    <t>micro_0132_D407.jpg</t>
+  </si>
+  <si>
+    <t>micro_0263_D406.jpg</t>
+  </si>
+  <si>
+    <t>micro_0134_D405.jpg</t>
+  </si>
+  <si>
+    <t>micro_0261_D404.jpg</t>
+  </si>
+  <si>
+    <t>micro_0133_YD409_D403.jpg</t>
+  </si>
+  <si>
+    <t>micro_0065_D402.jpg</t>
+  </si>
+  <si>
+    <t>micro_0290_D401.jpg</t>
+  </si>
+  <si>
+    <t>micro_0255_D250.jpg</t>
+  </si>
+  <si>
+    <t>micro_0071_D248.jpg</t>
+  </si>
+  <si>
+    <t>micro_0151_D2472600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0016_D246.jpg</t>
+  </si>
+  <si>
+    <t>micro_0150_D245.jpg</t>
+  </si>
+  <si>
+    <t>micro_0073_D242.jpg</t>
+  </si>
+  <si>
+    <t>micro_0090_OD240.jpg</t>
+  </si>
+  <si>
+    <t>micro_0148_D2392000.jpg</t>
+  </si>
+  <si>
+    <t>micro_0018_D238.jpg</t>
+  </si>
+  <si>
+    <t>micro_0147_D2372600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0021_2D236.jpg</t>
+  </si>
+  <si>
+    <t>micro_0043_D235.jpg</t>
+  </si>
+  <si>
+    <t>micro_0203_0D234.jpg</t>
+  </si>
+  <si>
+    <t>micro_0210_D233.jpg</t>
+  </si>
+  <si>
+    <t>micro_0249_OD232.jpg</t>
+  </si>
+  <si>
+    <t>micro_0182_D231.jpg</t>
+  </si>
+  <si>
+    <t>micro_0252_OOD230.jpg</t>
+  </si>
+  <si>
+    <t>micro_0237_D229.jpg</t>
+  </si>
+  <si>
+    <t>micro_0256_D228.jpg</t>
+  </si>
+  <si>
+    <t>micro_0042_D227.jpg</t>
+  </si>
+  <si>
+    <t>micro_0254_D226.jpg</t>
+  </si>
+  <si>
+    <t>micro_0183_D225.jpg</t>
+  </si>
+  <si>
+    <t>micro_0125_D224.jpg</t>
+  </si>
+  <si>
+    <t>micro_0235_D223.jpg</t>
+  </si>
+  <si>
+    <t>micro_0129_D222.jpg</t>
+  </si>
+  <si>
+    <t>micro_0239_D221.jpg</t>
+  </si>
+  <si>
+    <t>micro_0127_D220.jpg</t>
+  </si>
+  <si>
+    <t>micro_0170_D219.jpg</t>
+  </si>
+  <si>
+    <t>micro_0126_D218.jpg</t>
+  </si>
+  <si>
+    <t>micro_0244_D217.jpg</t>
+  </si>
+  <si>
+    <t>micro_0087_D216.jpg</t>
+  </si>
+  <si>
+    <t>micro_0175_D215.jpg</t>
+  </si>
+  <si>
+    <t>micro_0086_D214.jpg</t>
+  </si>
+  <si>
+    <t>micro_0179_D213.jpg</t>
+  </si>
+  <si>
+    <t>micro_0083_D212.jpg</t>
+  </si>
+  <si>
+    <t>micro_0246_D211.jpg</t>
+  </si>
+  <si>
+    <t>micro_0084_D210.jpg</t>
+  </si>
+  <si>
+    <t>micro_0245_D209.jpg</t>
+  </si>
+  <si>
+    <t>micro_0088_D208.jpg</t>
+  </si>
+  <si>
+    <t>micro_0241_D207.jpg</t>
+  </si>
+  <si>
+    <t>micro_0081_D206.jpg</t>
+  </si>
+  <si>
+    <t>micro_0000_DD205.jpg</t>
+  </si>
+  <si>
+    <t>micro_0193_D204.jpg</t>
+  </si>
+  <si>
+    <t>micro_0169_D203.jpg</t>
+  </si>
+  <si>
+    <t>micro_0189_D202.jpg</t>
+  </si>
+  <si>
+    <t>micro_0068_D201_QO.jpg</t>
+  </si>
+  <si>
     <t>YSBⅡ</t>
   </si>
   <si>
+    <t>XLⅠ</t>
+  </si>
+  <si>
+    <t>XJ</t>
+  </si>
+  <si>
+    <t>XDⅡ2</t>
+  </si>
+  <si>
+    <t>X40Ⅲ</t>
+  </si>
+  <si>
+    <t>X408</t>
+  </si>
+  <si>
+    <t>X407</t>
+  </si>
+  <si>
+    <t>X406</t>
+  </si>
+  <si>
+    <t>X405</t>
+  </si>
+  <si>
+    <t>X404</t>
+  </si>
+  <si>
+    <t>X402</t>
+  </si>
+  <si>
+    <t>X401</t>
+  </si>
+  <si>
+    <t>X325</t>
+  </si>
+  <si>
+    <t>X20Ⅵ</t>
+  </si>
+  <si>
+    <t>X209</t>
+  </si>
+  <si>
+    <t>X208</t>
+  </si>
+  <si>
+    <t>X207</t>
+  </si>
+  <si>
+    <t>X206</t>
+  </si>
+  <si>
+    <t>X205</t>
+  </si>
+  <si>
+    <t>X203</t>
+  </si>
+  <si>
+    <t>X202</t>
+  </si>
+  <si>
+    <t>X201</t>
+  </si>
+  <si>
+    <t>SL40Ⅲ</t>
+  </si>
+  <si>
+    <t>SL408</t>
+  </si>
+  <si>
+    <t>SL407</t>
+  </si>
+  <si>
+    <t>SL406</t>
+  </si>
+  <si>
+    <t>SL405</t>
+  </si>
+  <si>
+    <t>SL404</t>
+  </si>
+  <si>
+    <t>SL402</t>
+  </si>
+  <si>
+    <t>SL401</t>
+  </si>
+  <si>
+    <t>SL301</t>
+  </si>
+  <si>
+    <t>SL20Ⅵ</t>
+  </si>
+  <si>
+    <t>SL203</t>
+  </si>
+  <si>
+    <t>SL202</t>
+  </si>
+  <si>
+    <t>SL201</t>
+  </si>
+  <si>
+    <t>SBⅡ</t>
+  </si>
+  <si>
+    <t>SBⅠ</t>
+  </si>
+  <si>
+    <t>FX201</t>
+  </si>
+  <si>
+    <t>FSL20Ⅵ</t>
+  </si>
+  <si>
+    <t>FSL201</t>
+  </si>
+  <si>
+    <t>D527</t>
+  </si>
+  <si>
+    <t>D523</t>
+  </si>
+  <si>
+    <t>D521</t>
+  </si>
+  <si>
+    <t>D519</t>
+  </si>
+  <si>
+    <t>D517</t>
+  </si>
+  <si>
+    <t>D515</t>
+  </si>
+  <si>
+    <t>D514</t>
+  </si>
+  <si>
+    <t>D513</t>
+  </si>
+  <si>
+    <t>D512</t>
+  </si>
+  <si>
+    <t>D511</t>
+  </si>
+  <si>
+    <t>D510</t>
+  </si>
+  <si>
+    <t>D509</t>
+  </si>
+  <si>
+    <t>D508</t>
+  </si>
+  <si>
+    <t>D507</t>
+  </si>
+  <si>
+    <t>D506</t>
+  </si>
+  <si>
+    <t>D505</t>
+  </si>
+  <si>
+    <t>D504</t>
+  </si>
+  <si>
+    <t>D503</t>
+  </si>
+  <si>
+    <t>D502</t>
+  </si>
+  <si>
+    <t>D501</t>
+  </si>
+  <si>
+    <t>D432</t>
+  </si>
+  <si>
+    <t>D430</t>
+  </si>
+  <si>
+    <t>D426</t>
+  </si>
+  <si>
+    <t>D424</t>
+  </si>
+  <si>
+    <t>D422</t>
+  </si>
+  <si>
+    <t>D420</t>
+  </si>
+  <si>
+    <t>D419</t>
+  </si>
+  <si>
+    <t>D418</t>
+  </si>
+  <si>
+    <t>D417</t>
+  </si>
+  <si>
+    <t>D416</t>
+  </si>
+  <si>
+    <t>D415</t>
+  </si>
+  <si>
+    <t>D414</t>
+  </si>
+  <si>
+    <t>D413</t>
+  </si>
+  <si>
+    <t>D412</t>
+  </si>
+  <si>
+    <t>D411</t>
+  </si>
+  <si>
+    <t>D410</t>
+  </si>
+  <si>
+    <t>D409</t>
+  </si>
+  <si>
+    <t>D408</t>
+  </si>
+  <si>
+    <t>D407</t>
+  </si>
+  <si>
+    <t>D406</t>
+  </si>
+  <si>
+    <t>D405</t>
+  </si>
+  <si>
+    <t>D404</t>
+  </si>
+  <si>
+    <t>D403</t>
+  </si>
+  <si>
+    <t>D402</t>
+  </si>
+  <si>
+    <t>D401</t>
+  </si>
+  <si>
+    <t>D250</t>
+  </si>
+  <si>
+    <t>D248</t>
+  </si>
+  <si>
+    <t>D247</t>
+  </si>
+  <si>
+    <t>D246</t>
+  </si>
+  <si>
+    <t>D245</t>
+  </si>
+  <si>
+    <t>D242</t>
+  </si>
+  <si>
+    <t>D240</t>
+  </si>
+  <si>
+    <t>D239</t>
+  </si>
+  <si>
+    <t>D238</t>
+  </si>
+  <si>
+    <t>D237</t>
+  </si>
+  <si>
+    <t>D236</t>
+  </si>
+  <si>
+    <t>D235</t>
+  </si>
+  <si>
+    <t>D234</t>
+  </si>
+  <si>
+    <t>D233</t>
+  </si>
+  <si>
+    <t>D232</t>
+  </si>
+  <si>
+    <t>D231</t>
+  </si>
+  <si>
+    <t>D230</t>
+  </si>
+  <si>
+    <t>D229</t>
+  </si>
+  <si>
+    <t>D228</t>
+  </si>
+  <si>
+    <t>D227</t>
+  </si>
+  <si>
+    <t>D226</t>
+  </si>
+  <si>
+    <t>D225</t>
+  </si>
+  <si>
+    <t>D224</t>
+  </si>
+  <si>
+    <t>D223</t>
+  </si>
+  <si>
+    <t>D222</t>
+  </si>
+  <si>
+    <t>D221</t>
+  </si>
+  <si>
+    <t>D220</t>
+  </si>
+  <si>
+    <t>D219</t>
+  </si>
+  <si>
+    <t>D218</t>
+  </si>
+  <si>
+    <t>D217</t>
+  </si>
+  <si>
+    <t>D216</t>
+  </si>
+  <si>
+    <t>D215</t>
+  </si>
+  <si>
+    <t>D214</t>
+  </si>
+  <si>
+    <t>D213</t>
+  </si>
+  <si>
+    <t>D212</t>
+  </si>
+  <si>
+    <t>D211</t>
+  </si>
+  <si>
+    <t>D210</t>
+  </si>
+  <si>
+    <t>D209</t>
+  </si>
+  <si>
+    <t>D208</t>
+  </si>
+  <si>
+    <t>D207</t>
+  </si>
+  <si>
+    <t>D206</t>
+  </si>
+  <si>
+    <t>D205</t>
+  </si>
+  <si>
+    <t>D204</t>
+  </si>
+  <si>
+    <t>D203</t>
+  </si>
+  <si>
+    <t>D202</t>
+  </si>
+  <si>
+    <t>D201</t>
+  </si>
+  <si>
     <t>color_detection</t>
   </si>
   <si>
     <t>Yes</t>
-  </si>
-  <si>
-    <t>micro_0103_1700XL1_80_00.jpg</t>
-  </si>
-  <si>
-    <t>XLⅠ</t>
-  </si>
-  <si>
-    <t>micro_0234_XJOO.jpg</t>
-  </si>
-  <si>
-    <t>XJ</t>
-  </si>
-  <si>
-    <t>micro_0004_XDII.jpg</t>
-  </si>
-  <si>
-    <t>XDⅡ2</t>
-  </si>
-  <si>
-    <t>micro_0031_1700X400.jpg</t>
-  </si>
-  <si>
-    <t>X40Ⅲ</t>
-  </si>
-  <si>
-    <t>micro_0160_2300X408.jpg</t>
-  </si>
-  <si>
-    <t>X408</t>
-  </si>
-  <si>
-    <t>micro_0159_1700X407.jpg</t>
-  </si>
-  <si>
-    <t>X407</t>
-  </si>
-  <si>
-    <t>micro_0157_2300X406.jpg</t>
-  </si>
-  <si>
-    <t>X406</t>
-  </si>
-  <si>
-    <t>micro_0156_1700X405.jpg</t>
-  </si>
-  <si>
-    <t>X405</t>
-  </si>
-  <si>
-    <t>micro_0155_2300X404.jpg</t>
-  </si>
-  <si>
-    <t>X404</t>
-  </si>
-  <si>
-    <t>micro_0029_2300X402.jpg</t>
-  </si>
-  <si>
-    <t>X402</t>
-  </si>
-  <si>
-    <t>micro_0142_X401.jpg</t>
-  </si>
-  <si>
-    <t>X401</t>
-  </si>
-  <si>
-    <t>micro_0141_X325.jpg</t>
-  </si>
-  <si>
-    <t>X325</t>
-  </si>
-  <si>
-    <t>micro_0075_X20VI.jpg</t>
-  </si>
-  <si>
-    <t>X20Ⅵ</t>
-  </si>
-  <si>
-    <t>micro_0140_X209.jpg</t>
-  </si>
-  <si>
-    <t>X209</t>
-  </si>
-  <si>
-    <t>micro_0139_X208.jpg</t>
-  </si>
-  <si>
-    <t>X208</t>
-  </si>
-  <si>
-    <t>micro_0138_X207.jpg</t>
-  </si>
-  <si>
-    <t>X207</t>
-  </si>
-  <si>
-    <t>micro_0079_X206.jpg</t>
-  </si>
-  <si>
-    <t>X206</t>
-  </si>
-  <si>
-    <t>micro_0135_X205.jpg</t>
-  </si>
-  <si>
-    <t>X205</t>
-  </si>
-  <si>
-    <t>micro_0074_X203.jpg</t>
-  </si>
-  <si>
-    <t>X203</t>
-  </si>
-  <si>
-    <t>micro_0168_1700X202.jpg</t>
-  </si>
-  <si>
-    <t>X202</t>
-  </si>
-  <si>
-    <t>micro_0167_2300X201.jpg</t>
-  </si>
-  <si>
-    <t>X201</t>
-  </si>
-  <si>
-    <t>micro_0109_SL40III.jpg</t>
-  </si>
-  <si>
-    <t>SL40Ⅲ</t>
-  </si>
-  <si>
-    <t>micro_0291_SL4082600.jpg</t>
-  </si>
-  <si>
-    <t>SL408</t>
-  </si>
-  <si>
-    <t>micro_0113_SL407.jpg</t>
-  </si>
-  <si>
-    <t>SL407</t>
-  </si>
-  <si>
-    <t>micro_0112_SL406.jpg</t>
-  </si>
-  <si>
-    <t>SL406</t>
-  </si>
-  <si>
-    <t>micro_0111_SL405.jpg</t>
-  </si>
-  <si>
-    <t>SL405</t>
-  </si>
-  <si>
-    <t>micro_0110_SL404.jpg</t>
-  </si>
-  <si>
-    <t>SL404</t>
-  </si>
-  <si>
-    <t>micro_0108_SL402.jpg</t>
-  </si>
-  <si>
-    <t>SL402</t>
-  </si>
-  <si>
-    <t>micro_0105_SL401.jpg</t>
-  </si>
-  <si>
-    <t>SL401</t>
-  </si>
-  <si>
-    <t>micro_0152_SL301.jpg</t>
-  </si>
-  <si>
-    <t>SL301</t>
-  </si>
-  <si>
-    <t>micro_0185_OO_0_SL20VI.jpg</t>
-  </si>
-  <si>
-    <t>SL20Ⅵ</t>
-  </si>
-  <si>
-    <t>micro_0273_SL203.jpg</t>
-  </si>
-  <si>
-    <t>SL203</t>
-  </si>
-  <si>
-    <t>micro_0212_SL202.jpg</t>
-  </si>
-  <si>
-    <t>SL202</t>
-  </si>
-  <si>
-    <t>micro_0211_SL201.jpg</t>
-  </si>
-  <si>
-    <t>SL201</t>
-  </si>
-  <si>
-    <t>micro_0190_O_SBII.jpg</t>
-  </si>
-  <si>
-    <t>SBⅡ</t>
-  </si>
-  <si>
-    <t>micro_0289_SBI.jpg</t>
-  </si>
-  <si>
-    <t>SBⅠ</t>
-  </si>
-  <si>
-    <t>micro_0231_FX201.jpg</t>
-  </si>
-  <si>
-    <t>FX201</t>
-  </si>
-  <si>
-    <t>micro_0287_FSL20VI.jpg</t>
-  </si>
-  <si>
-    <t>FSL20Ⅵ</t>
-  </si>
-  <si>
-    <t>micro_0272_AFSL201.jpg</t>
-  </si>
-  <si>
-    <t>FSL201</t>
-  </si>
-  <si>
-    <t>micro_0007_0D527.jpg</t>
-  </si>
-  <si>
-    <t>D527</t>
-  </si>
-  <si>
-    <t>micro_0096_D523.jpg</t>
-  </si>
-  <si>
-    <t>D523</t>
-  </si>
-  <si>
-    <t>micro_0095_D521.jpg</t>
-  </si>
-  <si>
-    <t>D521</t>
-  </si>
-  <si>
-    <t>micro_0098_D519.jpg</t>
-  </si>
-  <si>
-    <t>D519</t>
-  </si>
-  <si>
-    <t>micro_0100_D517.jpg</t>
-  </si>
-  <si>
-    <t>D517</t>
-  </si>
-  <si>
-    <t>micro_0226_D515.jpg</t>
-  </si>
-  <si>
-    <t>D515</t>
-  </si>
-  <si>
-    <t>micro_0218_D514.jpg</t>
-  </si>
-  <si>
-    <t>D514</t>
-  </si>
-  <si>
-    <t>micro_0270_D513.jpg</t>
-  </si>
-  <si>
-    <t>D513</t>
-  </si>
-  <si>
-    <t>micro_0230_D512.jpg</t>
-  </si>
-  <si>
-    <t>D512</t>
-  </si>
-  <si>
-    <t>micro_0271_D511.jpg</t>
-  </si>
-  <si>
-    <t>D511</t>
-  </si>
-  <si>
-    <t>micro_0010_D510.jpg</t>
-  </si>
-  <si>
-    <t>D510</t>
-  </si>
-  <si>
-    <t>micro_0201_D509.jpg</t>
-  </si>
-  <si>
-    <t>D509</t>
-  </si>
-  <si>
-    <t>micro_0164_D508.jpg</t>
-  </si>
-  <si>
-    <t>D508</t>
-  </si>
-  <si>
-    <t>micro_0199_D507.jpg</t>
-  </si>
-  <si>
-    <t>D507</t>
-  </si>
-  <si>
-    <t>micro_0220_D506.jpg</t>
-  </si>
-  <si>
-    <t>D506</t>
-  </si>
-  <si>
-    <t>micro_0264_D505.jpg</t>
-  </si>
-  <si>
-    <t>D505</t>
-  </si>
-  <si>
-    <t>micro_0163_D504.jpg</t>
-  </si>
-  <si>
-    <t>D504</t>
-  </si>
-  <si>
-    <t>micro_0114_O_D503.jpg</t>
-  </si>
-  <si>
-    <t>D503</t>
-  </si>
-  <si>
-    <t>micro_0166_D502.jpg</t>
-  </si>
-  <si>
-    <t>D502</t>
-  </si>
-  <si>
-    <t>micro_0117_D501.jpg</t>
-  </si>
-  <si>
-    <t>D501</t>
-  </si>
-  <si>
-    <t>micro_0034_D432.jpg</t>
-  </si>
-  <si>
-    <t>D432</t>
-  </si>
-  <si>
-    <t>micro_0032_D430.jpg</t>
-  </si>
-  <si>
-    <t>D430</t>
-  </si>
-  <si>
-    <t>micro_0035_D426.jpg</t>
-  </si>
-  <si>
-    <t>D426</t>
-  </si>
-  <si>
-    <t>micro_0056_D424.jpg</t>
-  </si>
-  <si>
-    <t>D424</t>
-  </si>
-  <si>
-    <t>micro_0049_D422.jpg</t>
-  </si>
-  <si>
-    <t>D422</t>
-  </si>
-  <si>
-    <t>micro_0051_D420.jpg</t>
-  </si>
-  <si>
-    <t>D420</t>
-  </si>
-  <si>
-    <t>micro_0104_D419.jpg</t>
-  </si>
-  <si>
-    <t>D419</t>
-  </si>
-  <si>
-    <t>micro_0025_D418.jpg</t>
-  </si>
-  <si>
-    <t>D418</t>
-  </si>
-  <si>
-    <t>micro_0275_0D417.jpg</t>
-  </si>
-  <si>
-    <t>D417</t>
-  </si>
-  <si>
-    <t>micro_0066_D416.jpg</t>
-  </si>
-  <si>
-    <t>D416</t>
-  </si>
-  <si>
-    <t>micro_0281_D415.jpg</t>
-  </si>
-  <si>
-    <t>D415</t>
-  </si>
-  <si>
-    <t>micro_0064_D414.jpg</t>
-  </si>
-  <si>
-    <t>D414</t>
-  </si>
-  <si>
-    <t>micro_0283_D413.jpg</t>
-  </si>
-  <si>
-    <t>D413</t>
-  </si>
-  <si>
-    <t>micro_0047_D412.jpg</t>
-  </si>
-  <si>
-    <t>D412</t>
-  </si>
-  <si>
-    <t>micro_0277_D411.jpg</t>
-  </si>
-  <si>
-    <t>D411</t>
-  </si>
-  <si>
-    <t>micro_0057_D410.jpg</t>
-  </si>
-  <si>
-    <t>D410</t>
-  </si>
-  <si>
-    <t>micro_0279_D409.jpg</t>
-  </si>
-  <si>
-    <t>D409</t>
-  </si>
-  <si>
-    <t>micro_0063_D408.jpg</t>
-  </si>
-  <si>
-    <t>D408</t>
-  </si>
-  <si>
-    <t>micro_0132_D407.jpg</t>
-  </si>
-  <si>
-    <t>D407</t>
-  </si>
-  <si>
-    <t>micro_0263_D406.jpg</t>
-  </si>
-  <si>
-    <t>D406</t>
-  </si>
-  <si>
-    <t>micro_0296_D405.jpg</t>
-  </si>
-  <si>
-    <t>D405</t>
-  </si>
-  <si>
-    <t>micro_0261_D404.jpg</t>
-  </si>
-  <si>
-    <t>D404</t>
-  </si>
-  <si>
-    <t>micro_0133_YD409_D403.jpg</t>
-  </si>
-  <si>
-    <t>D403</t>
-  </si>
-  <si>
-    <t>micro_0065_D402.jpg</t>
-  </si>
-  <si>
-    <t>D402</t>
-  </si>
-  <si>
-    <t>micro_0131_D401.jpg</t>
-  </si>
-  <si>
-    <t>D401</t>
-  </si>
-  <si>
-    <t>micro_0089_D3116.jpg</t>
-  </si>
-  <si>
-    <t>D3116</t>
-  </si>
-  <si>
-    <t>micro_0255_D250.jpg</t>
-  </si>
-  <si>
-    <t>D250</t>
-  </si>
-  <si>
-    <t>micro_0071_D248.jpg</t>
-  </si>
-  <si>
-    <t>D248</t>
-  </si>
-  <si>
-    <t>micro_0151_D2472600.jpg</t>
-  </si>
-  <si>
-    <t>D247</t>
-  </si>
-  <si>
-    <t>micro_0016_D246.jpg</t>
-  </si>
-  <si>
-    <t>D246</t>
-  </si>
-  <si>
-    <t>micro_0150_D245.jpg</t>
-  </si>
-  <si>
-    <t>D245</t>
-  </si>
-  <si>
-    <t>micro_0073_D242.jpg</t>
-  </si>
-  <si>
-    <t>D242</t>
-  </si>
-  <si>
-    <t>micro_0090_OD240.jpg</t>
-  </si>
-  <si>
-    <t>D240</t>
-  </si>
-  <si>
-    <t>micro_0148_D2392000.jpg</t>
-  </si>
-  <si>
-    <t>D239</t>
-  </si>
-  <si>
-    <t>micro_0018_D238.jpg</t>
-  </si>
-  <si>
-    <t>D238</t>
-  </si>
-  <si>
-    <t>micro_0147_D2372600.jpg</t>
-  </si>
-  <si>
-    <t>D237</t>
-  </si>
-  <si>
-    <t>micro_0021_2D236.jpg</t>
-  </si>
-  <si>
-    <t>D236</t>
-  </si>
-  <si>
-    <t>micro_0043_D235.jpg</t>
-  </si>
-  <si>
-    <t>D235</t>
-  </si>
-  <si>
-    <t>micro_0203_0D234.jpg</t>
-  </si>
-  <si>
-    <t>D234</t>
-  </si>
-  <si>
-    <t>micro_0210_D233.jpg</t>
-  </si>
-  <si>
-    <t>D233</t>
-  </si>
-  <si>
-    <t>micro_0249_OD232.jpg</t>
-  </si>
-  <si>
-    <t>D232</t>
-  </si>
-  <si>
-    <t>micro_0182_D231.jpg</t>
-  </si>
-  <si>
-    <t>D231</t>
-  </si>
-  <si>
-    <t>micro_0252_OOD230.jpg</t>
-  </si>
-  <si>
-    <t>D230</t>
-  </si>
-  <si>
-    <t>micro_0237_D229.jpg</t>
-  </si>
-  <si>
-    <t>D229</t>
-  </si>
-  <si>
-    <t>micro_0256_D228.jpg</t>
-  </si>
-  <si>
-    <t>D228</t>
-  </si>
-  <si>
-    <t>micro_0042_D227.jpg</t>
-  </si>
-  <si>
-    <t>D227</t>
-  </si>
-  <si>
-    <t>micro_0254_D226.jpg</t>
-  </si>
-  <si>
-    <t>D226</t>
-  </si>
-  <si>
-    <t>micro_0183_D225.jpg</t>
-  </si>
-  <si>
-    <t>D225</t>
-  </si>
-  <si>
-    <t>micro_0125_D224.jpg</t>
-  </si>
-  <si>
-    <t>D224</t>
-  </si>
-  <si>
-    <t>micro_0235_D223.jpg</t>
-  </si>
-  <si>
-    <t>D223</t>
-  </si>
-  <si>
-    <t>micro_0129_D222.jpg</t>
-  </si>
-  <si>
-    <t>D222</t>
-  </si>
-  <si>
-    <t>micro_0239_D221.jpg</t>
-  </si>
-  <si>
-    <t>D221</t>
-  </si>
-  <si>
-    <t>micro_0127_D220.jpg</t>
-  </si>
-  <si>
-    <t>D220</t>
-  </si>
-  <si>
-    <t>micro_0170_D219.jpg</t>
-  </si>
-  <si>
-    <t>D219</t>
-  </si>
-  <si>
-    <t>micro_0126_D218.jpg</t>
-  </si>
-  <si>
-    <t>D218</t>
-  </si>
-  <si>
-    <t>micro_0244_D217.jpg</t>
-  </si>
-  <si>
-    <t>D217</t>
-  </si>
-  <si>
-    <t>micro_0087_D216.jpg</t>
-  </si>
-  <si>
-    <t>D216</t>
-  </si>
-  <si>
-    <t>micro_0175_D215.jpg</t>
-  </si>
-  <si>
-    <t>D215</t>
-  </si>
-  <si>
-    <t>micro_0086_D214.jpg</t>
-  </si>
-  <si>
-    <t>D214</t>
-  </si>
-  <si>
-    <t>micro_0179_D213.jpg</t>
-  </si>
-  <si>
-    <t>D213</t>
-  </si>
-  <si>
-    <t>micro_0083_D212.jpg</t>
-  </si>
-  <si>
-    <t>D212</t>
-  </si>
-  <si>
-    <t>micro_0246_D211.jpg</t>
-  </si>
-  <si>
-    <t>D211</t>
-  </si>
-  <si>
-    <t>micro_0084_D210.jpg</t>
-  </si>
-  <si>
-    <t>D210</t>
-  </si>
-  <si>
-    <t>micro_0245_D209.jpg</t>
-  </si>
-  <si>
-    <t>D209</t>
-  </si>
-  <si>
-    <t>micro_0088_D208.jpg</t>
-  </si>
-  <si>
-    <t>D208</t>
-  </si>
-  <si>
-    <t>micro_0241_D207.jpg</t>
-  </si>
-  <si>
-    <t>D207</t>
-  </si>
-  <si>
-    <t>micro_0081_D206.jpg</t>
-  </si>
-  <si>
-    <t>D206</t>
-  </si>
-  <si>
-    <t>micro_0000_DD205.jpg</t>
-  </si>
-  <si>
-    <t>D205</t>
-  </si>
-  <si>
-    <t>micro_0193_D204.jpg</t>
-  </si>
-  <si>
-    <t>D204</t>
-  </si>
-  <si>
-    <t>micro_0169_D203.jpg</t>
-  </si>
-  <si>
-    <t>D203</t>
-  </si>
-  <si>
-    <t>micro_0189_D202.jpg</t>
-  </si>
-  <si>
-    <t>D202</t>
-  </si>
-  <si>
-    <t>micro_0068_D201_QO.jpg</t>
-  </si>
-  <si>
-    <t>D201</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1241,312 +879,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1829,17 +1173,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:N133"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
-  <cols>
-    <col min="3" max="3" width="12.9230769230769"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N132"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
@@ -1890,13 +1231,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="C2">
         <v>0.922767162322998</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1911,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1931,16 +1272,16 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="C3">
-        <v>0.979434370994568</v>
+        <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1955,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1970,21 +1311,21 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>147</v>
       </c>
       <c r="C4">
-        <v>0.908977508544922</v>
+        <v>0.9089775085449219</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1999,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -2019,16 +1360,16 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>148</v>
       </c>
       <c r="C5">
-        <v>0.756766498088837</v>
+        <v>0.7567664980888367</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -2043,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2063,16 +1404,16 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>149</v>
       </c>
       <c r="C6">
-        <v>0.936048984527588</v>
+        <v>0.9360489845275879</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -2087,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -2102,21 +1443,21 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>150</v>
       </c>
       <c r="C7">
-        <v>0.98980438709259</v>
+        <v>0.9898043870925903</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -2131,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -2146,21 +1487,21 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>151</v>
       </c>
       <c r="C8">
-        <v>0.980020582675934</v>
+        <v>0.9800205826759338</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -2175,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -2190,21 +1531,21 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="C9">
-        <v>0.986609637737274</v>
+        <v>0.9866096377372742</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -2219,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2239,16 +1580,16 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>153</v>
       </c>
       <c r="C10">
-        <v>0.982588768005371</v>
+        <v>0.9825887680053711</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -2263,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2278,21 +1619,21 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>154</v>
       </c>
       <c r="C11">
-        <v>0.985435843467712</v>
+        <v>0.9854358434677124</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -2307,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2327,16 +1668,16 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>155</v>
       </c>
       <c r="C12">
-        <v>0.986951112747192</v>
+        <v>0.9869511127471924</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -2351,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2366,21 +1707,21 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>156</v>
       </c>
       <c r="C13">
-        <v>0.988358616828918</v>
+        <v>0.9883586168289185</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -2395,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -2410,21 +1751,21 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>157</v>
       </c>
       <c r="C14">
-        <v>0.982721090316772</v>
+        <v>0.9827210903167725</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -2439,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2454,21 +1795,21 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>158</v>
       </c>
       <c r="C15">
-        <v>0.98913449048996</v>
+        <v>0.9891344904899597</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -2483,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2498,21 +1839,21 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="C16">
-        <v>0.984901964664459</v>
+        <v>0.9849019646644592</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -2527,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2547,16 +1888,16 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="C17">
-        <v>0.983111679553986</v>
+        <v>0.9831116795539856</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2571,7 +1912,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2586,21 +1927,21 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>161</v>
       </c>
       <c r="C18">
         <v>0.979184627532959</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2615,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2630,21 +1971,21 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>162</v>
       </c>
       <c r="C19">
-        <v>0.982077360153198</v>
+        <v>0.9820773601531982</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2659,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2679,16 +2020,16 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>163</v>
       </c>
       <c r="C20">
-        <v>0.992621064186096</v>
+        <v>0.9926210641860962</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2703,7 +2044,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2718,21 +2059,21 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="C21">
         <v>0.991193413734436</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2747,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2762,21 +2103,21 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>165</v>
       </c>
       <c r="C22">
-        <v>0.975940585136414</v>
+        <v>0.9759405851364136</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2791,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2806,21 +2147,21 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="C23">
-        <v>0.993631660938263</v>
+        <v>0.9936316609382629</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2835,7 +2176,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2850,21 +2191,21 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="C24">
-        <v>0.983439445495605</v>
+        <v>0.9834394454956055</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2879,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2894,21 +2235,21 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="C25">
-        <v>0.993823945522308</v>
+        <v>0.9938239455223083</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2923,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2943,16 +2284,16 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="C26">
-        <v>0.997099578380585</v>
+        <v>0.9971064329147339</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2967,36 +2308,36 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26">
         <v>0</v>
       </c>
       <c r="N26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>170</v>
       </c>
       <c r="C27">
-        <v>0.997689545154572</v>
+        <v>0.9976895451545715</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -3011,7 +2352,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -3031,16 +2372,16 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="C28">
-        <v>0.995999217033386</v>
+        <v>0.9959992170333862</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -3055,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -3070,21 +2411,21 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>172</v>
       </c>
       <c r="C29">
-        <v>0.99710738658905</v>
+        <v>0.9971073865890503</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -3099,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -3119,16 +2460,16 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="C30">
-        <v>0.996883392333984</v>
+        <v>0.9968833923339844</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -3143,7 +2484,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -3158,21 +2499,21 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="C31">
-        <v>0.9585862159729</v>
+        <v>0.9585862159729004</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -3187,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -3202,21 +2543,21 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="C32">
-        <v>0.99848335981369</v>
+        <v>0.9984833598136902</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -3231,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -3246,21 +2587,21 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="C33">
-        <v>0.996042430400848</v>
+        <v>0.9960424304008484</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -3275,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -3287,24 +2628,24 @@
         <v>1</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>81</v>
+        <v>177</v>
       </c>
       <c r="C34">
-        <v>0.998810112476349</v>
+        <v>0.9988101124763489</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -3319,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -3334,21 +2675,21 @@
         <v>0</v>
       </c>
       <c r="N34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="C35">
-        <v>0.97547721862793</v>
+        <v>0.9754772186279297</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -3363,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3378,21 +2719,21 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>179</v>
       </c>
       <c r="C36">
-        <v>0.967378795146942</v>
+        <v>0.9673787951469421</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -3407,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -3422,21 +2763,21 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>87</v>
+        <v>180</v>
       </c>
       <c r="C37">
-        <v>0.767745614051819</v>
+        <v>0.7677456140518188</v>
       </c>
       <c r="D37" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3451,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -3471,16 +2812,16 @@
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>181</v>
       </c>
       <c r="C38">
-        <v>0.894055366516113</v>
+        <v>0.8940553665161133</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -3495,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -3510,21 +2851,21 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="C39">
-        <v>0.99658191204071</v>
+        <v>0.9965819120407104</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3539,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -3559,16 +2900,16 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="C40">
-        <v>0.998970866203308</v>
+        <v>0.9989708662033081</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3583,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -3598,21 +2939,21 @@
         <v>0</v>
       </c>
       <c r="N40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="C41">
-        <v>0.999165236949921</v>
+        <v>0.9991652369499207</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3627,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -3642,21 +2983,21 @@
         <v>0</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="C42">
-        <v>0.999000132083893</v>
+        <v>0.9990001320838928</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3671,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3686,21 +3027,21 @@
         <v>1</v>
       </c>
       <c r="N42">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>98</v>
+        <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="C43">
-        <v>0.999042212963104</v>
+        <v>0.9990422129631042</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3715,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3730,21 +3071,21 @@
         <v>3</v>
       </c>
       <c r="N43">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="C44">
-        <v>0.996248424053192</v>
+        <v>0.9962484240531921</v>
       </c>
       <c r="D44" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3759,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3774,21 +3115,21 @@
         <v>1</v>
       </c>
       <c r="N44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="C45">
-        <v>0.995609939098358</v>
+        <v>0.9956099390983582</v>
       </c>
       <c r="D45" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3803,7 +3144,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3818,21 +3159,21 @@
         <v>2</v>
       </c>
       <c r="N45">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="C46">
-        <v>0.999369502067566</v>
+        <v>0.9993695020675659</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3847,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3862,21 +3203,21 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="C47">
-        <v>0.999027788639069</v>
+        <v>0.9990277886390686</v>
       </c>
       <c r="D47" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3891,7 +3232,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3903,24 +3244,24 @@
         <v>0</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N47">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="C48">
-        <v>0.999590218067169</v>
+        <v>0.9995902180671692</v>
       </c>
       <c r="D48" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3935,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3950,21 +3291,21 @@
         <v>1</v>
       </c>
       <c r="N48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="C49">
-        <v>0.999411702156067</v>
+        <v>0.9994117021560669</v>
       </c>
       <c r="D49" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3979,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3994,21 +3335,21 @@
         <v>1</v>
       </c>
       <c r="N49">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>113</v>
+        <v>193</v>
       </c>
       <c r="C50">
-        <v>0.999428272247314</v>
+        <v>0.9994282722473145</v>
       </c>
       <c r="D50" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -4023,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -4038,21 +3379,21 @@
         <v>1</v>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>194</v>
       </c>
       <c r="C51">
         <v>0.999479353427887</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -4067,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -4082,21 +3423,21 @@
         <v>1</v>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>195</v>
       </c>
       <c r="C52">
-        <v>0.998457193374634</v>
+        <v>0.9984571933746338</v>
       </c>
       <c r="D52" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -4111,7 +3452,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -4126,21 +3467,21 @@
         <v>1</v>
       </c>
       <c r="N52">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>119</v>
+        <v>196</v>
       </c>
       <c r="C53">
-        <v>0.99813187122345</v>
+        <v>0.9981318712234497</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -4155,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -4170,21 +3511,21 @@
         <v>1</v>
       </c>
       <c r="N53">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="C54">
         <v>0.999025285243988</v>
       </c>
       <c r="D54" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -4199,7 +3540,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -4214,21 +3555,21 @@
         <v>2</v>
       </c>
       <c r="N54">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="C55">
         <v>0.933538019657135</v>
       </c>
       <c r="D55" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -4243,7 +3584,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -4255,24 +3596,24 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>199</v>
       </c>
       <c r="C56">
-        <v>0.998995363712311</v>
+        <v>0.9989953637123108</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -4287,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -4299,24 +3640,24 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N56">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>127</v>
+        <v>200</v>
       </c>
       <c r="C57">
-        <v>0.998640179634094</v>
+        <v>0.9986401796340942</v>
       </c>
       <c r="D57" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4331,7 +3672,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -4346,21 +3687,21 @@
         <v>3</v>
       </c>
       <c r="N57">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>201</v>
       </c>
       <c r="C58">
-        <v>0.999037563800812</v>
+        <v>0.9990375638008118</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4375,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -4390,21 +3731,21 @@
         <v>1</v>
       </c>
       <c r="N58">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="C59">
-        <v>0.878909468650818</v>
+        <v>0.8789094686508179</v>
       </c>
       <c r="D59" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -4419,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4434,21 +3775,21 @@
         <v>3</v>
       </c>
       <c r="N59">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="C60">
-        <v>0.998813688755035</v>
+        <v>0.9988136887550354</v>
       </c>
       <c r="D60" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4463,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -4478,21 +3819,21 @@
         <v>1</v>
       </c>
       <c r="N60">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="C61">
-        <v>0.990991115570068</v>
+        <v>0.9909911155700684</v>
       </c>
       <c r="D61" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -4507,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -4522,21 +3863,21 @@
         <v>1</v>
       </c>
       <c r="N61">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="C62">
-        <v>0.998318433761597</v>
+        <v>0.9983184337615967</v>
       </c>
       <c r="D62" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -4551,7 +3892,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -4566,21 +3907,21 @@
         <v>2</v>
       </c>
       <c r="N62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="C63">
-        <v>0.999444603919983</v>
+        <v>0.9994446039199829</v>
       </c>
       <c r="D63" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4595,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -4615,16 +3956,16 @@
     </row>
     <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="C64">
-        <v>0.999382138252258</v>
+        <v>0.9993821382522583</v>
       </c>
       <c r="D64" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4639,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4654,21 +3995,21 @@
         <v>1</v>
       </c>
       <c r="N64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="C65">
-        <v>0.997601628303528</v>
+        <v>0.9976016283035278</v>
       </c>
       <c r="D65" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4683,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4703,16 +4044,16 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" t="s">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>145</v>
+        <v>209</v>
       </c>
       <c r="C66">
-        <v>0.999007225036621</v>
+        <v>0.9990072250366211</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4727,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4739,24 +4080,24 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" t="s">
-        <v>146</v>
+        <v>79</v>
       </c>
       <c r="B67" t="s">
-        <v>147</v>
+        <v>210</v>
       </c>
       <c r="C67">
-        <v>0.999165773391724</v>
+        <v>0.9991657733917236</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4771,7 +4112,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4783,24 +4124,24 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="C68">
         <v>0.997841477394104</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4815,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4835,16 +4176,16 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>150</v>
+        <v>81</v>
       </c>
       <c r="B69" t="s">
-        <v>151</v>
+        <v>212</v>
       </c>
       <c r="C69">
-        <v>0.997644543647766</v>
+        <v>0.9976445436477661</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4859,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4874,21 +4215,21 @@
         <v>2</v>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" t="s">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="B70" t="s">
-        <v>153</v>
+        <v>213</v>
       </c>
       <c r="C70">
-        <v>0.998023271560669</v>
+        <v>0.9980232715606689</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4903,7 +4244,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4923,16 +4264,16 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="B71" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="C71">
-        <v>0.999061822891235</v>
+        <v>0.9990618228912354</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4947,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4967,16 +4308,16 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72" t="s">
-        <v>156</v>
+        <v>84</v>
       </c>
       <c r="B72" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="C72">
-        <v>0.999475955963135</v>
+        <v>0.9994759559631348</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4991,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -5006,21 +4347,21 @@
         <v>3</v>
       </c>
       <c r="N72">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="C73">
-        <v>0.999207198619843</v>
+        <v>0.9992071986198425</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -5035,7 +4376,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -5050,21 +4391,21 @@
         <v>2</v>
       </c>
       <c r="N73">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>161</v>
+        <v>217</v>
       </c>
       <c r="C74">
-        <v>0.998555243015289</v>
+        <v>0.9985552430152893</v>
       </c>
       <c r="D74" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -5079,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -5094,21 +4435,21 @@
         <v>2</v>
       </c>
       <c r="N74">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" t="s">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="B75" t="s">
-        <v>163</v>
+        <v>218</v>
       </c>
       <c r="C75">
-        <v>0.997600972652435</v>
+        <v>0.9976009726524353</v>
       </c>
       <c r="D75" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -5123,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -5135,24 +4476,24 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N75">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" t="s">
-        <v>164</v>
+        <v>88</v>
       </c>
       <c r="B76" t="s">
-        <v>165</v>
+        <v>219</v>
       </c>
       <c r="C76">
-        <v>0.988409817218781</v>
+        <v>0.9884098172187805</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -5167,7 +4508,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -5179,24 +4520,24 @@
         <v>0</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N76">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" t="s">
-        <v>166</v>
+        <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>167</v>
+        <v>220</v>
       </c>
       <c r="C77">
-        <v>0.783249199390411</v>
+        <v>0.7832491993904114</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5211,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -5226,21 +4567,21 @@
         <v>2</v>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" t="s">
-        <v>168</v>
+        <v>90</v>
       </c>
       <c r="B78" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="C78">
-        <v>0.995502591133118</v>
+        <v>0.9955025911331177</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5255,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -5270,21 +4611,21 @@
         <v>3</v>
       </c>
       <c r="N78">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" t="s">
-        <v>170</v>
+        <v>91</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="C79">
-        <v>0.999555587768555</v>
+        <v>0.9995555877685547</v>
       </c>
       <c r="D79" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5299,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -5314,21 +4655,21 @@
         <v>2</v>
       </c>
       <c r="N79">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" t="s">
-        <v>172</v>
+        <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>173</v>
+        <v>223</v>
       </c>
       <c r="C80">
-        <v>0.997513651847839</v>
+        <v>0.9975136518478394</v>
       </c>
       <c r="D80" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5343,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -5358,21 +4699,21 @@
         <v>1</v>
       </c>
       <c r="N80">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
+        <v>224</v>
       </c>
       <c r="C81">
-        <v>0.997211933135986</v>
+        <v>0.9972119331359863</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5387,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -5402,21 +4743,21 @@
         <v>1</v>
       </c>
       <c r="N81">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" t="s">
-        <v>176</v>
+        <v>94</v>
       </c>
       <c r="B82" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="C82">
-        <v>0.998041272163391</v>
+        <v>0.9970172047615051</v>
       </c>
       <c r="D82" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -5431,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -5443,24 +4784,24 @@
         <v>0</v>
       </c>
       <c r="M82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N82">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>226</v>
       </c>
       <c r="C83">
         <v>0.997714638710022</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5475,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -5487,7 +4828,7 @@
         <v>0</v>
       </c>
       <c r="M83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N83">
         <v>1</v>
@@ -5495,16 +4836,16 @@
     </row>
     <row r="84" spans="1:14">
       <c r="A84" t="s">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="B84" t="s">
-        <v>181</v>
+        <v>227</v>
       </c>
       <c r="C84">
-        <v>0.931635975837708</v>
+        <v>0.9316359758377075</v>
       </c>
       <c r="D84" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5519,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -5539,16 +4880,16 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" t="s">
-        <v>182</v>
+        <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="C85">
-        <v>0.998109936714172</v>
+        <v>0.9981099367141724</v>
       </c>
       <c r="D85" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5563,7 +4904,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -5578,21 +4919,21 @@
         <v>1</v>
       </c>
       <c r="N85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>185</v>
+        <v>229</v>
       </c>
       <c r="C86">
-        <v>0.998637616634369</v>
+        <v>0.996095597743988</v>
       </c>
       <c r="D86" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5607,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -5622,21 +4963,21 @@
         <v>1</v>
       </c>
       <c r="N86">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="B87" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="C87">
-        <v>0.999771952629089</v>
+        <v>0.9881560802459717</v>
       </c>
       <c r="D87" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5651,7 +4992,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5663,24 +5004,24 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" t="s">
-        <v>188</v>
+        <v>100</v>
       </c>
       <c r="B88" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="C88">
-        <v>0.988156080245972</v>
+        <v>0.9993869662284851</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5695,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5715,16 +5056,16 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" t="s">
-        <v>190</v>
+        <v>101</v>
       </c>
       <c r="B89" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="C89">
-        <v>0.999386966228485</v>
+        <v>0.9876304268836975</v>
       </c>
       <c r="D89" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5739,7 +5080,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5754,21 +5095,21 @@
         <v>1</v>
       </c>
       <c r="N89">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" t="s">
-        <v>192</v>
+        <v>102</v>
       </c>
       <c r="B90" t="s">
-        <v>193</v>
+        <v>233</v>
       </c>
       <c r="C90">
-        <v>0.987630426883698</v>
+        <v>0.9915251135826111</v>
       </c>
       <c r="D90" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5783,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5803,16 +5144,16 @@
     </row>
     <row r="91" spans="1:14">
       <c r="A91" t="s">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="B91" t="s">
-        <v>195</v>
+        <v>234</v>
       </c>
       <c r="C91">
-        <v>0.991525113582611</v>
+        <v>0.9993435144424438</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5827,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5847,16 +5188,16 @@
     </row>
     <row r="92" spans="1:14">
       <c r="A92" t="s">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c r="B92" t="s">
-        <v>197</v>
+        <v>235</v>
       </c>
       <c r="C92">
-        <v>0.999343514442444</v>
+        <v>0.9956748485565186</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5871,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5891,16 +5232,16 @@
     </row>
     <row r="93" spans="1:14">
       <c r="A93" t="s">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="B93" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="C93">
-        <v>0.995674848556519</v>
+        <v>0.9915837645530701</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5915,36 +5256,36 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93">
         <v>0</v>
       </c>
       <c r="L93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M93">
         <v>1</v>
       </c>
       <c r="N93">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" t="s">
-        <v>200</v>
+        <v>106</v>
       </c>
       <c r="B94" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="C94">
-        <v>0.99158376455307</v>
+        <v>0.9992069602012634</v>
       </c>
       <c r="D94" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5959,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5974,21 +5315,21 @@
         <v>1</v>
       </c>
       <c r="N94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" t="s">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="B95" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="C95">
-        <v>0.999206960201263</v>
+        <v>0.9964823126792908</v>
       </c>
       <c r="D95" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -6003,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -6023,16 +5364,16 @@
     </row>
     <row r="96" spans="1:14">
       <c r="A96" t="s">
-        <v>204</v>
+        <v>108</v>
       </c>
       <c r="B96" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="C96">
-        <v>0.996482312679291</v>
+        <v>0.9991474747657776</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -6047,7 +5388,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -6067,16 +5408,16 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" t="s">
-        <v>206</v>
+        <v>109</v>
       </c>
       <c r="B97" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="C97">
-        <v>0.999147474765778</v>
+        <v>0.9979246258735657</v>
       </c>
       <c r="D97" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6091,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -6111,16 +5452,16 @@
     </row>
     <row r="98" spans="1:14">
       <c r="A98" t="s">
-        <v>208</v>
+        <v>110</v>
       </c>
       <c r="B98" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="C98">
-        <v>0.997924625873566</v>
+        <v>0.9995026588439941</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6135,7 +5476,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -6150,21 +5491,21 @@
         <v>1</v>
       </c>
       <c r="N98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" t="s">
-        <v>210</v>
+        <v>111</v>
       </c>
       <c r="B99" t="s">
-        <v>211</v>
+        <v>242</v>
       </c>
       <c r="C99">
-        <v>0.999502658843994</v>
+        <v>0.9919981956481934</v>
       </c>
       <c r="D99" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6179,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -6194,21 +5535,21 @@
         <v>1</v>
       </c>
       <c r="N99">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" t="s">
-        <v>212</v>
+        <v>112</v>
       </c>
       <c r="B100" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="C100">
-        <v>0.991998195648193</v>
+        <v>0.8529298901557922</v>
       </c>
       <c r="D100" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6223,7 +5564,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -6238,21 +5579,21 @@
         <v>1</v>
       </c>
       <c r="N100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="C101">
-        <v>0.852929890155792</v>
+        <v>0.9926774501800537</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6267,10 +5608,10 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101">
         <v>0</v>
@@ -6287,16 +5628,16 @@
     </row>
     <row r="102" spans="1:14">
       <c r="A102" t="s">
-        <v>216</v>
+        <v>114</v>
       </c>
       <c r="B102" t="s">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="C102">
-        <v>0.992677450180054</v>
+        <v>0.9982547760009766</v>
       </c>
       <c r="D102" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6311,7 +5652,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -6326,21 +5667,21 @@
         <v>1</v>
       </c>
       <c r="N102">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" t="s">
-        <v>218</v>
+        <v>115</v>
       </c>
       <c r="B103" t="s">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="C103">
-        <v>0.998254776000977</v>
+        <v>0.9919293522834778</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6355,7 +5696,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -6370,21 +5711,21 @@
         <v>1</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="B104" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="C104">
-        <v>0.991929352283478</v>
+        <v>0.9978511333465576</v>
       </c>
       <c r="D104" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6399,36 +5740,36 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104">
         <v>1</v>
       </c>
       <c r="N104">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" t="s">
-        <v>222</v>
+        <v>117</v>
       </c>
       <c r="B105" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C105">
-        <v>0.997851133346558</v>
+        <v>0.999393105506897</v>
       </c>
       <c r="D105" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6443,36 +5784,36 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N105">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:14">
       <c r="A106" t="s">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="B106" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="C106">
-        <v>0.999393105506897</v>
+        <v>0.9981414675712585</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6487,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -6507,16 +5848,16 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" t="s">
-        <v>226</v>
+        <v>119</v>
       </c>
       <c r="B107" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="C107">
-        <v>0.998141467571259</v>
+        <v>0.995561420917511</v>
       </c>
       <c r="D107" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6531,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -6551,16 +5892,16 @@
     </row>
     <row r="108" spans="1:14">
       <c r="A108" t="s">
-        <v>228</v>
+        <v>120</v>
       </c>
       <c r="B108" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C108">
-        <v>0.995561420917511</v>
+        <v>0.99856036901474</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6575,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6587,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="M108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -6595,16 +5936,16 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" t="s">
-        <v>230</v>
+        <v>121</v>
       </c>
       <c r="B109" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C109">
-        <v>0.99856036901474</v>
+        <v>0.9979491829872131</v>
       </c>
       <c r="D109" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6619,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -6631,24 +5972,24 @@
         <v>0</v>
       </c>
       <c r="M109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N109">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" t="s">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="B110" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C110">
-        <v>0.997949182987213</v>
+        <v>0.9989242553710938</v>
       </c>
       <c r="D110" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6663,36 +6004,36 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110">
         <v>2</v>
       </c>
       <c r="N110">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" t="s">
-        <v>234</v>
+        <v>123</v>
       </c>
       <c r="B111" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C111">
-        <v>0.998924255371094</v>
+        <v>0.9987018704414368</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6707,36 +6048,36 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111">
         <v>2</v>
       </c>
       <c r="N111">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" t="s">
-        <v>236</v>
+        <v>124</v>
       </c>
       <c r="B112" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C112">
-        <v>0.998701870441437</v>
+        <v>0.9980301260948181</v>
       </c>
       <c r="D112" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6751,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -6763,24 +6104,24 @@
         <v>0</v>
       </c>
       <c r="M112">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N112">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" t="s">
-        <v>238</v>
+        <v>125</v>
       </c>
       <c r="B113" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C113">
-        <v>0.998030126094818</v>
+        <v>0.9988909959793091</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6795,7 +6136,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6810,21 +6151,21 @@
         <v>2</v>
       </c>
       <c r="N113">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" t="s">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="B114" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="C114">
-        <v>0.998890995979309</v>
+        <v>0.9961404204368591</v>
       </c>
       <c r="D114" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6839,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -6854,21 +6195,21 @@
         <v>2</v>
       </c>
       <c r="N114">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" t="s">
-        <v>242</v>
+        <v>127</v>
       </c>
       <c r="B115" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="C115">
-        <v>0.996140420436859</v>
+        <v>0.9958701133728027</v>
       </c>
       <c r="D115" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6883,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6895,24 +6236,24 @@
         <v>0</v>
       </c>
       <c r="M115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N115">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" t="s">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="B116" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="C116">
-        <v>0.995870113372803</v>
+        <v>0.998413622379303</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6927,7 +6268,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6939,24 +6280,24 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N116">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" t="s">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="B117" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C117">
-        <v>0.998413622379303</v>
+        <v>0.9992607235908508</v>
       </c>
       <c r="D117" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6971,7 +6312,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -6983,7 +6324,7 @@
         <v>0</v>
       </c>
       <c r="M117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -6991,16 +6332,16 @@
     </row>
     <row r="118" spans="1:14">
       <c r="A118" t="s">
-        <v>248</v>
+        <v>130</v>
       </c>
       <c r="B118" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C118">
-        <v>0.999260723590851</v>
+        <v>0.9961749315261841</v>
       </c>
       <c r="D118" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7015,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -7027,24 +6368,24 @@
         <v>0</v>
       </c>
       <c r="M118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N118">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" t="s">
-        <v>250</v>
+        <v>131</v>
       </c>
       <c r="B119" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="C119">
-        <v>0.996174931526184</v>
+        <v>0.9993590712547302</v>
       </c>
       <c r="D119" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7059,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -7079,16 +6420,16 @@
     </row>
     <row r="120" spans="1:14">
       <c r="A120" t="s">
-        <v>252</v>
+        <v>132</v>
       </c>
       <c r="B120" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C120">
-        <v>0.99935907125473</v>
+        <v>0.9987558722496033</v>
       </c>
       <c r="D120" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7103,7 +6444,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -7115,24 +6456,24 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N120">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:14">
       <c r="A121" t="s">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="B121" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="C121">
-        <v>0.998755872249603</v>
+        <v>0.9992091655731201</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7147,7 +6488,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -7162,21 +6503,21 @@
         <v>2</v>
       </c>
       <c r="N121">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" t="s">
-        <v>256</v>
+        <v>134</v>
       </c>
       <c r="B122" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C122">
-        <v>0.99920916557312</v>
+        <v>0.9622448682785034</v>
       </c>
       <c r="D122" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7191,7 +6532,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -7206,21 +6547,21 @@
         <v>2</v>
       </c>
       <c r="N122">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" t="s">
-        <v>258</v>
+        <v>135</v>
       </c>
       <c r="B123" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C123">
-        <v>0.962244868278503</v>
+        <v>0.9945164322853088</v>
       </c>
       <c r="D123" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7235,7 +6576,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -7247,24 +6588,24 @@
         <v>0</v>
       </c>
       <c r="M123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" t="s">
-        <v>260</v>
+        <v>136</v>
       </c>
       <c r="B124" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C124">
-        <v>0.994516432285309</v>
+        <v>0.995938241481781</v>
       </c>
       <c r="D124" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7279,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -7291,24 +6632,24 @@
         <v>0</v>
       </c>
       <c r="M124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N124">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" t="s">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="B125" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C125">
-        <v>0.995938241481781</v>
+        <v>0.998788058757782</v>
       </c>
       <c r="D125" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7323,7 +6664,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -7335,24 +6676,24 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N125">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" t="s">
-        <v>264</v>
+        <v>138</v>
       </c>
       <c r="B126" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C126">
-        <v>0.998788058757782</v>
+        <v>0.9871893525123596</v>
       </c>
       <c r="D126" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7367,7 +6708,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -7379,24 +6720,24 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N126">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" t="s">
-        <v>266</v>
+        <v>139</v>
       </c>
       <c r="B127" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C127">
-        <v>0.98718935251236</v>
+        <v>0.9990460872650146</v>
       </c>
       <c r="D127" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7411,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -7423,24 +6764,24 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N127">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:14">
       <c r="A128" t="s">
-        <v>268</v>
+        <v>140</v>
       </c>
       <c r="B128" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C128">
-        <v>0.999046087265015</v>
+        <v>0.978120744228363</v>
       </c>
       <c r="D128" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7455,7 +6796,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -7470,21 +6811,21 @@
         <v>1</v>
       </c>
       <c r="N128">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" t="s">
-        <v>270</v>
+        <v>141</v>
       </c>
       <c r="B129" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C129">
-        <v>0.978120744228363</v>
+        <v>0.9937021136283875</v>
       </c>
       <c r="D129" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -7499,10 +6840,10 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -7511,7 +6852,7 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N129">
         <v>2</v>
@@ -7519,16 +6860,16 @@
     </row>
     <row r="130" spans="1:14">
       <c r="A130" t="s">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="B130" t="s">
         <v>273</v>
       </c>
       <c r="C130">
-        <v>0.993702113628387</v>
+        <v>0.9984340667724609</v>
       </c>
       <c r="D130" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -7543,10 +6884,10 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130">
         <v>0</v>
@@ -7555,24 +6896,24 @@
         <v>0</v>
       </c>
       <c r="M130">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N130">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" t="s">
+        <v>143</v>
+      </c>
+      <c r="B131" t="s">
         <v>274</v>
       </c>
-      <c r="B131" t="s">
-        <v>275</v>
-      </c>
       <c r="C131">
-        <v>0.998434066772461</v>
+        <v>0.9967972040176392</v>
       </c>
       <c r="D131" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -7587,10 +6928,10 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -7599,24 +6940,24 @@
         <v>0</v>
       </c>
       <c r="M131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N131">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:14">
       <c r="A132" t="s">
-        <v>276</v>
+        <v>144</v>
       </c>
       <c r="B132" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C132">
-        <v>0.996797204017639</v>
+        <v>0.9973806738853455</v>
       </c>
       <c r="D132" t="s">
-        <v>16</v>
+        <v>276</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7631,10 +6972,10 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>17</v>
+        <v>277</v>
       </c>
       <c r="J132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -7643,58 +6984,13 @@
         <v>0</v>
       </c>
       <c r="M132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="133" spans="1:14">
-      <c r="A133" t="s">
-        <v>278</v>
-      </c>
-      <c r="B133" t="s">
-        <v>279</v>
-      </c>
-      <c r="C133">
-        <v>0.997380673885345</v>
-      </c>
-      <c r="D133" t="s">
-        <v>16</v>
-      </c>
-      <c r="E133">
-        <v>0</v>
-      </c>
-      <c r="F133" t="b">
-        <v>0</v>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133" t="s">
-        <v>17</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133">
-        <v>2</v>
-      </c>
-      <c r="N133">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -1,20 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView windowWidth="29400" windowHeight="10700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="276">
   <si>
     <t>filename</t>
   </si>
@@ -61,817 +74,1154 @@
     <t>micro_0192_YSB_II.jpg</t>
   </si>
   <si>
+    <t>YSBⅡ</t>
+  </si>
+  <si>
+    <t>color_detection</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>micro_0103_1700XL1_80_00.jpg</t>
   </si>
   <si>
+    <t>XLⅠ</t>
+  </si>
+  <si>
     <t>micro_0234_XJOO.jpg</t>
   </si>
   <si>
-    <t>micro_0004_XDII.jpg</t>
+    <t>XJ</t>
   </si>
   <si>
     <t>micro_0031_1700X400.jpg</t>
   </si>
   <si>
+    <t>X40Ⅲ</t>
+  </si>
+  <si>
     <t>micro_0160_2300X408.jpg</t>
   </si>
   <si>
+    <t>X408</t>
+  </si>
+  <si>
     <t>micro_0159_1700X407.jpg</t>
   </si>
   <si>
+    <t>X407</t>
+  </si>
+  <si>
     <t>micro_0157_2300X406.jpg</t>
   </si>
   <si>
+    <t>X406</t>
+  </si>
+  <si>
     <t>micro_0156_1700X405.jpg</t>
   </si>
   <si>
+    <t>X405</t>
+  </si>
+  <si>
     <t>micro_0155_2300X404.jpg</t>
   </si>
   <si>
+    <t>X404</t>
+  </si>
+  <si>
     <t>micro_0029_2300X402.jpg</t>
   </si>
   <si>
+    <t>X402</t>
+  </si>
+  <si>
     <t>micro_0142_X401.jpg</t>
   </si>
   <si>
+    <t>X401</t>
+  </si>
+  <si>
     <t>micro_0141_X325.jpg</t>
   </si>
   <si>
+    <t>X325</t>
+  </si>
+  <si>
     <t>micro_0075_X20VI.jpg</t>
   </si>
   <si>
+    <t>X20Ⅵ</t>
+  </si>
+  <si>
     <t>micro_0140_X209.jpg</t>
   </si>
   <si>
+    <t>X209</t>
+  </si>
+  <si>
     <t>micro_0139_X208.jpg</t>
   </si>
   <si>
+    <t>X208</t>
+  </si>
+  <si>
     <t>micro_0138_X207.jpg</t>
   </si>
   <si>
+    <t>X207</t>
+  </si>
+  <si>
     <t>micro_0079_X206.jpg</t>
   </si>
   <si>
+    <t>X206</t>
+  </si>
+  <si>
     <t>micro_0135_X205.jpg</t>
   </si>
   <si>
+    <t>X205</t>
+  </si>
+  <si>
     <t>micro_0074_X203.jpg</t>
   </si>
   <si>
+    <t>X203</t>
+  </si>
+  <si>
     <t>micro_0168_1700X202.jpg</t>
   </si>
   <si>
+    <t>X202</t>
+  </si>
+  <si>
     <t>micro_0167_2300X201.jpg</t>
   </si>
   <si>
+    <t>X201</t>
+  </si>
+  <si>
     <t>micro_0109_SL40III.jpg</t>
   </si>
   <si>
+    <t>SL40Ⅲ</t>
+  </si>
+  <si>
     <t>micro_0296_SL4082600.jpg</t>
   </si>
   <si>
+    <t>SL408</t>
+  </si>
+  <si>
     <t>micro_0291_SL407.jpg</t>
   </si>
   <si>
+    <t>SL407</t>
+  </si>
+  <si>
     <t>micro_0112_SL406.jpg</t>
   </si>
   <si>
+    <t>SL406</t>
+  </si>
+  <si>
     <t>micro_0111_SL405.jpg</t>
   </si>
   <si>
+    <t>SL405</t>
+  </si>
+  <si>
     <t>micro_0110_SL404.jpg</t>
   </si>
   <si>
+    <t>SL404</t>
+  </si>
+  <si>
     <t>micro_0108_SL402.jpg</t>
   </si>
   <si>
+    <t>SL402</t>
+  </si>
+  <si>
     <t>micro_0105_SL401.jpg</t>
   </si>
   <si>
+    <t>SL401</t>
+  </si>
+  <si>
     <t>micro_0152_SL301.jpg</t>
   </si>
   <si>
+    <t>SL301</t>
+  </si>
+  <si>
     <t>micro_0185_OO_0_SL20VI.jpg</t>
   </si>
   <si>
+    <t>SL20Ⅵ</t>
+  </si>
+  <si>
     <t>micro_0273_SL203.jpg</t>
   </si>
   <si>
+    <t>SL203</t>
+  </si>
+  <si>
     <t>micro_0212_SL202.jpg</t>
   </si>
   <si>
+    <t>SL202</t>
+  </si>
+  <si>
     <t>micro_0211_SL201.jpg</t>
   </si>
   <si>
+    <t>SL201</t>
+  </si>
+  <si>
     <t>micro_0190_O_SBII.jpg</t>
   </si>
   <si>
+    <t>SBⅡ</t>
+  </si>
+  <si>
     <t>micro_0289_SBI.jpg</t>
   </si>
   <si>
+    <t>SBⅠ</t>
+  </si>
+  <si>
     <t>micro_0231_FX201.jpg</t>
   </si>
   <si>
+    <t>FX201</t>
+  </si>
+  <si>
     <t>micro_0287_FSL20VI.jpg</t>
   </si>
   <si>
+    <t>FSL20Ⅵ</t>
+  </si>
+  <si>
     <t>micro_0272_AFSL201.jpg</t>
   </si>
   <si>
+    <t>FSL201</t>
+  </si>
+  <si>
     <t>micro_0007_0D527.jpg</t>
   </si>
   <si>
+    <t>D527</t>
+  </si>
+  <si>
     <t>micro_0096_D523.jpg</t>
   </si>
   <si>
+    <t>D523</t>
+  </si>
+  <si>
     <t>micro_0095_D521.jpg</t>
   </si>
   <si>
+    <t>D521</t>
+  </si>
+  <si>
     <t>micro_0098_D519.jpg</t>
   </si>
   <si>
+    <t>D519</t>
+  </si>
+  <si>
     <t>micro_0100_D517.jpg</t>
   </si>
   <si>
+    <t>D517</t>
+  </si>
+  <si>
     <t>micro_0226_D515.jpg</t>
   </si>
   <si>
+    <t>D515</t>
+  </si>
+  <si>
     <t>micro_0218_D514.jpg</t>
   </si>
   <si>
+    <t>D514</t>
+  </si>
+  <si>
     <t>micro_0270_D513.jpg</t>
   </si>
   <si>
+    <t>D513</t>
+  </si>
+  <si>
     <t>micro_0230_D512.jpg</t>
   </si>
   <si>
+    <t>D512</t>
+  </si>
+  <si>
     <t>micro_0271_D511.jpg</t>
   </si>
   <si>
+    <t>D511</t>
+  </si>
+  <si>
     <t>micro_0010_D510.jpg</t>
   </si>
   <si>
+    <t>D510</t>
+  </si>
+  <si>
     <t>micro_0201_D509.jpg</t>
   </si>
   <si>
+    <t>D509</t>
+  </si>
+  <si>
     <t>micro_0164_D508.jpg</t>
   </si>
   <si>
+    <t>D508</t>
+  </si>
+  <si>
     <t>micro_0199_D507.jpg</t>
   </si>
   <si>
+    <t>D507</t>
+  </si>
+  <si>
     <t>micro_0220_D506.jpg</t>
   </si>
   <si>
+    <t>D506</t>
+  </si>
+  <si>
     <t>micro_0264_D505.jpg</t>
   </si>
   <si>
+    <t>D505</t>
+  </si>
+  <si>
     <t>micro_0163_D504.jpg</t>
   </si>
   <si>
+    <t>D504</t>
+  </si>
+  <si>
     <t>micro_0114_O_D503.jpg</t>
   </si>
   <si>
+    <t>D503</t>
+  </si>
+  <si>
     <t>micro_0166_D502.jpg</t>
   </si>
   <si>
+    <t>D502</t>
+  </si>
+  <si>
     <t>micro_0117_D501.jpg</t>
   </si>
   <si>
+    <t>D501</t>
+  </si>
+  <si>
     <t>micro_0034_D432.jpg</t>
   </si>
   <si>
+    <t>D432</t>
+  </si>
+  <si>
     <t>micro_0032_D430.jpg</t>
   </si>
   <si>
+    <t>D430</t>
+  </si>
+  <si>
     <t>micro_0035_D426.jpg</t>
   </si>
   <si>
+    <t>D426</t>
+  </si>
+  <si>
     <t>micro_0056_D424.jpg</t>
   </si>
   <si>
+    <t>D424</t>
+  </si>
+  <si>
     <t>micro_0049_D422.jpg</t>
   </si>
   <si>
+    <t>D422</t>
+  </si>
+  <si>
     <t>micro_0051_D420.jpg</t>
   </si>
   <si>
+    <t>D420</t>
+  </si>
+  <si>
     <t>micro_0104_D419.jpg</t>
   </si>
   <si>
+    <t>D419</t>
+  </si>
+  <si>
     <t>micro_0025_D418.jpg</t>
   </si>
   <si>
+    <t>D418</t>
+  </si>
+  <si>
     <t>micro_0275_0D417.jpg</t>
   </si>
   <si>
+    <t>D417</t>
+  </si>
+  <si>
     <t>micro_0066_D416.jpg</t>
   </si>
   <si>
+    <t>D416</t>
+  </si>
+  <si>
     <t>micro_0281_D415.jpg</t>
   </si>
   <si>
+    <t>D415</t>
+  </si>
+  <si>
     <t>micro_0064_D414.jpg</t>
   </si>
   <si>
+    <t>D414</t>
+  </si>
+  <si>
     <t>micro_0283_D413.jpg</t>
   </si>
   <si>
+    <t>D413</t>
+  </si>
+  <si>
     <t>micro_0047_D412.jpg</t>
   </si>
   <si>
+    <t>D412</t>
+  </si>
+  <si>
     <t>micro_0277_D411.jpg</t>
   </si>
   <si>
+    <t>D411</t>
+  </si>
+  <si>
     <t>micro_0057_D410.jpg</t>
   </si>
   <si>
+    <t>D410</t>
+  </si>
+  <si>
     <t>micro_0279_D409.jpg</t>
   </si>
   <si>
+    <t>D409</t>
+  </si>
+  <si>
     <t>micro_0063_D408.jpg</t>
   </si>
   <si>
+    <t>D408</t>
+  </si>
+  <si>
     <t>micro_0132_D407.jpg</t>
   </si>
   <si>
+    <t>D407</t>
+  </si>
+  <si>
     <t>micro_0263_D406.jpg</t>
   </si>
   <si>
+    <t>D406</t>
+  </si>
+  <si>
     <t>micro_0134_D405.jpg</t>
   </si>
   <si>
+    <t>D405</t>
+  </si>
+  <si>
     <t>micro_0261_D404.jpg</t>
   </si>
   <si>
+    <t>D404</t>
+  </si>
+  <si>
     <t>micro_0133_YD409_D403.jpg</t>
   </si>
   <si>
+    <t>D403</t>
+  </si>
+  <si>
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
+    <t>D402</t>
+  </si>
+  <si>
     <t>micro_0290_D401.jpg</t>
   </si>
   <si>
+    <t>D401</t>
+  </si>
+  <si>
     <t>micro_0255_D250.jpg</t>
   </si>
   <si>
+    <t>D250</t>
+  </si>
+  <si>
     <t>micro_0071_D248.jpg</t>
   </si>
   <si>
+    <t>D248</t>
+  </si>
+  <si>
     <t>micro_0151_D2472600.jpg</t>
   </si>
   <si>
+    <t>D247</t>
+  </si>
+  <si>
     <t>micro_0016_D246.jpg</t>
   </si>
   <si>
+    <t>D246</t>
+  </si>
+  <si>
     <t>micro_0150_D245.jpg</t>
   </si>
   <si>
+    <t>D245</t>
+  </si>
+  <si>
     <t>micro_0073_D242.jpg</t>
   </si>
   <si>
+    <t>D242</t>
+  </si>
+  <si>
     <t>micro_0090_OD240.jpg</t>
   </si>
   <si>
+    <t>D240</t>
+  </si>
+  <si>
     <t>micro_0148_D2392000.jpg</t>
   </si>
   <si>
+    <t>D239</t>
+  </si>
+  <si>
     <t>micro_0018_D238.jpg</t>
   </si>
   <si>
+    <t>D238</t>
+  </si>
+  <si>
     <t>micro_0147_D2372600.jpg</t>
   </si>
   <si>
+    <t>D237</t>
+  </si>
+  <si>
     <t>micro_0021_2D236.jpg</t>
   </si>
   <si>
+    <t>D236</t>
+  </si>
+  <si>
     <t>micro_0043_D235.jpg</t>
   </si>
   <si>
+    <t>D235</t>
+  </si>
+  <si>
     <t>micro_0203_0D234.jpg</t>
   </si>
   <si>
+    <t>D234</t>
+  </si>
+  <si>
     <t>micro_0210_D233.jpg</t>
   </si>
   <si>
+    <t>D233</t>
+  </si>
+  <si>
     <t>micro_0249_OD232.jpg</t>
   </si>
   <si>
+    <t>D232</t>
+  </si>
+  <si>
     <t>micro_0182_D231.jpg</t>
   </si>
   <si>
+    <t>D231</t>
+  </si>
+  <si>
     <t>micro_0252_OOD230.jpg</t>
   </si>
   <si>
+    <t>D230</t>
+  </si>
+  <si>
     <t>micro_0237_D229.jpg</t>
   </si>
   <si>
+    <t>D229</t>
+  </si>
+  <si>
     <t>micro_0256_D228.jpg</t>
   </si>
   <si>
+    <t>D228</t>
+  </si>
+  <si>
     <t>micro_0042_D227.jpg</t>
   </si>
   <si>
+    <t>D227</t>
+  </si>
+  <si>
     <t>micro_0254_D226.jpg</t>
   </si>
   <si>
+    <t>D226</t>
+  </si>
+  <si>
     <t>micro_0183_D225.jpg</t>
   </si>
   <si>
+    <t>D225</t>
+  </si>
+  <si>
     <t>micro_0125_D224.jpg</t>
   </si>
   <si>
+    <t>D224</t>
+  </si>
+  <si>
     <t>micro_0235_D223.jpg</t>
   </si>
   <si>
+    <t>D223</t>
+  </si>
+  <si>
     <t>micro_0129_D222.jpg</t>
   </si>
   <si>
+    <t>D222</t>
+  </si>
+  <si>
     <t>micro_0239_D221.jpg</t>
   </si>
   <si>
+    <t>D221</t>
+  </si>
+  <si>
     <t>micro_0127_D220.jpg</t>
   </si>
   <si>
+    <t>D220</t>
+  </si>
+  <si>
     <t>micro_0170_D219.jpg</t>
   </si>
   <si>
+    <t>D219</t>
+  </si>
+  <si>
     <t>micro_0126_D218.jpg</t>
   </si>
   <si>
+    <t>D218</t>
+  </si>
+  <si>
     <t>micro_0244_D217.jpg</t>
   </si>
   <si>
+    <t>D217</t>
+  </si>
+  <si>
     <t>micro_0087_D216.jpg</t>
   </si>
   <si>
+    <t>D216</t>
+  </si>
+  <si>
     <t>micro_0175_D215.jpg</t>
   </si>
   <si>
+    <t>D215</t>
+  </si>
+  <si>
     <t>micro_0086_D214.jpg</t>
   </si>
   <si>
+    <t>D214</t>
+  </si>
+  <si>
     <t>micro_0179_D213.jpg</t>
   </si>
   <si>
+    <t>D213</t>
+  </si>
+  <si>
     <t>micro_0083_D212.jpg</t>
   </si>
   <si>
+    <t>D212</t>
+  </si>
+  <si>
     <t>micro_0246_D211.jpg</t>
   </si>
   <si>
+    <t>D211</t>
+  </si>
+  <si>
     <t>micro_0084_D210.jpg</t>
   </si>
   <si>
+    <t>D210</t>
+  </si>
+  <si>
     <t>micro_0245_D209.jpg</t>
   </si>
   <si>
+    <t>D209</t>
+  </si>
+  <si>
     <t>micro_0088_D208.jpg</t>
   </si>
   <si>
+    <t>D208</t>
+  </si>
+  <si>
     <t>micro_0241_D207.jpg</t>
   </si>
   <si>
+    <t>D207</t>
+  </si>
+  <si>
     <t>micro_0081_D206.jpg</t>
   </si>
   <si>
+    <t>D206</t>
+  </si>
+  <si>
     <t>micro_0000_DD205.jpg</t>
   </si>
   <si>
+    <t>D205</t>
+  </si>
+  <si>
     <t>micro_0193_D204.jpg</t>
   </si>
   <si>
+    <t>D204</t>
+  </si>
+  <si>
     <t>micro_0169_D203.jpg</t>
   </si>
   <si>
+    <t>D203</t>
+  </si>
+  <si>
     <t>micro_0189_D202.jpg</t>
   </si>
   <si>
+    <t>D202</t>
+  </si>
+  <si>
     <t>micro_0068_D201_QO.jpg</t>
   </si>
   <si>
-    <t>YSBⅡ</t>
-  </si>
-  <si>
-    <t>XLⅠ</t>
-  </si>
-  <si>
-    <t>XJ</t>
-  </si>
-  <si>
-    <t>XDⅡ2</t>
-  </si>
-  <si>
-    <t>X40Ⅲ</t>
-  </si>
-  <si>
-    <t>X408</t>
-  </si>
-  <si>
-    <t>X407</t>
-  </si>
-  <si>
-    <t>X406</t>
-  </si>
-  <si>
-    <t>X405</t>
-  </si>
-  <si>
-    <t>X404</t>
-  </si>
-  <si>
-    <t>X402</t>
-  </si>
-  <si>
-    <t>X401</t>
-  </si>
-  <si>
-    <t>X325</t>
-  </si>
-  <si>
-    <t>X20Ⅵ</t>
-  </si>
-  <si>
-    <t>X209</t>
-  </si>
-  <si>
-    <t>X208</t>
-  </si>
-  <si>
-    <t>X207</t>
-  </si>
-  <si>
-    <t>X206</t>
-  </si>
-  <si>
-    <t>X205</t>
-  </si>
-  <si>
-    <t>X203</t>
-  </si>
-  <si>
-    <t>X202</t>
-  </si>
-  <si>
-    <t>X201</t>
-  </si>
-  <si>
-    <t>SL40Ⅲ</t>
-  </si>
-  <si>
-    <t>SL408</t>
-  </si>
-  <si>
-    <t>SL407</t>
-  </si>
-  <si>
-    <t>SL406</t>
-  </si>
-  <si>
-    <t>SL405</t>
-  </si>
-  <si>
-    <t>SL404</t>
-  </si>
-  <si>
-    <t>SL402</t>
-  </si>
-  <si>
-    <t>SL401</t>
-  </si>
-  <si>
-    <t>SL301</t>
-  </si>
-  <si>
-    <t>SL20Ⅵ</t>
-  </si>
-  <si>
-    <t>SL203</t>
-  </si>
-  <si>
-    <t>SL202</t>
-  </si>
-  <si>
-    <t>SL201</t>
-  </si>
-  <si>
-    <t>SBⅡ</t>
-  </si>
-  <si>
-    <t>SBⅠ</t>
-  </si>
-  <si>
-    <t>FX201</t>
-  </si>
-  <si>
-    <t>FSL20Ⅵ</t>
-  </si>
-  <si>
-    <t>FSL201</t>
-  </si>
-  <si>
-    <t>D527</t>
-  </si>
-  <si>
-    <t>D523</t>
-  </si>
-  <si>
-    <t>D521</t>
-  </si>
-  <si>
-    <t>D519</t>
-  </si>
-  <si>
-    <t>D517</t>
-  </si>
-  <si>
-    <t>D515</t>
-  </si>
-  <si>
-    <t>D514</t>
-  </si>
-  <si>
-    <t>D513</t>
-  </si>
-  <si>
-    <t>D512</t>
-  </si>
-  <si>
-    <t>D511</t>
-  </si>
-  <si>
-    <t>D510</t>
-  </si>
-  <si>
-    <t>D509</t>
-  </si>
-  <si>
-    <t>D508</t>
-  </si>
-  <si>
-    <t>D507</t>
-  </si>
-  <si>
-    <t>D506</t>
-  </si>
-  <si>
-    <t>D505</t>
-  </si>
-  <si>
-    <t>D504</t>
-  </si>
-  <si>
-    <t>D503</t>
-  </si>
-  <si>
-    <t>D502</t>
-  </si>
-  <si>
-    <t>D501</t>
-  </si>
-  <si>
-    <t>D432</t>
-  </si>
-  <si>
-    <t>D430</t>
-  </si>
-  <si>
-    <t>D426</t>
-  </si>
-  <si>
-    <t>D424</t>
-  </si>
-  <si>
-    <t>D422</t>
-  </si>
-  <si>
-    <t>D420</t>
-  </si>
-  <si>
-    <t>D419</t>
-  </si>
-  <si>
-    <t>D418</t>
-  </si>
-  <si>
-    <t>D417</t>
-  </si>
-  <si>
-    <t>D416</t>
-  </si>
-  <si>
-    <t>D415</t>
-  </si>
-  <si>
-    <t>D414</t>
-  </si>
-  <si>
-    <t>D413</t>
-  </si>
-  <si>
-    <t>D412</t>
-  </si>
-  <si>
-    <t>D411</t>
-  </si>
-  <si>
-    <t>D410</t>
-  </si>
-  <si>
-    <t>D409</t>
-  </si>
-  <si>
-    <t>D408</t>
-  </si>
-  <si>
-    <t>D407</t>
-  </si>
-  <si>
-    <t>D406</t>
-  </si>
-  <si>
-    <t>D405</t>
-  </si>
-  <si>
-    <t>D404</t>
-  </si>
-  <si>
-    <t>D403</t>
-  </si>
-  <si>
-    <t>D402</t>
-  </si>
-  <si>
-    <t>D401</t>
-  </si>
-  <si>
-    <t>D250</t>
-  </si>
-  <si>
-    <t>D248</t>
-  </si>
-  <si>
-    <t>D247</t>
-  </si>
-  <si>
-    <t>D246</t>
-  </si>
-  <si>
-    <t>D245</t>
-  </si>
-  <si>
-    <t>D242</t>
-  </si>
-  <si>
-    <t>D240</t>
-  </si>
-  <si>
-    <t>D239</t>
-  </si>
-  <si>
-    <t>D238</t>
-  </si>
-  <si>
-    <t>D237</t>
-  </si>
-  <si>
-    <t>D236</t>
-  </si>
-  <si>
-    <t>D235</t>
-  </si>
-  <si>
-    <t>D234</t>
-  </si>
-  <si>
-    <t>D233</t>
-  </si>
-  <si>
-    <t>D232</t>
-  </si>
-  <si>
-    <t>D231</t>
-  </si>
-  <si>
-    <t>D230</t>
-  </si>
-  <si>
-    <t>D229</t>
-  </si>
-  <si>
-    <t>D228</t>
-  </si>
-  <si>
-    <t>D227</t>
-  </si>
-  <si>
-    <t>D226</t>
-  </si>
-  <si>
-    <t>D225</t>
-  </si>
-  <si>
-    <t>D224</t>
-  </si>
-  <si>
-    <t>D223</t>
-  </si>
-  <si>
-    <t>D222</t>
-  </si>
-  <si>
-    <t>D221</t>
-  </si>
-  <si>
-    <t>D220</t>
-  </si>
-  <si>
-    <t>D219</t>
-  </si>
-  <si>
-    <t>D218</t>
-  </si>
-  <si>
-    <t>D217</t>
-  </si>
-  <si>
-    <t>D216</t>
-  </si>
-  <si>
-    <t>D215</t>
-  </si>
-  <si>
-    <t>D214</t>
-  </si>
-  <si>
-    <t>D213</t>
-  </si>
-  <si>
-    <t>D212</t>
-  </si>
-  <si>
-    <t>D211</t>
-  </si>
-  <si>
-    <t>D210</t>
-  </si>
-  <si>
-    <t>D209</t>
-  </si>
-  <si>
-    <t>D208</t>
-  </si>
-  <si>
-    <t>D207</t>
-  </si>
-  <si>
-    <t>D206</t>
-  </si>
-  <si>
-    <t>D205</t>
-  </si>
-  <si>
-    <t>D204</t>
-  </si>
-  <si>
-    <t>D203</t>
-  </si>
-  <si>
-    <t>D202</t>
-  </si>
-  <si>
     <t>D201</t>
-  </si>
-  <si>
-    <t>color_detection</t>
-  </si>
-  <si>
-    <t>Yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -879,18 +1229,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1173,14 +1817,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N132"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N131"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="3" max="3" width="12.9230769230769"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" t="s">
@@ -1231,13 +1878,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>0.922767162322998</v>
       </c>
       <c r="D2" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1252,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1272,16 +1919,16 @@
     </row>
     <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>19</v>
       </c>
       <c r="C3">
-        <v>0.9794343709945679</v>
+        <v>0.979434370994568</v>
       </c>
       <c r="D3" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1296,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1316,16 +1963,16 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>0.9089775085449219</v>
+        <v>0.908977508544922</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1340,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1360,16 +2007,16 @@
     </row>
     <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>0.7567664980888367</v>
+        <v>0.936048984527588</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1384,10 +2031,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1399,21 +2046,21 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>0.9360489845275879</v>
+        <v>0.98980438709259</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1428,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1443,21 +2090,21 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
       <c r="C7">
-        <v>0.9898043870925903</v>
+        <v>0.980020582675934</v>
       </c>
       <c r="D7" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1472,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1492,16 +2139,16 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>29</v>
       </c>
       <c r="C8">
-        <v>0.9800205826759338</v>
+        <v>0.986609637737274</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1516,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1531,21 +2178,21 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>0.9866096377372742</v>
+        <v>0.982588768005371</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1560,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1575,21 +2222,21 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>33</v>
       </c>
       <c r="C10">
-        <v>0.9825887680053711</v>
+        <v>0.985435843467712</v>
       </c>
       <c r="D10" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1604,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1619,21 +2266,21 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="C11">
-        <v>0.9854358434677124</v>
+        <v>0.986951112747192</v>
       </c>
       <c r="D11" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1648,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1668,16 +2315,16 @@
     </row>
     <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="C12">
-        <v>0.9869511127471924</v>
+        <v>0.988358616828918</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1692,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1707,21 +2354,21 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>156</v>
+        <v>39</v>
       </c>
       <c r="C13">
-        <v>0.9883586168289185</v>
+        <v>0.982721090316772</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1736,13 +2383,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -1756,16 +2403,16 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="C14">
-        <v>0.9827210903167725</v>
+        <v>0.98913449048996</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1780,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1795,21 +2442,21 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="C15">
-        <v>0.9891344904899597</v>
+        <v>0.984901964664459</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1824,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1844,16 +2491,16 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="C16">
-        <v>0.9849019646644592</v>
+        <v>0.983111679553986</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1868,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1883,21 +2530,21 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B17" t="s">
-        <v>160</v>
+        <v>47</v>
       </c>
       <c r="C17">
-        <v>0.9831116795539856</v>
+        <v>0.979184627532959</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1912,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1927,21 +2574,21 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
-        <v>161</v>
+        <v>49</v>
       </c>
       <c r="C18">
-        <v>0.979184627532959</v>
+        <v>0.982077360153198</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1956,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1976,16 +2623,16 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="C19">
-        <v>0.9820773601531982</v>
+        <v>0.992621064186096</v>
       </c>
       <c r="D19" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2000,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2020,16 +2667,16 @@
     </row>
     <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="C20">
-        <v>0.9926210641860962</v>
+        <v>0.991193413734436</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2044,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2064,16 +2711,16 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="C21">
-        <v>0.991193413734436</v>
+        <v>0.975940585136414</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2088,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2108,16 +2755,16 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>165</v>
+        <v>57</v>
       </c>
       <c r="C22">
-        <v>0.9759405851364136</v>
+        <v>0.993631660938263</v>
       </c>
       <c r="D22" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2132,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2152,16 +2799,16 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>59</v>
       </c>
       <c r="C23">
-        <v>0.9936316609382629</v>
+        <v>0.983439445495605</v>
       </c>
       <c r="D23" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2176,36 +2823,36 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>61</v>
       </c>
       <c r="C24">
-        <v>0.9834394454956055</v>
+        <v>0.993823945522308</v>
       </c>
       <c r="D24" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2220,36 +2867,36 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>63</v>
       </c>
       <c r="C25">
-        <v>0.9938239455223083</v>
+        <v>0.997106432914734</v>
       </c>
       <c r="D25" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2264,16 +2911,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -2284,16 +2931,16 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="C26">
-        <v>0.9971064329147339</v>
+        <v>0.997689545154572</v>
       </c>
       <c r="D26" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2308,16 +2955,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -2328,16 +2975,16 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>67</v>
       </c>
       <c r="C27">
-        <v>0.9976895451545715</v>
+        <v>0.995999217033386</v>
       </c>
       <c r="D27" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2352,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2372,16 +3019,16 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>69</v>
       </c>
       <c r="C28">
-        <v>0.9959992170333862</v>
+        <v>0.99710738658905</v>
       </c>
       <c r="D28" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2396,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2416,16 +3063,16 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="C29">
-        <v>0.9971073865890503</v>
+        <v>0.996883392333984</v>
       </c>
       <c r="D29" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2440,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2455,21 +3102,21 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="C30">
-        <v>0.9968833923339844</v>
+        <v>0.9585862159729</v>
       </c>
       <c r="D30" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2484,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2499,21 +3146,21 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="C31">
-        <v>0.9585862159729004</v>
+        <v>0.99848335981369</v>
       </c>
       <c r="D31" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2528,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2543,21 +3190,21 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="C32">
-        <v>0.9984833598136902</v>
+        <v>0.996042430400848</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2572,36 +3219,36 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32">
         <v>1</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="C33">
-        <v>0.9960424304008484</v>
+        <v>0.998810112476349</v>
       </c>
       <c r="D33" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2616,36 +3263,36 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33">
         <v>1</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B34" t="s">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="C34">
-        <v>0.9988101124763489</v>
+        <v>0.97547721862793</v>
       </c>
       <c r="D34" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2660,7 +3307,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2680,16 +3327,16 @@
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="B35" t="s">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="C35">
-        <v>0.9754772186279297</v>
+        <v>0.967378795146942</v>
       </c>
       <c r="D35" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2704,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2719,21 +3366,21 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>85</v>
       </c>
       <c r="C36">
-        <v>0.9673787951469421</v>
+        <v>0.767745614051819</v>
       </c>
       <c r="D36" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2748,13 +3395,13 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -2768,16 +3415,16 @@
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="C37">
-        <v>0.7677456140518188</v>
+        <v>0.894055366516113</v>
       </c>
       <c r="D37" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2792,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2807,21 +3454,21 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B38" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="C38">
-        <v>0.8940553665161133</v>
+        <v>0.99658191204071</v>
       </c>
       <c r="D38" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2836,13 +3483,13 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38">
         <v>1</v>
@@ -2856,16 +3503,16 @@
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>91</v>
       </c>
       <c r="C39">
-        <v>0.9965819120407104</v>
+        <v>0.998970866203308</v>
       </c>
       <c r="D39" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2880,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2900,16 +3547,16 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B40" t="s">
-        <v>183</v>
+        <v>93</v>
       </c>
       <c r="C40">
-        <v>0.9989708662033081</v>
+        <v>0.999165236949921</v>
       </c>
       <c r="D40" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2924,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2944,16 +3591,16 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="B41" t="s">
-        <v>184</v>
+        <v>95</v>
       </c>
       <c r="C41">
-        <v>0.9991652369499207</v>
+        <v>0.999000132083893</v>
       </c>
       <c r="D41" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2968,7 +3615,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2977,10 +3624,10 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -2988,16 +3635,16 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>185</v>
+        <v>97</v>
       </c>
       <c r="C42">
-        <v>0.9990001320838928</v>
+        <v>0.999042212963104</v>
       </c>
       <c r="D42" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3012,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3024,24 +3671,24 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="B43" t="s">
-        <v>186</v>
+        <v>99</v>
       </c>
       <c r="C43">
-        <v>0.9990422129631042</v>
+        <v>0.996248424053192</v>
       </c>
       <c r="D43" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3056,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3068,24 +3715,24 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="B44" t="s">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="C44">
-        <v>0.9962484240531921</v>
+        <v>0.995609939098358</v>
       </c>
       <c r="D44" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3100,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3112,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -3120,16 +3767,16 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="B45" t="s">
-        <v>188</v>
+        <v>103</v>
       </c>
       <c r="C45">
-        <v>0.9956099390983582</v>
+        <v>0.999369502067566</v>
       </c>
       <c r="D45" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3144,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3156,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -3164,16 +3811,16 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="C46">
-        <v>0.9993695020675659</v>
+        <v>0.999027788639069</v>
       </c>
       <c r="D46" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3188,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3208,16 +3855,16 @@
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="B47" t="s">
-        <v>190</v>
+        <v>107</v>
       </c>
       <c r="C47">
-        <v>0.9990277886390686</v>
+        <v>0.999590218067169</v>
       </c>
       <c r="D47" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3232,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3252,16 +3899,16 @@
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="B48" t="s">
-        <v>191</v>
+        <v>109</v>
       </c>
       <c r="C48">
-        <v>0.9995902180671692</v>
+        <v>0.999411702156067</v>
       </c>
       <c r="D48" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3276,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3291,21 +3938,21 @@
         <v>1</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="B49" t="s">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="C49">
-        <v>0.9994117021560669</v>
+        <v>0.999428272247314</v>
       </c>
       <c r="D49" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3320,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3340,16 +3987,16 @@
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="B50" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="C50">
-        <v>0.9994282722473145</v>
+        <v>0.999479353427887</v>
       </c>
       <c r="D50" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3364,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3379,21 +4026,21 @@
         <v>1</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="B51" t="s">
-        <v>194</v>
+        <v>115</v>
       </c>
       <c r="C51">
-        <v>0.999479353427887</v>
+        <v>0.998457193374634</v>
       </c>
       <c r="D51" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3408,7 +4055,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3423,21 +4070,21 @@
         <v>1</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="B52" t="s">
-        <v>195</v>
+        <v>117</v>
       </c>
       <c r="C52">
-        <v>0.9984571933746338</v>
+        <v>0.99813187122345</v>
       </c>
       <c r="D52" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3452,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3467,21 +4114,21 @@
         <v>1</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="B53" t="s">
-        <v>196</v>
+        <v>119</v>
       </c>
       <c r="C53">
-        <v>0.9981318712234497</v>
+        <v>0.999025285243988</v>
       </c>
       <c r="D53" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3496,7 +4143,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3508,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -3516,16 +4163,16 @@
     </row>
     <row r="54" spans="1:14">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="B54" t="s">
-        <v>197</v>
+        <v>121</v>
       </c>
       <c r="C54">
-        <v>0.999025285243988</v>
+        <v>0.933538019657135</v>
       </c>
       <c r="D54" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3540,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3552,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="M54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N54">
         <v>1</v>
@@ -3560,16 +4207,16 @@
     </row>
     <row r="55" spans="1:14">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>122</v>
       </c>
       <c r="B55" t="s">
-        <v>198</v>
+        <v>123</v>
       </c>
       <c r="C55">
-        <v>0.933538019657135</v>
+        <v>0.998995363712311</v>
       </c>
       <c r="D55" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3584,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3596,24 +4243,24 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c r="B56" t="s">
-        <v>199</v>
+        <v>125</v>
       </c>
       <c r="C56">
-        <v>0.9989953637123108</v>
+        <v>0.998640179634094</v>
       </c>
       <c r="D56" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3628,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3640,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56">
         <v>2</v>
@@ -3648,16 +4295,16 @@
     </row>
     <row r="57" spans="1:14">
       <c r="A57" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="B57" t="s">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="C57">
-        <v>0.9986401796340942</v>
+        <v>0.999037563800812</v>
       </c>
       <c r="D57" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3672,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -3684,7 +4331,7 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N57">
         <v>2</v>
@@ -3692,16 +4339,16 @@
     </row>
     <row r="58" spans="1:14">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>128</v>
       </c>
       <c r="B58" t="s">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="C58">
-        <v>0.9990375638008118</v>
+        <v>0.878909468650818</v>
       </c>
       <c r="D58" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3716,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -3728,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N58">
         <v>2</v>
@@ -3736,16 +4383,16 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="B59" t="s">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="C59">
-        <v>0.8789094686508179</v>
+        <v>0.998813688755035</v>
       </c>
       <c r="D59" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3760,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3772,24 +4419,24 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N59">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="B60" t="s">
-        <v>203</v>
+        <v>133</v>
       </c>
       <c r="C60">
-        <v>0.9988136887550354</v>
+        <v>0.990991115570068</v>
       </c>
       <c r="D60" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3804,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3819,21 +4466,21 @@
         <v>1</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="B61" t="s">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="C61">
-        <v>0.9909911155700684</v>
+        <v>0.998318433761597</v>
       </c>
       <c r="D61" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3848,7 +4495,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -3860,7 +4507,7 @@
         <v>0</v>
       </c>
       <c r="M61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -3868,16 +4515,16 @@
     </row>
     <row r="62" spans="1:14">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>136</v>
       </c>
       <c r="B62" t="s">
-        <v>205</v>
+        <v>137</v>
       </c>
       <c r="C62">
-        <v>0.9983184337615967</v>
+        <v>0.999444603919983</v>
       </c>
       <c r="D62" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3892,7 +4539,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -3907,21 +4554,21 @@
         <v>2</v>
       </c>
       <c r="N62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="B63" t="s">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="C63">
-        <v>0.9994446039199829</v>
+        <v>0.999382138252258</v>
       </c>
       <c r="D63" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3936,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -3948,24 +4595,24 @@
         <v>0</v>
       </c>
       <c r="M63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>141</v>
       </c>
       <c r="C64">
-        <v>0.9993821382522583</v>
+        <v>0.997601628303528</v>
       </c>
       <c r="D64" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3980,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -3995,21 +4642,21 @@
         <v>1</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="C65">
-        <v>0.9976016283035278</v>
+        <v>0.999007225036621</v>
       </c>
       <c r="D65" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4024,7 +4671,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4044,16 +4691,16 @@
     </row>
     <row r="66" spans="1:14">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
-        <v>209</v>
+        <v>145</v>
       </c>
       <c r="C66">
-        <v>0.9990072250366211</v>
+        <v>0.999165773391724</v>
       </c>
       <c r="D66" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4068,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4080,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -4088,16 +4735,16 @@
     </row>
     <row r="67" spans="1:14">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="B67" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="C67">
-        <v>0.9991657733917236</v>
+        <v>0.997841477394104</v>
       </c>
       <c r="D67" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4112,7 +4759,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4124,7 +4771,7 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N67">
         <v>1</v>
@@ -4132,16 +4779,16 @@
     </row>
     <row r="68" spans="1:14">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>148</v>
       </c>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
       <c r="C68">
-        <v>0.997841477394104</v>
+        <v>0.997644543647766</v>
       </c>
       <c r="D68" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4156,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4168,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N68">
         <v>1</v>
@@ -4176,16 +4823,16 @@
     </row>
     <row r="69" spans="1:14">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>150</v>
       </c>
       <c r="B69" t="s">
-        <v>212</v>
+        <v>151</v>
       </c>
       <c r="C69">
-        <v>0.9976445436477661</v>
+        <v>0.998023271560669</v>
       </c>
       <c r="D69" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4200,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4212,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N69">
         <v>1</v>
@@ -4220,16 +4867,16 @@
     </row>
     <row r="70" spans="1:14">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="B70" t="s">
-        <v>213</v>
+        <v>153</v>
       </c>
       <c r="C70">
-        <v>0.9980232715606689</v>
+        <v>0.999061822891235</v>
       </c>
       <c r="D70" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4244,7 +4891,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4264,16 +4911,16 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71" t="s">
-        <v>83</v>
+        <v>154</v>
       </c>
       <c r="B71" t="s">
-        <v>214</v>
+        <v>155</v>
       </c>
       <c r="C71">
-        <v>0.9990618228912354</v>
+        <v>0.999475955963135</v>
       </c>
       <c r="D71" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4288,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4300,24 +4947,24 @@
         <v>0</v>
       </c>
       <c r="M71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
       <c r="B72" t="s">
-        <v>215</v>
+        <v>157</v>
       </c>
       <c r="C72">
-        <v>0.9994759559631348</v>
+        <v>0.999207198619843</v>
       </c>
       <c r="D72" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4332,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4344,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N72">
         <v>0</v>
@@ -4352,16 +4999,16 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73" t="s">
-        <v>85</v>
+        <v>158</v>
       </c>
       <c r="B73" t="s">
-        <v>216</v>
+        <v>159</v>
       </c>
       <c r="C73">
-        <v>0.9992071986198425</v>
+        <v>0.998555243015289</v>
       </c>
       <c r="D73" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4376,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4396,16 +5043,16 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="B74" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="C74">
-        <v>0.9985552430152893</v>
+        <v>0.997600972652435</v>
       </c>
       <c r="D74" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4420,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4435,21 +5082,21 @@
         <v>2</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="B75" t="s">
-        <v>218</v>
+        <v>163</v>
       </c>
       <c r="C75">
-        <v>0.9976009726524353</v>
+        <v>0.988409817218781</v>
       </c>
       <c r="D75" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4464,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4479,21 +5126,21 @@
         <v>2</v>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="B76" t="s">
-        <v>219</v>
+        <v>165</v>
       </c>
       <c r="C76">
-        <v>0.9884098172187805</v>
+        <v>0.783249199390411</v>
       </c>
       <c r="D76" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4508,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4528,16 +5175,16 @@
     </row>
     <row r="77" spans="1:14">
       <c r="A77" t="s">
-        <v>89</v>
+        <v>166</v>
       </c>
       <c r="B77" t="s">
-        <v>220</v>
+        <v>167</v>
       </c>
       <c r="C77">
-        <v>0.7832491993904114</v>
+        <v>0.995502591133118</v>
       </c>
       <c r="D77" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4552,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4564,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="M77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N77">
         <v>1</v>
@@ -4572,16 +5219,16 @@
     </row>
     <row r="78" spans="1:14">
       <c r="A78" t="s">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="C78">
-        <v>0.9955025911331177</v>
+        <v>0.999555587768555</v>
       </c>
       <c r="D78" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4596,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4608,24 +5255,24 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" t="s">
-        <v>91</v>
+        <v>170</v>
       </c>
       <c r="B79" t="s">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="C79">
-        <v>0.9995555877685547</v>
+        <v>0.997513651847839</v>
       </c>
       <c r="D79" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -4640,7 +5287,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4652,7 +5299,7 @@
         <v>0</v>
       </c>
       <c r="M79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N79">
         <v>0</v>
@@ -4660,16 +5307,16 @@
     </row>
     <row r="80" spans="1:14">
       <c r="A80" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="B80" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="C80">
-        <v>0.9975136518478394</v>
+        <v>0.997211933135986</v>
       </c>
       <c r="D80" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -4684,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4699,21 +5346,21 @@
         <v>1</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" t="s">
-        <v>93</v>
+        <v>174</v>
       </c>
       <c r="B81" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="C81">
-        <v>0.9972119331359863</v>
+        <v>0.997017204761505</v>
       </c>
       <c r="D81" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -4728,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4748,16 +5395,16 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="B82" t="s">
-        <v>225</v>
+        <v>177</v>
       </c>
       <c r="C82">
-        <v>0.9970172047615051</v>
+        <v>0.997714638710022</v>
       </c>
       <c r="D82" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -4772,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -4792,16 +5439,16 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="B83" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
       <c r="C83">
-        <v>0.997714638710022</v>
+        <v>0.931635975837708</v>
       </c>
       <c r="D83" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4816,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -4836,16 +5483,16 @@
     </row>
     <row r="84" spans="1:14">
       <c r="A84" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="B84" t="s">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="C84">
-        <v>0.9316359758377075</v>
+        <v>0.998109936714172</v>
       </c>
       <c r="D84" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -4860,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -4875,21 +5522,21 @@
         <v>1</v>
       </c>
       <c r="N84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" t="s">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="B85" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="C85">
-        <v>0.9981099367141724</v>
+        <v>0.996095597743988</v>
       </c>
       <c r="D85" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4904,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -4919,21 +5566,21 @@
         <v>1</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" t="s">
-        <v>98</v>
+        <v>184</v>
       </c>
       <c r="B86" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="C86">
-        <v>0.996095597743988</v>
+        <v>0.988156080245972</v>
       </c>
       <c r="D86" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4948,7 +5595,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -4963,21 +5610,21 @@
         <v>1</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="B87" t="s">
-        <v>230</v>
+        <v>187</v>
       </c>
       <c r="C87">
-        <v>0.9881560802459717</v>
+        <v>0.999386966228485</v>
       </c>
       <c r="D87" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -4992,7 +5639,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5007,21 +5654,21 @@
         <v>1</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" t="s">
-        <v>100</v>
+        <v>188</v>
       </c>
       <c r="B88" t="s">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="C88">
-        <v>0.9993869662284851</v>
+        <v>0.987630426883698</v>
       </c>
       <c r="D88" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5036,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5056,16 +5703,16 @@
     </row>
     <row r="89" spans="1:14">
       <c r="A89" t="s">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="B89" t="s">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="C89">
-        <v>0.9876304268836975</v>
+        <v>0.991525113582611</v>
       </c>
       <c r="D89" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5080,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5100,16 +5747,16 @@
     </row>
     <row r="90" spans="1:14">
       <c r="A90" t="s">
-        <v>102</v>
+        <v>192</v>
       </c>
       <c r="B90" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="C90">
-        <v>0.9915251135826111</v>
+        <v>0.999343514442444</v>
       </c>
       <c r="D90" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5124,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5144,16 +5791,16 @@
     </row>
     <row r="91" spans="1:14">
       <c r="A91" t="s">
-        <v>103</v>
+        <v>194</v>
       </c>
       <c r="B91" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="C91">
-        <v>0.9993435144424438</v>
+        <v>0.995674848556519</v>
       </c>
       <c r="D91" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5168,7 +5815,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5188,16 +5835,16 @@
     </row>
     <row r="92" spans="1:14">
       <c r="A92" t="s">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="B92" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="C92">
-        <v>0.9956748485565186</v>
+        <v>0.99158376455307</v>
       </c>
       <c r="D92" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5212,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5227,21 +5874,21 @@
         <v>1</v>
       </c>
       <c r="N92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" t="s">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="B93" t="s">
-        <v>236</v>
+        <v>199</v>
       </c>
       <c r="C93">
-        <v>0.9915837645530701</v>
+        <v>0.999206960201263</v>
       </c>
       <c r="D93" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5256,7 +5903,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5276,16 +5923,16 @@
     </row>
     <row r="94" spans="1:14">
       <c r="A94" t="s">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="B94" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="C94">
-        <v>0.9992069602012634</v>
+        <v>0.996482312679291</v>
       </c>
       <c r="D94" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5300,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5315,21 +5962,21 @@
         <v>1</v>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" t="s">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="B95" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="C95">
-        <v>0.9964823126792908</v>
+        <v>0.999147474765778</v>
       </c>
       <c r="D95" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5344,7 +5991,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5364,16 +6011,16 @@
     </row>
     <row r="96" spans="1:14">
       <c r="A96" t="s">
-        <v>108</v>
+        <v>204</v>
       </c>
       <c r="B96" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="C96">
-        <v>0.9991474747657776</v>
+        <v>0.997924625873566</v>
       </c>
       <c r="D96" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5388,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5408,16 +6055,16 @@
     </row>
     <row r="97" spans="1:14">
       <c r="A97" t="s">
-        <v>109</v>
+        <v>206</v>
       </c>
       <c r="B97" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="C97">
-        <v>0.9979246258735657</v>
+        <v>0.999502658843994</v>
       </c>
       <c r="D97" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -5432,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -5447,21 +6094,21 @@
         <v>1</v>
       </c>
       <c r="N97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" t="s">
-        <v>110</v>
+        <v>208</v>
       </c>
       <c r="B98" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="C98">
-        <v>0.9995026588439941</v>
+        <v>0.991998195648193</v>
       </c>
       <c r="D98" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -5476,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -5496,16 +6143,16 @@
     </row>
     <row r="99" spans="1:14">
       <c r="A99" t="s">
-        <v>111</v>
+        <v>210</v>
       </c>
       <c r="B99" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="C99">
-        <v>0.9919981956481934</v>
+        <v>0.852929890155792</v>
       </c>
       <c r="D99" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -5520,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -5540,16 +6187,16 @@
     </row>
     <row r="100" spans="1:14">
       <c r="A100" t="s">
-        <v>112</v>
+        <v>212</v>
       </c>
       <c r="B100" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="C100">
-        <v>0.8529298901557922</v>
+        <v>0.992677450180054</v>
       </c>
       <c r="D100" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -5564,7 +6211,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -5579,21 +6226,21 @@
         <v>1</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>214</v>
       </c>
       <c r="B101" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="C101">
-        <v>0.9926774501800537</v>
+        <v>0.998254776000977</v>
       </c>
       <c r="D101" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -5608,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -5623,21 +6270,21 @@
         <v>1</v>
       </c>
       <c r="N101">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" t="s">
-        <v>114</v>
+        <v>216</v>
       </c>
       <c r="B102" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="C102">
-        <v>0.9982547760009766</v>
+        <v>0.991929352283478</v>
       </c>
       <c r="D102" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -5652,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -5672,16 +6319,16 @@
     </row>
     <row r="103" spans="1:14">
       <c r="A103" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="C103">
-        <v>0.9919293522834778</v>
+        <v>0.997851133346558</v>
       </c>
       <c r="D103" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -5696,36 +6343,36 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M103">
         <v>1</v>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" t="s">
-        <v>116</v>
+        <v>220</v>
       </c>
       <c r="B104" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="C104">
-        <v>0.9978511333465576</v>
+        <v>0.999393105506897</v>
       </c>
       <c r="D104" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -5740,36 +6387,36 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104">
         <v>1</v>
       </c>
       <c r="N104">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:14">
       <c r="A105" t="s">
-        <v>117</v>
+        <v>222</v>
       </c>
       <c r="B105" t="s">
-        <v>248</v>
+        <v>223</v>
       </c>
       <c r="C105">
-        <v>0.999393105506897</v>
+        <v>0.998141467571259</v>
       </c>
       <c r="D105" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -5784,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -5804,16 +6451,16 @@
     </row>
     <row r="106" spans="1:14">
       <c r="A106" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="B106" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C106">
-        <v>0.9981414675712585</v>
+        <v>0.995561420917511</v>
       </c>
       <c r="D106" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -5828,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -5848,16 +6495,16 @@
     </row>
     <row r="107" spans="1:14">
       <c r="A107" t="s">
-        <v>119</v>
+        <v>226</v>
       </c>
       <c r="B107" t="s">
-        <v>250</v>
+        <v>227</v>
       </c>
       <c r="C107">
-        <v>0.995561420917511</v>
+        <v>0.99856036901474</v>
       </c>
       <c r="D107" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -5872,7 +6519,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -5884,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="M107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N107">
         <v>1</v>
@@ -5892,16 +6539,16 @@
     </row>
     <row r="108" spans="1:14">
       <c r="A108" t="s">
-        <v>120</v>
+        <v>228</v>
       </c>
       <c r="B108" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="C108">
-        <v>0.99856036901474</v>
+        <v>0.997949182987213</v>
       </c>
       <c r="D108" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -5916,7 +6563,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -5928,7 +6575,7 @@
         <v>0</v>
       </c>
       <c r="M108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -5936,16 +6583,16 @@
     </row>
     <row r="109" spans="1:14">
       <c r="A109" t="s">
-        <v>121</v>
+        <v>230</v>
       </c>
       <c r="B109" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="C109">
-        <v>0.9979491829872131</v>
+        <v>0.998924255371094</v>
       </c>
       <c r="D109" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -5960,36 +6607,36 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N109">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:14">
       <c r="A110" t="s">
-        <v>122</v>
+        <v>232</v>
       </c>
       <c r="B110" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="C110">
-        <v>0.9989242553710938</v>
+        <v>0.998701870441437</v>
       </c>
       <c r="D110" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6004,36 +6651,36 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110">
         <v>2</v>
       </c>
       <c r="N110">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:14">
       <c r="A111" t="s">
-        <v>123</v>
+        <v>234</v>
       </c>
       <c r="B111" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="C111">
-        <v>0.9987018704414368</v>
+        <v>0.998030126094818</v>
       </c>
       <c r="D111" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6048,7 +6695,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6063,21 +6710,21 @@
         <v>2</v>
       </c>
       <c r="N111">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:14">
       <c r="A112" t="s">
-        <v>124</v>
+        <v>236</v>
       </c>
       <c r="B112" t="s">
-        <v>255</v>
+        <v>237</v>
       </c>
       <c r="C112">
-        <v>0.9980301260948181</v>
+        <v>0.998890995979309</v>
       </c>
       <c r="D112" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6092,7 +6739,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -6107,21 +6754,21 @@
         <v>2</v>
       </c>
       <c r="N112">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:14">
       <c r="A113" t="s">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="B113" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="C113">
-        <v>0.9988909959793091</v>
+        <v>0.996140420436859</v>
       </c>
       <c r="D113" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6136,7 +6783,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6151,21 +6798,21 @@
         <v>2</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:14">
       <c r="A114" t="s">
-        <v>126</v>
+        <v>240</v>
       </c>
       <c r="B114" t="s">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="C114">
-        <v>0.9961404204368591</v>
+        <v>0.995870113372803</v>
       </c>
       <c r="D114" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6180,7 +6827,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -6192,24 +6839,24 @@
         <v>0</v>
       </c>
       <c r="M114">
+        <v>1</v>
+      </c>
+      <c r="N114">
         <v>2</v>
-      </c>
-      <c r="N114">
-        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:14">
       <c r="A115" t="s">
-        <v>127</v>
+        <v>242</v>
       </c>
       <c r="B115" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C115">
-        <v>0.9958701133728027</v>
+        <v>0.998413622379303</v>
       </c>
       <c r="D115" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6224,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6239,21 +6886,21 @@
         <v>1</v>
       </c>
       <c r="N115">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:14">
       <c r="A116" t="s">
-        <v>128</v>
+        <v>244</v>
       </c>
       <c r="B116" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="C116">
-        <v>0.998413622379303</v>
+        <v>0.999260723590851</v>
       </c>
       <c r="D116" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6268,7 +6915,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6280,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N116">
         <v>1</v>
@@ -6288,16 +6935,16 @@
     </row>
     <row r="117" spans="1:14">
       <c r="A117" t="s">
-        <v>129</v>
+        <v>246</v>
       </c>
       <c r="B117" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="C117">
-        <v>0.9992607235908508</v>
+        <v>0.996174931526184</v>
       </c>
       <c r="D117" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6312,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -6324,24 +6971,24 @@
         <v>0</v>
       </c>
       <c r="M117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N117">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:14">
       <c r="A118" t="s">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="B118" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="C118">
-        <v>0.9961749315261841</v>
+        <v>0.99935907125473</v>
       </c>
       <c r="D118" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -6356,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -6368,24 +7015,24 @@
         <v>0</v>
       </c>
       <c r="M118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:14">
       <c r="A119" t="s">
-        <v>131</v>
+        <v>250</v>
       </c>
       <c r="B119" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C119">
-        <v>0.9993590712547302</v>
+        <v>0.998755872249603</v>
       </c>
       <c r="D119" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -6400,7 +7047,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6412,24 +7059,24 @@
         <v>0</v>
       </c>
       <c r="M119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:14">
       <c r="A120" t="s">
-        <v>132</v>
+        <v>252</v>
       </c>
       <c r="B120" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C120">
-        <v>0.9987558722496033</v>
+        <v>0.99920916557312</v>
       </c>
       <c r="D120" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6444,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6456,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N120">
         <v>0</v>
@@ -6464,16 +7111,16 @@
     </row>
     <row r="121" spans="1:14">
       <c r="A121" t="s">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="B121" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C121">
-        <v>0.9992091655731201</v>
+        <v>0.962244868278503</v>
       </c>
       <c r="D121" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -6488,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6503,21 +7150,21 @@
         <v>2</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:14">
       <c r="A122" t="s">
-        <v>134</v>
+        <v>256</v>
       </c>
       <c r="B122" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="C122">
-        <v>0.9622448682785034</v>
+        <v>0.994516432285309</v>
       </c>
       <c r="D122" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -6532,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -6544,24 +7191,24 @@
         <v>0</v>
       </c>
       <c r="M122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N122">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:14">
       <c r="A123" t="s">
-        <v>135</v>
+        <v>258</v>
       </c>
       <c r="B123" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C123">
-        <v>0.9945164322853088</v>
+        <v>0.995938241481781</v>
       </c>
       <c r="D123" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -6576,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -6588,24 +7235,24 @@
         <v>0</v>
       </c>
       <c r="M123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:14">
       <c r="A124" t="s">
-        <v>136</v>
+        <v>260</v>
       </c>
       <c r="B124" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C124">
-        <v>0.995938241481781</v>
+        <v>0.998788058757782</v>
       </c>
       <c r="D124" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -6620,7 +7267,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -6632,24 +7279,24 @@
         <v>0</v>
       </c>
       <c r="M124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N124">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:14">
       <c r="A125" t="s">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="B125" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C125">
-        <v>0.998788058757782</v>
+        <v>0.98718935251236</v>
       </c>
       <c r="D125" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -6664,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -6676,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N125">
         <v>1</v>
@@ -6684,16 +7331,16 @@
     </row>
     <row r="126" spans="1:14">
       <c r="A126" t="s">
-        <v>138</v>
+        <v>264</v>
       </c>
       <c r="B126" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C126">
-        <v>0.9871893525123596</v>
+        <v>0.999046087265015</v>
       </c>
       <c r="D126" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -6708,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -6720,24 +7367,24 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N126">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:14">
       <c r="A127" t="s">
-        <v>139</v>
+        <v>266</v>
       </c>
       <c r="B127" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C127">
-        <v>0.9990460872650146</v>
+        <v>0.978120744228363</v>
       </c>
       <c r="D127" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -6752,7 +7399,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -6772,16 +7419,16 @@
     </row>
     <row r="128" spans="1:14">
       <c r="A128" t="s">
-        <v>140</v>
+        <v>268</v>
       </c>
       <c r="B128" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C128">
-        <v>0.978120744228363</v>
+        <v>0.993702113628387</v>
       </c>
       <c r="D128" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -6796,10 +7443,10 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128">
         <v>0</v>
@@ -6808,24 +7455,24 @@
         <v>0</v>
       </c>
       <c r="M128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:14">
       <c r="A129" t="s">
-        <v>141</v>
+        <v>270</v>
       </c>
       <c r="B129" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C129">
-        <v>0.9937021136283875</v>
+        <v>0.998434066772461</v>
       </c>
       <c r="D129" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -6840,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -6852,24 +7499,24 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:14">
       <c r="A130" t="s">
-        <v>142</v>
+        <v>272</v>
       </c>
       <c r="B130" t="s">
         <v>273</v>
       </c>
       <c r="C130">
-        <v>0.9984340667724609</v>
+        <v>0.996797204017639</v>
       </c>
       <c r="D130" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -6884,10 +7531,10 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130">
         <v>0</v>
@@ -6896,24 +7543,24 @@
         <v>0</v>
       </c>
       <c r="M130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N130">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:14">
       <c r="A131" t="s">
-        <v>143</v>
+        <v>274</v>
       </c>
       <c r="B131" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C131">
-        <v>0.9967972040176392</v>
+        <v>0.997380673885345</v>
       </c>
       <c r="D131" t="s">
-        <v>276</v>
+        <v>16</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -6928,10 +7575,10 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>277</v>
+        <v>17</v>
       </c>
       <c r="J131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -6940,57 +7587,14 @@
         <v>0</v>
       </c>
       <c r="M131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:14">
-      <c r="A132" t="s">
-        <v>144</v>
-      </c>
-      <c r="B132" t="s">
-        <v>275</v>
-      </c>
-      <c r="C132">
-        <v>0.9973806738853455</v>
-      </c>
-      <c r="D132" t="s">
-        <v>276</v>
-      </c>
-      <c r="E132">
-        <v>0</v>
-      </c>
-      <c r="F132" t="b">
-        <v>0</v>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132" t="s">
-        <v>277</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
-        <v>1</v>
-      </c>
-      <c r="N132">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="279">
   <si>
     <t>filename</t>
   </si>
@@ -67,9 +67,6 @@
     <t>micro_0234_XJOO.jpg</t>
   </si>
   <si>
-    <t>micro_0004_XDII.jpg</t>
-  </si>
-  <si>
     <t>micro_0031_1700X400.jpg</t>
   </si>
   <si>
@@ -127,10 +124,10 @@
     <t>micro_0109_SL40III.jpg</t>
   </si>
   <si>
-    <t>micro_0296_SL4082600.jpg</t>
-  </si>
-  <si>
-    <t>micro_0291_SL407.jpg</t>
+    <t>micro_0293_SL4082600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0296_SL407.jpg</t>
   </si>
   <si>
     <t>micro_0112_SL406.jpg</t>
@@ -238,6 +235,9 @@
     <t>micro_0117_D501.jpg</t>
   </si>
   <si>
+    <t>micro_0209_D501.jpg</t>
+  </si>
+  <si>
     <t>micro_0034_D432.jpg</t>
   </si>
   <si>
@@ -298,7 +298,7 @@
     <t>micro_0263_D406.jpg</t>
   </si>
   <si>
-    <t>micro_0134_D405.jpg</t>
+    <t>micro_0296_D405.jpg</t>
   </si>
   <si>
     <t>micro_0261_D404.jpg</t>
@@ -310,7 +310,7 @@
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
-    <t>micro_0290_D401.jpg</t>
+    <t>micro_0131_D401.jpg</t>
   </si>
   <si>
     <t>micro_0255_D250.jpg</t>
@@ -331,6 +331,9 @@
     <t>micro_0073_D242.jpg</t>
   </si>
   <si>
+    <t>micro_0015_OOD240.jpg</t>
+  </si>
+  <si>
     <t>micro_0090_OD240.jpg</t>
   </si>
   <si>
@@ -358,6 +361,9 @@
     <t>micro_0249_OD232.jpg</t>
   </si>
   <si>
+    <t>micro_0205_0D232.jpg</t>
+  </si>
+  <si>
     <t>micro_0182_D231.jpg</t>
   </si>
   <si>
@@ -458,9 +464,6 @@
   </si>
   <si>
     <t>XJ</t>
-  </si>
-  <si>
-    <t>XDⅡ2</t>
   </si>
   <si>
     <t>X40Ⅲ</t>
@@ -1179,7 +1182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N132"/>
+  <dimension ref="A1:N134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1231,13 +1234,13 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C2">
         <v>0.922767162322998</v>
       </c>
       <c r="D2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1252,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1275,13 +1278,13 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C3">
         <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1296,7 +1299,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1319,13 +1322,13 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C4">
         <v>0.9089775085449219</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1340,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1363,13 +1366,13 @@
         <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C5">
-        <v>0.7567664980888367</v>
+        <v>0.9360489845275879</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1384,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -1399,7 +1402,7 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1407,13 +1410,13 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C6">
-        <v>0.9360489845275879</v>
+        <v>0.9898043870925903</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1428,7 +1431,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1443,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1451,13 +1454,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C7">
-        <v>0.9898043870925903</v>
+        <v>0.9800205826759338</v>
       </c>
       <c r="D7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1472,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1495,13 +1498,13 @@
         <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C8">
-        <v>0.9800205826759338</v>
+        <v>0.9866096377372742</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1516,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1531,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1539,13 +1542,13 @@
         <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C9">
-        <v>0.9866096377372742</v>
+        <v>0.9825887680053711</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1560,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1575,7 +1578,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1583,13 +1586,13 @@
         <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C10">
-        <v>0.9825887680053711</v>
+        <v>0.9854358434677124</v>
       </c>
       <c r="D10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1604,7 +1607,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1619,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1627,13 +1630,13 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C11">
-        <v>0.9854358434677124</v>
+        <v>0.9869511127471924</v>
       </c>
       <c r="D11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1648,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1671,13 +1674,13 @@
         <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C12">
-        <v>0.9869511127471924</v>
+        <v>0.9883586168289185</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1692,7 +1695,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1707,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1715,13 +1718,13 @@
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C13">
-        <v>0.9883586168289185</v>
+        <v>0.9827210903167725</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1736,13 +1739,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -1759,13 +1762,13 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C14">
-        <v>0.9827210903167725</v>
+        <v>0.9891344904899597</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1780,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1795,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1803,13 +1806,13 @@
         <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C15">
-        <v>0.9891344904899597</v>
+        <v>0.9849019646644592</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1824,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1847,13 +1850,13 @@
         <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C16">
-        <v>0.9849019646644592</v>
+        <v>0.9831116795539856</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1868,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1883,7 +1886,7 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1891,13 +1894,13 @@
         <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C17">
-        <v>0.9831116795539856</v>
+        <v>0.979184627532959</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1912,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1927,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1935,13 +1938,13 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C18">
-        <v>0.979184627532959</v>
+        <v>0.9820773601531982</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1956,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1979,13 +1982,13 @@
         <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C19">
-        <v>0.9820773601531982</v>
+        <v>0.9926210641860962</v>
       </c>
       <c r="D19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2000,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2023,13 +2026,13 @@
         <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C20">
-        <v>0.9926210641860962</v>
+        <v>0.991193413734436</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2044,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2067,13 +2070,13 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C21">
-        <v>0.991193413734436</v>
+        <v>0.9759405851364136</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2088,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2111,13 +2114,13 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C22">
-        <v>0.9759405851364136</v>
+        <v>0.9936316609382629</v>
       </c>
       <c r="D22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2132,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2155,13 +2158,13 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C23">
-        <v>0.9936316609382629</v>
+        <v>0.9834394454956055</v>
       </c>
       <c r="D23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2176,22 +2179,22 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23">
         <v>0</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2199,13 +2202,13 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C24">
-        <v>0.9834394454956055</v>
+        <v>0.9938239455223083</v>
       </c>
       <c r="D24" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2220,22 +2223,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24">
         <v>0</v>
       </c>
       <c r="N24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -2243,13 +2246,13 @@
         <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C25">
-        <v>0.9938239455223083</v>
+        <v>0.9959491491317749</v>
       </c>
       <c r="D25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2264,16 +2267,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -2287,13 +2290,13 @@
         <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C26">
-        <v>0.9971064329147339</v>
+        <v>0.9976895451545715</v>
       </c>
       <c r="D26" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2308,16 +2311,16 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -2331,13 +2334,13 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C27">
-        <v>0.9976895451545715</v>
+        <v>0.9959992170333862</v>
       </c>
       <c r="D27" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2352,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2375,13 +2378,13 @@
         <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C28">
-        <v>0.9959992170333862</v>
+        <v>0.9971073865890503</v>
       </c>
       <c r="D28" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2396,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2419,13 +2422,13 @@
         <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C29">
-        <v>0.9971073865890503</v>
+        <v>0.9968833923339844</v>
       </c>
       <c r="D29" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2440,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2455,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2463,13 +2466,13 @@
         <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C30">
-        <v>0.9968833923339844</v>
+        <v>0.9585862159729004</v>
       </c>
       <c r="D30" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2484,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2499,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2507,13 +2510,13 @@
         <v>43</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C31">
-        <v>0.9585862159729004</v>
+        <v>0.9984833598136902</v>
       </c>
       <c r="D31" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2528,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2543,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -2551,13 +2554,13 @@
         <v>44</v>
       </c>
       <c r="B32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C32">
-        <v>0.9984833598136902</v>
+        <v>0.9960424304008484</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2572,22 +2575,22 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J32">
         <v>1</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32">
         <v>1</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2595,13 +2598,13 @@
         <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C33">
-        <v>0.9960424304008484</v>
+        <v>0.9988101124763489</v>
       </c>
       <c r="D33" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2616,22 +2619,22 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J33">
         <v>1</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33">
         <v>1</v>
       </c>
       <c r="M33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -2639,13 +2642,13 @@
         <v>46</v>
       </c>
       <c r="B34" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C34">
-        <v>0.9988101124763489</v>
+        <v>0.9754772186279297</v>
       </c>
       <c r="D34" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2660,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2683,13 +2686,13 @@
         <v>47</v>
       </c>
       <c r="B35" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C35">
-        <v>0.9754772186279297</v>
+        <v>0.9673787951469421</v>
       </c>
       <c r="D35" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2704,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2719,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -2727,13 +2730,13 @@
         <v>48</v>
       </c>
       <c r="B36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C36">
-        <v>0.9673787951469421</v>
+        <v>0.7677456140518188</v>
       </c>
       <c r="D36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2748,13 +2751,13 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -2771,13 +2774,13 @@
         <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C37">
-        <v>0.7677456140518188</v>
+        <v>0.8940553665161133</v>
       </c>
       <c r="D37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2792,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2807,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2815,13 +2818,13 @@
         <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C38">
-        <v>0.8940553665161133</v>
+        <v>0.9965819120407104</v>
       </c>
       <c r="D38" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2836,13 +2839,13 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38">
         <v>1</v>
@@ -2859,13 +2862,13 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C39">
-        <v>0.9965819120407104</v>
+        <v>0.9989708662033081</v>
       </c>
       <c r="D39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2880,7 +2883,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2903,13 +2906,13 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C40">
-        <v>0.9989708662033081</v>
+        <v>0.9991652369499207</v>
       </c>
       <c r="D40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2924,7 +2927,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2947,13 +2950,13 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C41">
-        <v>0.9991652369499207</v>
+        <v>0.9991592764854431</v>
       </c>
       <c r="D41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2968,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2977,10 +2980,10 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -2991,13 +2994,13 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C42">
-        <v>0.9990001320838928</v>
+        <v>0.9991186261177063</v>
       </c>
       <c r="D42" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3012,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3024,10 +3027,10 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -3035,13 +3038,13 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C43">
-        <v>0.9990422129631042</v>
+        <v>0.9952852725982666</v>
       </c>
       <c r="D43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3056,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3068,10 +3071,10 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -3079,13 +3082,13 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C44">
-        <v>0.9962484240531921</v>
+        <v>0.9953067898750305</v>
       </c>
       <c r="D44" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3100,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3112,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -3123,13 +3126,13 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C45">
-        <v>0.9956099390983582</v>
+        <v>0.9992667436599731</v>
       </c>
       <c r="D45" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3144,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3156,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -3167,13 +3170,13 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C46">
-        <v>0.9993695020675659</v>
+        <v>0.9991705417633057</v>
       </c>
       <c r="D46" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3188,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3211,13 +3214,13 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C47">
-        <v>0.9990277886390686</v>
+        <v>0.999667763710022</v>
       </c>
       <c r="D47" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3232,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3255,13 +3258,13 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C48">
-        <v>0.9995902180671692</v>
+        <v>0.9995352625846863</v>
       </c>
       <c r="D48" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3276,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3291,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="N48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -3299,13 +3302,13 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C49">
-        <v>0.9994117021560669</v>
+        <v>0.9993976354598999</v>
       </c>
       <c r="D49" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3320,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3343,13 +3346,13 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C50">
-        <v>0.9994282722473145</v>
+        <v>0.9994799494743347</v>
       </c>
       <c r="D50" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3364,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3379,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -3387,13 +3390,13 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C51">
-        <v>0.999479353427887</v>
+        <v>0.9982963800430298</v>
       </c>
       <c r="D51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3408,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3423,7 +3426,7 @@
         <v>1</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -3431,13 +3434,13 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C52">
-        <v>0.9984571933746338</v>
+        <v>0.998166561126709</v>
       </c>
       <c r="D52" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3452,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3475,13 +3478,13 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C53">
-        <v>0.9981318712234497</v>
+        <v>0.9988658428192139</v>
       </c>
       <c r="D53" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3496,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3508,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N53">
         <v>1</v>
@@ -3519,13 +3522,13 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C54">
-        <v>0.999025285243988</v>
+        <v>0.9980804920196533</v>
       </c>
       <c r="D54" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3540,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3552,10 +3555,10 @@
         <v>0</v>
       </c>
       <c r="M54">
+        <v>1</v>
+      </c>
+      <c r="N54">
         <v>2</v>
-      </c>
-      <c r="N54">
-        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -3563,13 +3566,13 @@
         <v>67</v>
       </c>
       <c r="B55" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C55">
-        <v>0.933538019657135</v>
+        <v>0.9991114735603333</v>
       </c>
       <c r="D55" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3584,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3596,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55">
         <v>1</v>
@@ -3607,13 +3610,13 @@
         <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C56">
-        <v>0.9989953637123108</v>
+        <v>0.9987078905105591</v>
       </c>
       <c r="D56" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3628,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3640,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56">
         <v>2</v>
@@ -3651,13 +3654,13 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C57">
-        <v>0.9986401796340942</v>
+        <v>0.9991089701652527</v>
       </c>
       <c r="D57" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3672,7 +3675,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -3684,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N57">
         <v>2</v>
@@ -3695,13 +3698,13 @@
         <v>70</v>
       </c>
       <c r="B58" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C58">
-        <v>0.9990375638008118</v>
+        <v>0.9810042381286621</v>
       </c>
       <c r="D58" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3716,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -3728,10 +3731,10 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N58">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -3739,13 +3742,13 @@
         <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C59">
-        <v>0.8789094686508179</v>
+        <v>0.9990440607070923</v>
       </c>
       <c r="D59" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3760,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3772,10 +3775,10 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N59">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -3783,13 +3786,13 @@
         <v>72</v>
       </c>
       <c r="B60" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C60">
-        <v>0.9988136887550354</v>
+        <v>0.9949619770050049</v>
       </c>
       <c r="D60" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3804,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3819,7 +3822,7 @@
         <v>1</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -3827,13 +3830,13 @@
         <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C61">
-        <v>0.9909911155700684</v>
+        <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3848,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -3871,13 +3874,13 @@
         <v>74</v>
       </c>
       <c r="B62" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C62">
-        <v>0.9983184337615967</v>
+        <v>0.9984354376792908</v>
       </c>
       <c r="D62" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3892,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -3915,13 +3918,13 @@
         <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C63">
-        <v>0.9994446039199829</v>
+        <v>0.9993854761123657</v>
       </c>
       <c r="D63" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3936,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -3951,7 +3954,7 @@
         <v>2</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -3959,13 +3962,13 @@
         <v>76</v>
       </c>
       <c r="B64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C64">
-        <v>0.9993821382522583</v>
+        <v>0.9993329048156738</v>
       </c>
       <c r="D64" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3980,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4003,13 +4006,13 @@
         <v>77</v>
       </c>
       <c r="B65" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C65">
-        <v>0.9976016283035278</v>
+        <v>0.9969677925109863</v>
       </c>
       <c r="D65" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4024,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4047,13 +4050,13 @@
         <v>78</v>
       </c>
       <c r="B66" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C66">
-        <v>0.9990072250366211</v>
+        <v>0.9995519518852234</v>
       </c>
       <c r="D66" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4068,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4091,13 +4094,13 @@
         <v>79</v>
       </c>
       <c r="B67" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C67">
-        <v>0.9991657733917236</v>
+        <v>0.9992239475250244</v>
       </c>
       <c r="D67" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4112,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4135,13 +4138,13 @@
         <v>80</v>
       </c>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C68">
-        <v>0.997841477394104</v>
+        <v>0.9972553253173828</v>
       </c>
       <c r="D68" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4156,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4179,13 +4182,13 @@
         <v>81</v>
       </c>
       <c r="B69" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C69">
-        <v>0.9976445436477661</v>
+        <v>0.9980692267417908</v>
       </c>
       <c r="D69" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4200,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4223,13 +4226,13 @@
         <v>82</v>
       </c>
       <c r="B70" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C70">
-        <v>0.9980232715606689</v>
+        <v>0.9959254264831543</v>
       </c>
       <c r="D70" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4244,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4267,13 +4270,13 @@
         <v>83</v>
       </c>
       <c r="B71" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C71">
-        <v>0.9990618228912354</v>
+        <v>0.9990965127944946</v>
       </c>
       <c r="D71" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4288,7 +4291,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4311,13 +4314,13 @@
         <v>84</v>
       </c>
       <c r="B72" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C72">
-        <v>0.9994759559631348</v>
+        <v>0.9995350241661072</v>
       </c>
       <c r="D72" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4332,7 +4335,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4355,13 +4358,13 @@
         <v>85</v>
       </c>
       <c r="B73" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C73">
-        <v>0.9992071986198425</v>
+        <v>0.9991962909698486</v>
       </c>
       <c r="D73" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4376,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4399,13 +4402,13 @@
         <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C74">
-        <v>0.9985552430152893</v>
+        <v>0.9979453086853027</v>
       </c>
       <c r="D74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4420,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4443,13 +4446,13 @@
         <v>87</v>
       </c>
       <c r="B75" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C75">
-        <v>0.9976009726524353</v>
+        <v>0.9969654083251953</v>
       </c>
       <c r="D75" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4464,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4479,7 +4482,7 @@
         <v>2</v>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -4487,13 +4490,13 @@
         <v>88</v>
       </c>
       <c r="B76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C76">
-        <v>0.9884098172187805</v>
+        <v>0.9930816888809204</v>
       </c>
       <c r="D76" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4508,7 +4511,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4531,13 +4534,13 @@
         <v>89</v>
       </c>
       <c r="B77" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C77">
-        <v>0.7832491993904114</v>
+        <v>0.8460029363632202</v>
       </c>
       <c r="D77" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4552,7 +4555,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4575,13 +4578,13 @@
         <v>90</v>
       </c>
       <c r="B78" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C78">
-        <v>0.9955025911331177</v>
+        <v>0.9959526658058167</v>
       </c>
       <c r="D78" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4596,7 +4599,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4611,7 +4614,7 @@
         <v>3</v>
       </c>
       <c r="N78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -4619,13 +4622,13 @@
         <v>91</v>
       </c>
       <c r="B79" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C79">
-        <v>0.9995555877685547</v>
+        <v>0.9994586706161499</v>
       </c>
       <c r="D79" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -4640,7 +4643,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4663,13 +4666,13 @@
         <v>92</v>
       </c>
       <c r="B80" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C80">
-        <v>0.9975136518478394</v>
+        <v>0.996728241443634</v>
       </c>
       <c r="D80" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -4684,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4707,13 +4710,13 @@
         <v>93</v>
       </c>
       <c r="B81" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C81">
-        <v>0.9972119331359863</v>
+        <v>0.9973512291908264</v>
       </c>
       <c r="D81" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -4728,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4751,13 +4754,13 @@
         <v>94</v>
       </c>
       <c r="B82" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C82">
-        <v>0.9970172047615051</v>
+        <v>0.9980469942092896</v>
       </c>
       <c r="D82" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -4772,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -4784,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="M82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -4795,13 +4798,13 @@
         <v>95</v>
       </c>
       <c r="B83" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C83">
-        <v>0.997714638710022</v>
+        <v>0.9978298544883728</v>
       </c>
       <c r="D83" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4816,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -4831,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="N83">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -4839,13 +4842,13 @@
         <v>96</v>
       </c>
       <c r="B84" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C84">
-        <v>0.9316359758377075</v>
+        <v>0.8626171350479126</v>
       </c>
       <c r="D84" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -4860,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -4883,13 +4886,13 @@
         <v>97</v>
       </c>
       <c r="B85" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C85">
-        <v>0.9981099367141724</v>
+        <v>0.9972398281097412</v>
       </c>
       <c r="D85" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4904,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -4927,13 +4930,13 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C86">
-        <v>0.996095597743988</v>
+        <v>0.9969408512115479</v>
       </c>
       <c r="D86" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4948,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -4971,13 +4974,13 @@
         <v>99</v>
       </c>
       <c r="B87" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C87">
-        <v>0.9881560802459717</v>
+        <v>0.9915247559547424</v>
       </c>
       <c r="D87" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -4992,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5004,10 +5007,10 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -5015,13 +5018,13 @@
         <v>100</v>
       </c>
       <c r="B88" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C88">
-        <v>0.9993869662284851</v>
+        <v>0.9995598793029785</v>
       </c>
       <c r="D88" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5036,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5059,13 +5062,13 @@
         <v>101</v>
       </c>
       <c r="B89" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C89">
-        <v>0.9876304268836975</v>
+        <v>0.8945754766464233</v>
       </c>
       <c r="D89" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5080,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5103,13 +5106,13 @@
         <v>102</v>
       </c>
       <c r="B90" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C90">
-        <v>0.9915251135826111</v>
+        <v>0.9960287809371948</v>
       </c>
       <c r="D90" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5124,7 +5127,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5147,13 +5150,13 @@
         <v>103</v>
       </c>
       <c r="B91" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C91">
-        <v>0.9993435144424438</v>
+        <v>0.9991824626922607</v>
       </c>
       <c r="D91" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5168,7 +5171,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5191,13 +5194,13 @@
         <v>104</v>
       </c>
       <c r="B92" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C92">
         <v>0.9956748485565186</v>
       </c>
       <c r="D92" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5212,7 +5215,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5235,13 +5238,13 @@
         <v>105</v>
       </c>
       <c r="B93" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C93">
-        <v>0.9915837645530701</v>
+        <v>0.9787474274635315</v>
       </c>
       <c r="D93" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5256,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5282,10 +5285,10 @@
         <v>237</v>
       </c>
       <c r="C94">
-        <v>0.9992069602012634</v>
+        <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5300,7 +5303,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5326,10 +5329,10 @@
         <v>238</v>
       </c>
       <c r="C95">
-        <v>0.9964823126792908</v>
+        <v>0.9993278980255127</v>
       </c>
       <c r="D95" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5344,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5359,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="N95">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -5370,10 +5373,10 @@
         <v>239</v>
       </c>
       <c r="C96">
-        <v>0.9991474747657776</v>
+        <v>0.9933540225028992</v>
       </c>
       <c r="D96" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5388,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5414,10 +5417,10 @@
         <v>240</v>
       </c>
       <c r="C97">
-        <v>0.9979246258735657</v>
+        <v>0.9988803863525391</v>
       </c>
       <c r="D97" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -5432,7 +5435,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -5458,10 +5461,10 @@
         <v>241</v>
       </c>
       <c r="C98">
-        <v>0.9995026588439941</v>
+        <v>0.9901755452156067</v>
       </c>
       <c r="D98" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -5476,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -5491,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -5502,10 +5505,10 @@
         <v>242</v>
       </c>
       <c r="C99">
-        <v>0.9919981956481934</v>
+        <v>0.999345064163208</v>
       </c>
       <c r="D99" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -5520,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -5546,10 +5549,10 @@
         <v>243</v>
       </c>
       <c r="C100">
-        <v>0.8529298901557922</v>
+        <v>0.9616943597793579</v>
       </c>
       <c r="D100" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -5564,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -5590,10 +5593,10 @@
         <v>244</v>
       </c>
       <c r="C101">
-        <v>0.9926774501800537</v>
+        <v>0.8529298901557922</v>
       </c>
       <c r="D101" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -5608,7 +5611,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -5623,7 +5626,7 @@
         <v>1</v>
       </c>
       <c r="N101">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -5634,10 +5637,10 @@
         <v>245</v>
       </c>
       <c r="C102">
-        <v>0.9982547760009766</v>
+        <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -5652,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -5664,10 +5667,10 @@
         <v>0</v>
       </c>
       <c r="M102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -5675,13 +5678,13 @@
         <v>115</v>
       </c>
       <c r="B103" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C103">
-        <v>0.9919293522834778</v>
+        <v>0.9913250803947449</v>
       </c>
       <c r="D103" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -5696,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -5708,10 +5711,10 @@
         <v>0</v>
       </c>
       <c r="M103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -5719,13 +5722,13 @@
         <v>116</v>
       </c>
       <c r="B104" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C104">
-        <v>0.9978511333465576</v>
+        <v>0.9982128739356995</v>
       </c>
       <c r="D104" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -5740,22 +5743,22 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104">
         <v>1</v>
       </c>
       <c r="N104">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -5763,13 +5766,13 @@
         <v>117</v>
       </c>
       <c r="B105" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C105">
-        <v>0.999393105506897</v>
+        <v>0.9876354336738586</v>
       </c>
       <c r="D105" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -5784,7 +5787,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -5796,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -5807,13 +5810,13 @@
         <v>118</v>
       </c>
       <c r="B106" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C106">
-        <v>0.9981414675712585</v>
+        <v>0.9978511333465576</v>
       </c>
       <c r="D106" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -5828,22 +5831,22 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106">
         <v>1</v>
       </c>
       <c r="N106">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -5851,13 +5854,13 @@
         <v>119</v>
       </c>
       <c r="B107" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C107">
-        <v>0.995561420917511</v>
+        <v>0.9994751811027527</v>
       </c>
       <c r="D107" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -5872,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -5887,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="N107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -5895,13 +5898,13 @@
         <v>120</v>
       </c>
       <c r="B108" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C108">
-        <v>0.99856036901474</v>
+        <v>0.9982790946960449</v>
       </c>
       <c r="D108" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -5916,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -5928,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="M108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -5939,13 +5942,13 @@
         <v>121</v>
       </c>
       <c r="B109" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C109">
-        <v>0.9979491829872131</v>
+        <v>0.9931647777557373</v>
       </c>
       <c r="D109" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -5960,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -5983,13 +5986,13 @@
         <v>122</v>
       </c>
       <c r="B110" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C110">
-        <v>0.9989242553710938</v>
+        <v>0.9983500242233276</v>
       </c>
       <c r="D110" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6004,22 +6007,22 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110">
         <v>2</v>
       </c>
       <c r="N110">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -6027,13 +6030,13 @@
         <v>123</v>
       </c>
       <c r="B111" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C111">
-        <v>0.9987018704414368</v>
+        <v>0.9937362670898438</v>
       </c>
       <c r="D111" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6048,7 +6051,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6060,10 +6063,10 @@
         <v>0</v>
       </c>
       <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
         <v>2</v>
-      </c>
-      <c r="N111">
-        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -6071,13 +6074,13 @@
         <v>124</v>
       </c>
       <c r="B112" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C112">
-        <v>0.9980301260948181</v>
+        <v>0.9989242553710938</v>
       </c>
       <c r="D112" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6092,16 +6095,16 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112">
         <v>2</v>
@@ -6115,13 +6118,13 @@
         <v>125</v>
       </c>
       <c r="B113" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C113">
-        <v>0.9988909959793091</v>
+        <v>0.9987581372261047</v>
       </c>
       <c r="D113" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6136,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6151,7 +6154,7 @@
         <v>2</v>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -6159,13 +6162,13 @@
         <v>126</v>
       </c>
       <c r="B114" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C114">
-        <v>0.9961404204368591</v>
+        <v>0.9983271360397339</v>
       </c>
       <c r="D114" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6180,22 +6183,22 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114">
         <v>2</v>
       </c>
       <c r="N114">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -6203,13 +6206,13 @@
         <v>127</v>
       </c>
       <c r="B115" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C115">
-        <v>0.9958701133728027</v>
+        <v>0.9987975358963013</v>
       </c>
       <c r="D115" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6224,7 +6227,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6236,10 +6239,10 @@
         <v>0</v>
       </c>
       <c r="M115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N115">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -6247,13 +6250,13 @@
         <v>128</v>
       </c>
       <c r="B116" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C116">
-        <v>0.998413622379303</v>
+        <v>0.9942725300788879</v>
       </c>
       <c r="D116" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6268,7 +6271,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6280,10 +6283,10 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N116">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -6291,13 +6294,13 @@
         <v>129</v>
       </c>
       <c r="B117" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C117">
-        <v>0.9992607235908508</v>
+        <v>0.9970023632049561</v>
       </c>
       <c r="D117" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6312,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -6324,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="M117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -6335,13 +6338,13 @@
         <v>130</v>
       </c>
       <c r="B118" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C118">
-        <v>0.9961749315261841</v>
+        <v>0.9984022974967957</v>
       </c>
       <c r="D118" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -6356,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -6371,7 +6374,7 @@
         <v>1</v>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -6379,13 +6382,13 @@
         <v>131</v>
       </c>
       <c r="B119" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C119">
-        <v>0.9993590712547302</v>
+        <v>0.999241828918457</v>
       </c>
       <c r="D119" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -6400,7 +6403,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6423,13 +6426,13 @@
         <v>132</v>
       </c>
       <c r="B120" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C120">
-        <v>0.9987558722496033</v>
+        <v>0.9961878061294556</v>
       </c>
       <c r="D120" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6444,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6467,13 +6470,13 @@
         <v>133</v>
       </c>
       <c r="B121" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C121">
-        <v>0.9992091655731201</v>
+        <v>0.9993798732757568</v>
       </c>
       <c r="D121" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -6488,7 +6491,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6503,7 +6506,7 @@
         <v>2</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -6511,13 +6514,13 @@
         <v>134</v>
       </c>
       <c r="B122" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C122">
-        <v>0.9622448682785034</v>
+        <v>0.9990472793579102</v>
       </c>
       <c r="D122" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -6532,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -6544,10 +6547,10 @@
         <v>0</v>
       </c>
       <c r="M122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N122">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -6555,13 +6558,13 @@
         <v>135</v>
       </c>
       <c r="B123" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C123">
-        <v>0.9945164322853088</v>
+        <v>0.9991445541381836</v>
       </c>
       <c r="D123" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -6576,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -6588,7 +6591,7 @@
         <v>0</v>
       </c>
       <c r="M123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N123">
         <v>0</v>
@@ -6599,13 +6602,13 @@
         <v>136</v>
       </c>
       <c r="B124" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C124">
-        <v>0.995938241481781</v>
+        <v>0.9142532348632812</v>
       </c>
       <c r="D124" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -6620,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -6643,13 +6646,13 @@
         <v>137</v>
       </c>
       <c r="B125" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C125">
-        <v>0.998788058757782</v>
+        <v>0.9972384572029114</v>
       </c>
       <c r="D125" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -6664,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -6679,7 +6682,7 @@
         <v>1</v>
       </c>
       <c r="N125">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -6687,13 +6690,13 @@
         <v>138</v>
       </c>
       <c r="B126" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C126">
-        <v>0.9871893525123596</v>
+        <v>0.9960039258003235</v>
       </c>
       <c r="D126" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -6708,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -6723,7 +6726,7 @@
         <v>2</v>
       </c>
       <c r="N126">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -6731,13 +6734,13 @@
         <v>139</v>
       </c>
       <c r="B127" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C127">
-        <v>0.9990460872650146</v>
+        <v>0.9987621903419495</v>
       </c>
       <c r="D127" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -6752,7 +6755,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -6767,7 +6770,7 @@
         <v>1</v>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -6775,13 +6778,13 @@
         <v>140</v>
       </c>
       <c r="B128" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C128">
-        <v>0.978120744228363</v>
+        <v>0.9937299489974976</v>
       </c>
       <c r="D128" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -6796,7 +6799,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -6808,10 +6811,10 @@
         <v>0</v>
       </c>
       <c r="M128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -6819,13 +6822,13 @@
         <v>141</v>
       </c>
       <c r="B129" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C129">
-        <v>0.9937021136283875</v>
+        <v>0.9990777969360352</v>
       </c>
       <c r="D129" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -6840,10 +6843,10 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -6852,10 +6855,10 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -6863,13 +6866,13 @@
         <v>142</v>
       </c>
       <c r="B130" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C130">
-        <v>0.9984340667724609</v>
+        <v>0.9922806620597839</v>
       </c>
       <c r="D130" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -6884,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -6896,10 +6899,10 @@
         <v>0</v>
       </c>
       <c r="M130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N130">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -6907,13 +6910,13 @@
         <v>143</v>
       </c>
       <c r="B131" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C131">
-        <v>0.9967972040176392</v>
+        <v>0.9937021136283875</v>
       </c>
       <c r="D131" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -6928,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J131">
         <v>1</v>
@@ -6943,7 +6946,7 @@
         <v>0</v>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -6951,42 +6954,130 @@
         <v>144</v>
       </c>
       <c r="B132" t="s">
+        <v>274</v>
+      </c>
+      <c r="C132">
+        <v>0.9984290599822998</v>
+      </c>
+      <c r="D132" t="s">
+        <v>277</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+      <c r="F132" t="b">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132" t="s">
+        <v>278</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>2</v>
+      </c>
+      <c r="N132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14">
+      <c r="A133" t="s">
+        <v>145</v>
+      </c>
+      <c r="B133" t="s">
         <v>275</v>
       </c>
-      <c r="C132">
-        <v>0.9973806738853455</v>
-      </c>
-      <c r="D132" t="s">
+      <c r="C133">
+        <v>0.9967972040176392</v>
+      </c>
+      <c r="D133" t="s">
+        <v>277</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133" t="b">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133" t="s">
+        <v>278</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14">
+      <c r="A134" t="s">
+        <v>146</v>
+      </c>
+      <c r="B134" t="s">
         <v>276</v>
       </c>
-      <c r="E132">
-        <v>0</v>
-      </c>
-      <c r="F132" t="b">
-        <v>0</v>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132" t="s">
-        <v>277</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132">
-        <v>1</v>
-      </c>
-      <c r="N132">
+      <c r="C134">
+        <v>0.8547114133834839</v>
+      </c>
+      <c r="D134" t="s">
+        <v>277</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134" t="s">
+        <v>278</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>1</v>
+      </c>
+      <c r="N134">
         <v>0</v>
       </c>
     </row>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="281">
   <si>
     <t>filename</t>
   </si>
@@ -58,6 +58,12 @@
     <t>white_centers</t>
   </si>
   <si>
+    <t>is_tri</t>
+  </si>
+  <si>
+    <t>is_double</t>
+  </si>
+  <si>
     <t>micro_0192_YSB_II.jpg</t>
   </si>
   <si>
@@ -124,10 +130,10 @@
     <t>micro_0109_SL40III.jpg</t>
   </si>
   <si>
-    <t>micro_0293_SL4082600.jpg</t>
-  </si>
-  <si>
-    <t>micro_0296_SL407.jpg</t>
+    <t>micro_0296_SL4082600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0294_SL407.jpg</t>
   </si>
   <si>
     <t>micro_0112_SL406.jpg</t>
@@ -298,7 +304,7 @@
     <t>micro_0263_D406.jpg</t>
   </si>
   <si>
-    <t>micro_0296_D405.jpg</t>
+    <t>micro_0134_D405.jpg</t>
   </si>
   <si>
     <t>micro_0261_D404.jpg</t>
@@ -310,7 +316,7 @@
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
-    <t>micro_0131_D401.jpg</t>
+    <t>micro_0290_D401.jpg</t>
   </si>
   <si>
     <t>micro_0255_D250.jpg</t>
@@ -331,12 +337,12 @@
     <t>micro_0073_D242.jpg</t>
   </si>
   <si>
+    <t>micro_0090_OD240.jpg</t>
+  </si>
+  <si>
     <t>micro_0015_OOD240.jpg</t>
   </si>
   <si>
-    <t>micro_0090_OD240.jpg</t>
-  </si>
-  <si>
     <t>micro_0148_D2392000.jpg</t>
   </si>
   <si>
@@ -358,10 +364,10 @@
     <t>micro_0210_D233.jpg</t>
   </si>
   <si>
+    <t>micro_0205_0D232.jpg</t>
+  </si>
+  <si>
     <t>micro_0249_OD232.jpg</t>
-  </si>
-  <si>
-    <t>micro_0205_0D232.jpg</t>
   </si>
   <si>
     <t>micro_0182_D231.jpg</t>
@@ -1182,10 +1188,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N134"/>
+  <dimension ref="A1:P134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1228,19 +1234,25 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C2">
         <v>0.922767162322998</v>
       </c>
       <c r="D2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1255,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1272,19 +1284,25 @@
       <c r="N2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C3">
         <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1299,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1316,19 +1334,25 @@
       <c r="N3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C4">
-        <v>0.9089775085449219</v>
+        <v>0.9991193413734436</v>
       </c>
       <c r="D4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1343,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1360,19 +1384,25 @@
       <c r="N4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C5">
         <v>0.9360489845275879</v>
       </c>
       <c r="D5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1387,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1404,19 +1434,25 @@
       <c r="N5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C6">
         <v>0.9898043870925903</v>
       </c>
       <c r="D6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1431,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1448,19 +1484,25 @@
       <c r="N6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C7">
         <v>0.9800205826759338</v>
       </c>
       <c r="D7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1475,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1492,19 +1534,25 @@
       <c r="N7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C8">
         <v>0.9866096377372742</v>
       </c>
       <c r="D8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1519,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1536,19 +1584,25 @@
       <c r="N8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C9">
         <v>0.9825887680053711</v>
       </c>
       <c r="D9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1563,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1580,19 +1634,25 @@
       <c r="N9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C10">
         <v>0.9854358434677124</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1607,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1624,19 +1684,25 @@
       <c r="N10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C11">
         <v>0.9869511127471924</v>
       </c>
       <c r="D11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1651,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1668,19 +1734,25 @@
       <c r="N11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C12">
         <v>0.9883586168289185</v>
       </c>
       <c r="D12" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1695,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1712,19 +1784,25 @@
       <c r="N12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C13">
         <v>0.9827210903167725</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1739,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1756,19 +1834,25 @@
       <c r="N13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C14">
-        <v>0.9891344904899597</v>
+        <v>0.8711124062538147</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1783,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1800,19 +1884,25 @@
       <c r="N14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C15">
         <v>0.9849019646644592</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1827,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1844,19 +1934,25 @@
       <c r="N15">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C16">
         <v>0.9831116795539856</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1871,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1888,19 +1984,25 @@
       <c r="N16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C17">
         <v>0.979184627532959</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1915,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -1932,19 +2034,25 @@
       <c r="N17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C18">
         <v>0.9820773601531982</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1959,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -1976,19 +2084,25 @@
       <c r="N18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C19">
         <v>0.9926210641860962</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2003,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2020,19 +2134,25 @@
       <c r="N19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C20">
         <v>0.991193413734436</v>
       </c>
       <c r="D20" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2047,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2064,19 +2184,25 @@
       <c r="N20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C21">
         <v>0.9759405851364136</v>
       </c>
       <c r="D21" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2091,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2108,19 +2234,25 @@
       <c r="N21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C22">
         <v>0.9936316609382629</v>
       </c>
       <c r="D22" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2135,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2152,19 +2284,25 @@
       <c r="N22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23">
         <v>0.9834394454956055</v>
       </c>
       <c r="D23" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2179,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2196,19 +2334,25 @@
       <c r="N23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24">
         <v>0.9938239455223083</v>
       </c>
       <c r="D24" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2223,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2240,19 +2384,25 @@
       <c r="N24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C25">
-        <v>0.9959491491317749</v>
+        <v>0.9971064329147339</v>
       </c>
       <c r="D25" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2267,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2284,19 +2434,25 @@
       <c r="N25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C26">
         <v>0.9976895451545715</v>
       </c>
       <c r="D26" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2311,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2328,19 +2484,25 @@
       <c r="N26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C27">
         <v>0.9959992170333862</v>
       </c>
       <c r="D27" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2355,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2372,19 +2534,25 @@
       <c r="N27">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C28">
         <v>0.9971073865890503</v>
       </c>
       <c r="D28" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2399,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2416,19 +2584,25 @@
       <c r="N28">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C29">
         <v>0.9968833923339844</v>
       </c>
       <c r="D29" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2443,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2460,19 +2634,25 @@
       <c r="N29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C30">
         <v>0.9585862159729004</v>
       </c>
       <c r="D30" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2487,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2504,19 +2684,25 @@
       <c r="N30">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C31">
         <v>0.9984833598136902</v>
       </c>
       <c r="D31" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2531,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2548,19 +2734,25 @@
       <c r="N31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C32">
         <v>0.9960424304008484</v>
       </c>
       <c r="D32" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2575,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2592,19 +2784,25 @@
       <c r="N32">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C33">
         <v>0.9988101124763489</v>
       </c>
       <c r="D33" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2619,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2636,19 +2834,25 @@
       <c r="N33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C34">
         <v>0.9754772186279297</v>
       </c>
       <c r="D34" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2663,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2680,19 +2884,25 @@
       <c r="N34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C35">
         <v>0.9673787951469421</v>
       </c>
       <c r="D35" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2707,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2724,19 +2934,25 @@
       <c r="N35">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C36">
         <v>0.7677456140518188</v>
       </c>
       <c r="D36" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2751,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2768,19 +2984,25 @@
       <c r="N36">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C37">
         <v>0.8940553665161133</v>
       </c>
       <c r="D37" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2795,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2812,19 +3034,25 @@
       <c r="N37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C38">
         <v>0.9965819120407104</v>
       </c>
       <c r="D38" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2839,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2856,19 +3084,25 @@
       <c r="N38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C39">
         <v>0.9989708662033081</v>
       </c>
       <c r="D39" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2883,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2900,19 +3134,25 @@
       <c r="N39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C40">
         <v>0.9991652369499207</v>
       </c>
       <c r="D40" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2927,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2944,19 +3184,25 @@
       <c r="N40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C41">
         <v>0.9991592764854431</v>
       </c>
       <c r="D41" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2971,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2988,19 +3234,25 @@
       <c r="N41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C42">
         <v>0.9991186261177063</v>
       </c>
       <c r="D42" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3015,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3032,19 +3284,25 @@
       <c r="N42">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C43">
         <v>0.9952852725982666</v>
       </c>
       <c r="D43" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3059,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3076,19 +3334,25 @@
       <c r="N43">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C44">
         <v>0.9953067898750305</v>
       </c>
       <c r="D44" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3103,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3120,19 +3384,25 @@
       <c r="N44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:14">
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C45">
         <v>0.9992667436599731</v>
       </c>
       <c r="D45" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3147,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3164,19 +3434,25 @@
       <c r="N45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C46">
         <v>0.9991705417633057</v>
       </c>
       <c r="D46" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3191,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3208,19 +3484,25 @@
       <c r="N46">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C47">
         <v>0.999667763710022</v>
       </c>
       <c r="D47" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3235,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3252,19 +3534,25 @@
       <c r="N47">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C48">
         <v>0.9995352625846863</v>
       </c>
       <c r="D48" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3279,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3296,19 +3584,25 @@
       <c r="N48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C49">
         <v>0.9993976354598999</v>
       </c>
       <c r="D49" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3323,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3340,19 +3634,25 @@
       <c r="N49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C50">
         <v>0.9994799494743347</v>
       </c>
       <c r="D50" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3367,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3384,19 +3684,25 @@
       <c r="N50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C51">
         <v>0.9982963800430298</v>
       </c>
       <c r="D51" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3411,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3428,19 +3734,25 @@
       <c r="N51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C52">
         <v>0.998166561126709</v>
       </c>
       <c r="D52" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3455,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3472,19 +3784,25 @@
       <c r="N52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C53">
         <v>0.9988658428192139</v>
       </c>
       <c r="D53" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3499,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3516,19 +3834,25 @@
       <c r="N53">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C54">
         <v>0.9980804920196533</v>
       </c>
       <c r="D54" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3543,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3560,19 +3884,25 @@
       <c r="N54">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C55">
         <v>0.9991114735603333</v>
       </c>
       <c r="D55" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3587,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3604,19 +3934,25 @@
       <c r="N55">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C56">
         <v>0.9987078905105591</v>
       </c>
       <c r="D56" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3631,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3648,19 +3984,25 @@
       <c r="N56">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C57">
         <v>0.9991089701652527</v>
       </c>
       <c r="D57" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3675,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -3692,19 +4034,25 @@
       <c r="N57">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B58" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C58">
         <v>0.9810042381286621</v>
       </c>
       <c r="D58" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3719,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -3736,19 +4084,25 @@
       <c r="N58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:14">
+      <c r="O58">
+        <v>0</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B59" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C59">
         <v>0.9990440607070923</v>
       </c>
       <c r="D59" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3763,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3780,19 +4134,25 @@
       <c r="N59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:14">
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B60" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C60">
         <v>0.9949619770050049</v>
       </c>
       <c r="D60" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3807,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3824,19 +4184,25 @@
       <c r="N60">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:14">
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3851,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -3868,19 +4234,25 @@
       <c r="N61">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:14">
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B62" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C62">
         <v>0.9984354376792908</v>
       </c>
       <c r="D62" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3895,7 +4267,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -3912,19 +4284,25 @@
       <c r="N62">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:14">
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B63" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C63">
         <v>0.9993854761123657</v>
       </c>
       <c r="D63" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3939,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -3956,19 +4334,25 @@
       <c r="N63">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:14">
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C64">
         <v>0.9993329048156738</v>
       </c>
       <c r="D64" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3983,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4000,19 +4384,25 @@
       <c r="N64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:14">
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
       <c r="A65" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B65" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C65">
         <v>0.9969677925109863</v>
       </c>
       <c r="D65" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4027,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4044,19 +4434,25 @@
       <c r="N65">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:14">
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C66">
         <v>0.9995519518852234</v>
       </c>
       <c r="D66" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4071,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4088,19 +4484,25 @@
       <c r="N66">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:14">
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B67" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C67">
         <v>0.9992239475250244</v>
       </c>
       <c r="D67" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4115,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4132,19 +4534,25 @@
       <c r="N67">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:14">
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
       <c r="A68" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B68" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C68">
         <v>0.9972553253173828</v>
       </c>
       <c r="D68" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4159,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4176,19 +4584,25 @@
       <c r="N68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:14">
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
       <c r="A69" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C69">
         <v>0.9980692267417908</v>
       </c>
       <c r="D69" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4203,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4220,19 +4634,25 @@
       <c r="N69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:14">
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
       <c r="A70" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C70">
         <v>0.9959254264831543</v>
       </c>
       <c r="D70" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4247,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4264,19 +4684,25 @@
       <c r="N70">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
       <c r="A71" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C71">
         <v>0.9990965127944946</v>
       </c>
       <c r="D71" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4291,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4308,19 +4734,25 @@
       <c r="N71">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:14">
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
       <c r="A72" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C72">
         <v>0.9995350241661072</v>
       </c>
       <c r="D72" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4335,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4352,19 +4784,25 @@
       <c r="N72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:14">
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
       <c r="A73" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C73">
         <v>0.9991962909698486</v>
       </c>
       <c r="D73" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4379,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4396,19 +4834,25 @@
       <c r="N73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:14">
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
       <c r="A74" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C74">
         <v>0.9979453086853027</v>
       </c>
       <c r="D74" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4423,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4440,19 +4884,25 @@
       <c r="N74">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="1:14">
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
       <c r="A75" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C75">
         <v>0.9969654083251953</v>
       </c>
       <c r="D75" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4467,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4484,19 +4934,25 @@
       <c r="N75">
         <v>3</v>
       </c>
-    </row>
-    <row r="76" spans="1:14">
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
       <c r="A76" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C76">
         <v>0.9930816888809204</v>
       </c>
       <c r="D76" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4511,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4528,19 +4984,25 @@
       <c r="N76">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:14">
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
       <c r="A77" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C77">
         <v>0.8460029363632202</v>
       </c>
       <c r="D77" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -4555,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4572,19 +5034,25 @@
       <c r="N77">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:14">
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
       <c r="A78" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C78">
         <v>0.9959526658058167</v>
       </c>
       <c r="D78" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -4599,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4616,19 +5084,25 @@
       <c r="N78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:14">
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
       <c r="A79" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C79">
         <v>0.9994586706161499</v>
       </c>
       <c r="D79" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -4643,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -4660,19 +5134,25 @@
       <c r="N79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:14">
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
       <c r="A80" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C80">
         <v>0.996728241443634</v>
       </c>
       <c r="D80" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -4687,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4704,19 +5184,25 @@
       <c r="N80">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="1:14">
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
       <c r="A81" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C81">
         <v>0.9973512291908264</v>
       </c>
       <c r="D81" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -4731,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4748,19 +5234,25 @@
       <c r="N81">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:14">
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
       <c r="A82" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C82">
-        <v>0.9980469942092896</v>
+        <v>0.9967225193977356</v>
       </c>
       <c r="D82" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -4775,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -4787,24 +5279,30 @@
         <v>0</v>
       </c>
       <c r="M82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N82">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:14">
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
       <c r="A83" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C83">
         <v>0.9978298544883728</v>
       </c>
       <c r="D83" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -4819,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -4836,19 +5334,25 @@
       <c r="N83">
         <v>2</v>
       </c>
-    </row>
-    <row r="84" spans="1:14">
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
       <c r="A84" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C84">
         <v>0.8626171350479126</v>
       </c>
       <c r="D84" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -4863,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -4880,19 +5384,25 @@
       <c r="N84">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:14">
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
       <c r="A85" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C85">
         <v>0.9972398281097412</v>
       </c>
       <c r="D85" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4907,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -4924,19 +5434,25 @@
       <c r="N85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:14">
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
       <c r="A86" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C86">
-        <v>0.9969408512115479</v>
+        <v>0.9967367053031921</v>
       </c>
       <c r="D86" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4951,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -4968,19 +5484,25 @@
       <c r="N86">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:14">
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
       <c r="A87" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C87">
         <v>0.9915247559547424</v>
       </c>
       <c r="D87" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -4995,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5012,19 +5534,25 @@
       <c r="N87">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:14">
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
       <c r="A88" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C88">
         <v>0.9995598793029785</v>
       </c>
       <c r="D88" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5039,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5056,19 +5584,25 @@
       <c r="N88">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:14">
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
       <c r="A89" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C89">
         <v>0.8945754766464233</v>
       </c>
       <c r="D89" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5083,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5100,19 +5634,25 @@
       <c r="N89">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:14">
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
       <c r="A90" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C90">
         <v>0.9960287809371948</v>
       </c>
       <c r="D90" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5127,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5144,19 +5684,25 @@
       <c r="N90">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:14">
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
       <c r="A91" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C91">
         <v>0.9991824626922607</v>
       </c>
       <c r="D91" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5171,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5188,19 +5734,25 @@
       <c r="N91">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:14">
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
       <c r="A92" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C92">
         <v>0.9956748485565186</v>
       </c>
       <c r="D92" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5215,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5232,63 +5784,75 @@
       <c r="N92">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:14">
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
       <c r="A93" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93" t="s">
+        <v>279</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93" t="b">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93" t="s">
+        <v>280</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="A94" t="s">
+        <v>108</v>
+      </c>
+      <c r="B94" t="s">
+        <v>239</v>
+      </c>
+      <c r="C94">
         <v>0.9787474274635315</v>
       </c>
-      <c r="D93" t="s">
-        <v>277</v>
-      </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93" t="b">
-        <v>0</v>
-      </c>
-      <c r="G93">
-        <v>0</v>
-      </c>
-      <c r="H93">
-        <v>0</v>
-      </c>
-      <c r="I93" t="s">
-        <v>278</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93">
-        <v>0</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>1</v>
-      </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14">
-      <c r="A94" t="s">
-        <v>106</v>
-      </c>
-      <c r="B94" t="s">
-        <v>237</v>
-      </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
       <c r="D94" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5303,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5320,19 +5884,25 @@
       <c r="N94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:14">
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
       <c r="A95" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C95">
         <v>0.9993278980255127</v>
       </c>
       <c r="D95" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5347,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5364,19 +5934,25 @@
       <c r="N95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:14">
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
       <c r="A96" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C96">
         <v>0.9933540225028992</v>
       </c>
       <c r="D96" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5391,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5408,19 +5984,25 @@
       <c r="N96">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:14">
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
       <c r="A97" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C97">
         <v>0.9988803863525391</v>
       </c>
       <c r="D97" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -5435,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -5452,19 +6034,25 @@
       <c r="N97">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:14">
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
       <c r="A98" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C98">
         <v>0.9901755452156067</v>
       </c>
       <c r="D98" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -5479,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -5496,19 +6084,25 @@
       <c r="N98">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:14">
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
       <c r="A99" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C99">
         <v>0.999345064163208</v>
       </c>
       <c r="D99" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -5523,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -5540,19 +6134,25 @@
       <c r="N99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:14">
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
       <c r="A100" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C100">
         <v>0.9616943597793579</v>
       </c>
       <c r="D100" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -5567,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -5584,19 +6184,25 @@
       <c r="N100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:14">
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C101">
         <v>0.8529298901557922</v>
       </c>
       <c r="D101" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -5611,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -5628,19 +6234,25 @@
       <c r="N101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:14">
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
       <c r="A102" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0.9913250803947449</v>
       </c>
       <c r="D102" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -5655,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -5672,19 +6284,25 @@
       <c r="N102">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:14">
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
       <c r="A103" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C103">
-        <v>0.9913250803947449</v>
+        <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -5699,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -5716,19 +6334,25 @@
       <c r="N103">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:14">
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
       <c r="A104" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C104">
         <v>0.9982128739356995</v>
       </c>
       <c r="D104" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -5743,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -5760,19 +6384,25 @@
       <c r="N104">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="1:14">
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
       <c r="A105" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C105">
         <v>0.9876354336738586</v>
       </c>
       <c r="D105" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -5787,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -5804,19 +6434,25 @@
       <c r="N105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:14">
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
       <c r="A106" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C106">
         <v>0.9978511333465576</v>
       </c>
       <c r="D106" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -5831,7 +6467,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J106">
         <v>1</v>
@@ -5848,19 +6484,25 @@
       <c r="N106">
         <v>3</v>
       </c>
-    </row>
-    <row r="107" spans="1:14">
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
       <c r="A107" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C107">
         <v>0.9994751811027527</v>
       </c>
       <c r="D107" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -5875,7 +6517,7 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -5892,19 +6534,25 @@
       <c r="N107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:14">
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
       <c r="A108" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C108">
         <v>0.9982790946960449</v>
       </c>
       <c r="D108" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -5919,7 +6567,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -5936,19 +6584,25 @@
       <c r="N108">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:14">
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
       <c r="A109" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C109">
         <v>0.9931647777557373</v>
       </c>
       <c r="D109" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -5963,7 +6617,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -5980,19 +6634,25 @@
       <c r="N109">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:14">
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
       <c r="A110" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C110">
         <v>0.9983500242233276</v>
       </c>
       <c r="D110" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6007,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6024,19 +6684,25 @@
       <c r="N110">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:14">
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
       <c r="A111" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C111">
         <v>0.9937362670898438</v>
       </c>
       <c r="D111" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6051,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6068,19 +6734,25 @@
       <c r="N111">
         <v>2</v>
       </c>
-    </row>
-    <row r="112" spans="1:14">
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
       <c r="A112" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C112">
         <v>0.9989242553710938</v>
       </c>
       <c r="D112" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6095,7 +6767,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J112">
         <v>1</v>
@@ -6112,19 +6784,25 @@
       <c r="N112">
         <v>2</v>
       </c>
-    </row>
-    <row r="113" spans="1:14">
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
       <c r="A113" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C113">
         <v>0.9987581372261047</v>
       </c>
       <c r="D113" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6139,7 +6817,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J113">
         <v>0</v>
@@ -6156,19 +6834,25 @@
       <c r="N113">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:14">
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
       <c r="A114" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B114" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C114">
         <v>0.9983271360397339</v>
       </c>
       <c r="D114" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6183,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -6200,19 +6884,25 @@
       <c r="N114">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" spans="1:14">
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
       <c r="A115" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C115">
         <v>0.9987975358963013</v>
       </c>
       <c r="D115" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6227,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6244,19 +6934,25 @@
       <c r="N115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:14">
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
       <c r="A116" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B116" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C116">
         <v>0.9942725300788879</v>
       </c>
       <c r="D116" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6271,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6288,19 +6984,25 @@
       <c r="N116">
         <v>2</v>
       </c>
-    </row>
-    <row r="117" spans="1:14">
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
       <c r="A117" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C117">
         <v>0.9970023632049561</v>
       </c>
       <c r="D117" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -6315,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -6332,19 +7034,25 @@
       <c r="N117">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:14">
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
       <c r="A118" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B118" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C118">
         <v>0.9984022974967957</v>
       </c>
       <c r="D118" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -6359,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -6376,19 +7084,25 @@
       <c r="N118">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:14">
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
       <c r="A119" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B119" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C119">
         <v>0.999241828918457</v>
       </c>
       <c r="D119" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -6403,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -6420,19 +7134,25 @@
       <c r="N119">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:14">
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
       <c r="A120" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B120" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C120">
         <v>0.9961878061294556</v>
       </c>
       <c r="D120" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -6447,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6464,19 +7184,25 @@
       <c r="N120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:14">
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
       <c r="A121" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B121" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C121">
         <v>0.9993798732757568</v>
       </c>
       <c r="D121" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -6491,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -6508,19 +7234,25 @@
       <c r="N121">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:14">
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
       <c r="A122" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B122" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C122">
         <v>0.9990472793579102</v>
       </c>
       <c r="D122" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -6535,7 +7267,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -6552,19 +7284,25 @@
       <c r="N122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:14">
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
       <c r="A123" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B123" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C123">
         <v>0.9991445541381836</v>
       </c>
       <c r="D123" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -6579,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -6596,19 +7334,25 @@
       <c r="N123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:14">
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
       <c r="A124" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B124" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C124">
         <v>0.9142532348632812</v>
       </c>
       <c r="D124" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -6623,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -6640,19 +7384,25 @@
       <c r="N124">
         <v>2</v>
       </c>
-    </row>
-    <row r="125" spans="1:14">
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
       <c r="A125" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B125" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C125">
         <v>0.9972384572029114</v>
       </c>
       <c r="D125" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -6667,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -6684,19 +7434,25 @@
       <c r="N125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:14">
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
       <c r="A126" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B126" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C126">
         <v>0.9960039258003235</v>
       </c>
       <c r="D126" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -6711,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -6728,19 +7484,25 @@
       <c r="N126">
         <v>2</v>
       </c>
-    </row>
-    <row r="127" spans="1:14">
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
       <c r="A127" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B127" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C127">
         <v>0.9987621903419495</v>
       </c>
       <c r="D127" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -6755,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -6772,19 +7534,25 @@
       <c r="N127">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:14">
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
       <c r="A128" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B128" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C128">
         <v>0.9937299489974976</v>
       </c>
       <c r="D128" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -6799,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -6816,19 +7584,25 @@
       <c r="N128">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:14">
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
       <c r="A129" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B129" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C129">
         <v>0.9990777969360352</v>
       </c>
       <c r="D129" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -6843,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -6860,19 +7634,25 @@
       <c r="N129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:14">
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
       <c r="A130" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B130" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C130">
         <v>0.9922806620597839</v>
       </c>
       <c r="D130" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -6887,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -6904,19 +7684,25 @@
       <c r="N130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:14">
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
       <c r="A131" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B131" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C131">
         <v>0.9937021136283875</v>
       </c>
       <c r="D131" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -6931,7 +7717,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J131">
         <v>1</v>
@@ -6948,19 +7734,25 @@
       <c r="N131">
         <v>2</v>
       </c>
-    </row>
-    <row r="132" spans="1:14">
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
       <c r="A132" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B132" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C132">
         <v>0.9984290599822998</v>
       </c>
       <c r="D132" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -6975,7 +7767,7 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -6992,19 +7784,25 @@
       <c r="N132">
         <v>2</v>
       </c>
-    </row>
-    <row r="133" spans="1:14">
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
       <c r="A133" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B133" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C133">
         <v>0.9967972040176392</v>
       </c>
       <c r="D133" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7019,36 +7817,42 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
+        <v>280</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134" t="s">
+        <v>148</v>
+      </c>
+      <c r="B134" t="s">
         <v>278</v>
-      </c>
-      <c r="J133">
-        <v>1</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133">
-        <v>0</v>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:14">
-      <c r="A134" t="s">
-        <v>146</v>
-      </c>
-      <c r="B134" t="s">
-        <v>276</v>
       </c>
       <c r="C134">
         <v>0.8547114133834839</v>
       </c>
       <c r="D134" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -7063,7 +7867,7 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J134">
         <v>0</v>
@@ -7078,6 +7882,12 @@
         <v>1</v>
       </c>
       <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
         <v>0</v>
       </c>
     </row>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="282">
   <si>
     <t>filename</t>
   </si>
@@ -133,7 +133,7 @@
     <t>micro_0296_SL4082600.jpg</t>
   </si>
   <si>
-    <t>micro_0294_SL407.jpg</t>
+    <t>micro_0296_SL407.jpg</t>
   </si>
   <si>
     <t>micro_0112_SL406.jpg</t>
@@ -304,7 +304,7 @@
     <t>micro_0263_D406.jpg</t>
   </si>
   <si>
-    <t>micro_0134_D405.jpg</t>
+    <t>micro_0296_D405.jpg</t>
   </si>
   <si>
     <t>micro_0261_D404.jpg</t>
@@ -316,6 +316,9 @@
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
+    <t>micro_0294_D401.jpg</t>
+  </si>
+  <si>
     <t>micro_0290_D401.jpg</t>
   </si>
   <si>
@@ -364,10 +367,10 @@
     <t>micro_0210_D233.jpg</t>
   </si>
   <si>
+    <t>micro_0249_OD232.jpg</t>
+  </si>
+  <si>
     <t>micro_0205_0D232.jpg</t>
-  </si>
-  <si>
-    <t>micro_0249_OD232.jpg</t>
   </si>
   <si>
     <t>micro_0182_D231.jpg</t>
@@ -1188,7 +1191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P134"/>
+  <dimension ref="A1:P135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1246,13 +1249,13 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C2">
         <v>0.922767162322998</v>
       </c>
       <c r="D2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1267,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1296,13 +1299,13 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C3">
         <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1317,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1332,13 +1335,13 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1346,13 +1349,13 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4">
         <v>0.9991193413734436</v>
       </c>
       <c r="D4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1367,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1396,13 +1399,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5">
         <v>0.9360489845275879</v>
       </c>
       <c r="D5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1417,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1446,13 +1449,13 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C6">
         <v>0.9898043870925903</v>
       </c>
       <c r="D6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1467,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1496,13 +1499,13 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C7">
         <v>0.9800205826759338</v>
       </c>
       <c r="D7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1517,7 +1520,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1546,13 +1549,13 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C8">
         <v>0.9866096377372742</v>
       </c>
       <c r="D8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1567,7 +1570,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1596,13 +1599,13 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C9">
         <v>0.9825887680053711</v>
       </c>
       <c r="D9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1617,7 +1620,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1646,13 +1649,13 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C10">
         <v>0.9854358434677124</v>
       </c>
       <c r="D10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1667,7 +1670,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1696,13 +1699,13 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11">
         <v>0.9869511127471924</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1717,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1746,13 +1749,13 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12">
         <v>0.9883586168289185</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1767,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1796,13 +1799,13 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13">
         <v>0.9827210903167725</v>
       </c>
       <c r="D13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1817,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1832,7 +1835,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1846,13 +1849,13 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14">
         <v>0.8711124062538147</v>
       </c>
       <c r="D14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1867,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1896,13 +1899,13 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C15">
         <v>0.9849019646644592</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1917,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1946,13 +1949,13 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C16">
         <v>0.9831116795539856</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1967,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1996,13 +1999,13 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C17">
         <v>0.979184627532959</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2017,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2046,13 +2049,13 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18">
         <v>0.9820773601531982</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2067,7 +2070,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2096,13 +2099,13 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19">
         <v>0.9926210641860962</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2117,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2146,13 +2149,13 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C20">
         <v>0.991193413734436</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2167,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2196,13 +2199,13 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21">
         <v>0.9759405851364136</v>
       </c>
       <c r="D21" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2217,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2246,13 +2249,13 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C22">
         <v>0.9936316609382629</v>
       </c>
       <c r="D22" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2267,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2296,13 +2299,13 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C23">
         <v>0.9834394454956055</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2317,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2346,13 +2349,13 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24">
         <v>0.9938239455223083</v>
       </c>
       <c r="D24" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2367,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2396,13 +2399,13 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25">
-        <v>0.9971064329147339</v>
+        <v>0.9959491491317749</v>
       </c>
       <c r="D25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2417,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2446,13 +2449,13 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26">
         <v>0.9976895451545715</v>
       </c>
       <c r="D26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2467,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2496,13 +2499,13 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C27">
         <v>0.9959992170333862</v>
       </c>
       <c r="D27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2517,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2546,13 +2549,13 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C28">
         <v>0.9971073865890503</v>
       </c>
       <c r="D28" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2567,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2596,13 +2599,13 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C29">
         <v>0.9968833923339844</v>
       </c>
       <c r="D29" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2617,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2646,13 +2649,13 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C30">
         <v>0.9585862159729004</v>
       </c>
       <c r="D30" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2667,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2696,13 +2699,13 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C31">
         <v>0.9984833598136902</v>
       </c>
       <c r="D31" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2717,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2746,13 +2749,13 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C32">
         <v>0.9960424304008484</v>
       </c>
       <c r="D32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2767,7 +2770,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2796,13 +2799,13 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C33">
         <v>0.9988101124763489</v>
       </c>
       <c r="D33" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2817,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2846,13 +2849,13 @@
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C34">
         <v>0.9754772186279297</v>
       </c>
       <c r="D34" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2867,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2896,13 +2899,13 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C35">
         <v>0.9673787951469421</v>
       </c>
       <c r="D35" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2917,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2946,13 +2949,13 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36">
         <v>0.7677456140518188</v>
       </c>
       <c r="D36" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2967,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2996,13 +2999,13 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C37">
         <v>0.8940553665161133</v>
       </c>
       <c r="D37" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3017,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -3046,13 +3049,13 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C38">
         <v>0.9965819120407104</v>
       </c>
       <c r="D38" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -3067,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -3096,13 +3099,13 @@
         <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C39">
         <v>0.9989708662033081</v>
       </c>
       <c r="D39" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3117,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -3146,13 +3149,13 @@
         <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C40">
         <v>0.9991652369499207</v>
       </c>
       <c r="D40" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3167,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -3196,13 +3199,13 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C41">
         <v>0.9991592764854431</v>
       </c>
       <c r="D41" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3217,7 +3220,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -3232,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -3246,13 +3249,13 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C42">
         <v>0.9991186261177063</v>
       </c>
       <c r="D42" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3267,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3282,7 +3285,7 @@
         <v>3</v>
       </c>
       <c r="N42">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -3296,13 +3299,13 @@
         <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C43">
         <v>0.9952852725982666</v>
       </c>
       <c r="D43" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3317,7 +3320,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3332,7 +3335,7 @@
         <v>1</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -3346,13 +3349,13 @@
         <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C44">
         <v>0.9953067898750305</v>
       </c>
       <c r="D44" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3367,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3396,13 +3399,13 @@
         <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C45">
         <v>0.9992667436599731</v>
       </c>
       <c r="D45" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3417,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3446,13 +3449,13 @@
         <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C46">
         <v>0.9991705417633057</v>
       </c>
       <c r="D46" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3467,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3482,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -3496,13 +3499,13 @@
         <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C47">
         <v>0.999667763710022</v>
       </c>
       <c r="D47" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3517,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3532,7 +3535,7 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -3546,13 +3549,13 @@
         <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C48">
         <v>0.9995352625846863</v>
       </c>
       <c r="D48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3567,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3596,13 +3599,13 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C49">
         <v>0.9993976354598999</v>
       </c>
       <c r="D49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3617,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3646,13 +3649,13 @@
         <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C50">
         <v>0.9994799494743347</v>
       </c>
       <c r="D50" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3667,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3682,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="N50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -3696,13 +3699,13 @@
         <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C51">
         <v>0.9982963800430298</v>
       </c>
       <c r="D51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3717,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3732,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -3746,13 +3749,13 @@
         <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C52">
         <v>0.998166561126709</v>
       </c>
       <c r="D52" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3767,7 +3770,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3796,13 +3799,13 @@
         <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C53">
         <v>0.9988658428192139</v>
       </c>
       <c r="D53" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3817,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3846,13 +3849,13 @@
         <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C54">
         <v>0.9980804920196533</v>
       </c>
       <c r="D54" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3867,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3882,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="N54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -3896,13 +3899,13 @@
         <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C55">
         <v>0.9991114735603333</v>
       </c>
       <c r="D55" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3917,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3946,13 +3949,13 @@
         <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C56">
         <v>0.9987078905105591</v>
       </c>
       <c r="D56" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3967,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3982,7 +3985,7 @@
         <v>3</v>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -3996,13 +3999,13 @@
         <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C57">
         <v>0.9991089701652527</v>
       </c>
       <c r="D57" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4017,7 +4020,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -4038,7 +4041,7 @@
         <v>0</v>
       </c>
       <c r="P57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4046,13 +4049,13 @@
         <v>72</v>
       </c>
       <c r="B58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C58">
         <v>0.9810042381286621</v>
       </c>
       <c r="D58" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4067,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -4096,13 +4099,13 @@
         <v>73</v>
       </c>
       <c r="B59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C59">
         <v>0.9990440607070923</v>
       </c>
       <c r="D59" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -4117,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4132,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -4146,13 +4149,13 @@
         <v>74</v>
       </c>
       <c r="B60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C60">
         <v>0.9949619770050049</v>
       </c>
       <c r="D60" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4167,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -4196,13 +4199,13 @@
         <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -4217,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -4246,13 +4249,13 @@
         <v>76</v>
       </c>
       <c r="B62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C62">
         <v>0.9984354376792908</v>
       </c>
       <c r="D62" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -4267,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -4282,7 +4285,7 @@
         <v>2</v>
       </c>
       <c r="N62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -4296,13 +4299,13 @@
         <v>77</v>
       </c>
       <c r="B63" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C63">
         <v>0.9993854761123657</v>
       </c>
       <c r="D63" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4317,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -4332,7 +4335,7 @@
         <v>2</v>
       </c>
       <c r="N63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -4346,13 +4349,13 @@
         <v>78</v>
       </c>
       <c r="B64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C64">
         <v>0.9993329048156738</v>
       </c>
       <c r="D64" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4367,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4396,13 +4399,13 @@
         <v>79</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C65">
         <v>0.9969677925109863</v>
       </c>
       <c r="D65" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4417,7 +4420,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4446,13 +4449,13 @@
         <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C66">
         <v>0.9995519518852234</v>
       </c>
       <c r="D66" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4467,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4496,13 +4499,13 @@
         <v>81</v>
       </c>
       <c r="B67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C67">
         <v>0.9992239475250244</v>
       </c>
       <c r="D67" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4517,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4532,7 +4535,7 @@
         <v>2</v>
       </c>
       <c r="N67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -4546,13 +4549,13 @@
         <v>82</v>
       </c>
       <c r="B68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C68">
         <v>0.9972553253173828</v>
       </c>
       <c r="D68" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4567,7 +4570,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4596,13 +4599,13 @@
         <v>83</v>
       </c>
       <c r="B69" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C69">
         <v>0.9980692267417908</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4617,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4632,7 +4635,7 @@
         <v>2</v>
       </c>
       <c r="N69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -4646,13 +4649,13 @@
         <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C70">
         <v>0.9959254264831543</v>
       </c>
       <c r="D70" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4667,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4696,13 +4699,13 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C71">
         <v>0.9990965127944946</v>
       </c>
       <c r="D71" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4717,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4746,13 +4749,13 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C72">
         <v>0.9995350241661072</v>
       </c>
       <c r="D72" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4767,7 +4770,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4782,7 +4785,7 @@
         <v>3</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -4796,13 +4799,13 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C73">
         <v>0.9991962909698486</v>
       </c>
       <c r="D73" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4817,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4832,7 +4835,7 @@
         <v>2</v>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -4846,13 +4849,13 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C74">
         <v>0.9979453086853027</v>
       </c>
       <c r="D74" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4867,7 +4870,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4882,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -4896,13 +4899,13 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C75">
         <v>0.9969654083251953</v>
       </c>
       <c r="D75" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4917,7 +4920,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4946,13 +4949,13 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C76">
         <v>0.9930816888809204</v>
       </c>
       <c r="D76" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4967,7 +4970,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4996,13 +4999,13 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C77">
         <v>0.8460029363632202</v>
       </c>
       <c r="D77" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5017,7 +5020,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -5046,13 +5049,13 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C78">
         <v>0.9959526658058167</v>
       </c>
       <c r="D78" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5067,7 +5070,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -5096,13 +5099,13 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C79">
         <v>0.9994586706161499</v>
       </c>
       <c r="D79" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5117,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -5132,7 +5135,7 @@
         <v>2</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -5146,13 +5149,13 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C80">
         <v>0.996728241443634</v>
       </c>
       <c r="D80" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5167,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -5196,13 +5199,13 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C81">
         <v>0.9973512291908264</v>
       </c>
       <c r="D81" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5217,7 +5220,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -5246,13 +5249,13 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C82">
-        <v>0.9967225193977356</v>
+        <v>0.9904835224151611</v>
       </c>
       <c r="D82" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -5267,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -5279,7 +5282,7 @@
         <v>0</v>
       </c>
       <c r="M82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -5296,13 +5299,13 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C83">
         <v>0.9978298544883728</v>
       </c>
       <c r="D83" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5317,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -5346,13 +5349,13 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C84">
         <v>0.8626171350479126</v>
       </c>
       <c r="D84" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5367,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -5396,13 +5399,13 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C85">
         <v>0.9972398281097412</v>
       </c>
       <c r="D85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5417,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -5446,13 +5449,13 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C86">
-        <v>0.9967367053031921</v>
+        <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5467,7 +5470,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -5499,10 +5502,10 @@
         <v>233</v>
       </c>
       <c r="C87">
-        <v>0.9915247559547424</v>
+        <v>0.9967367053031921</v>
       </c>
       <c r="D87" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5517,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5529,7 +5532,7 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -5549,10 +5552,10 @@
         <v>234</v>
       </c>
       <c r="C88">
-        <v>0.9995598793029785</v>
+        <v>0.9915247559547424</v>
       </c>
       <c r="D88" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5567,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5579,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="M88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -5599,10 +5602,10 @@
         <v>235</v>
       </c>
       <c r="C89">
-        <v>0.8945754766464233</v>
+        <v>0.9995598793029785</v>
       </c>
       <c r="D89" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5617,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5649,10 +5652,10 @@
         <v>236</v>
       </c>
       <c r="C90">
-        <v>0.9960287809371948</v>
+        <v>0.8945754766464233</v>
       </c>
       <c r="D90" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5667,7 +5670,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5699,10 +5702,10 @@
         <v>237</v>
       </c>
       <c r="C91">
-        <v>0.9991824626922607</v>
+        <v>0.9960287809371948</v>
       </c>
       <c r="D91" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5717,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5749,10 +5752,10 @@
         <v>238</v>
       </c>
       <c r="C92">
-        <v>0.9956748485565186</v>
+        <v>0.9991824626922607</v>
       </c>
       <c r="D92" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5767,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5799,10 +5802,10 @@
         <v>239</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>0.9956748485565186</v>
       </c>
       <c r="D93" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5817,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5832,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -5846,13 +5849,13 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C94">
-        <v>0.9787474274635315</v>
+        <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5867,7 +5870,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5882,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -5899,10 +5902,10 @@
         <v>240</v>
       </c>
       <c r="C95">
-        <v>0.9993278980255127</v>
+        <v>0.9787474274635315</v>
       </c>
       <c r="D95" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5917,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5932,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -5949,10 +5952,10 @@
         <v>241</v>
       </c>
       <c r="C96">
-        <v>0.9933540225028992</v>
+        <v>0.9993278980255127</v>
       </c>
       <c r="D96" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5967,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5982,7 +5985,7 @@
         <v>1</v>
       </c>
       <c r="N96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -5999,10 +6002,10 @@
         <v>242</v>
       </c>
       <c r="C97">
-        <v>0.9988803863525391</v>
+        <v>0.9933540225028992</v>
       </c>
       <c r="D97" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6017,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -6049,10 +6052,10 @@
         <v>243</v>
       </c>
       <c r="C98">
-        <v>0.9901755452156067</v>
+        <v>0.9988803863525391</v>
       </c>
       <c r="D98" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6067,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -6099,10 +6102,10 @@
         <v>244</v>
       </c>
       <c r="C99">
-        <v>0.999345064163208</v>
+        <v>0.9901755452156067</v>
       </c>
       <c r="D99" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6117,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -6132,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -6149,10 +6152,10 @@
         <v>245</v>
       </c>
       <c r="C100">
-        <v>0.9616943597793579</v>
+        <v>0.999345064163208</v>
       </c>
       <c r="D100" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6167,7 +6170,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -6182,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -6199,10 +6202,10 @@
         <v>246</v>
       </c>
       <c r="C101">
-        <v>0.8529298901557922</v>
+        <v>0.9616943597793579</v>
       </c>
       <c r="D101" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6217,7 +6220,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -6249,10 +6252,10 @@
         <v>247</v>
       </c>
       <c r="C102">
-        <v>0.9913250803947449</v>
+        <v>0.8529298901557922</v>
       </c>
       <c r="D102" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6267,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -6279,10 +6282,10 @@
         <v>0</v>
       </c>
       <c r="M102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -6296,13 +6299,13 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C103">
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6317,7 +6320,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -6332,7 +6335,7 @@
         <v>2</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -6349,10 +6352,10 @@
         <v>248</v>
       </c>
       <c r="C104">
-        <v>0.9982128739356995</v>
+        <v>0.9913250803947449</v>
       </c>
       <c r="D104" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6367,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -6379,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="M104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -6399,10 +6402,10 @@
         <v>249</v>
       </c>
       <c r="C105">
-        <v>0.9876354336738586</v>
+        <v>0.9982128739356995</v>
       </c>
       <c r="D105" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6417,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -6429,7 +6432,7 @@
         <v>0</v>
       </c>
       <c r="M105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N105">
         <v>0</v>
@@ -6449,10 +6452,10 @@
         <v>250</v>
       </c>
       <c r="C106">
-        <v>0.9978511333465576</v>
+        <v>0.9876354336738586</v>
       </c>
       <c r="D106" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6467,22 +6470,22 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
         <v>2</v>
       </c>
-      <c r="L106">
-        <v>1</v>
-      </c>
-      <c r="M106">
-        <v>1</v>
-      </c>
       <c r="N106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -6499,10 +6502,10 @@
         <v>251</v>
       </c>
       <c r="C107">
-        <v>0.9994751811027527</v>
+        <v>0.9978511333465576</v>
       </c>
       <c r="D107" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6517,22 +6520,22 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107">
         <v>1</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -6549,10 +6552,10 @@
         <v>252</v>
       </c>
       <c r="C108">
-        <v>0.9982790946960449</v>
+        <v>0.9994751811027527</v>
       </c>
       <c r="D108" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6567,7 +6570,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6582,7 +6585,7 @@
         <v>1</v>
       </c>
       <c r="N108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -6599,10 +6602,10 @@
         <v>253</v>
       </c>
       <c r="C109">
-        <v>0.9931647777557373</v>
+        <v>0.9982790946960449</v>
       </c>
       <c r="D109" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6617,7 +6620,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -6649,10 +6652,10 @@
         <v>254</v>
       </c>
       <c r="C110">
-        <v>0.9983500242233276</v>
+        <v>0.9931647777557373</v>
       </c>
       <c r="D110" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6667,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6679,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="M110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -6699,10 +6702,10 @@
         <v>255</v>
       </c>
       <c r="C111">
-        <v>0.9937362670898438</v>
+        <v>0.9983500242233276</v>
       </c>
       <c r="D111" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6717,7 +6720,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6729,10 +6732,10 @@
         <v>0</v>
       </c>
       <c r="M111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -6749,10 +6752,10 @@
         <v>256</v>
       </c>
       <c r="C112">
-        <v>0.9989242553710938</v>
+        <v>0.9937362670898438</v>
       </c>
       <c r="D112" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6767,19 +6770,19 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N112">
         <v>2</v>
@@ -6788,7 +6791,7 @@
         <v>0</v>
       </c>
       <c r="P112">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -6799,10 +6802,10 @@
         <v>257</v>
       </c>
       <c r="C113">
-        <v>0.9987581372261047</v>
+        <v>0.9989242553710938</v>
       </c>
       <c r="D113" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6817,22 +6820,22 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113">
         <v>2</v>
       </c>
       <c r="N113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -6849,10 +6852,10 @@
         <v>258</v>
       </c>
       <c r="C114">
-        <v>0.9983271360397339</v>
+        <v>0.9987581372261047</v>
       </c>
       <c r="D114" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6867,22 +6870,22 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114">
         <v>2</v>
       </c>
       <c r="N114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -6899,10 +6902,10 @@
         <v>259</v>
       </c>
       <c r="C115">
-        <v>0.9987975358963013</v>
+        <v>0.9983271360397339</v>
       </c>
       <c r="D115" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6917,22 +6920,22 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115">
         <v>2</v>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -6949,10 +6952,10 @@
         <v>260</v>
       </c>
       <c r="C116">
-        <v>0.9942725300788879</v>
+        <v>0.9987975358963013</v>
       </c>
       <c r="D116" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6967,7 +6970,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6979,10 +6982,10 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -6999,10 +7002,10 @@
         <v>261</v>
       </c>
       <c r="C117">
-        <v>0.9970023632049561</v>
+        <v>0.9942725300788879</v>
       </c>
       <c r="D117" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7017,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -7029,7 +7032,7 @@
         <v>0</v>
       </c>
       <c r="M117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -7049,10 +7052,10 @@
         <v>262</v>
       </c>
       <c r="C118">
-        <v>0.9984022974967957</v>
+        <v>0.9970023632049561</v>
       </c>
       <c r="D118" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7067,7 +7070,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -7099,10 +7102,10 @@
         <v>263</v>
       </c>
       <c r="C119">
-        <v>0.999241828918457</v>
+        <v>0.9984022974967957</v>
       </c>
       <c r="D119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7117,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -7129,7 +7132,7 @@
         <v>0</v>
       </c>
       <c r="M119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -7149,10 +7152,10 @@
         <v>264</v>
       </c>
       <c r="C120">
-        <v>0.9961878061294556</v>
+        <v>0.999241828918457</v>
       </c>
       <c r="D120" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7167,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -7179,10 +7182,10 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -7199,10 +7202,10 @@
         <v>265</v>
       </c>
       <c r="C121">
-        <v>0.9993798732757568</v>
+        <v>0.9961878061294556</v>
       </c>
       <c r="D121" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7217,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -7229,10 +7232,10 @@
         <v>0</v>
       </c>
       <c r="M121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -7249,10 +7252,10 @@
         <v>266</v>
       </c>
       <c r="C122">
-        <v>0.9990472793579102</v>
+        <v>0.9993798732757568</v>
       </c>
       <c r="D122" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7267,7 +7270,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -7279,10 +7282,10 @@
         <v>0</v>
       </c>
       <c r="M122">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -7299,10 +7302,10 @@
         <v>267</v>
       </c>
       <c r="C123">
-        <v>0.9991445541381836</v>
+        <v>0.9990472793579102</v>
       </c>
       <c r="D123" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7317,7 +7320,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -7332,7 +7335,7 @@
         <v>2</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -7349,10 +7352,10 @@
         <v>268</v>
       </c>
       <c r="C124">
-        <v>0.9142532348632812</v>
+        <v>0.9991445541381836</v>
       </c>
       <c r="D124" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7367,7 +7370,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -7382,7 +7385,7 @@
         <v>2</v>
       </c>
       <c r="N124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -7399,10 +7402,10 @@
         <v>269</v>
       </c>
       <c r="C125">
-        <v>0.9972384572029114</v>
+        <v>0.9142532348632812</v>
       </c>
       <c r="D125" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7417,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -7429,10 +7432,10 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -7449,10 +7452,10 @@
         <v>270</v>
       </c>
       <c r="C126">
-        <v>0.9960039258003235</v>
+        <v>0.9972384572029114</v>
       </c>
       <c r="D126" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7467,7 +7470,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -7479,10 +7482,10 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -7499,10 +7502,10 @@
         <v>271</v>
       </c>
       <c r="C127">
-        <v>0.9987621903419495</v>
+        <v>0.9960039258003235</v>
       </c>
       <c r="D127" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7517,7 +7520,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -7529,10 +7532,10 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -7549,10 +7552,10 @@
         <v>272</v>
       </c>
       <c r="C128">
-        <v>0.9937299489974976</v>
+        <v>0.9987621903419495</v>
       </c>
       <c r="D128" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7567,7 +7570,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -7579,7 +7582,7 @@
         <v>0</v>
       </c>
       <c r="M128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N128">
         <v>1</v>
@@ -7599,10 +7602,10 @@
         <v>273</v>
       </c>
       <c r="C129">
-        <v>0.9990777969360352</v>
+        <v>0.9937299489974976</v>
       </c>
       <c r="D129" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -7617,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -7629,10 +7632,10 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -7649,10 +7652,10 @@
         <v>274</v>
       </c>
       <c r="C130">
-        <v>0.9922806620597839</v>
+        <v>0.9990777969360352</v>
       </c>
       <c r="D130" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -7667,7 +7670,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -7699,10 +7702,10 @@
         <v>275</v>
       </c>
       <c r="C131">
-        <v>0.9937021136283875</v>
+        <v>0.9922806620597839</v>
       </c>
       <c r="D131" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -7717,10 +7720,10 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -7729,16 +7732,16 @@
         <v>0</v>
       </c>
       <c r="M131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O131">
         <v>0</v>
       </c>
       <c r="P131">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -7749,10 +7752,10 @@
         <v>276</v>
       </c>
       <c r="C132">
-        <v>0.9984290599822998</v>
+        <v>0.9937021136283875</v>
       </c>
       <c r="D132" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7767,10 +7770,10 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -7779,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="M132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N132">
         <v>2</v>
@@ -7799,10 +7802,10 @@
         <v>277</v>
       </c>
       <c r="C133">
-        <v>0.9967972040176392</v>
+        <v>0.9984290599822998</v>
       </c>
       <c r="D133" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7817,10 +7820,10 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -7829,10 +7832,10 @@
         <v>0</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -7849,45 +7852,95 @@
         <v>278</v>
       </c>
       <c r="C134">
+        <v>0.9967972040176392</v>
+      </c>
+      <c r="D134" t="s">
+        <v>280</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134" t="b">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134" t="s">
+        <v>281</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135" t="s">
+        <v>149</v>
+      </c>
+      <c r="B135" t="s">
+        <v>279</v>
+      </c>
+      <c r="C135">
         <v>0.8547114133834839</v>
       </c>
-      <c r="D134" t="s">
-        <v>279</v>
-      </c>
-      <c r="E134">
-        <v>0</v>
-      </c>
-      <c r="F134" t="b">
-        <v>0</v>
-      </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134" t="s">
-        <v>280</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134">
-        <v>1</v>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
+      <c r="D135" t="s">
+        <v>280</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135" t="b">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135" t="s">
+        <v>281</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
         <v>0</v>
       </c>
     </row>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="281">
   <si>
     <t>filename</t>
   </si>
@@ -130,7 +130,7 @@
     <t>micro_0109_SL40III.jpg</t>
   </si>
   <si>
-    <t>micro_0296_SL4082600.jpg</t>
+    <t>micro_0295_SL4082600.jpg</t>
   </si>
   <si>
     <t>micro_0296_SL407.jpg</t>
@@ -316,9 +316,6 @@
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
-    <t>micro_0294_D401.jpg</t>
-  </si>
-  <si>
     <t>micro_0290_D401.jpg</t>
   </si>
   <si>
@@ -340,12 +337,12 @@
     <t>micro_0073_D242.jpg</t>
   </si>
   <si>
+    <t>micro_0015_OOD240.jpg</t>
+  </si>
+  <si>
     <t>micro_0090_OD240.jpg</t>
   </si>
   <si>
-    <t>micro_0015_OOD240.jpg</t>
-  </si>
-  <si>
     <t>micro_0148_D2392000.jpg</t>
   </si>
   <si>
@@ -367,10 +364,10 @@
     <t>micro_0210_D233.jpg</t>
   </si>
   <si>
+    <t>micro_0205_0D232.jpg</t>
+  </si>
+  <si>
     <t>micro_0249_OD232.jpg</t>
-  </si>
-  <si>
-    <t>micro_0205_0D232.jpg</t>
   </si>
   <si>
     <t>micro_0182_D231.jpg</t>
@@ -1191,7 +1188,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P135"/>
+  <dimension ref="A1:P134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1249,13 +1246,13 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C2">
         <v>0.922767162322998</v>
       </c>
       <c r="D2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1270,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1299,13 +1296,13 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C3">
         <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1320,7 +1317,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1349,13 +1346,13 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4">
         <v>0.9991193413734436</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1370,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1399,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5">
         <v>0.9360489845275879</v>
       </c>
       <c r="D5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1420,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1449,13 +1446,13 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C6">
         <v>0.9898043870925903</v>
       </c>
       <c r="D6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1470,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1499,13 +1496,13 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7">
         <v>0.9800205826759338</v>
       </c>
       <c r="D7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1520,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1549,13 +1546,13 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C8">
         <v>0.9866096377372742</v>
       </c>
       <c r="D8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1570,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1599,13 +1596,13 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C9">
         <v>0.9825887680053711</v>
       </c>
       <c r="D9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1620,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1649,13 +1646,13 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C10">
         <v>0.9854358434677124</v>
       </c>
       <c r="D10" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1670,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1699,13 +1696,13 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C11">
         <v>0.9869511127471924</v>
       </c>
       <c r="D11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1720,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1749,13 +1746,13 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C12">
         <v>0.9883586168289185</v>
       </c>
       <c r="D12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1770,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1799,13 +1796,13 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13">
         <v>0.9827210903167725</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1820,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1849,13 +1846,13 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C14">
         <v>0.8711124062538147</v>
       </c>
       <c r="D14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1870,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1899,13 +1896,13 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C15">
         <v>0.9849019646644592</v>
       </c>
       <c r="D15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1920,7 +1917,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1949,13 +1946,13 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C16">
         <v>0.9831116795539856</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1970,7 +1967,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1999,13 +1996,13 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C17">
         <v>0.979184627532959</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2020,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2049,13 +2046,13 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C18">
         <v>0.9820773601531982</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2070,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2099,13 +2096,13 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C19">
         <v>0.9926210641860962</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2120,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2149,13 +2146,13 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C20">
         <v>0.991193413734436</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2170,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2199,13 +2196,13 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C21">
         <v>0.9759405851364136</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2220,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2249,13 +2246,13 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C22">
         <v>0.9936316609382629</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2270,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2299,13 +2296,13 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C23">
         <v>0.9834394454956055</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2320,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2349,13 +2346,13 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C24">
-        <v>0.9938239455223083</v>
+        <v>0.982405424118042</v>
       </c>
       <c r="D24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2370,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2399,13 +2396,13 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C25">
-        <v>0.9959491491317749</v>
+        <v>0.9976034164428711</v>
       </c>
       <c r="D25" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2420,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2449,13 +2446,13 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C26">
         <v>0.9976895451545715</v>
       </c>
       <c r="D26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2470,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2499,13 +2496,13 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27">
         <v>0.9959992170333862</v>
       </c>
       <c r="D27" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2520,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2549,13 +2546,13 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C28">
         <v>0.9971073865890503</v>
       </c>
       <c r="D28" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2570,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2599,13 +2596,13 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C29">
         <v>0.9968833923339844</v>
       </c>
       <c r="D29" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2620,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2649,13 +2646,13 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C30">
         <v>0.9585862159729004</v>
       </c>
       <c r="D30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2670,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2699,13 +2696,13 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C31">
         <v>0.9984833598136902</v>
       </c>
       <c r="D31" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2720,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2749,13 +2746,13 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C32">
         <v>0.9960424304008484</v>
       </c>
       <c r="D32" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2770,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2785,13 +2782,13 @@
         <v>1</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -2799,13 +2796,13 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C33">
         <v>0.9988101124763489</v>
       </c>
       <c r="D33" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2820,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2849,13 +2846,13 @@
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C34">
         <v>0.9754772186279297</v>
       </c>
       <c r="D34" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2870,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2899,13 +2896,13 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C35">
         <v>0.9673787951469421</v>
       </c>
       <c r="D35" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2920,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2949,13 +2946,13 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C36">
         <v>0.7677456140518188</v>
       </c>
       <c r="D36" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2970,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2999,13 +2996,13 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C37">
         <v>0.8940553665161133</v>
       </c>
       <c r="D37" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3020,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -3049,13 +3046,13 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C38">
         <v>0.9965819120407104</v>
       </c>
       <c r="D38" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -3070,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -3099,13 +3096,13 @@
         <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C39">
         <v>0.9989708662033081</v>
       </c>
       <c r="D39" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3120,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -3149,13 +3146,13 @@
         <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C40">
         <v>0.9991652369499207</v>
       </c>
       <c r="D40" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3170,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -3199,13 +3196,13 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C41">
         <v>0.9991592764854431</v>
       </c>
       <c r="D41" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3220,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -3249,13 +3246,13 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C42">
         <v>0.9991186261177063</v>
       </c>
       <c r="D42" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3270,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3299,13 +3296,13 @@
         <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C43">
         <v>0.9952852725982666</v>
       </c>
       <c r="D43" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3320,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3349,13 +3346,13 @@
         <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C44">
         <v>0.9953067898750305</v>
       </c>
       <c r="D44" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3370,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3399,13 +3396,13 @@
         <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C45">
         <v>0.9992667436599731</v>
       </c>
       <c r="D45" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3420,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3449,13 +3446,13 @@
         <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C46">
         <v>0.9991705417633057</v>
       </c>
       <c r="D46" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3470,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3499,13 +3496,13 @@
         <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C47">
         <v>0.999667763710022</v>
       </c>
       <c r="D47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3520,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3549,13 +3546,13 @@
         <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C48">
         <v>0.9995352625846863</v>
       </c>
       <c r="D48" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3570,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3599,13 +3596,13 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C49">
         <v>0.9993976354598999</v>
       </c>
       <c r="D49" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3620,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3649,13 +3646,13 @@
         <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C50">
         <v>0.9994799494743347</v>
       </c>
       <c r="D50" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3670,7 +3667,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3699,13 +3696,13 @@
         <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C51">
         <v>0.9982963800430298</v>
       </c>
       <c r="D51" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3720,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3749,13 +3746,13 @@
         <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C52">
         <v>0.998166561126709</v>
       </c>
       <c r="D52" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3770,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3799,13 +3796,13 @@
         <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C53">
         <v>0.9988658428192139</v>
       </c>
       <c r="D53" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3820,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3849,13 +3846,13 @@
         <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C54">
         <v>0.9980804920196533</v>
       </c>
       <c r="D54" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3870,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3899,13 +3896,13 @@
         <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C55">
         <v>0.9991114735603333</v>
       </c>
       <c r="D55" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3920,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3949,13 +3946,13 @@
         <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C56">
         <v>0.9987078905105591</v>
       </c>
       <c r="D56" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3970,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3999,13 +3996,13 @@
         <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C57">
         <v>0.9991089701652527</v>
       </c>
       <c r="D57" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4020,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -4049,13 +4046,13 @@
         <v>72</v>
       </c>
       <c r="B58" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C58">
         <v>0.9810042381286621</v>
       </c>
       <c r="D58" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4070,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -4099,13 +4096,13 @@
         <v>73</v>
       </c>
       <c r="B59" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C59">
         <v>0.9990440607070923</v>
       </c>
       <c r="D59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -4120,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4149,13 +4146,13 @@
         <v>74</v>
       </c>
       <c r="B60" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C60">
         <v>0.9949619770050049</v>
       </c>
       <c r="D60" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4170,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -4199,13 +4196,13 @@
         <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -4220,7 +4217,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -4249,13 +4246,13 @@
         <v>76</v>
       </c>
       <c r="B62" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C62">
         <v>0.9984354376792908</v>
       </c>
       <c r="D62" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -4270,7 +4267,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -4299,13 +4296,13 @@
         <v>77</v>
       </c>
       <c r="B63" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C63">
         <v>0.9993854761123657</v>
       </c>
       <c r="D63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4320,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -4349,13 +4346,13 @@
         <v>78</v>
       </c>
       <c r="B64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C64">
         <v>0.9993329048156738</v>
       </c>
       <c r="D64" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4370,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4399,13 +4396,13 @@
         <v>79</v>
       </c>
       <c r="B65" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C65">
         <v>0.9969677925109863</v>
       </c>
       <c r="D65" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4420,7 +4417,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4449,13 +4446,13 @@
         <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C66">
         <v>0.9995519518852234</v>
       </c>
       <c r="D66" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4470,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4499,13 +4496,13 @@
         <v>81</v>
       </c>
       <c r="B67" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C67">
         <v>0.9992239475250244</v>
       </c>
       <c r="D67" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4520,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4549,13 +4546,13 @@
         <v>82</v>
       </c>
       <c r="B68" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C68">
         <v>0.9972553253173828</v>
       </c>
       <c r="D68" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4570,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4599,13 +4596,13 @@
         <v>83</v>
       </c>
       <c r="B69" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C69">
         <v>0.9980692267417908</v>
       </c>
       <c r="D69" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4620,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4649,13 +4646,13 @@
         <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C70">
         <v>0.9959254264831543</v>
       </c>
       <c r="D70" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4670,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4699,13 +4696,13 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C71">
         <v>0.9990965127944946</v>
       </c>
       <c r="D71" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4720,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4749,13 +4746,13 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C72">
         <v>0.9995350241661072</v>
       </c>
       <c r="D72" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4770,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4799,13 +4796,13 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C73">
         <v>0.9991962909698486</v>
       </c>
       <c r="D73" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4820,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4849,13 +4846,13 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C74">
         <v>0.9979453086853027</v>
       </c>
       <c r="D74" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4870,7 +4867,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4899,13 +4896,13 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C75">
         <v>0.9969654083251953</v>
       </c>
       <c r="D75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4920,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4949,13 +4946,13 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C76">
         <v>0.9930816888809204</v>
       </c>
       <c r="D76" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4970,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4999,13 +4996,13 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C77">
         <v>0.8460029363632202</v>
       </c>
       <c r="D77" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5020,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -5049,13 +5046,13 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C78">
         <v>0.9959526658058167</v>
       </c>
       <c r="D78" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5070,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -5099,13 +5096,13 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C79">
         <v>0.9994586706161499</v>
       </c>
       <c r="D79" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5120,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -5149,13 +5146,13 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C80">
         <v>0.996728241443634</v>
       </c>
       <c r="D80" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5170,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -5199,13 +5196,13 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C81">
         <v>0.9973512291908264</v>
       </c>
       <c r="D81" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5220,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -5249,13 +5246,13 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C82">
-        <v>0.9904835224151611</v>
+        <v>0.9980469942092896</v>
       </c>
       <c r="D82" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -5270,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -5299,13 +5296,13 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C83">
         <v>0.9978298544883728</v>
       </c>
       <c r="D83" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5320,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -5349,13 +5346,13 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C84">
         <v>0.8626171350479126</v>
       </c>
       <c r="D84" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5370,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -5399,13 +5396,13 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C85">
         <v>0.9972398281097412</v>
       </c>
       <c r="D85" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5420,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -5449,13 +5446,13 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>0.9967367053031921</v>
       </c>
       <c r="D86" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5470,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -5502,10 +5499,10 @@
         <v>233</v>
       </c>
       <c r="C87">
-        <v>0.9967367053031921</v>
+        <v>0.9915247559547424</v>
       </c>
       <c r="D87" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5520,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5532,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -5552,10 +5549,10 @@
         <v>234</v>
       </c>
       <c r="C88">
-        <v>0.9915247559547424</v>
+        <v>0.9995598793029785</v>
       </c>
       <c r="D88" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5570,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5582,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="M88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N88">
         <v>1</v>
@@ -5602,10 +5599,10 @@
         <v>235</v>
       </c>
       <c r="C89">
-        <v>0.9995598793029785</v>
+        <v>0.8945754766464233</v>
       </c>
       <c r="D89" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5620,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5652,10 +5649,10 @@
         <v>236</v>
       </c>
       <c r="C90">
-        <v>0.8945754766464233</v>
+        <v>0.9960287809371948</v>
       </c>
       <c r="D90" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5670,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5702,10 +5699,10 @@
         <v>237</v>
       </c>
       <c r="C91">
-        <v>0.9960287809371948</v>
+        <v>0.9991824626922607</v>
       </c>
       <c r="D91" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5720,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5752,10 +5749,10 @@
         <v>238</v>
       </c>
       <c r="C92">
-        <v>0.9991824626922607</v>
+        <v>0.9956748485565186</v>
       </c>
       <c r="D92" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5770,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5802,10 +5799,10 @@
         <v>239</v>
       </c>
       <c r="C93">
-        <v>0.9956748485565186</v>
+        <v>0.9787474274635315</v>
       </c>
       <c r="D93" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5820,7 +5817,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5849,13 +5846,13 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C94">
         <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5870,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5902,10 +5899,10 @@
         <v>240</v>
       </c>
       <c r="C95">
-        <v>0.9787474274635315</v>
+        <v>0.9993278980255127</v>
       </c>
       <c r="D95" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5920,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5935,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="N95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -5952,10 +5949,10 @@
         <v>241</v>
       </c>
       <c r="C96">
-        <v>0.9993278980255127</v>
+        <v>0.9933540225028992</v>
       </c>
       <c r="D96" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5970,7 +5967,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5985,7 +5982,7 @@
         <v>1</v>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -6002,10 +5999,10 @@
         <v>242</v>
       </c>
       <c r="C97">
-        <v>0.9933540225028992</v>
+        <v>0.9988803863525391</v>
       </c>
       <c r="D97" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6020,7 +6017,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -6052,10 +6049,10 @@
         <v>243</v>
       </c>
       <c r="C98">
-        <v>0.9988803863525391</v>
+        <v>0.9901755452156067</v>
       </c>
       <c r="D98" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6070,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -6102,10 +6099,10 @@
         <v>244</v>
       </c>
       <c r="C99">
-        <v>0.9901755452156067</v>
+        <v>0.999345064163208</v>
       </c>
       <c r="D99" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6120,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -6152,10 +6149,10 @@
         <v>245</v>
       </c>
       <c r="C100">
-        <v>0.999345064163208</v>
+        <v>0.9616943597793579</v>
       </c>
       <c r="D100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6170,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -6185,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="N100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -6202,10 +6199,10 @@
         <v>246</v>
       </c>
       <c r="C101">
-        <v>0.9616943597793579</v>
+        <v>0.8529298901557922</v>
       </c>
       <c r="D101" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6220,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -6252,10 +6249,10 @@
         <v>247</v>
       </c>
       <c r="C102">
-        <v>0.8529298901557922</v>
+        <v>0.9913250803947449</v>
       </c>
       <c r="D102" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6270,7 +6267,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -6282,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="M102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -6299,13 +6296,13 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C103">
         <v>1</v>
       </c>
       <c r="D103" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6320,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -6352,10 +6349,10 @@
         <v>248</v>
       </c>
       <c r="C104">
-        <v>0.9913250803947449</v>
+        <v>0.9982128739356995</v>
       </c>
       <c r="D104" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6370,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -6382,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="M104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -6402,10 +6399,10 @@
         <v>249</v>
       </c>
       <c r="C105">
-        <v>0.9982128739356995</v>
+        <v>0.9876354336738586</v>
       </c>
       <c r="D105" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6420,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -6432,10 +6429,10 @@
         <v>0</v>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105">
         <v>0</v>
@@ -6452,10 +6449,10 @@
         <v>250</v>
       </c>
       <c r="C106">
-        <v>0.9876354336738586</v>
+        <v>0.9978511333465576</v>
       </c>
       <c r="D106" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6470,22 +6467,22 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -6502,10 +6499,10 @@
         <v>251</v>
       </c>
       <c r="C107">
-        <v>0.9978511333465576</v>
+        <v>0.9994751811027527</v>
       </c>
       <c r="D107" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6520,22 +6517,22 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K107">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M107">
         <v>1</v>
       </c>
       <c r="N107">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -6552,10 +6549,10 @@
         <v>252</v>
       </c>
       <c r="C108">
-        <v>0.9994751811027527</v>
+        <v>0.9982790946960449</v>
       </c>
       <c r="D108" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6570,7 +6567,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6585,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -6602,10 +6599,10 @@
         <v>253</v>
       </c>
       <c r="C109">
-        <v>0.9982790946960449</v>
+        <v>0.9931647777557373</v>
       </c>
       <c r="D109" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6620,7 +6617,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -6652,10 +6649,10 @@
         <v>254</v>
       </c>
       <c r="C110">
-        <v>0.9931647777557373</v>
+        <v>0.9983500242233276</v>
       </c>
       <c r="D110" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6670,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6682,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="M110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -6702,10 +6699,10 @@
         <v>255</v>
       </c>
       <c r="C111">
-        <v>0.9983500242233276</v>
+        <v>0.9937362670898438</v>
       </c>
       <c r="D111" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6720,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6732,10 +6729,10 @@
         <v>0</v>
       </c>
       <c r="M111">
+        <v>1</v>
+      </c>
+      <c r="N111">
         <v>2</v>
-      </c>
-      <c r="N111">
-        <v>1</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -6752,10 +6749,10 @@
         <v>256</v>
       </c>
       <c r="C112">
-        <v>0.9937362670898438</v>
+        <v>0.9989242553710938</v>
       </c>
       <c r="D112" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6770,22 +6767,22 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -6802,10 +6799,10 @@
         <v>257</v>
       </c>
       <c r="C113">
-        <v>0.9989242553710938</v>
+        <v>0.9987581372261047</v>
       </c>
       <c r="D113" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6820,22 +6817,22 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113">
         <v>2</v>
       </c>
       <c r="N113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -6852,10 +6849,10 @@
         <v>258</v>
       </c>
       <c r="C114">
-        <v>0.9987581372261047</v>
+        <v>0.9983271360397339</v>
       </c>
       <c r="D114" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6870,16 +6867,16 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114">
         <v>2</v>
@@ -6902,10 +6899,10 @@
         <v>259</v>
       </c>
       <c r="C115">
-        <v>0.9983271360397339</v>
+        <v>0.9987975358963013</v>
       </c>
       <c r="D115" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6920,22 +6917,22 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115">
         <v>2</v>
       </c>
       <c r="N115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -6952,10 +6949,10 @@
         <v>260</v>
       </c>
       <c r="C116">
-        <v>0.9987975358963013</v>
+        <v>0.9942725300788879</v>
       </c>
       <c r="D116" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6970,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6982,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N116">
         <v>1</v>
@@ -7002,10 +6999,10 @@
         <v>261</v>
       </c>
       <c r="C117">
-        <v>0.9942725300788879</v>
+        <v>0.9970023632049561</v>
       </c>
       <c r="D117" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7020,7 +7017,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -7032,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="M117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -7052,10 +7049,10 @@
         <v>262</v>
       </c>
       <c r="C118">
-        <v>0.9970023632049561</v>
+        <v>0.9984022974967957</v>
       </c>
       <c r="D118" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7070,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -7102,10 +7099,10 @@
         <v>263</v>
       </c>
       <c r="C119">
-        <v>0.9984022974967957</v>
+        <v>0.999241828918457</v>
       </c>
       <c r="D119" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7120,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -7132,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="M119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -7152,10 +7149,10 @@
         <v>264</v>
       </c>
       <c r="C120">
-        <v>0.999241828918457</v>
+        <v>0.9961878061294556</v>
       </c>
       <c r="D120" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7170,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -7182,10 +7179,10 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -7202,10 +7199,10 @@
         <v>265</v>
       </c>
       <c r="C121">
-        <v>0.9961878061294556</v>
+        <v>0.9993798732757568</v>
       </c>
       <c r="D121" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7220,7 +7217,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -7232,10 +7229,10 @@
         <v>0</v>
       </c>
       <c r="M121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -7252,10 +7249,10 @@
         <v>266</v>
       </c>
       <c r="C122">
-        <v>0.9993798732757568</v>
+        <v>0.9990472793579102</v>
       </c>
       <c r="D122" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7270,7 +7267,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -7302,10 +7299,10 @@
         <v>267</v>
       </c>
       <c r="C123">
-        <v>0.9990472793579102</v>
+        <v>0.9991445541381836</v>
       </c>
       <c r="D123" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7320,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -7335,7 +7332,7 @@
         <v>2</v>
       </c>
       <c r="N123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -7352,10 +7349,10 @@
         <v>268</v>
       </c>
       <c r="C124">
-        <v>0.9991445541381836</v>
+        <v>0.9142532348632812</v>
       </c>
       <c r="D124" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7370,7 +7367,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -7385,7 +7382,7 @@
         <v>2</v>
       </c>
       <c r="N124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -7402,10 +7399,10 @@
         <v>269</v>
       </c>
       <c r="C125">
-        <v>0.9142532348632812</v>
+        <v>0.9972384572029114</v>
       </c>
       <c r="D125" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7420,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -7432,10 +7429,10 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N125">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -7452,10 +7449,10 @@
         <v>270</v>
       </c>
       <c r="C126">
-        <v>0.9972384572029114</v>
+        <v>0.9960039258003235</v>
       </c>
       <c r="D126" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7470,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -7482,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -7502,10 +7499,10 @@
         <v>271</v>
       </c>
       <c r="C127">
-        <v>0.9960039258003235</v>
+        <v>0.9987621903419495</v>
       </c>
       <c r="D127" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7520,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -7532,10 +7529,10 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -7552,10 +7549,10 @@
         <v>272</v>
       </c>
       <c r="C128">
-        <v>0.9987621903419495</v>
+        <v>0.9937299489974976</v>
       </c>
       <c r="D128" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7570,7 +7567,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -7582,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="M128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -7602,10 +7599,10 @@
         <v>273</v>
       </c>
       <c r="C129">
-        <v>0.9937299489974976</v>
+        <v>0.9990777969360352</v>
       </c>
       <c r="D129" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -7620,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -7632,10 +7629,10 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -7652,10 +7649,10 @@
         <v>274</v>
       </c>
       <c r="C130">
-        <v>0.9990777969360352</v>
+        <v>0.9922806620597839</v>
       </c>
       <c r="D130" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -7670,7 +7667,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -7702,10 +7699,10 @@
         <v>275</v>
       </c>
       <c r="C131">
-        <v>0.9922806620597839</v>
+        <v>0.9937021136283875</v>
       </c>
       <c r="D131" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -7720,10 +7717,10 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -7732,10 +7729,10 @@
         <v>0</v>
       </c>
       <c r="M131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -7752,10 +7749,10 @@
         <v>276</v>
       </c>
       <c r="C132">
-        <v>0.9937021136283875</v>
+        <v>0.9984290599822998</v>
       </c>
       <c r="D132" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7770,10 +7767,10 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -7782,10 +7779,10 @@
         <v>0</v>
       </c>
       <c r="M132">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -7802,10 +7799,10 @@
         <v>277</v>
       </c>
       <c r="C133">
-        <v>0.9984290599822998</v>
+        <v>0.9967972040176392</v>
       </c>
       <c r="D133" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7820,10 +7817,10 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -7832,10 +7829,10 @@
         <v>0</v>
       </c>
       <c r="M133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -7852,10 +7849,10 @@
         <v>278</v>
       </c>
       <c r="C134">
-        <v>0.9967972040176392</v>
+        <v>0.8547114133834839</v>
       </c>
       <c r="D134" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -7870,10 +7867,10 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134">
         <v>0</v>
@@ -7882,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="M134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N134">
         <v>0</v>
@@ -7891,56 +7888,6 @@
         <v>0</v>
       </c>
       <c r="P134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16">
-      <c r="A135" t="s">
-        <v>149</v>
-      </c>
-      <c r="B135" t="s">
-        <v>279</v>
-      </c>
-      <c r="C135">
-        <v>0.8547114133834839</v>
-      </c>
-      <c r="D135" t="s">
-        <v>280</v>
-      </c>
-      <c r="E135">
-        <v>0</v>
-      </c>
-      <c r="F135" t="b">
-        <v>0</v>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135" t="s">
-        <v>281</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>1</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
         <v>0</v>
       </c>
     </row>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -130,10 +130,10 @@
     <t>micro_0109_SL40III.jpg</t>
   </si>
   <si>
-    <t>micro_0295_SL4082600.jpg</t>
-  </si>
-  <si>
-    <t>micro_0296_SL407.jpg</t>
+    <t>micro_0291_SL4082600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0113_SL407.jpg</t>
   </si>
   <si>
     <t>micro_0112_SL406.jpg</t>
@@ -316,7 +316,7 @@
     <t>micro_0065_D402.jpg</t>
   </si>
   <si>
-    <t>micro_0290_D401.jpg</t>
+    <t>micro_0131_D401.jpg</t>
   </si>
   <si>
     <t>micro_0255_D250.jpg</t>
@@ -337,12 +337,12 @@
     <t>micro_0073_D242.jpg</t>
   </si>
   <si>
+    <t>micro_0090_OD240.jpg</t>
+  </si>
+  <si>
     <t>micro_0015_OOD240.jpg</t>
   </si>
   <si>
-    <t>micro_0090_OD240.jpg</t>
-  </si>
-  <si>
     <t>micro_0148_D2392000.jpg</t>
   </si>
   <si>
@@ -364,10 +364,10 @@
     <t>micro_0210_D233.jpg</t>
   </si>
   <si>
+    <t>micro_0249_OD232.jpg</t>
+  </si>
+  <si>
     <t>micro_0205_0D232.jpg</t>
-  </si>
-  <si>
-    <t>micro_0249_OD232.jpg</t>
   </si>
   <si>
     <t>micro_0182_D231.jpg</t>
@@ -2349,7 +2349,7 @@
         <v>171</v>
       </c>
       <c r="C24">
-        <v>0.982405424118042</v>
+        <v>0.9938239455223083</v>
       </c>
       <c r="D24" t="s">
         <v>279</v>
@@ -2399,7 +2399,7 @@
         <v>172</v>
       </c>
       <c r="C25">
-        <v>0.9976034164428711</v>
+        <v>0.9970995783805847</v>
       </c>
       <c r="D25" t="s">
         <v>279</v>
@@ -2423,10 +2423,10 @@
         <v>1</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -2782,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -5449,7 +5449,7 @@
         <v>232</v>
       </c>
       <c r="C86">
-        <v>0.9967367053031921</v>
+        <v>0.9969408512115479</v>
       </c>
       <c r="D86" t="s">
         <v>279</v>
@@ -5799,7 +5799,7 @@
         <v>239</v>
       </c>
       <c r="C93">
-        <v>0.9787474274635315</v>
+        <v>1</v>
       </c>
       <c r="D93" t="s">
         <v>279</v>
@@ -5849,7 +5849,7 @@
         <v>239</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0.9787474274635315</v>
       </c>
       <c r="D94" t="s">
         <v>279</v>
@@ -6249,7 +6249,7 @@
         <v>247</v>
       </c>
       <c r="C102">
-        <v>0.9913250803947449</v>
+        <v>1</v>
       </c>
       <c r="D102" t="s">
         <v>279</v>
@@ -6299,7 +6299,7 @@
         <v>247</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0.9913250803947449</v>
       </c>
       <c r="D103" t="s">
         <v>279</v>
@@ -6482,7 +6482,7 @@
         <v>1</v>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -6782,7 +6782,7 @@
         <v>2</v>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -6882,7 +6882,7 @@
         <v>2</v>
       </c>
       <c r="N114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="N131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O131">
         <v>0</v>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="283">
   <si>
     <t>filename</t>
   </si>
@@ -64,403 +64,406 @@
     <t>is_double</t>
   </si>
   <si>
-    <t>micro_0192_YSB_II.jpg</t>
-  </si>
-  <si>
-    <t>micro_0103_1700XL1_80_00.jpg</t>
-  </si>
-  <si>
-    <t>micro_0234_XJOO.jpg</t>
-  </si>
-  <si>
-    <t>micro_0031_1700X400.jpg</t>
-  </si>
-  <si>
-    <t>micro_0160_2300X408.jpg</t>
-  </si>
-  <si>
-    <t>micro_0159_1700X407.jpg</t>
-  </si>
-  <si>
-    <t>micro_0157_2300X406.jpg</t>
-  </si>
-  <si>
-    <t>micro_0156_1700X405.jpg</t>
-  </si>
-  <si>
-    <t>micro_0155_2300X404.jpg</t>
-  </si>
-  <si>
-    <t>micro_0029_2300X402.jpg</t>
-  </si>
-  <si>
-    <t>micro_0142_X401.jpg</t>
-  </si>
-  <si>
-    <t>micro_0141_X325.jpg</t>
-  </si>
-  <si>
-    <t>micro_0075_X20VI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0140_X209.jpg</t>
-  </si>
-  <si>
-    <t>micro_0139_X208.jpg</t>
-  </si>
-  <si>
-    <t>micro_0138_X207.jpg</t>
-  </si>
-  <si>
-    <t>micro_0079_X206.jpg</t>
-  </si>
-  <si>
-    <t>micro_0135_X205.jpg</t>
-  </si>
-  <si>
-    <t>micro_0074_X203.jpg</t>
-  </si>
-  <si>
-    <t>micro_0168_1700X202.jpg</t>
-  </si>
-  <si>
-    <t>micro_0167_2300X201.jpg</t>
-  </si>
-  <si>
-    <t>micro_0109_SL40III.jpg</t>
-  </si>
-  <si>
-    <t>micro_0291_SL4082600.jpg</t>
-  </si>
-  <si>
-    <t>micro_0113_SL407.jpg</t>
-  </si>
-  <si>
-    <t>micro_0112_SL406.jpg</t>
-  </si>
-  <si>
-    <t>micro_0111_SL405.jpg</t>
-  </si>
-  <si>
-    <t>micro_0110_SL404.jpg</t>
-  </si>
-  <si>
-    <t>micro_0108_SL402.jpg</t>
-  </si>
-  <si>
-    <t>micro_0105_SL401.jpg</t>
-  </si>
-  <si>
-    <t>micro_0152_SL301.jpg</t>
-  </si>
-  <si>
-    <t>micro_0185_OO_0_SL20VI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0273_SL203.jpg</t>
-  </si>
-  <si>
-    <t>micro_0212_SL202.jpg</t>
-  </si>
-  <si>
-    <t>micro_0211_SL201.jpg</t>
-  </si>
-  <si>
-    <t>micro_0190_O_SBII.jpg</t>
-  </si>
-  <si>
-    <t>micro_0289_SBI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0231_FX201.jpg</t>
-  </si>
-  <si>
-    <t>micro_0287_FSL20VI.jpg</t>
-  </si>
-  <si>
-    <t>micro_0272_AFSL201.jpg</t>
-  </si>
-  <si>
-    <t>micro_0007_0D527.jpg</t>
-  </si>
-  <si>
-    <t>micro_0096_D523.jpg</t>
-  </si>
-  <si>
-    <t>micro_0095_D521.jpg</t>
-  </si>
-  <si>
-    <t>micro_0098_D519.jpg</t>
-  </si>
-  <si>
-    <t>micro_0100_D517.jpg</t>
-  </si>
-  <si>
-    <t>micro_0226_D515.jpg</t>
-  </si>
-  <si>
-    <t>micro_0218_D514.jpg</t>
-  </si>
-  <si>
-    <t>micro_0270_D513.jpg</t>
-  </si>
-  <si>
-    <t>micro_0230_D512.jpg</t>
-  </si>
-  <si>
-    <t>micro_0271_D511.jpg</t>
-  </si>
-  <si>
-    <t>micro_0010_D510.jpg</t>
-  </si>
-  <si>
-    <t>micro_0201_D509.jpg</t>
-  </si>
-  <si>
-    <t>micro_0164_D508.jpg</t>
-  </si>
-  <si>
-    <t>micro_0199_D507.jpg</t>
-  </si>
-  <si>
-    <t>micro_0220_D506.jpg</t>
-  </si>
-  <si>
-    <t>micro_0264_D505.jpg</t>
-  </si>
-  <si>
-    <t>micro_0163_D504.jpg</t>
-  </si>
-  <si>
-    <t>micro_0114_O_D503.jpg</t>
-  </si>
-  <si>
-    <t>micro_0166_D502.jpg</t>
-  </si>
-  <si>
-    <t>micro_0117_D501.jpg</t>
-  </si>
-  <si>
-    <t>micro_0209_D501.jpg</t>
-  </si>
-  <si>
-    <t>micro_0034_D432.jpg</t>
-  </si>
-  <si>
-    <t>micro_0032_D430.jpg</t>
-  </si>
-  <si>
-    <t>micro_0035_D426.jpg</t>
-  </si>
-  <si>
-    <t>micro_0056_D424.jpg</t>
-  </si>
-  <si>
-    <t>micro_0049_D422.jpg</t>
-  </si>
-  <si>
-    <t>micro_0051_D420.jpg</t>
-  </si>
-  <si>
-    <t>micro_0104_D419.jpg</t>
-  </si>
-  <si>
-    <t>micro_0025_D418.jpg</t>
-  </si>
-  <si>
-    <t>micro_0275_0D417.jpg</t>
-  </si>
-  <si>
-    <t>micro_0066_D416.jpg</t>
-  </si>
-  <si>
-    <t>micro_0281_D415.jpg</t>
-  </si>
-  <si>
-    <t>micro_0064_D414.jpg</t>
-  </si>
-  <si>
-    <t>micro_0283_D413.jpg</t>
-  </si>
-  <si>
-    <t>micro_0047_D412.jpg</t>
-  </si>
-  <si>
-    <t>micro_0277_D411.jpg</t>
-  </si>
-  <si>
-    <t>micro_0057_D410.jpg</t>
-  </si>
-  <si>
-    <t>micro_0279_D409.jpg</t>
-  </si>
-  <si>
-    <t>micro_0063_D408.jpg</t>
-  </si>
-  <si>
-    <t>micro_0132_D407.jpg</t>
-  </si>
-  <si>
-    <t>micro_0263_D406.jpg</t>
-  </si>
-  <si>
-    <t>micro_0296_D405.jpg</t>
-  </si>
-  <si>
-    <t>micro_0261_D404.jpg</t>
-  </si>
-  <si>
-    <t>micro_0133_YD409_D403.jpg</t>
-  </si>
-  <si>
-    <t>micro_0065_D402.jpg</t>
-  </si>
-  <si>
-    <t>micro_0131_D401.jpg</t>
-  </si>
-  <si>
-    <t>micro_0255_D250.jpg</t>
-  </si>
-  <si>
-    <t>micro_0071_D248.jpg</t>
-  </si>
-  <si>
-    <t>micro_0151_D2472600.jpg</t>
-  </si>
-  <si>
-    <t>micro_0016_D246.jpg</t>
-  </si>
-  <si>
-    <t>micro_0150_D245.jpg</t>
-  </si>
-  <si>
-    <t>micro_0073_D242.jpg</t>
-  </si>
-  <si>
-    <t>micro_0090_OD240.jpg</t>
-  </si>
-  <si>
-    <t>micro_0015_OOD240.jpg</t>
-  </si>
-  <si>
-    <t>micro_0148_D2392000.jpg</t>
-  </si>
-  <si>
-    <t>micro_0018_D238.jpg</t>
-  </si>
-  <si>
-    <t>micro_0147_D2372600.jpg</t>
-  </si>
-  <si>
-    <t>micro_0021_2D236.jpg</t>
-  </si>
-  <si>
-    <t>micro_0043_D235.jpg</t>
-  </si>
-  <si>
-    <t>micro_0203_0D234.jpg</t>
-  </si>
-  <si>
-    <t>micro_0210_D233.jpg</t>
-  </si>
-  <si>
-    <t>micro_0249_OD232.jpg</t>
-  </si>
-  <si>
-    <t>micro_0205_0D232.jpg</t>
-  </si>
-  <si>
-    <t>micro_0182_D231.jpg</t>
-  </si>
-  <si>
-    <t>micro_0252_OOD230.jpg</t>
-  </si>
-  <si>
-    <t>micro_0237_D229.jpg</t>
-  </si>
-  <si>
-    <t>micro_0256_D228.jpg</t>
-  </si>
-  <si>
-    <t>micro_0042_D227.jpg</t>
-  </si>
-  <si>
-    <t>micro_0254_D226.jpg</t>
-  </si>
-  <si>
-    <t>micro_0183_D225.jpg</t>
-  </si>
-  <si>
-    <t>micro_0125_D224.jpg</t>
-  </si>
-  <si>
-    <t>micro_0235_D223.jpg</t>
-  </si>
-  <si>
-    <t>micro_0129_D222.jpg</t>
-  </si>
-  <si>
-    <t>micro_0239_D221.jpg</t>
-  </si>
-  <si>
-    <t>micro_0127_D220.jpg</t>
-  </si>
-  <si>
-    <t>micro_0170_D219.jpg</t>
-  </si>
-  <si>
-    <t>micro_0126_D218.jpg</t>
-  </si>
-  <si>
-    <t>micro_0244_D217.jpg</t>
-  </si>
-  <si>
-    <t>micro_0087_D216.jpg</t>
-  </si>
-  <si>
-    <t>micro_0175_D215.jpg</t>
-  </si>
-  <si>
-    <t>micro_0086_D214.jpg</t>
-  </si>
-  <si>
-    <t>micro_0179_D213.jpg</t>
-  </si>
-  <si>
-    <t>micro_0083_D212.jpg</t>
-  </si>
-  <si>
-    <t>micro_0246_D211.jpg</t>
-  </si>
-  <si>
-    <t>micro_0084_D210.jpg</t>
-  </si>
-  <si>
-    <t>micro_0245_D209.jpg</t>
-  </si>
-  <si>
-    <t>micro_0088_D208.jpg</t>
-  </si>
-  <si>
-    <t>micro_0241_D207.jpg</t>
-  </si>
-  <si>
-    <t>micro_0081_D206.jpg</t>
+    <t>micro_0008_YSB_II.jpg</t>
+  </si>
+  <si>
+    <t>micro_0123_1700XL1_80_00.jpg</t>
+  </si>
+  <si>
+    <t>micro_0286_XJ.jpg</t>
+  </si>
+  <si>
+    <t>micro_0036_1700X400.jpg</t>
+  </si>
+  <si>
+    <t>micro_0194_2300X408.jpg</t>
+  </si>
+  <si>
+    <t>micro_0193_1700X407.jpg</t>
+  </si>
+  <si>
+    <t>micro_0191_2300X406.jpg</t>
+  </si>
+  <si>
+    <t>micro_0190_1700X405.jpg</t>
+  </si>
+  <si>
+    <t>micro_0189_2300X404.jpg</t>
+  </si>
+  <si>
+    <t>micro_0171_2300X402.jpg</t>
+  </si>
+  <si>
+    <t>micro_0031_X401.jpg</t>
+  </si>
+  <si>
+    <t>micro_0166_X325.jpg</t>
+  </si>
+  <si>
+    <t>micro_0087_X20VI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0165_X209.jpg</t>
+  </si>
+  <si>
+    <t>micro_0164_X208.jpg</t>
+  </si>
+  <si>
+    <t>micro_0173_X2070.jpg</t>
+  </si>
+  <si>
+    <t>micro_0091_X206.jpg</t>
+  </si>
+  <si>
+    <t>micro_0160_X205.jpg</t>
+  </si>
+  <si>
+    <t>micro_0086_X203.jpg</t>
+  </si>
+  <si>
+    <t>micro_0206_1700X202.jpg</t>
+  </si>
+  <si>
+    <t>micro_0207_X201.jpg</t>
+  </si>
+  <si>
+    <t>micro_0135_00SL40II.jpg</t>
+  </si>
+  <si>
+    <t>micro_0356_SL4082600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0356_SL407.jpg</t>
+  </si>
+  <si>
+    <t>micro_0132_SL406.jpg</t>
+  </si>
+  <si>
+    <t>micro_0131_SL405.jpg</t>
+  </si>
+  <si>
+    <t>micro_0130_SL404.jpg</t>
+  </si>
+  <si>
+    <t>micro_0345_SL402.jpg</t>
+  </si>
+  <si>
+    <t>micro_0344_SL401.jpg</t>
+  </si>
+  <si>
+    <t>micro_0343_SL301.jpg</t>
+  </si>
+  <si>
+    <t>micro_0046_OO_SL20VI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0261_SL2032600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0260_SL202.jpg</t>
+  </si>
+  <si>
+    <t>micro_0259_SL201.jpg</t>
+  </si>
+  <si>
+    <t>micro_0233_O_SBII.jpg</t>
+  </si>
+  <si>
+    <t>micro_0349_SBI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0282_FX201.jpg</t>
+  </si>
+  <si>
+    <t>micro_0346_FSL20VI.jpg</t>
+  </si>
+  <si>
+    <t>micro_0331_AFSL201.jpg</t>
+  </si>
+  <si>
+    <t>micro_0017_D527.jpg</t>
+  </si>
+  <si>
+    <t>micro_0116_D523.jpg</t>
+  </si>
+  <si>
+    <t>micro_0115_D521.jpg</t>
+  </si>
+  <si>
+    <t>micro_0118_D519.jpg</t>
+  </si>
+  <si>
+    <t>micro_0279_D517.jpg</t>
+  </si>
+  <si>
+    <t>micro_0324_D515.jpg</t>
+  </si>
+  <si>
+    <t>micro_0280_D514.jpg</t>
+  </si>
+  <si>
+    <t>micro_0329_D513.jpg</t>
+  </si>
+  <si>
+    <t>micro_0272_D512.jpg</t>
+  </si>
+  <si>
+    <t>micro_0330_D511.jpg</t>
+  </si>
+  <si>
+    <t>micro_0268_D510.jpg</t>
+  </si>
+  <si>
+    <t>micro_0245_D509.jpg</t>
+  </si>
+  <si>
+    <t>micro_0270_D508.jpg</t>
+  </si>
+  <si>
+    <t>micro_0326_D507.jpg</t>
+  </si>
+  <si>
+    <t>micro_0203_D506.jpg</t>
+  </si>
+  <si>
+    <t>micro_0323_D505.jpg</t>
+  </si>
+  <si>
+    <t>micro_0142_D504.jpg</t>
+  </si>
+  <si>
+    <t>micro_0137_O_D503.jpg</t>
+  </si>
+  <si>
+    <t>micro_0204_D502.jpg</t>
+  </si>
+  <si>
+    <t>micro_0257_D501.jpg</t>
+  </si>
+  <si>
+    <t>micro_0140_D501.jpg</t>
+  </si>
+  <si>
+    <t>micro_0039_D432.jpg</t>
+  </si>
+  <si>
+    <t>micro_0037_D430.jpg</t>
+  </si>
+  <si>
+    <t>micro_0062_D426.jpg</t>
+  </si>
+  <si>
+    <t>micro_0042_D424.jpg</t>
+  </si>
+  <si>
+    <t>micro_0057_D422.jpg</t>
+  </si>
+  <si>
+    <t>micro_0059_D420.jpg</t>
+  </si>
+  <si>
+    <t>micro_0051_D419.jpg</t>
+  </si>
+  <si>
+    <t>micro_0028_D418.jpg</t>
+  </si>
+  <si>
+    <t>micro_0134_D417.jpg</t>
+  </si>
+  <si>
+    <t>micro_0061_D416.jpg</t>
+  </si>
+  <si>
+    <t>micro_0340_D415.jpg</t>
+  </si>
+  <si>
+    <t>micro_0074_D414.jpg</t>
+  </si>
+  <si>
+    <t>micro_0342_D413.jpg</t>
+  </si>
+  <si>
+    <t>micro_0068_D412.jpg</t>
+  </si>
+  <si>
+    <t>micro_0336_D411.jpg</t>
+  </si>
+  <si>
+    <t>micro_0067_D410.jpg</t>
+  </si>
+  <si>
+    <t>micro_0338_D409.jpg</t>
+  </si>
+  <si>
+    <t>micro_0073_D408.jpg</t>
+  </si>
+  <si>
+    <t>micro_0335_D407.jpg</t>
+  </si>
+  <si>
+    <t>micro_0072_D406.jpg</t>
+  </si>
+  <si>
+    <t>micro_0354_D405.jpg</t>
+  </si>
+  <si>
+    <t>micro_0070_D404.jpg</t>
+  </si>
+  <si>
+    <t>micro_0157_YD409_D403.jpg</t>
+  </si>
+  <si>
+    <t>micro_0075_D402.jpg</t>
+  </si>
+  <si>
+    <t>micro_0352_D401.jpg</t>
+  </si>
+  <si>
+    <t>micro_0309_D250.jpg</t>
+  </si>
+  <si>
+    <t>micro_0083_D248.jpg</t>
+  </si>
+  <si>
+    <t>micro_0186_D247.jpg</t>
+  </si>
+  <si>
+    <t>micro_0111_D246.jpg</t>
+  </si>
+  <si>
+    <t>micro_0178_D245.jpg</t>
+  </si>
+  <si>
+    <t>micro_0030_D244.jpg</t>
+  </si>
+  <si>
+    <t>micro_0085_D242.jpg</t>
+  </si>
+  <si>
+    <t>micro_0109_OD240.jpg</t>
+  </si>
+  <si>
+    <t>micro_0319_D240.jpg</t>
+  </si>
+  <si>
+    <t>micro_0183_D239.jpg</t>
+  </si>
+  <si>
+    <t>micro_0021_D238.jpg</t>
+  </si>
+  <si>
+    <t>micro_0266_D237.jpg</t>
+  </si>
+  <si>
+    <t>micro_0307_AD236.jpg</t>
+  </si>
+  <si>
+    <t>micro_0177_D2352600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0318_D234.jpg</t>
+  </si>
+  <si>
+    <t>micro_0258_D233.jpg</t>
+  </si>
+  <si>
+    <t>micro_0254_D232.jpg</t>
+  </si>
+  <si>
+    <t>micro_0303_OD232.jpg</t>
+  </si>
+  <si>
+    <t>micro_0224_D231.jpg</t>
+  </si>
+  <si>
+    <t>micro_0321_D230.jpg</t>
+  </si>
+  <si>
+    <t>micro_0047_D229.jpg</t>
+  </si>
+  <si>
+    <t>micro_0310_D228.jpg</t>
+  </si>
+  <si>
+    <t>micro_0295_D227.jpg</t>
+  </si>
+  <si>
+    <t>micro_0308_D226.jpg</t>
+  </si>
+  <si>
+    <t>micro_0210_D225.jpg</t>
+  </si>
+  <si>
+    <t>micro_0148_D224.jpg</t>
+  </si>
+  <si>
+    <t>micro_0211_D223.jpg</t>
+  </si>
+  <si>
+    <t>micro_0152_D222.jpg</t>
+  </si>
+  <si>
+    <t>micro_0215_D221.jpg</t>
+  </si>
+  <si>
+    <t>micro_0150_D220.jpg</t>
+  </si>
+  <si>
+    <t>micro_0221_OD219.jpg</t>
+  </si>
+  <si>
+    <t>micro_0149_D218.jpg</t>
+  </si>
+  <si>
+    <t>micro_0296_D217.jpg</t>
+  </si>
+  <si>
+    <t>micro_0153_D216.jpg</t>
+  </si>
+  <si>
+    <t>micro_0214_D215.jpg</t>
+  </si>
+  <si>
+    <t>micro_0101_D214.jpg</t>
+  </si>
+  <si>
+    <t>micro_0218_D213.jpg</t>
+  </si>
+  <si>
+    <t>micro_0106_OD212.jpg</t>
+  </si>
+  <si>
+    <t>micro_0300_0_D211.jpg</t>
+  </si>
+  <si>
+    <t>micro_0107_D210O.jpg</t>
+  </si>
+  <si>
+    <t>micro_0297_D209.jpg</t>
+  </si>
+  <si>
+    <t>micro_0103_D208.jpg</t>
+  </si>
+  <si>
+    <t>micro_0081_D207.jpg</t>
+  </si>
+  <si>
+    <t>micro_0105_D2060.jpg</t>
   </si>
   <si>
     <t>micro_0000_DD205.jpg</t>
   </si>
   <si>
-    <t>micro_0193_D204.jpg</t>
-  </si>
-  <si>
-    <t>micro_0169_D203.jpg</t>
-  </si>
-  <si>
-    <t>micro_0189_D202.jpg</t>
-  </si>
-  <si>
-    <t>micro_0068_D201_QO.jpg</t>
+    <t>micro_0236_D204.jpg</t>
+  </si>
+  <si>
+    <t>micro_0208_D203.jpg</t>
+  </si>
+  <si>
+    <t>micro_0276_D202.jpg</t>
+  </si>
+  <si>
+    <t>micro_0004_D201.jpg</t>
   </si>
   <si>
     <t>YSBⅡ</t>
@@ -728,6 +731,9 @@
   </si>
   <si>
     <t>D245</t>
+  </si>
+  <si>
+    <t>D244</t>
   </si>
   <si>
     <t>D242</t>
@@ -1188,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P134"/>
+  <dimension ref="A1:P135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1246,13 +1252,13 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C2">
-        <v>0.922767162322998</v>
+        <v>0.9714210629463196</v>
       </c>
       <c r="D2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1267,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1296,13 +1302,13 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C3">
         <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1317,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1346,13 +1352,13 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4">
-        <v>0.9991193413734436</v>
+        <v>0.9916391372680664</v>
       </c>
       <c r="D4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1367,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1396,13 +1402,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5">
         <v>0.9360489845275879</v>
       </c>
       <c r="D5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1417,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1446,13 +1452,13 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C6">
         <v>0.9898043870925903</v>
       </c>
       <c r="D6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1467,7 +1473,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1496,13 +1502,13 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C7">
         <v>0.9800205826759338</v>
       </c>
       <c r="D7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1517,7 +1523,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1546,13 +1552,13 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C8">
         <v>0.9866096377372742</v>
       </c>
       <c r="D8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1567,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1596,13 +1602,13 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C9">
         <v>0.9825887680053711</v>
       </c>
       <c r="D9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1617,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1646,13 +1652,13 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C10">
         <v>0.9854358434677124</v>
       </c>
       <c r="D10" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1667,7 +1673,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1696,13 +1702,13 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11">
-        <v>0.9869511127471924</v>
+        <v>0.9839249849319458</v>
       </c>
       <c r="D11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1717,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1746,13 +1752,13 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12">
-        <v>0.9883586168289185</v>
+        <v>0.9880355000495911</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1767,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1796,13 +1802,13 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13">
         <v>0.9827210903167725</v>
       </c>
       <c r="D13" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1817,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1846,13 +1852,13 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14">
         <v>0.8711124062538147</v>
       </c>
       <c r="D14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1867,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1896,13 +1902,13 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C15">
         <v>0.9849019646644592</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1917,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1946,13 +1952,13 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C16">
         <v>0.9831116795539856</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1967,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -1996,13 +2002,13 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C17">
-        <v>0.979184627532959</v>
+        <v>0.9768341779708862</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2017,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2046,13 +2052,13 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18">
         <v>0.9820773601531982</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2067,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2096,13 +2102,13 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19">
         <v>0.9926210641860962</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2117,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2146,13 +2152,13 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C20">
         <v>0.991193413734436</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2167,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2196,13 +2202,13 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C21">
         <v>0.9759405851364136</v>
       </c>
       <c r="D21" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2217,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2246,13 +2252,13 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C22">
-        <v>0.9936316609382629</v>
+        <v>0.9946767091751099</v>
       </c>
       <c r="D22" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2267,7 +2273,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2282,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -2296,13 +2302,13 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C23">
-        <v>0.9834394454956055</v>
+        <v>0.9923974871635437</v>
       </c>
       <c r="D23" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2317,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2346,13 +2352,13 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24">
         <v>0.9938239455223083</v>
       </c>
       <c r="D24" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2367,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2396,13 +2402,13 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25">
-        <v>0.9970995783805847</v>
+        <v>0.9959491491317749</v>
       </c>
       <c r="D25" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2417,16 +2423,16 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J25">
         <v>1</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -2446,13 +2452,13 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C26">
         <v>0.9976895451545715</v>
       </c>
       <c r="D26" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2467,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2496,13 +2502,13 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C27">
         <v>0.9959992170333862</v>
       </c>
       <c r="D27" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2517,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2546,13 +2552,13 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C28">
         <v>0.9971073865890503</v>
       </c>
       <c r="D28" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2567,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2596,13 +2602,13 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C29">
         <v>0.9968833923339844</v>
       </c>
       <c r="D29" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2617,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2646,13 +2652,13 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C30">
-        <v>0.9585862159729004</v>
+        <v>0.9933208227157593</v>
       </c>
       <c r="D30" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2667,7 +2673,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2696,13 +2702,13 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C31">
-        <v>0.9984833598136902</v>
+        <v>0.9971753358840942</v>
       </c>
       <c r="D31" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2717,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2746,13 +2752,13 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C32">
-        <v>0.9960424304008484</v>
+        <v>0.9958525896072388</v>
       </c>
       <c r="D32" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2767,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2779,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="M32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -2796,13 +2802,13 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C33">
-        <v>0.9988101124763489</v>
+        <v>0.9987233877182007</v>
       </c>
       <c r="D33" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2817,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2846,13 +2852,13 @@
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C34">
         <v>0.9754772186279297</v>
       </c>
       <c r="D34" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2867,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2896,13 +2902,13 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C35">
         <v>0.9673787951469421</v>
       </c>
       <c r="D35" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2917,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2946,13 +2952,13 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36">
         <v>0.7677456140518188</v>
       </c>
       <c r="D36" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2967,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2996,13 +3002,13 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C37">
-        <v>0.8940553665161133</v>
+        <v>0.9030734300613403</v>
       </c>
       <c r="D37" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3017,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -3046,13 +3052,13 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C38">
         <v>0.9965819120407104</v>
       </c>
       <c r="D38" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -3067,7 +3073,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -3096,13 +3102,13 @@
         <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C39">
         <v>0.9989708662033081</v>
       </c>
       <c r="D39" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3117,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -3146,13 +3152,13 @@
         <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C40">
         <v>0.9991652369499207</v>
       </c>
       <c r="D40" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3167,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -3196,13 +3202,13 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C41">
-        <v>0.9991592764854431</v>
+        <v>0.9989938735961914</v>
       </c>
       <c r="D41" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3217,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -3229,10 +3235,10 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -3246,13 +3252,13 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C42">
         <v>0.9991186261177063</v>
       </c>
       <c r="D42" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3267,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3296,13 +3302,13 @@
         <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C43">
         <v>0.9952852725982666</v>
       </c>
       <c r="D43" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3317,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3346,13 +3352,13 @@
         <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C44">
         <v>0.9953067898750305</v>
       </c>
       <c r="D44" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3367,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3396,13 +3402,13 @@
         <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C45">
-        <v>0.9992667436599731</v>
+        <v>0.9992556571960449</v>
       </c>
       <c r="D45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3417,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3446,13 +3452,13 @@
         <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C46">
-        <v>0.9991705417633057</v>
+        <v>0.9994583129882812</v>
       </c>
       <c r="D46" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3467,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3482,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -3496,13 +3502,13 @@
         <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C47">
-        <v>0.999667763710022</v>
+        <v>0.9995577931404114</v>
       </c>
       <c r="D47" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3517,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3532,7 +3538,7 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -3546,13 +3552,13 @@
         <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C48">
         <v>0.9995352625846863</v>
       </c>
       <c r="D48" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3567,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3596,13 +3602,13 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C49">
-        <v>0.9993976354598999</v>
+        <v>0.999538242816925</v>
       </c>
       <c r="D49" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3617,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3646,13 +3652,13 @@
         <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C50">
         <v>0.9994799494743347</v>
       </c>
       <c r="D50" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3667,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3696,13 +3702,13 @@
         <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C51">
-        <v>0.9982963800430298</v>
+        <v>0.9944444894790649</v>
       </c>
       <c r="D51" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3717,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3746,13 +3752,13 @@
         <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C52">
         <v>0.998166561126709</v>
       </c>
       <c r="D52" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3767,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3796,13 +3802,13 @@
         <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C53">
-        <v>0.9988658428192139</v>
+        <v>0.9985004067420959</v>
       </c>
       <c r="D53" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3817,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3846,13 +3852,13 @@
         <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C54">
-        <v>0.9980804920196533</v>
+        <v>0.9974443912506104</v>
       </c>
       <c r="D54" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3867,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3896,13 +3902,13 @@
         <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C55">
-        <v>0.9991114735603333</v>
+        <v>0.9989598989486694</v>
       </c>
       <c r="D55" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3917,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3932,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -3946,13 +3952,13 @@
         <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C56">
         <v>0.9987078905105591</v>
       </c>
       <c r="D56" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3967,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3996,13 +4002,13 @@
         <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C57">
-        <v>0.9991089701652527</v>
+        <v>0.9985486268997192</v>
       </c>
       <c r="D57" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4017,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -4046,13 +4052,13 @@
         <v>72</v>
       </c>
       <c r="B58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C58">
         <v>0.9810042381286621</v>
       </c>
       <c r="D58" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4067,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -4096,13 +4102,13 @@
         <v>73</v>
       </c>
       <c r="B59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C59">
         <v>0.9990440607070923</v>
       </c>
       <c r="D59" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -4117,7 +4123,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4146,13 +4152,13 @@
         <v>74</v>
       </c>
       <c r="B60" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C60">
-        <v>0.9949619770050049</v>
+        <v>1</v>
       </c>
       <c r="D60" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4167,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -4196,13 +4202,13 @@
         <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0.9949619770050049</v>
       </c>
       <c r="D61" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -4217,7 +4223,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -4246,13 +4252,13 @@
         <v>76</v>
       </c>
       <c r="B62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C62">
         <v>0.9984354376792908</v>
       </c>
       <c r="D62" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -4267,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -4296,13 +4302,13 @@
         <v>77</v>
       </c>
       <c r="B63" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C63">
         <v>0.9993854761123657</v>
       </c>
       <c r="D63" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4317,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -4346,13 +4352,13 @@
         <v>78</v>
       </c>
       <c r="B64" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C64">
-        <v>0.9993329048156738</v>
+        <v>0.999595582485199</v>
       </c>
       <c r="D64" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4367,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4396,13 +4402,13 @@
         <v>79</v>
       </c>
       <c r="B65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C65">
-        <v>0.9969677925109863</v>
+        <v>0.9975582957267761</v>
       </c>
       <c r="D65" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4417,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4446,13 +4452,13 @@
         <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C66">
         <v>0.9995519518852234</v>
       </c>
       <c r="D66" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4467,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4496,13 +4502,13 @@
         <v>81</v>
       </c>
       <c r="B67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C67">
         <v>0.9992239475250244</v>
       </c>
       <c r="D67" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4517,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4546,13 +4552,13 @@
         <v>82</v>
       </c>
       <c r="B68" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C68">
-        <v>0.9972553253173828</v>
+        <v>0.9989912509918213</v>
       </c>
       <c r="D68" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4567,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4596,13 +4602,13 @@
         <v>83</v>
       </c>
       <c r="B69" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C69">
         <v>0.9980692267417908</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4617,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4646,13 +4652,13 @@
         <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C70">
-        <v>0.9959254264831543</v>
+        <v>0.9993839859962463</v>
       </c>
       <c r="D70" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4667,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4696,13 +4702,13 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C71">
-        <v>0.9990965127944946</v>
+        <v>0.9957826137542725</v>
       </c>
       <c r="D71" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4717,7 +4723,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4746,13 +4752,13 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C72">
         <v>0.9995350241661072</v>
       </c>
       <c r="D72" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4767,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4796,13 +4802,13 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C73">
         <v>0.9991962909698486</v>
       </c>
       <c r="D73" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4817,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4846,13 +4852,13 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C74">
         <v>0.9979453086853027</v>
       </c>
       <c r="D74" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4867,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4896,13 +4902,13 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C75">
-        <v>0.9969654083251953</v>
+        <v>0.9963642954826355</v>
       </c>
       <c r="D75" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4917,7 +4923,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4932,7 +4938,7 @@
         <v>2</v>
       </c>
       <c r="N75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -4946,13 +4952,13 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C76">
         <v>0.9930816888809204</v>
       </c>
       <c r="D76" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4967,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4996,13 +5002,13 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C77">
         <v>0.8460029363632202</v>
       </c>
       <c r="D77" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5017,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -5046,13 +5052,13 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C78">
         <v>0.9959526658058167</v>
       </c>
       <c r="D78" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5067,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -5096,13 +5102,13 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C79">
         <v>0.9994586706161499</v>
       </c>
       <c r="D79" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5117,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -5146,13 +5152,13 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C80">
-        <v>0.996728241443634</v>
+        <v>0.9977346062660217</v>
       </c>
       <c r="D80" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5167,7 +5173,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -5182,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -5196,13 +5202,13 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C81">
-        <v>0.9973512291908264</v>
+        <v>0.9993370175361633</v>
       </c>
       <c r="D81" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5217,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -5246,13 +5252,13 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C82">
         <v>0.9980469942092896</v>
       </c>
       <c r="D82" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -5267,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -5296,13 +5302,13 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C83">
         <v>0.9978298544883728</v>
       </c>
       <c r="D83" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5317,7 +5323,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -5346,13 +5352,13 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C84">
         <v>0.8626171350479126</v>
       </c>
       <c r="D84" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5367,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -5396,13 +5402,13 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C85">
         <v>0.9972398281097412</v>
       </c>
       <c r="D85" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5417,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -5446,13 +5452,13 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C86">
-        <v>0.9969408512115479</v>
+        <v>0.9967367053031921</v>
       </c>
       <c r="D86" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5467,7 +5473,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -5496,13 +5502,13 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C87">
         <v>0.9915247559547424</v>
       </c>
       <c r="D87" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5517,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5546,13 +5552,13 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C88">
         <v>0.9995598793029785</v>
       </c>
       <c r="D88" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5567,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5596,13 +5602,13 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C89">
-        <v>0.8945754766464233</v>
+        <v>0.9988371133804321</v>
       </c>
       <c r="D89" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5617,7 +5623,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5646,13 +5652,13 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C90">
-        <v>0.9960287809371948</v>
+        <v>0.9977865815162659</v>
       </c>
       <c r="D90" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5667,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5696,13 +5702,13 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C91">
         <v>0.9991824626922607</v>
       </c>
       <c r="D91" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5717,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5746,13 +5752,13 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C92">
-        <v>0.9956748485565186</v>
+        <v>0.9949779510498047</v>
       </c>
       <c r="D92" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5767,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5796,13 +5802,13 @@
         <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>0.9956748485565186</v>
       </c>
       <c r="D93" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5817,7 +5823,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5846,13 +5852,13 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C94">
-        <v>0.9787474274635315</v>
+        <v>1</v>
       </c>
       <c r="D94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5867,7 +5873,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5896,13 +5902,13 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C95">
-        <v>0.9993278980255127</v>
+        <v>0.9924148321151733</v>
       </c>
       <c r="D95" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5917,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5932,7 +5938,7 @@
         <v>1</v>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -5946,13 +5952,13 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C96">
-        <v>0.9933540225028992</v>
+        <v>0.9990327954292297</v>
       </c>
       <c r="D96" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5967,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5982,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="N96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -5996,13 +6002,13 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C97">
-        <v>0.9988803863525391</v>
+        <v>0.9933540225028992</v>
       </c>
       <c r="D97" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6017,7 +6023,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -6046,13 +6052,13 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C98">
-        <v>0.9901755452156067</v>
+        <v>0.9992632269859314</v>
       </c>
       <c r="D98" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6067,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -6096,13 +6102,13 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C99">
-        <v>0.999345064163208</v>
+        <v>0.9882216453552246</v>
       </c>
       <c r="D99" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6117,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -6146,13 +6152,13 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C100">
-        <v>0.9616943597793579</v>
+        <v>0.9993331432342529</v>
       </c>
       <c r="D100" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6167,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -6182,7 +6188,7 @@
         <v>1</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -6196,13 +6202,13 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C101">
-        <v>0.8529298901557922</v>
+        <v>0.9826395511627197</v>
       </c>
       <c r="D101" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6217,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -6246,13 +6252,13 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0.8529298901557922</v>
       </c>
       <c r="D102" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6267,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -6279,10 +6285,10 @@
         <v>0</v>
       </c>
       <c r="M102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -6296,13 +6302,13 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C103">
-        <v>0.9913250803947449</v>
+        <v>0.9972063302993774</v>
       </c>
       <c r="D103" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6317,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -6346,13 +6352,13 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C104">
-        <v>0.9982128739356995</v>
+        <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6367,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -6379,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="M104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -6396,13 +6402,13 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C105">
-        <v>0.9876354336738586</v>
+        <v>0.9982128739356995</v>
       </c>
       <c r="D105" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6417,7 +6423,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -6429,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="M105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105">
         <v>0</v>
@@ -6446,13 +6452,13 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C106">
-        <v>0.9978511333465576</v>
+        <v>0.9911179542541504</v>
       </c>
       <c r="D106" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6467,22 +6473,22 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106">
         <v>1</v>
       </c>
       <c r="N106">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -6496,13 +6502,13 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C107">
-        <v>0.9994751811027527</v>
+        <v>0.9979790449142456</v>
       </c>
       <c r="D107" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6517,22 +6523,22 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M107">
         <v>1</v>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -6546,13 +6552,13 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C108">
-        <v>0.9982790946960449</v>
+        <v>0.9994751811027527</v>
       </c>
       <c r="D108" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6567,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6582,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="N108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -6596,13 +6602,13 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C109">
-        <v>0.9931647777557373</v>
+        <v>0.9983197450637817</v>
       </c>
       <c r="D109" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6617,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -6646,13 +6652,13 @@
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C110">
-        <v>0.9983500242233276</v>
+        <v>0.9931647777557373</v>
       </c>
       <c r="D110" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6667,7 +6673,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6679,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="M110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N110">
         <v>1</v>
@@ -6696,13 +6702,13 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C111">
-        <v>0.9937362670898438</v>
+        <v>0.9982962012290955</v>
       </c>
       <c r="D111" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6717,7 +6723,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6732,7 +6738,7 @@
         <v>1</v>
       </c>
       <c r="N111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -6746,13 +6752,13 @@
         <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C112">
-        <v>0.9989242553710938</v>
+        <v>0.9937362670898438</v>
       </c>
       <c r="D112" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6767,19 +6773,19 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N112">
         <v>2</v>
@@ -6796,13 +6802,13 @@
         <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C113">
-        <v>0.9987581372261047</v>
+        <v>0.9977945685386658</v>
       </c>
       <c r="D113" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6817,22 +6823,22 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113">
         <v>2</v>
       </c>
       <c r="N113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -6846,13 +6852,13 @@
         <v>128</v>
       </c>
       <c r="B114" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C114">
-        <v>0.9983271360397339</v>
+        <v>0.9987581372261047</v>
       </c>
       <c r="D114" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6867,22 +6873,22 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114">
         <v>2</v>
       </c>
       <c r="N114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -6896,13 +6902,13 @@
         <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C115">
-        <v>0.9987975358963013</v>
+        <v>0.9986618161201477</v>
       </c>
       <c r="D115" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6917,7 +6923,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6926,13 +6932,13 @@
         <v>0</v>
       </c>
       <c r="L115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M115">
         <v>2</v>
       </c>
       <c r="N115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -6946,13 +6952,13 @@
         <v>130</v>
       </c>
       <c r="B116" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C116">
-        <v>0.9942725300788879</v>
+        <v>0.9987975358963013</v>
       </c>
       <c r="D116" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6967,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6979,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N116">
         <v>1</v>
@@ -6996,13 +7002,13 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C117">
-        <v>0.9970023632049561</v>
+        <v>0.9982305765151978</v>
       </c>
       <c r="D117" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7017,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -7029,7 +7035,7 @@
         <v>0</v>
       </c>
       <c r="M117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -7046,13 +7052,13 @@
         <v>132</v>
       </c>
       <c r="B118" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C118">
-        <v>0.9984022974967957</v>
+        <v>0.9970023632049561</v>
       </c>
       <c r="D118" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7067,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -7096,13 +7102,13 @@
         <v>133</v>
       </c>
       <c r="B119" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C119">
-        <v>0.999241828918457</v>
+        <v>0.9984022974967957</v>
       </c>
       <c r="D119" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7117,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -7129,10 +7135,10 @@
         <v>0</v>
       </c>
       <c r="M119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -7146,13 +7152,13 @@
         <v>134</v>
       </c>
       <c r="B120" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C120">
-        <v>0.9961878061294556</v>
+        <v>0.999241828918457</v>
       </c>
       <c r="D120" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7167,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -7179,10 +7185,10 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -7196,13 +7202,13 @@
         <v>135</v>
       </c>
       <c r="B121" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C121">
-        <v>0.9993798732757568</v>
+        <v>0.9961878061294556</v>
       </c>
       <c r="D121" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7217,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -7229,10 +7235,10 @@
         <v>0</v>
       </c>
       <c r="M121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -7246,13 +7252,13 @@
         <v>136</v>
       </c>
       <c r="B122" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C122">
-        <v>0.9990472793579102</v>
+        <v>0.9993798732757568</v>
       </c>
       <c r="D122" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7267,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -7296,13 +7302,13 @@
         <v>137</v>
       </c>
       <c r="B123" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C123">
-        <v>0.9991445541381836</v>
+        <v>0.9990472793579102</v>
       </c>
       <c r="D123" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7317,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -7332,7 +7338,7 @@
         <v>2</v>
       </c>
       <c r="N123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -7346,13 +7352,13 @@
         <v>138</v>
       </c>
       <c r="B124" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C124">
-        <v>0.9142532348632812</v>
+        <v>0.9971425533294678</v>
       </c>
       <c r="D124" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7367,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -7382,7 +7388,7 @@
         <v>2</v>
       </c>
       <c r="N124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -7396,13 +7402,13 @@
         <v>139</v>
       </c>
       <c r="B125" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C125">
-        <v>0.9972384572029114</v>
+        <v>0.9939090013504028</v>
       </c>
       <c r="D125" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7417,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -7432,7 +7438,7 @@
         <v>1</v>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -7446,13 +7452,13 @@
         <v>140</v>
       </c>
       <c r="B126" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C126">
-        <v>0.9960039258003235</v>
+        <v>0.9954636096954346</v>
       </c>
       <c r="D126" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7467,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -7479,10 +7485,10 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -7496,13 +7502,13 @@
         <v>141</v>
       </c>
       <c r="B127" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C127">
-        <v>0.9987621903419495</v>
+        <v>0.9960039258003235</v>
       </c>
       <c r="D127" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7517,7 +7523,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -7529,10 +7535,10 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -7546,13 +7552,13 @@
         <v>142</v>
       </c>
       <c r="B128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C128">
-        <v>0.9937299489974976</v>
+        <v>0.9987621903419495</v>
       </c>
       <c r="D128" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7567,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -7579,10 +7585,10 @@
         <v>0</v>
       </c>
       <c r="M128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -7596,13 +7602,13 @@
         <v>143</v>
       </c>
       <c r="B129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C129">
-        <v>0.9990777969360352</v>
+        <v>0.9884992837905884</v>
       </c>
       <c r="D129" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -7617,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -7629,10 +7635,10 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -7646,13 +7652,13 @@
         <v>144</v>
       </c>
       <c r="B130" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C130">
-        <v>0.9922806620597839</v>
+        <v>0.9988750219345093</v>
       </c>
       <c r="D130" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -7667,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -7696,13 +7702,13 @@
         <v>145</v>
       </c>
       <c r="B131" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C131">
-        <v>0.9937021136283875</v>
+        <v>0.9922806620597839</v>
       </c>
       <c r="D131" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -7717,10 +7723,10 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -7729,10 +7735,10 @@
         <v>0</v>
       </c>
       <c r="M131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -7746,13 +7752,13 @@
         <v>146</v>
       </c>
       <c r="B132" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C132">
-        <v>0.9984290599822998</v>
+        <v>0.9937021136283875</v>
       </c>
       <c r="D132" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7767,10 +7773,10 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -7779,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
         <v>2</v>
-      </c>
-      <c r="N132">
-        <v>1</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -7796,13 +7802,13 @@
         <v>147</v>
       </c>
       <c r="B133" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C133">
-        <v>0.9967972040176392</v>
+        <v>0.9984290599822998</v>
       </c>
       <c r="D133" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7817,10 +7823,10 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -7829,10 +7835,10 @@
         <v>0</v>
       </c>
       <c r="M133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -7846,13 +7852,13 @@
         <v>148</v>
       </c>
       <c r="B134" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C134">
-        <v>0.8547114133834839</v>
+        <v>0.9972376823425293</v>
       </c>
       <c r="D134" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -7867,27 +7873,77 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
+        <v>282</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>1</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135" t="s">
+        <v>149</v>
+      </c>
+      <c r="B135" t="s">
         <v>280</v>
       </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134">
-        <v>1</v>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
+      <c r="C135">
+        <v>0.9957590103149414</v>
+      </c>
+      <c r="D135" t="s">
+        <v>281</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135" t="b">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135" t="s">
+        <v>282</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
         <v>0</v>
       </c>
     </row>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -130,10 +130,10 @@
     <t>micro_0135_00SL40II.jpg</t>
   </si>
   <si>
-    <t>micro_0356_SL4082600.jpg</t>
-  </si>
-  <si>
-    <t>micro_0356_SL407.jpg</t>
+    <t>micro_0136_SL4082800.jpg</t>
+  </si>
+  <si>
+    <t>micro_0133_SL407.jpg</t>
   </si>
   <si>
     <t>micro_0132_SL406.jpg</t>
@@ -238,12 +238,12 @@
     <t>micro_0204_D502.jpg</t>
   </si>
   <si>
+    <t>micro_0140_D501.jpg</t>
+  </si>
+  <si>
     <t>micro_0257_D501.jpg</t>
   </si>
   <si>
-    <t>micro_0140_D501.jpg</t>
-  </si>
-  <si>
     <t>micro_0039_D432.jpg</t>
   </si>
   <si>
@@ -298,13 +298,13 @@
     <t>micro_0073_D408.jpg</t>
   </si>
   <si>
-    <t>micro_0335_D407.jpg</t>
+    <t>micro_0355_D407.jpg</t>
   </si>
   <si>
     <t>micro_0072_D406.jpg</t>
   </si>
   <si>
-    <t>micro_0354_D405.jpg</t>
+    <t>micro_0158_D405.jpg</t>
   </si>
   <si>
     <t>micro_0070_D404.jpg</t>
@@ -316,7 +316,7 @@
     <t>micro_0075_D402.jpg</t>
   </si>
   <si>
-    <t>micro_0352_D401.jpg</t>
+    <t>micro_0354_D401.jpg</t>
   </si>
   <si>
     <t>micro_0309_D250.jpg</t>
@@ -340,12 +340,12 @@
     <t>micro_0085_D242.jpg</t>
   </si>
   <si>
+    <t>micro_0319_D240.jpg</t>
+  </si>
+  <si>
     <t>micro_0109_OD240.jpg</t>
   </si>
   <si>
-    <t>micro_0319_D240.jpg</t>
-  </si>
-  <si>
     <t>micro_0183_D239.jpg</t>
   </si>
   <si>
@@ -367,10 +367,10 @@
     <t>micro_0258_D233.jpg</t>
   </si>
   <si>
+    <t>micro_0303_OD232.jpg</t>
+  </si>
+  <si>
     <t>micro_0254_D232.jpg</t>
-  </si>
-  <si>
-    <t>micro_0303_OD232.jpg</t>
   </si>
   <si>
     <t>micro_0224_D231.jpg</t>
@@ -2355,7 +2355,7 @@
         <v>172</v>
       </c>
       <c r="C24">
-        <v>0.9938239455223083</v>
+        <v>0.9625397324562073</v>
       </c>
       <c r="D24" t="s">
         <v>281</v>
@@ -2405,7 +2405,7 @@
         <v>173</v>
       </c>
       <c r="C25">
-        <v>0.9959491491317749</v>
+        <v>0.9970995783805847</v>
       </c>
       <c r="D25" t="s">
         <v>281</v>
@@ -2429,10 +2429,10 @@
         <v>1</v>
       </c>
       <c r="K25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -4155,7 +4155,7 @@
         <v>208</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0.9949619770050049</v>
       </c>
       <c r="D60" t="s">
         <v>281</v>
@@ -4205,7 +4205,7 @@
         <v>208</v>
       </c>
       <c r="C61">
-        <v>0.9949619770050049</v>
+        <v>1</v>
       </c>
       <c r="D61" t="s">
         <v>281</v>
@@ -5155,7 +5155,7 @@
         <v>227</v>
       </c>
       <c r="C80">
-        <v>0.9977346062660217</v>
+        <v>0.9979954957962036</v>
       </c>
       <c r="D80" t="s">
         <v>281</v>
@@ -5188,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="N80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -5255,7 +5255,7 @@
         <v>229</v>
       </c>
       <c r="C82">
-        <v>0.9980469942092896</v>
+        <v>0.9967225193977356</v>
       </c>
       <c r="D82" t="s">
         <v>281</v>
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="M82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -5855,7 +5855,7 @@
         <v>241</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0.9924148321151733</v>
       </c>
       <c r="D94" t="s">
         <v>281</v>
@@ -5905,7 +5905,7 @@
         <v>241</v>
       </c>
       <c r="C95">
-        <v>0.9924148321151733</v>
+        <v>1</v>
       </c>
       <c r="D95" t="s">
         <v>281</v>
@@ -6305,7 +6305,7 @@
         <v>249</v>
       </c>
       <c r="C103">
-        <v>0.9972063302993774</v>
+        <v>1</v>
       </c>
       <c r="D103" t="s">
         <v>281</v>
@@ -6355,7 +6355,7 @@
         <v>249</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0.9972063302993774</v>
       </c>
       <c r="D104" t="s">
         <v>281</v>

--- a/template/t7_ocr_report.xlsx
+++ b/template/t7_ocr_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="285">
   <si>
     <t>filename</t>
   </si>
@@ -130,10 +130,10 @@
     <t>micro_0135_00SL40II.jpg</t>
   </si>
   <si>
-    <t>micro_0136_SL4082800.jpg</t>
-  </si>
-  <si>
-    <t>micro_0133_SL407.jpg</t>
+    <t>micro_0356_SL4082600.jpg</t>
+  </si>
+  <si>
+    <t>micro_0354_SL407.jpg</t>
   </si>
   <si>
     <t>micro_0132_SL406.jpg</t>
@@ -184,6 +184,9 @@
     <t>micro_0017_D527.jpg</t>
   </si>
   <si>
+    <t>micro_0011_D525.jpg</t>
+  </si>
+  <si>
     <t>micro_0116_D523.jpg</t>
   </si>
   <si>
@@ -238,12 +241,12 @@
     <t>micro_0204_D502.jpg</t>
   </si>
   <si>
+    <t>micro_0257_D501.jpg</t>
+  </si>
+  <si>
     <t>micro_0140_D501.jpg</t>
   </si>
   <si>
-    <t>micro_0257_D501.jpg</t>
-  </si>
-  <si>
     <t>micro_0039_D432.jpg</t>
   </si>
   <si>
@@ -298,7 +301,7 @@
     <t>micro_0073_D408.jpg</t>
   </si>
   <si>
-    <t>micro_0355_D407.jpg</t>
+    <t>micro_0335_D407.jpg</t>
   </si>
   <si>
     <t>micro_0072_D406.jpg</t>
@@ -316,7 +319,7 @@
     <t>micro_0075_D402.jpg</t>
   </si>
   <si>
-    <t>micro_0354_D401.jpg</t>
+    <t>micro_0155_D401.jpg</t>
   </si>
   <si>
     <t>micro_0309_D250.jpg</t>
@@ -584,6 +587,9 @@
   </si>
   <si>
     <t>D527</t>
+  </si>
+  <si>
+    <t>D525</t>
   </si>
   <si>
     <t>D523</t>
@@ -1194,7 +1200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P135"/>
+  <dimension ref="A1:P136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1252,13 +1258,13 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C2">
         <v>0.9714210629463196</v>
       </c>
       <c r="D2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1273,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1302,13 +1308,13 @@
         <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C3">
         <v>0.9794343709945679</v>
       </c>
       <c r="D3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1323,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1352,13 +1358,13 @@
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C4">
         <v>0.9916391372680664</v>
       </c>
       <c r="D4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1373,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1402,13 +1408,13 @@
         <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C5">
         <v>0.9360489845275879</v>
       </c>
       <c r="D5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1423,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1452,13 +1458,13 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C6">
         <v>0.9898043870925903</v>
       </c>
       <c r="D6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1473,7 +1479,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1502,13 +1508,13 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C7">
         <v>0.9800205826759338</v>
       </c>
       <c r="D7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1523,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1552,13 +1558,13 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C8">
         <v>0.9866096377372742</v>
       </c>
       <c r="D8" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1573,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1602,13 +1608,13 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C9">
         <v>0.9825887680053711</v>
       </c>
       <c r="D9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1623,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1652,13 +1658,13 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C10">
         <v>0.9854358434677124</v>
       </c>
       <c r="D10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1673,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1702,13 +1708,13 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C11">
         <v>0.9839249849319458</v>
       </c>
       <c r="D11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1723,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1752,13 +1758,13 @@
         <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12">
         <v>0.9880355000495911</v>
       </c>
       <c r="D12" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1773,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1802,13 +1808,13 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13">
         <v>0.9827210903167725</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1823,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1852,13 +1858,13 @@
         <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C14">
         <v>0.8711124062538147</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1873,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1902,13 +1908,13 @@
         <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C15">
         <v>0.9849019646644592</v>
       </c>
       <c r="D15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1923,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -1952,13 +1958,13 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C16">
         <v>0.9831116795539856</v>
       </c>
       <c r="D16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1973,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2002,13 +2008,13 @@
         <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C17">
         <v>0.9768341779708862</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -2023,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2052,13 +2058,13 @@
         <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C18">
         <v>0.9820773601531982</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -2073,7 +2079,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2102,13 +2108,13 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19">
         <v>0.9926210641860962</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -2123,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2152,13 +2158,13 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20">
         <v>0.991193413734436</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -2173,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2202,13 +2208,13 @@
         <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C21">
         <v>0.9759405851364136</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -2223,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2252,13 +2258,13 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C22">
         <v>0.9946767091751099</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -2273,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2302,13 +2308,13 @@
         <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23">
         <v>0.9923974871635437</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -2323,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2352,13 +2358,13 @@
         <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24">
-        <v>0.9625397324562073</v>
+        <v>0.9938239455223083</v>
       </c>
       <c r="D24" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -2373,7 +2379,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2402,13 +2408,13 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25">
-        <v>0.9970995783805847</v>
+        <v>0.9971064329147339</v>
       </c>
       <c r="D25" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -2423,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2452,13 +2458,13 @@
         <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C26">
         <v>0.9976895451545715</v>
       </c>
       <c r="D26" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2473,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2502,13 +2508,13 @@
         <v>41</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27">
         <v>0.9959992170333862</v>
       </c>
       <c r="D27" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -2523,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2552,13 +2558,13 @@
         <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C28">
         <v>0.9971073865890503</v>
       </c>
       <c r="D28" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2573,7 +2579,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2602,13 +2608,13 @@
         <v>43</v>
       </c>
       <c r="B29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C29">
         <v>0.9968833923339844</v>
       </c>
       <c r="D29" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2623,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2652,13 +2658,13 @@
         <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C30">
         <v>0.9933208227157593</v>
       </c>
       <c r="D30" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2673,7 +2679,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2702,13 +2708,13 @@
         <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C31">
         <v>0.9971753358840942</v>
       </c>
       <c r="D31" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2723,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2752,13 +2758,13 @@
         <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C32">
         <v>0.9958525896072388</v>
       </c>
       <c r="D32" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2773,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2785,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N32">
         <v>3</v>
@@ -2802,13 +2808,13 @@
         <v>47</v>
       </c>
       <c r="B33" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C33">
         <v>0.9987233877182007</v>
       </c>
       <c r="D33" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2823,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2852,13 +2858,13 @@
         <v>48</v>
       </c>
       <c r="B34" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C34">
         <v>0.9754772186279297</v>
       </c>
       <c r="D34" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2873,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2902,13 +2908,13 @@
         <v>49</v>
       </c>
       <c r="B35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C35">
         <v>0.9673787951469421</v>
       </c>
       <c r="D35" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2923,7 +2929,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2952,13 +2958,13 @@
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C36">
         <v>0.7677456140518188</v>
       </c>
       <c r="D36" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2973,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -3002,13 +3008,13 @@
         <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C37">
         <v>0.9030734300613403</v>
       </c>
       <c r="D37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -3023,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -3052,13 +3058,13 @@
         <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C38">
         <v>0.9965819120407104</v>
       </c>
       <c r="D38" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -3073,7 +3079,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -3102,13 +3108,13 @@
         <v>53</v>
       </c>
       <c r="B39" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C39">
         <v>0.9989708662033081</v>
       </c>
       <c r="D39" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -3123,7 +3129,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -3152,13 +3158,13 @@
         <v>54</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C40">
         <v>0.9991652369499207</v>
       </c>
       <c r="D40" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -3173,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -3202,13 +3208,13 @@
         <v>55</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C41">
         <v>0.9989938735961914</v>
       </c>
       <c r="D41" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -3223,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -3235,10 +3241,10 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -3252,13 +3258,13 @@
         <v>56</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C42">
-        <v>0.9991186261177063</v>
+        <v>0.9982006549835205</v>
       </c>
       <c r="D42" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -3273,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -3285,10 +3291,10 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N42">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -3302,13 +3308,13 @@
         <v>57</v>
       </c>
       <c r="B43" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C43">
-        <v>0.9952852725982666</v>
+        <v>0.9991186261177063</v>
       </c>
       <c r="D43" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -3323,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="I43" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -3352,13 +3358,13 @@
         <v>58</v>
       </c>
       <c r="B44" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C44">
-        <v>0.9953067898750305</v>
+        <v>0.9952852725982666</v>
       </c>
       <c r="D44" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -3373,7 +3379,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J44">
         <v>0</v>
@@ -3385,10 +3391,10 @@
         <v>0</v>
       </c>
       <c r="M44">
+        <v>1</v>
+      </c>
+      <c r="N44">
         <v>2</v>
-      </c>
-      <c r="N44">
-        <v>1</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -3402,13 +3408,13 @@
         <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C45">
-        <v>0.9992556571960449</v>
+        <v>0.9953067898750305</v>
       </c>
       <c r="D45" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -3423,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -3438,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -3452,13 +3458,13 @@
         <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C46">
-        <v>0.9994583129882812</v>
+        <v>0.9992556571960449</v>
       </c>
       <c r="D46" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -3473,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -3488,7 +3494,7 @@
         <v>1</v>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -3502,13 +3508,13 @@
         <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C47">
-        <v>0.9995577931404114</v>
+        <v>0.9994583129882812</v>
       </c>
       <c r="D47" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -3523,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -3538,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="N47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -3552,13 +3558,13 @@
         <v>62</v>
       </c>
       <c r="B48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C48">
-        <v>0.9995352625846863</v>
+        <v>0.9995577931404114</v>
       </c>
       <c r="D48" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -3573,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -3588,7 +3594,7 @@
         <v>1</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -3602,13 +3608,13 @@
         <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C49">
-        <v>0.999538242816925</v>
+        <v>0.9995352625846863</v>
       </c>
       <c r="D49" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -3623,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J49">
         <v>0</v>
@@ -3652,13 +3658,13 @@
         <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C50">
-        <v>0.9994799494743347</v>
+        <v>0.999538242816925</v>
       </c>
       <c r="D50" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -3673,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3688,7 +3694,7 @@
         <v>1</v>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -3702,13 +3708,13 @@
         <v>65</v>
       </c>
       <c r="B51" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C51">
-        <v>0.9944444894790649</v>
+        <v>0.9994799494743347</v>
       </c>
       <c r="D51" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -3723,7 +3729,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3738,7 +3744,7 @@
         <v>1</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -3752,13 +3758,13 @@
         <v>66</v>
       </c>
       <c r="B52" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C52">
-        <v>0.998166561126709</v>
+        <v>0.9944444894790649</v>
       </c>
       <c r="D52" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -3773,7 +3779,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J52">
         <v>0</v>
@@ -3788,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -3802,13 +3808,13 @@
         <v>67</v>
       </c>
       <c r="B53" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C53">
-        <v>0.9985004067420959</v>
+        <v>0.998166561126709</v>
       </c>
       <c r="D53" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -3823,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J53">
         <v>0</v>
@@ -3835,10 +3841,10 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -3852,13 +3858,13 @@
         <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C54">
-        <v>0.9974443912506104</v>
+        <v>0.9985004067420959</v>
       </c>
       <c r="D54" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -3873,7 +3879,7 @@
         <v>0</v>
       </c>
       <c r="I54" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J54">
         <v>0</v>
@@ -3888,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="N54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -3902,13 +3908,13 @@
         <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C55">
-        <v>0.9989598989486694</v>
+        <v>0.9974443912506104</v>
       </c>
       <c r="D55" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -3923,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3935,10 +3941,10 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -3952,13 +3958,13 @@
         <v>70</v>
       </c>
       <c r="B56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C56">
-        <v>0.9987078905105591</v>
+        <v>0.9989598989486694</v>
       </c>
       <c r="D56" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3973,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3985,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -4002,13 +4008,13 @@
         <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C57">
-        <v>0.9985486268997192</v>
+        <v>0.9987078905105591</v>
       </c>
       <c r="D57" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -4023,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J57">
         <v>0</v>
@@ -4038,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -4052,13 +4058,13 @@
         <v>72</v>
       </c>
       <c r="B58" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C58">
-        <v>0.9810042381286621</v>
+        <v>0.9985486268997192</v>
       </c>
       <c r="D58" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -4073,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -4085,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N58">
         <v>1</v>
@@ -4102,13 +4108,13 @@
         <v>73</v>
       </c>
       <c r="B59" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C59">
-        <v>0.9990440607070923</v>
+        <v>0.9810042381286621</v>
       </c>
       <c r="D59" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -4123,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="I59" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -4152,13 +4158,13 @@
         <v>74</v>
       </c>
       <c r="B60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C60">
-        <v>0.9949619770050049</v>
+        <v>0.9990440607070923</v>
       </c>
       <c r="D60" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -4173,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -4188,7 +4194,7 @@
         <v>1</v>
       </c>
       <c r="N60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -4202,13 +4208,13 @@
         <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -4223,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -4238,7 +4244,7 @@
         <v>1</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -4252,13 +4258,13 @@
         <v>76</v>
       </c>
       <c r="B62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C62">
-        <v>0.9984354376792908</v>
+        <v>0.9949619770050049</v>
       </c>
       <c r="D62" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -4273,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J62">
         <v>0</v>
@@ -4285,7 +4291,7 @@
         <v>0</v>
       </c>
       <c r="M62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N62">
         <v>2</v>
@@ -4302,13 +4308,13 @@
         <v>77</v>
       </c>
       <c r="B63" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C63">
-        <v>0.9993854761123657</v>
+        <v>0.9984354376792908</v>
       </c>
       <c r="D63" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -4323,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -4335,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="M63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N63">
         <v>2</v>
@@ -4352,13 +4358,13 @@
         <v>78</v>
       </c>
       <c r="B64" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C64">
-        <v>0.999595582485199</v>
+        <v>0.9993854761123657</v>
       </c>
       <c r="D64" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -4373,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -4388,7 +4394,7 @@
         <v>1</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -4402,13 +4408,13 @@
         <v>79</v>
       </c>
       <c r="B65" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C65">
-        <v>0.9975582957267761</v>
+        <v>0.999595582485199</v>
       </c>
       <c r="D65" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -4423,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4438,7 +4444,7 @@
         <v>1</v>
       </c>
       <c r="N65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -4452,13 +4458,13 @@
         <v>80</v>
       </c>
       <c r="B66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C66">
-        <v>0.9995519518852234</v>
+        <v>0.9975582957267761</v>
       </c>
       <c r="D66" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -4473,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4502,13 +4508,13 @@
         <v>81</v>
       </c>
       <c r="B67" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C67">
-        <v>0.9992239475250244</v>
+        <v>0.9995519518852234</v>
       </c>
       <c r="D67" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -4523,7 +4529,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -4535,10 +4541,10 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -4552,13 +4558,13 @@
         <v>82</v>
       </c>
       <c r="B68" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C68">
-        <v>0.9989912509918213</v>
+        <v>0.9992239475250244</v>
       </c>
       <c r="D68" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -4573,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J68">
         <v>0</v>
@@ -4588,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -4602,13 +4608,13 @@
         <v>83</v>
       </c>
       <c r="B69" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C69">
-        <v>0.9980692267417908</v>
+        <v>0.9989912509918213</v>
       </c>
       <c r="D69" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -4623,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -4635,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -4652,13 +4658,13 @@
         <v>84</v>
       </c>
       <c r="B70" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C70">
-        <v>0.9993839859962463</v>
+        <v>0.9980692267417908</v>
       </c>
       <c r="D70" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -4673,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4688,7 +4694,7 @@
         <v>1</v>
       </c>
       <c r="N70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -4702,13 +4708,13 @@
         <v>85</v>
       </c>
       <c r="B71" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C71">
-        <v>0.9957826137542725</v>
+        <v>0.9993839859962463</v>
       </c>
       <c r="D71" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -4723,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4752,13 +4758,13 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C72">
-        <v>0.9995350241661072</v>
+        <v>0.9957826137542725</v>
       </c>
       <c r="D72" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -4773,7 +4779,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -4785,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N72">
         <v>1</v>
@@ -4802,13 +4808,13 @@
         <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C73">
-        <v>0.9991962909698486</v>
+        <v>0.9995350241661072</v>
       </c>
       <c r="D73" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -4823,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J73">
         <v>0</v>
@@ -4835,7 +4841,7 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N73">
         <v>1</v>
@@ -4852,13 +4858,13 @@
         <v>88</v>
       </c>
       <c r="B74" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C74">
-        <v>0.9979453086853027</v>
+        <v>0.9991962909698486</v>
       </c>
       <c r="D74" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -4873,7 +4879,7 @@
         <v>0</v>
       </c>
       <c r="I74" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J74">
         <v>0</v>
@@ -4885,7 +4891,7 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N74">
         <v>1</v>
@@ -4902,13 +4908,13 @@
         <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C75">
-        <v>0.9963642954826355</v>
+        <v>0.9979453086853027</v>
       </c>
       <c r="D75" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -4923,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4935,10 +4941,10 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -4952,13 +4958,13 @@
         <v>90</v>
       </c>
       <c r="B76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C76">
-        <v>0.9930816888809204</v>
+        <v>0.9963642954826355</v>
       </c>
       <c r="D76" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -4973,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4985,10 +4991,10 @@
         <v>0</v>
       </c>
       <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76">
         <v>2</v>
-      </c>
-      <c r="N76">
-        <v>1</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -5002,13 +5008,13 @@
         <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C77">
-        <v>0.8460029363632202</v>
+        <v>0.9930816888809204</v>
       </c>
       <c r="D77" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -5023,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -5035,7 +5041,7 @@
         <v>0</v>
       </c>
       <c r="M77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N77">
         <v>1</v>
@@ -5052,13 +5058,13 @@
         <v>92</v>
       </c>
       <c r="B78" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C78">
-        <v>0.9959526658058167</v>
+        <v>0.8460029363632202</v>
       </c>
       <c r="D78" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -5073,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -5085,10 +5091,10 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -5102,13 +5108,13 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C79">
-        <v>0.9994586706161499</v>
+        <v>0.9959526658058167</v>
       </c>
       <c r="D79" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -5123,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J79">
         <v>0</v>
@@ -5135,10 +5141,10 @@
         <v>0</v>
       </c>
       <c r="M79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -5152,13 +5158,13 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C80">
-        <v>0.9979954957962036</v>
+        <v>0.9994586706161499</v>
       </c>
       <c r="D80" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -5173,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -5188,7 +5194,7 @@
         <v>1</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -5202,13 +5208,13 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C81">
-        <v>0.9993370175361633</v>
+        <v>0.9977346062660217</v>
       </c>
       <c r="D81" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -5223,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -5252,13 +5258,13 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C82">
-        <v>0.9967225193977356</v>
+        <v>0.9993370175361633</v>
       </c>
       <c r="D82" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -5273,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J82">
         <v>0</v>
@@ -5302,13 +5308,13 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C83">
-        <v>0.9978298544883728</v>
+        <v>0.9967225193977356</v>
       </c>
       <c r="D83" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -5323,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J83">
         <v>0</v>
@@ -5338,7 +5344,7 @@
         <v>1</v>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -5352,13 +5358,13 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C84">
-        <v>0.8626171350479126</v>
+        <v>0.9978298544883728</v>
       </c>
       <c r="D84" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -5373,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J84">
         <v>0</v>
@@ -5388,7 +5394,7 @@
         <v>1</v>
       </c>
       <c r="N84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -5402,13 +5408,13 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C85">
-        <v>0.9972398281097412</v>
+        <v>0.8626171350479126</v>
       </c>
       <c r="D85" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -5423,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -5438,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -5452,13 +5458,13 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C86">
-        <v>0.9967367053031921</v>
+        <v>0.9972398281097412</v>
       </c>
       <c r="D86" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -5473,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -5488,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="N86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -5502,13 +5508,13 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C87">
-        <v>0.9915247559547424</v>
+        <v>0.9969408512115479</v>
       </c>
       <c r="D87" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -5523,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J87">
         <v>0</v>
@@ -5535,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -5552,13 +5558,13 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C88">
-        <v>0.9995598793029785</v>
+        <v>0.9915247559547424</v>
       </c>
       <c r="D88" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -5573,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -5602,13 +5608,13 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C89">
-        <v>0.9988371133804321</v>
+        <v>0.9995598793029785</v>
       </c>
       <c r="D89" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -5623,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -5652,13 +5658,13 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C90">
-        <v>0.9977865815162659</v>
+        <v>0.9988371133804321</v>
       </c>
       <c r="D90" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -5673,7 +5679,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5702,13 +5708,13 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C91">
-        <v>0.9991824626922607</v>
+        <v>0.9977865815162659</v>
       </c>
       <c r="D91" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -5723,7 +5729,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5752,13 +5758,13 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C92">
-        <v>0.9949779510498047</v>
+        <v>0.9991824626922607</v>
       </c>
       <c r="D92" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -5773,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J92">
         <v>0</v>
@@ -5802,13 +5808,13 @@
         <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C93">
-        <v>0.9956748485565186</v>
+        <v>0.9949779510498047</v>
       </c>
       <c r="D93" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -5823,7 +5829,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -5852,13 +5858,13 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C94">
-        <v>0.9924148321151733</v>
+        <v>0.9956748485565186</v>
       </c>
       <c r="D94" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -5873,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J94">
         <v>0</v>
@@ -5902,13 +5908,13 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>0.9924148321151733</v>
       </c>
       <c r="D95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -5923,7 +5929,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5952,13 +5958,13 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C96">
-        <v>0.9990327954292297</v>
+        <v>1</v>
       </c>
       <c r="D96" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -5973,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5985,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="M96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -6002,13 +6008,13 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C97">
-        <v>0.9933540225028992</v>
+        <v>0.9990327954292297</v>
       </c>
       <c r="D97" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -6023,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="I97" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -6038,7 +6044,7 @@
         <v>1</v>
       </c>
       <c r="N97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -6052,13 +6058,13 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C98">
-        <v>0.9992632269859314</v>
+        <v>0.9933540225028992</v>
       </c>
       <c r="D98" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -6073,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J98">
         <v>0</v>
@@ -6102,13 +6108,13 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C99">
-        <v>0.9882216453552246</v>
+        <v>0.9992632269859314</v>
       </c>
       <c r="D99" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -6123,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -6152,13 +6158,13 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C100">
-        <v>0.9993331432342529</v>
+        <v>0.9882216453552246</v>
       </c>
       <c r="D100" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -6173,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -6202,13 +6208,13 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C101">
-        <v>0.9826395511627197</v>
+        <v>0.9993331432342529</v>
       </c>
       <c r="D101" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -6223,7 +6229,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -6238,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -6252,13 +6258,13 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C102">
-        <v>0.8529298901557922</v>
+        <v>0.9826395511627197</v>
       </c>
       <c r="D102" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -6273,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -6302,13 +6308,13 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0.8529298901557922</v>
       </c>
       <c r="D103" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -6323,7 +6329,7 @@
         <v>0</v>
       </c>
       <c r="I103" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -6335,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="M103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N103">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -6352,13 +6358,13 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C104">
-        <v>0.9972063302993774</v>
+        <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -6373,7 +6379,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -6385,7 +6391,7 @@
         <v>0</v>
       </c>
       <c r="M104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N104">
         <v>2</v>
@@ -6402,13 +6408,13 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C105">
-        <v>0.9982128739356995</v>
+        <v>0.9972063302993774</v>
       </c>
       <c r="D105" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -6423,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="I105" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -6438,7 +6444,7 @@
         <v>1</v>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105">
         <v>0</v>
@@ -6452,13 +6458,13 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C106">
-        <v>0.9911179542541504</v>
+        <v>0.9982128739356995</v>
       </c>
       <c r="D106" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -6473,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="I106" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -6488,7 +6494,7 @@
         <v>1</v>
       </c>
       <c r="N106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -6502,13 +6508,13 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C107">
-        <v>0.9979790449142456</v>
+        <v>0.9911179542541504</v>
       </c>
       <c r="D107" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -6523,22 +6529,22 @@
         <v>0</v>
       </c>
       <c r="I107" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107">
         <v>2</v>
-      </c>
-      <c r="L107">
-        <v>1</v>
-      </c>
-      <c r="M107">
-        <v>1</v>
-      </c>
-      <c r="N107">
-        <v>3</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -6552,13 +6558,13 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C108">
-        <v>0.9994751811027527</v>
+        <v>0.9979790449142456</v>
       </c>
       <c r="D108" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -6573,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -6588,7 +6594,7 @@
         <v>1</v>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -6602,13 +6608,13 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C109">
-        <v>0.9983197450637817</v>
+        <v>0.9994751811027527</v>
       </c>
       <c r="D109" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -6623,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="I109" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J109">
         <v>0</v>
@@ -6638,7 +6644,7 @@
         <v>1</v>
       </c>
       <c r="N109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -6652,13 +6658,13 @@
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C110">
-        <v>0.9931647777557373</v>
+        <v>0.9983197450637817</v>
       </c>
       <c r="D110" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -6673,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="I110" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6688,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="N110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -6702,13 +6708,13 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C111">
-        <v>0.9982962012290955</v>
+        <v>0.9931647777557373</v>
       </c>
       <c r="D111" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -6723,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="I111" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6738,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -6752,13 +6758,13 @@
         <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C112">
-        <v>0.9937362670898438</v>
+        <v>0.9982962012290955</v>
       </c>
       <c r="D112" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -6773,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -6785,10 +6791,10 @@
         <v>0</v>
       </c>
       <c r="M112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -6802,13 +6808,13 @@
         <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C113">
-        <v>0.9977945685386658</v>
+        <v>0.9937362670898438</v>
       </c>
       <c r="D113" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -6823,22 +6829,22 @@
         <v>0</v>
       </c>
       <c r="I113" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -6852,13 +6858,13 @@
         <v>128</v>
       </c>
       <c r="B114" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C114">
-        <v>0.9987581372261047</v>
+        <v>0.9977945685386658</v>
       </c>
       <c r="D114" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -6873,7 +6879,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -6885,7 +6891,7 @@
         <v>0</v>
       </c>
       <c r="M114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -6902,13 +6908,13 @@
         <v>129</v>
       </c>
       <c r="B115" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C115">
-        <v>0.9986618161201477</v>
+        <v>0.9987581372261047</v>
       </c>
       <c r="D115" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -6923,7 +6929,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6932,13 +6938,13 @@
         <v>0</v>
       </c>
       <c r="L115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -6952,13 +6958,13 @@
         <v>130</v>
       </c>
       <c r="B116" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C116">
-        <v>0.9987975358963013</v>
+        <v>0.9986618161201477</v>
       </c>
       <c r="D116" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -6973,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="I116" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6985,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N116">
         <v>1</v>
@@ -7002,13 +7008,13 @@
         <v>131</v>
       </c>
       <c r="B117" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C117">
-        <v>0.9982305765151978</v>
+        <v>0.9987975358963013</v>
       </c>
       <c r="D117" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -7023,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="I117" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J117">
         <v>0</v>
@@ -7052,13 +7058,13 @@
         <v>132</v>
       </c>
       <c r="B118" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C118">
-        <v>0.9970023632049561</v>
+        <v>0.9982305765151978</v>
       </c>
       <c r="D118" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -7073,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="I118" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -7085,7 +7091,7 @@
         <v>0</v>
       </c>
       <c r="M118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N118">
         <v>1</v>
@@ -7102,13 +7108,13 @@
         <v>133</v>
       </c>
       <c r="B119" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C119">
-        <v>0.9984022974967957</v>
+        <v>0.9970023632049561</v>
       </c>
       <c r="D119" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -7123,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -7138,7 +7144,7 @@
         <v>1</v>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -7152,13 +7158,13 @@
         <v>134</v>
       </c>
       <c r="B120" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C120">
-        <v>0.999241828918457</v>
+        <v>0.9984022974967957</v>
       </c>
       <c r="D120" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -7173,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -7185,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N120">
         <v>2</v>
@@ -7202,13 +7208,13 @@
         <v>135</v>
       </c>
       <c r="B121" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C121">
-        <v>0.9961878061294556</v>
+        <v>0.999241828918457</v>
       </c>
       <c r="D121" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -7223,7 +7229,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -7238,7 +7244,7 @@
         <v>1</v>
       </c>
       <c r="N121">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -7252,13 +7258,13 @@
         <v>136</v>
       </c>
       <c r="B122" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C122">
-        <v>0.9993798732757568</v>
+        <v>0.9961878061294556</v>
       </c>
       <c r="D122" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7273,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="I122" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J122">
         <v>0</v>
@@ -7285,10 +7291,10 @@
         <v>0</v>
       </c>
       <c r="M122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N122">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -7302,13 +7308,13 @@
         <v>137</v>
       </c>
       <c r="B123" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C123">
-        <v>0.9990472793579102</v>
+        <v>0.9993798732757568</v>
       </c>
       <c r="D123" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -7323,7 +7329,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J123">
         <v>0</v>
@@ -7335,7 +7341,7 @@
         <v>0</v>
       </c>
       <c r="M123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N123">
         <v>2</v>
@@ -7352,13 +7358,13 @@
         <v>138</v>
       </c>
       <c r="B124" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C124">
-        <v>0.9971425533294678</v>
+        <v>0.9990472793579102</v>
       </c>
       <c r="D124" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -7373,7 +7379,7 @@
         <v>0</v>
       </c>
       <c r="I124" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J124">
         <v>0</v>
@@ -7385,10 +7391,10 @@
         <v>0</v>
       </c>
       <c r="M124">
+        <v>1</v>
+      </c>
+      <c r="N124">
         <v>2</v>
-      </c>
-      <c r="N124">
-        <v>1</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -7402,13 +7408,13 @@
         <v>139</v>
       </c>
       <c r="B125" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C125">
-        <v>0.9939090013504028</v>
+        <v>0.9971425533294678</v>
       </c>
       <c r="D125" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -7423,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="I125" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J125">
         <v>0</v>
@@ -7452,13 +7458,13 @@
         <v>140</v>
       </c>
       <c r="B126" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C126">
-        <v>0.9954636096954346</v>
+        <v>0.9939090013504028</v>
       </c>
       <c r="D126" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -7473,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="I126" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J126">
         <v>0</v>
@@ -7488,7 +7494,7 @@
         <v>1</v>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -7502,13 +7508,13 @@
         <v>141</v>
       </c>
       <c r="B127" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C127">
-        <v>0.9960039258003235</v>
+        <v>0.9954636096954346</v>
       </c>
       <c r="D127" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -7523,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J127">
         <v>0</v>
@@ -7535,10 +7541,10 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -7552,13 +7558,13 @@
         <v>142</v>
       </c>
       <c r="B128" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C128">
-        <v>0.9987621903419495</v>
+        <v>0.9960039258003235</v>
       </c>
       <c r="D128" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -7573,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -7602,13 +7608,13 @@
         <v>143</v>
       </c>
       <c r="B129" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C129">
-        <v>0.9884992837905884</v>
+        <v>0.9987621903419495</v>
       </c>
       <c r="D129" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -7623,7 +7629,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J129">
         <v>0</v>
@@ -7635,10 +7641,10 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -7652,13 +7658,13 @@
         <v>144</v>
       </c>
       <c r="B130" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C130">
-        <v>0.9988750219345093</v>
+        <v>0.9884992837905884</v>
       </c>
       <c r="D130" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -7673,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -7688,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O130">
         <v>0</v>
@@ -7702,13 +7708,13 @@
         <v>145</v>
       </c>
       <c r="B131" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C131">
-        <v>0.9922806620597839</v>
+        <v>0.9988750219345093</v>
       </c>
       <c r="D131" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -7723,7 +7729,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -7752,13 +7758,13 @@
         <v>146</v>
       </c>
       <c r="B132" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C132">
-        <v>0.9937021136283875</v>
+        <v>0.9922806620597839</v>
       </c>
       <c r="D132" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -7773,10 +7779,10 @@
         <v>0</v>
       </c>
       <c r="I132" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -7785,10 +7791,10 @@
         <v>0</v>
       </c>
       <c r="M132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N132">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -7802,13 +7808,13 @@
         <v>147</v>
       </c>
       <c r="B133" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C133">
-        <v>0.9984290599822998</v>
+        <v>0.9937021136283875</v>
       </c>
       <c r="D133" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -7823,10 +7829,10 @@
         <v>0</v>
       </c>
       <c r="I133" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133">
         <v>0</v>
@@ -7835,10 +7841,10 @@
         <v>0</v>
       </c>
       <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
         <v>2</v>
-      </c>
-      <c r="N133">
-        <v>1</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -7852,13 +7858,13 @@
         <v>148</v>
       </c>
       <c r="B134" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C134">
-        <v>0.9972376823425293</v>
+        <v>0.9984290599822998</v>
       </c>
       <c r="D134" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -7873,10 +7879,10 @@
         <v>0</v>
       </c>
       <c r="I134" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K134">
         <v>0</v>
@@ -7885,7 +7891,7 @@
         <v>0</v>
       </c>
       <c r="M134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N134">
         <v>1</v>
@@ -7902,48 +7908,98 @@
         <v>149</v>
       </c>
       <c r="B135" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C135">
+        <v>0.9972376823425293</v>
+      </c>
+      <c r="D135" t="s">
+        <v>283</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135" t="b">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135" t="s">
+        <v>284</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>1</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136" t="s">
+        <v>150</v>
+      </c>
+      <c r="B136" t="s">
+        <v>282</v>
+      </c>
+      <c r="C136">
         <v>0.9957590103149414</v>
       </c>
-      <c r="D135" t="s">
-        <v>281</v>
-      </c>
-      <c r="E135">
-        <v>0</v>
-      </c>
-      <c r="F135" t="b">
-        <v>0</v>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135" t="s">
-        <v>282</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135">
-        <v>1</v>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
+      <c r="D136" t="s">
+        <v>283</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136" t="b">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136" t="s">
+        <v>284</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>0</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
         <v>0</v>
       </c>
     </row>
